--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:L250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20024,6 +20024,26 @@
           <t>2026-03-01_diff</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2026-03-02_price</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026-03-02_buy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-03-02_ratio</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-03-02_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20036,7 +20056,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20060,7 +20079,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20085,7 +20103,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20110,7 +20127,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20135,7 +20151,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20160,7 +20175,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20185,7 +20199,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20210,7 +20223,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20235,7 +20247,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20260,7 +20271,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20285,7 +20295,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20310,7 +20319,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20335,7 +20343,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20360,7 +20367,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20385,7 +20391,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20410,7 +20415,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20435,7 +20439,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20460,7 +20463,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20485,7 +20487,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20510,7 +20511,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20535,7 +20535,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20560,7 +20559,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20585,7 +20583,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20610,7 +20607,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20635,7 +20631,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20660,7 +20655,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20685,7 +20679,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20710,7 +20703,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20735,7 +20727,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20760,7 +20751,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20785,7 +20775,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20810,7 +20799,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20835,7 +20823,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20860,7 +20847,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20885,7 +20871,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20910,7 +20895,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20935,7 +20919,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20960,7 +20943,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -20985,7 +20967,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21010,7 +20991,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21035,7 +21015,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21060,7 +21039,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21085,7 +21063,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21110,7 +21087,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21135,7 +21111,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21160,7 +21135,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21185,7 +21159,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21210,7 +21183,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21235,7 +21207,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21259,7 +21230,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21283,7 +21253,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21307,7 +21276,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21331,7 +21299,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21355,7 +21322,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21380,7 +21346,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21404,7 +21369,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21428,7 +21392,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21452,7 +21415,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21476,7 +21438,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21500,7 +21461,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21524,7 +21484,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21548,7 +21507,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21572,7 +21530,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21596,7 +21553,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21620,7 +21576,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21644,7 +21599,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21668,7 +21622,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21692,7 +21645,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21716,7 +21668,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21740,7 +21691,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21764,7 +21714,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21788,7 +21737,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21812,7 +21760,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21836,7 +21783,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21860,7 +21806,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21884,7 +21829,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21908,7 +21852,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21932,7 +21875,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21956,7 +21898,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -21980,7 +21921,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -22004,7 +21944,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -22028,7 +21967,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -22052,7 +21990,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -22076,7 +22013,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -22100,7 +22036,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -22124,7 +22059,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -22149,7 +22083,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22174,7 +22107,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22199,7 +22131,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22224,7 +22155,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22249,7 +22179,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22274,7 +22203,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22299,7 +22227,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22324,7 +22251,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22349,7 +22275,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22374,7 +22299,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22399,7 +22323,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22424,7 +22347,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22449,7 +22371,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22474,7 +22395,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22499,7 +22419,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22524,7 +22443,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22549,7 +22467,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22574,7 +22491,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22599,7 +22515,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22624,7 +22539,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22649,7 +22563,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22674,7 +22587,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22699,7 +22611,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22724,7 +22635,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22749,7 +22659,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22774,7 +22683,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22799,7 +22707,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22824,7 +22731,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22849,7 +22755,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22874,7 +22779,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22899,7 +22803,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22924,7 +22827,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22949,7 +22851,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22974,7 +22875,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -22999,7 +22899,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23024,7 +22923,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23049,7 +22947,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23074,7 +22971,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23099,7 +22995,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23124,7 +23019,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23149,7 +23043,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23174,7 +23067,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23199,7 +23091,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23224,7 +23115,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23249,7 +23139,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23274,7 +23163,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23299,7 +23187,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23324,7 +23211,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23349,7 +23235,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23374,7 +23259,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23399,7 +23283,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23424,7 +23307,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23449,7 +23331,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23474,7 +23355,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23499,7 +23379,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23524,7 +23403,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23549,7 +23427,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23574,7 +23451,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23599,7 +23475,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23624,7 +23499,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23649,7 +23523,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23674,7 +23547,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23699,7 +23571,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -23710,6 +23581,2477 @@
       </c>
       <c r="F150" t="n">
         <v>34240</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>〔状態C〕リザードンex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>220</v>
+      </c>
+      <c r="J151" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プラズマ団のしたっぱ
+その他]</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>3580</v>
+      </c>
+      <c r="J152" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>〔状態B〕サザンドラex
+SV8]</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>4780</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コアルヒー
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>730</v>
+      </c>
+      <c r="J154" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バチュル
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>930</v>
+      </c>
+      <c r="J155" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジヘッド
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>420</v>
+      </c>
+      <c r="J156" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のガルーラex
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>380</v>
+      </c>
+      <c r="J157" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>〔状態C〕モクロー(ポケモンカードフェスタ2017)
+その他]</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>790</v>
+      </c>
+      <c r="J158" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>〔状態B〕オクタン
+S8b]</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>320</v>
+      </c>
+      <c r="J159" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブリガロンBREAK
+XY]</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>380</v>
+      </c>
+      <c r="J160" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>〔状態C〕ネモ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>480</v>
+      </c>
+      <c r="J161" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本草エネルギー(フレンドバトル)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>320</v>
+      </c>
+      <c r="J162" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハイダイ
+SV7]</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>480</v>
+      </c>
+      <c r="J163" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>〔状態A-〕チオンジェンex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>480</v>
+      </c>
+      <c r="J164" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>〔状態B〕メロコ
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>1480</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コレクレー
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>380</v>
+      </c>
+      <c r="J166" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>〔状態C〕キュウコンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>730</v>
+      </c>
+      <c r="J167" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グレイシア(YU NAGABA)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>8980</v>
+      </c>
+      <c r="J168" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フーディンex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>6280</v>
+      </c>
+      <c r="J169" t="n">
+        <v>5024</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キュレムVMAX
+S11]</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>730</v>
+      </c>
+      <c r="J170" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウツーV
+S10b]</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>690</v>
+      </c>
+      <c r="J171" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>〔状態C〕マナフィ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>370</v>
+      </c>
+      <c r="J172" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>〔状態B〕スコヴィラン
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>280</v>
+      </c>
+      <c r="J173" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>〔状態B〕フシギダネ(未開封)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>4480</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ダートじてんしゃ
+XY]</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>250</v>
+      </c>
+      <c r="J175" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウールー
+s4a]</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>450</v>
+      </c>
+      <c r="J176" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エーフィV
+S6a]</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>250</v>
+      </c>
+      <c r="J177" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ソルガレオGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>450</v>
+      </c>
+      <c r="J178" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マーシャドー＆カイリキーGX
+sm10]</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>690</v>
+      </c>
+      <c r="J179" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジュラルドンVMAX
+S7D]</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>730</v>
+      </c>
+      <c r="J180" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オンバーンGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>3080</v>
+      </c>
+      <c r="J181" t="n">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ホップ(SR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>1880</v>
+      </c>
+      <c r="J182" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒードランGX
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>1090</v>
+      </c>
+      <c r="J183" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>〔状態A-〕はくばバドレックスVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>490</v>
+      </c>
+      <c r="J184" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ビクティニV(ひろがるほのお)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>6280</v>
+      </c>
+      <c r="J185" t="n">
+        <v>5024</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プレシャスボール
+sm12]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>250</v>
+      </c>
+      <c r="J186" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>〔状態B〕ガブリアスCLV.X(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>1280</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プルメリ
+sm3]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>12800</v>
+      </c>
+      <c r="J188" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルギアGX
+sm8]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>2090</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マグカルゴGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>580</v>
+      </c>
+      <c r="J190" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルカリオ＆メルメタルGX(SA)
+SM9b]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>20300</v>
+      </c>
+      <c r="J191" t="n">
+        <v>16240</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラピオンV(S4)
+s4]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>380</v>
+      </c>
+      <c r="J192" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>〔状態B〕チコリータ(マクドナルド)
+その他]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>32800</v>
+      </c>
+      <c r="J193" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>〔状態B〕サーナイトexδ-デルタ種(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>〔状態B〕ガラルフリーザーV
+S5a]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>880</v>
+      </c>
+      <c r="J195" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ(YU NAGABA/未開封)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>15800</v>
+      </c>
+      <c r="J196" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>〔状態B〕ともだちてちょう
+その他]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>1480</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラプラスVMAX
+s1]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>1180</v>
+      </c>
+      <c r="J198" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼクロム
+その他]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>39800</v>
+      </c>
+      <c r="J199" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>〔状態B〕フライゴンGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>880</v>
+      </c>
+      <c r="J200" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>〔状態B〕オーロット＆ヨノワールGX(SA)
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>4980</v>
+      </c>
+      <c r="J201" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>〔状態B〕ウカッツ
+s4a]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>280</v>
+      </c>
+      <c r="J202" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>〔状態C〕ホワイトキュレムGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>880</v>
+      </c>
+      <c r="J203" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ
+XY]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>6480</v>
+      </c>
+      <c r="J204" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>〔状態C〕レックウザGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>15800</v>
+      </c>
+      <c r="J205" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>〔状態B〕セキタンザンV
+s3a]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>280</v>
+      </c>
+      <c r="J206" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ＆ゼクロムGX
+sm9]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>15800</v>
+      </c>
+      <c r="J207" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>〔状態B〕ルナアーラGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>3280</v>
+      </c>
+      <c r="J208" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>〔状態B〕ザオボー
+sm8]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ひかるミュウ
+旧裏]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>328000</v>
+      </c>
+      <c r="J210" t="n">
+        <v>262400</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>〔状態B〕大きなおまもり
+s1a]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>890</v>
+      </c>
+      <c r="J211" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>〔状態B〕マッシブーンGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>780</v>
+      </c>
+      <c r="J212" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケモンレンジャー
+XY]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>9980</v>
+      </c>
+      <c r="J213" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本草エネルギー
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>780</v>
+      </c>
+      <c r="J214" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ダイゴのメタグロスex
+M2a]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>4580</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガシビルドンex
+M2a]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>830</v>
+      </c>
+      <c r="J216" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ロケット団のマタドガス</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>7480</v>
+      </c>
+      <c r="J217" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>イオルブV</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>1180</v>
+      </c>
+      <c r="J218" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>レシラムGX</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>680</v>
+      </c>
+      <c r="J219" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ミロカロス</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>680</v>
+      </c>
+      <c r="J220" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>アシマリ</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>名探偵ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>22800</v>
+      </c>
+      <c r="J222" t="n">
+        <v>18240</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ジバコイルex</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>480</v>
+      </c>
+      <c r="J223" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ピカチュウex</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>280</v>
+      </c>
+      <c r="J224" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フーディン
+M1S]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>630</v>
+      </c>
+      <c r="J225" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>〔状態B〕シロデスナex
+SV8]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>280</v>
+      </c>
+      <c r="J226" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>サーナイト</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>680</v>
+      </c>
+      <c r="J227" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>リオル(マクドナルド)</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>280</v>
+      </c>
+      <c r="J228" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>チャーレムex</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>480</v>
+      </c>
+      <c r="J229" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>エルレイドV</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>1680</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ルガルガンVMAX</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>780</v>
+      </c>
+      <c r="J231" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕メガアブソルex</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>9980</v>
+      </c>
+      <c r="J232" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ペパーのマフィティフex</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>480</v>
+      </c>
+      <c r="J233" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ゾロア</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>680</v>
+      </c>
+      <c r="J234" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕バンギラス</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>7980</v>
+      </c>
+      <c r="J235" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ブラッキーV</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>480</v>
+      </c>
+      <c r="J236" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>アローラベトベトンGX</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>2980</v>
+      </c>
+      <c r="J237" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>サーナイト＆ニンフィアGX</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>4280</v>
+      </c>
+      <c r="J238" t="n">
+        <v>3424</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>カジッチュ</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>680</v>
+      </c>
+      <c r="J239" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>イーブイGX</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>26800</v>
+      </c>
+      <c r="J240" t="n">
+        <v>21440</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>くろおび</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>780</v>
+      </c>
+      <c r="J241" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>改造ハンマー</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>10800</v>
+      </c>
+      <c r="J242" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>魅惑のポフレ</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J243" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>基本草エネルギー(チャンピオンズリーグ2024)</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>580</v>
+      </c>
+      <c r="J244" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ルミタン</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>4980</v>
+      </c>
+      <c r="J245" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ボールガイ</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>480</v>
+      </c>
+      <c r="J246" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>メイのはげまし</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>19800</v>
+      </c>
+      <c r="J247" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>〔状態C〕イベルタルBREAK
+XY]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>420</v>
+      </c>
+      <c r="J248" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヒビキのバクフーン
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>980</v>
+      </c>
+      <c r="J249" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>〔状態C〕ユキメノコ
+S7R]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>780</v>
+      </c>
+      <c r="J250" t="n">
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L250"/>
+  <dimension ref="A1:P307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20044,6 +20044,26 @@
           <t>2026-03-02_diff</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026-03-03_price</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2026-03-03_buy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2026-03-03_ratio</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2026-03-03_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23595,7 +23615,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23620,7 +23639,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23645,7 +23663,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23670,7 +23687,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23695,7 +23711,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23720,7 +23735,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23745,7 +23759,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23770,7 +23783,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23795,7 +23807,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23820,7 +23831,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23845,7 +23855,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23870,7 +23879,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23895,7 +23903,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23920,7 +23927,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23945,7 +23951,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23970,7 +23975,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -23995,7 +23999,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24020,7 +24023,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24045,7 +24047,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24070,7 +24071,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24095,7 +24095,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24120,7 +24119,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24145,7 +24143,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24170,7 +24167,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24195,7 +24191,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24220,7 +24215,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24245,7 +24239,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24270,7 +24263,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24295,7 +24287,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24320,7 +24311,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24345,7 +24335,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24370,7 +24359,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24395,7 +24383,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24420,7 +24407,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24445,7 +24431,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24470,7 +24455,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24495,7 +24479,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24520,7 +24503,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24545,7 +24527,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24570,7 +24551,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24595,7 +24575,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24620,7 +24599,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24645,7 +24623,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24670,7 +24647,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24695,7 +24671,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24720,7 +24695,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24745,7 +24719,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24770,7 +24743,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24795,7 +24767,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24820,7 +24791,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24845,7 +24815,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24870,7 +24839,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24895,7 +24863,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24920,7 +24887,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24945,7 +24911,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24970,7 +24935,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -24995,7 +24959,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25020,7 +24983,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25045,7 +25007,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25070,7 +25031,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25095,7 +25055,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25120,7 +25079,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25145,7 +25103,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25170,7 +25127,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25195,7 +25151,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25220,7 +25175,6 @@
           <t>MA</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25244,7 +25198,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25268,7 +25221,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25292,7 +25244,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25316,7 +25267,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25340,7 +25290,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25364,7 +25313,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25388,7 +25336,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25412,7 +25359,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25437,7 +25383,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25462,7 +25407,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25486,7 +25430,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25510,7 +25453,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25534,7 +25476,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25558,7 +25499,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25582,7 +25522,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25606,7 +25545,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25630,7 +25568,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25654,7 +25591,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25678,7 +25614,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25702,7 +25637,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25726,7 +25660,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25750,7 +25683,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25774,7 +25706,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25798,7 +25729,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25822,7 +25752,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25846,7 +25775,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25870,7 +25798,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25894,7 +25821,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25918,7 +25844,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25942,7 +25867,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25966,7 +25890,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -25991,7 +25914,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -26016,7 +25938,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -26041,7 +25962,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -26052,6 +25972,1431 @@
       </c>
       <c r="J250" t="n">
         <v>624</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本水エネルギー(フレンドバトル)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M251" t="n">
+        <v>320</v>
+      </c>
+      <c r="N251" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本超エネルギー(フレンドバトル)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M252" t="n">
+        <v>350</v>
+      </c>
+      <c r="N252" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本炎エネルギー(フレンドバトル)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M253" t="n">
+        <v>450</v>
+      </c>
+      <c r="N253" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガミミロップex
+M2]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M254" t="n">
+        <v>1190</v>
+      </c>
+      <c r="N254" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>〔状態A-〕クイタラン
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M255" t="n">
+        <v>730</v>
+      </c>
+      <c r="N255" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>〔状態A-〕デンチュラ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M256" t="n">
+        <v>530</v>
+      </c>
+      <c r="N256" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>〔状態A-〕モグリュー
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M257" t="n">
+        <v>530</v>
+      </c>
+      <c r="N257" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>〔状態A-〕Nの筋書き
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M258" t="n">
+        <v>6980</v>
+      </c>
+      <c r="N258" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のニャース
+SV10]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M259" t="n">
+        <v>1390</v>
+      </c>
+      <c r="N259" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>〔状態C〕Nのゾロア(未開封)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M260" t="n">
+        <v>320</v>
+      </c>
+      <c r="N260" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>〔状態B〕オーベムBREAK
+その他]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M261" t="n">
+        <v>880</v>
+      </c>
+      <c r="N261" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トドロクツキex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M262" t="n">
+        <v>3580</v>
+      </c>
+      <c r="N262" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブラックキュレムex
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M263" t="n">
+        <v>480</v>
+      </c>
+      <c r="N263" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レントラーex
+SV6]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M264" t="n">
+        <v>580</v>
+      </c>
+      <c r="N264" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハヤシガメ
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M265" t="n">
+        <v>380</v>
+      </c>
+      <c r="N265" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジャッジマン
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M266" t="n">
+        <v>680</v>
+      </c>
+      <c r="N266" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブビィ
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M267" t="n">
+        <v>480</v>
+      </c>
+      <c r="N267" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フーパEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M268" t="n">
+        <v>330</v>
+      </c>
+      <c r="N268" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本炎エネルギー(ジムチャレンジ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M269" t="n">
+        <v>420</v>
+      </c>
+      <c r="N269" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>〔状態C〕リザードンex
+SV3]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M270" t="n">
+        <v>220</v>
+      </c>
+      <c r="N270" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゲノセクト
+その他]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M271" t="n">
+        <v>580</v>
+      </c>
+      <c r="N271" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>〔状態B〕ギラティナVSTAR
+S11]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M272" t="n">
+        <v>1980</v>
+      </c>
+      <c r="N272" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラウドボーンex
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M273" t="n">
+        <v>4180</v>
+      </c>
+      <c r="N273" t="n">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>〔状態A-〕デカグースGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M274" t="n">
+        <v>260</v>
+      </c>
+      <c r="N274" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メロン
+S12a]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M275" t="n">
+        <v>1090</v>
+      </c>
+      <c r="N275" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>〔状態A-〕セレナ
+S11a]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M276" t="n">
+        <v>1680</v>
+      </c>
+      <c r="N276" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジムバッジ(ナギ)
+XY]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M277" t="n">
+        <v>4780</v>
+      </c>
+      <c r="N277" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トゲデマル
+その他]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M278" t="n">
+        <v>2990</v>
+      </c>
+      <c r="N278" t="n">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジャローダV
+S11a]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M279" t="n">
+        <v>4480</v>
+      </c>
+      <c r="N279" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>〔状態B〕ガラルヤドキングVMAX
+S5a]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M280" t="n">
+        <v>1180</v>
+      </c>
+      <c r="N280" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒトカゲ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M281" t="n">
+        <v>730</v>
+      </c>
+      <c r="N281" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フェローチェGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M282" t="n">
+        <v>1390</v>
+      </c>
+      <c r="N282" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>〔状態A-〕地底探険隊
+sm6]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>26800</v>
+      </c>
+      <c r="N283" t="n">
+        <v>21440</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジュカインEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M284" t="n">
+        <v>1280</v>
+      </c>
+      <c r="N284" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メタグロスGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M285" t="n">
+        <v>330</v>
+      </c>
+      <c r="N285" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スクールガール
+S7D]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M286" t="n">
+        <v>730</v>
+      </c>
+      <c r="N286" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>〔状態A-〕にせオーキドはかせ(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M287" t="n">
+        <v>730</v>
+      </c>
+      <c r="N287" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウδ-デルタ種(明治)
+その他]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M288" t="n">
+        <v>29800</v>
+      </c>
+      <c r="N288" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サカキの追放
+sm10]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
+        <v>1690</v>
+      </c>
+      <c r="N289" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>〔状態A-〕くろおび
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M290" t="n">
+        <v>680</v>
+      </c>
+      <c r="N290" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マルヤクデV
+s4a]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M291" t="n">
+        <v>260</v>
+      </c>
+      <c r="N291" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アーマーガアV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M292" t="n">
+        <v>830</v>
+      </c>
+      <c r="N292" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>〔状態C〕チコリータ(マクドナルド)
+その他]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M293" t="n">
+        <v>23800</v>
+      </c>
+      <c r="N293" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>〔状態C〕マナフィ
+その他]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M294" t="n">
+        <v>980</v>
+      </c>
+      <c r="N294" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>〔状態B〕ガラルファイヤーV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M295" t="n">
+        <v>830</v>
+      </c>
+      <c r="N295" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>〔状態B〕ボルケニオンV
+S6H]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M296" t="n">
+        <v>280</v>
+      </c>
+      <c r="N296" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>〔状態B〕コバルオンEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M297" t="n">
+        <v>5490</v>
+      </c>
+      <c r="N297" t="n">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウ(古代文字Nintendo前期)
+その他]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M298" t="n">
+        <v>42800</v>
+      </c>
+      <c r="N298" t="n">
+        <v>34240</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>〔状態C〕エレキパワー
+sm7]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M299" t="n">
+        <v>980</v>
+      </c>
+      <c r="N299" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>〔状態C〕イエッサンV
+S-P]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M300" t="n">
+        <v>6480</v>
+      </c>
+      <c r="N300" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>〔状態B〕MギャラドスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M301" t="n">
+        <v>6480</v>
+      </c>
+      <c r="N301" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>〔状態B〕オーロット＆ヨノワールGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M302" t="n">
+        <v>1780</v>
+      </c>
+      <c r="N302" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヤレユータン
+その他]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M303" t="n">
+        <v>5980</v>
+      </c>
+      <c r="N303" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>〔状態B〕ウルトラネクロズマ
+その他]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M304" t="n">
+        <v>5480</v>
+      </c>
+      <c r="N304" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>〔状態B〕おじょうさま
+sm11a]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M305" t="n">
+        <v>590</v>
+      </c>
+      <c r="N305" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラメシヤ
+M2a]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M306" t="n">
+        <v>480</v>
+      </c>
+      <c r="N306" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガユキメノコex
+M2a]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M307" t="n">
+        <v>3080</v>
+      </c>
+      <c r="N307" t="n">
+        <v>2464</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P307"/>
+  <dimension ref="A1:T409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20064,6 +20064,26 @@
           <t>2026-03-03_diff</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2026-03-04_price</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2026-03-04_buy</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2026-03-04_ratio</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2026-03-04_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25986,7 +26006,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26011,7 +26030,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26036,7 +26054,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26061,7 +26078,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26086,7 +26102,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26111,7 +26126,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26136,7 +26150,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26161,7 +26174,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26186,7 +26198,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26211,7 +26222,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26236,7 +26246,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26261,7 +26270,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26286,7 +26294,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26311,7 +26318,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26336,7 +26342,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26361,7 +26366,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26386,7 +26390,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26411,7 +26414,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26436,7 +26438,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26461,7 +26462,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26486,7 +26486,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26511,7 +26510,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26536,7 +26534,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26561,7 +26558,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26586,7 +26582,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26611,7 +26606,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26636,7 +26630,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26661,7 +26654,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26686,7 +26678,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26711,7 +26702,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26736,7 +26726,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26761,7 +26750,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26786,7 +26774,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26811,7 +26798,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26836,7 +26822,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26861,7 +26846,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26886,7 +26870,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26911,7 +26894,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26936,7 +26918,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26961,7 +26942,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -26986,7 +26966,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27011,7 +26990,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27036,7 +27014,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27061,7 +27038,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27086,7 +27062,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27111,7 +27086,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27136,7 +27110,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27161,7 +27134,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27186,7 +27158,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27211,7 +27182,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27236,7 +27206,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27261,7 +27230,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27286,7 +27254,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27311,7 +27278,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27336,7 +27302,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27361,7 +27326,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27386,7 +27350,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27397,6 +27360,2518 @@
       </c>
       <c r="N307" t="n">
         <v>2464</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>サザンドラex</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>280</v>
+      </c>
+      <c r="R308" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>〔状態C〕テツノイバラ
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>280</v>
+      </c>
+      <c r="R309" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本悪エネルギー(フレンドバトル)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>350</v>
+      </c>
+      <c r="R310" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケモンいれかえ
+M2]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q311" t="n">
+        <v>450</v>
+      </c>
+      <c r="R311" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>〔状態B〕ビクティニ(未開封/AR仕様)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q312" t="n">
+        <v>1980</v>
+      </c>
+      <c r="R312" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>〔状態B〕ウルガモス
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q313" t="n">
+        <v>980</v>
+      </c>
+      <c r="R313" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ナンジャモのタイカイデン
+SV9]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q314" t="n">
+        <v>580</v>
+      </c>
+      <c r="R314" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヨルノズクBREAK
+その他]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q315" t="n">
+        <v>2780</v>
+      </c>
+      <c r="R315" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブリジュラスex
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q316" t="n">
+        <v>480</v>
+      </c>
+      <c r="R316" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラティアス(ジャンボカード)
+ジャンボカード]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q317" t="n">
+        <v>680</v>
+      </c>
+      <c r="R317" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カイデン
+SV6]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q318" t="n">
+        <v>380</v>
+      </c>
+      <c r="R318" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウミトリオex
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q319" t="n">
+        <v>380</v>
+      </c>
+      <c r="R319" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シャリタツ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q320" t="n">
+        <v>260</v>
+      </c>
+      <c r="R320" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サーナイトex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q321" t="n">
+        <v>690</v>
+      </c>
+      <c r="R321" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グソクムシャex
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q322" t="n">
+        <v>1680</v>
+      </c>
+      <c r="R322" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミガルーサ
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q323" t="n">
+        <v>480</v>
+      </c>
+      <c r="R323" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本闘エネルギー(チャンピオンズリーグ2024)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q324" t="n">
+        <v>480</v>
+      </c>
+      <c r="R324" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>〔状態C〕ウインディex
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q325" t="n">
+        <v>380</v>
+      </c>
+      <c r="R325" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本雷エネルギー(ステーション)
+その他]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q326" t="n">
+        <v>230</v>
+      </c>
+      <c r="R326" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アノクサ
+SV2P]</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q327" t="n">
+        <v>450</v>
+      </c>
+      <c r="R327" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ホシガリス
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q328" t="n">
+        <v>380</v>
+      </c>
+      <c r="R328" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スター団のしたっぱ
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q329" t="n">
+        <v>480</v>
+      </c>
+      <c r="R329" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q330" t="n">
+        <v>480</v>
+      </c>
+      <c r="R330" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポンチョを着たイーブイ(SW/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q331" t="n">
+        <v>248000</v>
+      </c>
+      <c r="R331" t="n">
+        <v>198400</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パルスワン
+s4a]</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q332" t="n">
+        <v>330</v>
+      </c>
+      <c r="R332" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シトロン
+XY]</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q333" t="n">
+        <v>350</v>
+      </c>
+      <c r="R333" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジュナイパー
+その他]</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q334" t="n">
+        <v>480</v>
+      </c>
+      <c r="R334" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エーフィV
+S6a]</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q335" t="n">
+        <v>250</v>
+      </c>
+      <c r="R335" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MバンギラスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q336" t="n">
+        <v>44800</v>
+      </c>
+      <c r="R336" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブースター
+その他]</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q337" t="n">
+        <v>15800</v>
+      </c>
+      <c r="R337" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ビクティニV(Vバレット)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q338" t="n">
+        <v>103000</v>
+      </c>
+      <c r="R338" t="n">
+        <v>82400</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウ(古代文字2019)
+その他]</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q339" t="n">
+        <v>70800</v>
+      </c>
+      <c r="R339" t="n">
+        <v>56640</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>〔状態A-〕クララ
+S5a]</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q340" t="n">
+        <v>11800</v>
+      </c>
+      <c r="R340" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミミッキュGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q341" t="n">
+        <v>9980</v>
+      </c>
+      <c r="R341" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グレイシアGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q342" t="n">
+        <v>5980</v>
+      </c>
+      <c r="R342" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q343" t="n">
+        <v>5280</v>
+      </c>
+      <c r="R343" t="n">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニンフィアGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q344" t="n">
+        <v>26800</v>
+      </c>
+      <c r="R344" t="n">
+        <v>21440</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブラッキー＆ダークライGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q345" t="n">
+        <v>21800</v>
+      </c>
+      <c r="R345" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カミツレのきらめき
+S8]</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q346" t="n">
+        <v>1690</v>
+      </c>
+      <c r="R346" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シロナの覇気
+S9]</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q347" t="n">
+        <v>690</v>
+      </c>
+      <c r="R347" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>〔状態C〕ラティオス
+その他]</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q348" t="n">
+        <v>2190</v>
+      </c>
+      <c r="R348" t="n">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>〔状態B〕まんたんのくすり
+その他]</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q349" t="n">
+        <v>3780</v>
+      </c>
+      <c r="R349" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼルネアスEX(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q350" t="n">
+        <v>1180</v>
+      </c>
+      <c r="R350" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブラッキーVMAX(SA)
+S6a]</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q351" t="n">
+        <v>468000</v>
+      </c>
+      <c r="R351" t="n">
+        <v>374400</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>〔状態B〕いちげきウーラオスV
+S5I]</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q352" t="n">
+        <v>320</v>
+      </c>
+      <c r="R352" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>〔状態B〕エアームドEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q353" t="n">
+        <v>3490</v>
+      </c>
+      <c r="R353" t="n">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本水エネルギー(LAWSON/ミラー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q354" t="n">
+        <v>2980</v>
+      </c>
+      <c r="R354" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>〔状態C〕ダートじてんしゃ
+sm7]</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q355" t="n">
+        <v>980</v>
+      </c>
+      <c r="R355" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>〔状態B〕ローズ
+S3]</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q356" t="n">
+        <v>280</v>
+      </c>
+      <c r="R356" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>〔状態B〕エーフィGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q357" t="n">
+        <v>15800</v>
+      </c>
+      <c r="R357" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>〔状態B〕ザシアンV
+s1]</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q358" t="n">
+        <v>490</v>
+      </c>
+      <c r="R358" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>〔状態B〕かいじゅうマニア
+sm10b]</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q359" t="n">
+        <v>680</v>
+      </c>
+      <c r="R359" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本フェアリーエネルギー(ファーストデザインキラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q360" t="n">
+        <v>44800</v>
+      </c>
+      <c r="R360" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヨコハマのピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q361" t="n">
+        <v>59800</v>
+      </c>
+      <c r="R361" t="n">
+        <v>47840</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジュナイパーGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q362" t="n">
+        <v>1180</v>
+      </c>
+      <c r="R362" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>〔状態B〕ギラティナEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q363" t="n">
+        <v>44800</v>
+      </c>
+      <c r="R363" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>〔状態B〕N
+その他]</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q364" t="n">
+        <v>44800</v>
+      </c>
+      <c r="R364" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>〔状態B〕エレザード
+M2a]</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q365" t="n">
+        <v>280</v>
+      </c>
+      <c r="R365" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕リザードンV(SA)</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q366" t="n">
+        <v>52800</v>
+      </c>
+      <c r="R366" t="n">
+        <v>42240</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>コロトックV</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q367" t="n">
+        <v>480</v>
+      </c>
+      <c r="R367" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>フクスロー</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q368" t="n">
+        <v>280</v>
+      </c>
+      <c r="R368" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>メラルバ</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q369" t="n">
+        <v>580</v>
+      </c>
+      <c r="R369" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>マグカルゴGX</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q370" t="n">
+        <v>1080</v>
+      </c>
+      <c r="R370" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>〔状態B〕ウッウ
+SV5a]</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q371" t="n">
+        <v>320</v>
+      </c>
+      <c r="R371" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>パオジアンex</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q372" t="n">
+        <v>980</v>
+      </c>
+      <c r="R372" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>ガラルヒヒダルマVMAX</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q373" t="n">
+        <v>680</v>
+      </c>
+      <c r="R373" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>シママ</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q374" t="n">
+        <v>580</v>
+      </c>
+      <c r="R374" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>カプ・コケコex</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q375" t="n">
+        <v>2380</v>
+      </c>
+      <c r="R375" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>カプ・コケコVMAX</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q376" t="n">
+        <v>780</v>
+      </c>
+      <c r="R376" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>メガサーナイトex</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>MUR</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q377" t="n">
+        <v>57800</v>
+      </c>
+      <c r="R377" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>フワンテ</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q378" t="n">
+        <v>380</v>
+      </c>
+      <c r="R378" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>ソルガレオ＆ルナアーラGX(SA)</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q379" t="n">
+        <v>29800</v>
+      </c>
+      <c r="R379" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>こくばバドレックスVMAX</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q380" t="n">
+        <v>220</v>
+      </c>
+      <c r="R380" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>オコリザル</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q381" t="n">
+        <v>380</v>
+      </c>
+      <c r="R381" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>イシヘンジンV</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q382" t="n">
+        <v>480</v>
+      </c>
+      <c r="R382" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>ゾロアーク</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q383" t="n">
+        <v>2380</v>
+      </c>
+      <c r="R383" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>〔状態B〕マシマシラex
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q384" t="n">
+        <v>280</v>
+      </c>
+      <c r="R384" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>ダストダス</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q385" t="n">
+        <v>480</v>
+      </c>
+      <c r="R385" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ゾロアークGX</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q386" t="n">
+        <v>280</v>
+      </c>
+      <c r="R386" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>メルタン</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q387" t="n">
+        <v>680</v>
+      </c>
+      <c r="R387" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>ギルガルドV</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q388" t="n">
+        <v>580</v>
+      </c>
+      <c r="R388" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>タルップル</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q389" t="n">
+        <v>580</v>
+      </c>
+      <c r="R389" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>テッカグヤGX</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q390" t="n">
+        <v>480</v>
+      </c>
+      <c r="R390" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ヒビキの冒険</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q391" t="n">
+        <v>14800</v>
+      </c>
+      <c r="R391" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>なかよしポフィン</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q392" t="n">
+        <v>220</v>
+      </c>
+      <c r="R392" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>〔PSA8鑑定済〕基本草エネルギー(クイックキラ)</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q393" t="n">
+        <v>52800</v>
+      </c>
+      <c r="R393" t="n">
+        <v>42240</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>基本超エネルギー(SS新デザイン)</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q394" t="n">
+        <v>380</v>
+      </c>
+      <c r="R394" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>基本草エネルギー(クイックキラ)</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q395" t="n">
+        <v>94800</v>
+      </c>
+      <c r="R395" t="n">
+        <v>75840</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>アセロラのいたずら</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q396" t="n">
+        <v>2380</v>
+      </c>
+      <c r="R396" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>タイム</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q397" t="n">
+        <v>480</v>
+      </c>
+      <c r="R397" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>フトゥー博士のシナリオ</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q398" t="n">
+        <v>1480</v>
+      </c>
+      <c r="R398" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕メイ</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q399" t="n">
+        <v>94800</v>
+      </c>
+      <c r="R399" t="n">
+        <v>75840</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>メリッサ</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q400" t="n">
+        <v>580</v>
+      </c>
+      <c r="R400" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>チェレンの気くばり</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q401" t="n">
+        <v>580</v>
+      </c>
+      <c r="R401" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>博士の研究/オーキド博士(25th)</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q402" t="n">
+        <v>480</v>
+      </c>
+      <c r="R402" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>ローズ</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q403" t="n">
+        <v>580</v>
+      </c>
+      <c r="R403" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>コルニ</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q404" t="n">
+        <v>138000</v>
+      </c>
+      <c r="R404" t="n">
+        <v>110400</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジャッジマン
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Q405" t="n">
+        <v>580</v>
+      </c>
+      <c r="R405" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>〔状態C〕ブラックキュレム
+その他]</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Q406" t="n">
+        <v>380</v>
+      </c>
+      <c r="R406" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>〔状態C〕コイキング
+その他]</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Q407" t="n">
+        <v>1280</v>
+      </c>
+      <c r="R407" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>〔状態A-〕チラチーノ
+その他]</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Q408" t="n">
+        <v>1090</v>
+      </c>
+      <c r="R408" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本雷エネルギー(フレンドバトル)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Q409" t="n">
+        <v>220</v>
+      </c>
+      <c r="R409" t="n">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T409"/>
+  <dimension ref="A1:X474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20084,6 +20084,26 @@
           <t>2026-03-04_diff</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2026-03-05_price</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2026-03-05_buy</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2026-03-05_ratio</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2026-03-05_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27373,7 +27393,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27398,7 +27417,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27423,7 +27441,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27448,7 +27465,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27473,7 +27489,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27498,7 +27513,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27523,7 +27537,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27548,7 +27561,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27573,7 +27585,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27598,7 +27609,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27623,7 +27633,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27648,7 +27657,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27673,7 +27681,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27698,7 +27705,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27723,7 +27729,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27748,7 +27753,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27773,7 +27777,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27798,7 +27801,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27823,7 +27825,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27848,7 +27849,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27873,7 +27873,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27898,7 +27897,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27923,7 +27921,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27948,7 +27945,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27973,7 +27969,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -27998,7 +27993,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28023,7 +28017,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28048,7 +28041,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28073,7 +28065,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28098,7 +28089,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28123,7 +28113,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28148,7 +28137,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28173,7 +28161,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28198,7 +28185,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28223,7 +28209,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28248,7 +28233,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28273,7 +28257,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28298,7 +28281,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28323,7 +28305,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28348,7 +28329,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28373,7 +28353,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28398,7 +28377,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28423,7 +28401,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28448,7 +28425,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28473,7 +28449,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28498,7 +28473,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28523,7 +28497,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28548,7 +28521,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28573,7 +28545,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28598,7 +28569,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28623,7 +28593,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28648,7 +28617,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28673,7 +28641,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28698,7 +28665,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28723,7 +28689,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28748,7 +28713,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28773,7 +28737,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28798,7 +28761,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28822,7 +28784,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28846,7 +28807,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28870,7 +28830,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28894,7 +28853,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28918,7 +28876,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28943,7 +28900,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28967,7 +28923,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -28991,7 +28946,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29015,7 +28969,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29039,7 +28992,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29063,7 +29015,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29087,7 +29038,6 @@
           <t>MUR</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29111,7 +29061,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29135,7 +29084,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29159,7 +29107,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29183,7 +29130,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29207,7 +29153,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29231,7 +29176,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29256,7 +29200,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29280,7 +29223,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29304,7 +29246,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29328,7 +29269,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29352,7 +29292,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29376,7 +29315,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29400,7 +29338,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29424,7 +29361,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29448,7 +29384,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29472,7 +29407,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29496,7 +29430,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29520,7 +29453,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29544,7 +29476,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29568,7 +29499,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29592,7 +29522,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29616,7 +29545,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29640,7 +29568,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29664,7 +29591,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29688,7 +29614,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29712,7 +29637,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29736,7 +29660,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29761,7 +29684,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -29786,7 +29708,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -29811,7 +29732,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -29836,7 +29756,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -29861,7 +29780,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -29872,6 +29790,1627 @@
       </c>
       <c r="R409" t="n">
         <v>176</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA9鑑定済〕リーリエ(SR仕様)</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U410" t="n">
+        <v>6980000</v>
+      </c>
+      <c r="V410" t="n">
+        <v>5584000</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>〔状態C〕テツノイバラ
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U411" t="n">
+        <v>280</v>
+      </c>
+      <c r="V411" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>〔状態A-〕デント
+その他]</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U412" t="n">
+        <v>1090</v>
+      </c>
+      <c r="V412" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>〔状態B〕ドリュウズ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U413" t="n">
+        <v>1680</v>
+      </c>
+      <c r="V413" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ギーマの一手
+M2]</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U414" t="n">
+        <v>450</v>
+      </c>
+      <c r="V414" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>〔状態A-〕こだわりメット
+その他]</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U415" t="n">
+        <v>260</v>
+      </c>
+      <c r="V415" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>〔状態B〕ビリジオン
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U416" t="n">
+        <v>880</v>
+      </c>
+      <c r="V416" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゴビット
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U417" t="n">
+        <v>580</v>
+      </c>
+      <c r="V417" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>〔状態A-〕モンメン
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U418" t="n">
+        <v>730</v>
+      </c>
+      <c r="V418" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>〔状態B〕Nの筋書き
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U419" t="n">
+        <v>5980</v>
+      </c>
+      <c r="V419" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シロナのロズレイド
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U420" t="n">
+        <v>1530</v>
+      </c>
+      <c r="V420" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>〔状態B〕Nのゾロア(未開封)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U421" t="n">
+        <v>580</v>
+      </c>
+      <c r="V421" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブラッキーex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U422" t="n">
+        <v>480</v>
+      </c>
+      <c r="V422" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルチアのアピール
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U423" t="n">
+        <v>4180</v>
+      </c>
+      <c r="V423" t="n">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>〔状態C〕ラティアスδ-デルタ種
+その他]</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U424" t="n">
+        <v>2790</v>
+      </c>
+      <c r="V424" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>〔状態B〕カイデン
+SV6]</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U425" t="n">
+        <v>280</v>
+      </c>
+      <c r="V425" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>〔状態B〕ビワ
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U426" t="n">
+        <v>1380</v>
+      </c>
+      <c r="V426" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヤミラミ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U427" t="n">
+        <v>280</v>
+      </c>
+      <c r="V427" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヤドン
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U428" t="n">
+        <v>730</v>
+      </c>
+      <c r="V428" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>〔状態B〕コソクムシ
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U429" t="n">
+        <v>320</v>
+      </c>
+      <c r="V429" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本雷エネルギー(チャンピオンズリーグ2024)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U430" t="n">
+        <v>830</v>
+      </c>
+      <c r="V430" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>〔状態B〕イーブイ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U431" t="n">
+        <v>1880</v>
+      </c>
+      <c r="V431" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>〔状態B〕カプ・テテフ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U432" t="n">
+        <v>15800</v>
+      </c>
+      <c r="V432" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ライム
+SV3]</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U433" t="n">
+        <v>380</v>
+      </c>
+      <c r="V433" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>〔状態B〕アーボックex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U434" t="n">
+        <v>280</v>
+      </c>
+      <c r="V434" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スピアーV(SA)
+S10P]</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U435" t="n">
+        <v>3680</v>
+      </c>
+      <c r="V435" t="n">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>〔状態B〕オリジンディアルガVSTAR
+S10D]</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U436" t="n">
+        <v>1280</v>
+      </c>
+      <c r="V436" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>〔状態B〕タマンチュラ
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U437" t="n">
+        <v>280</v>
+      </c>
+      <c r="V437" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ストリンダー
+s4a]</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U438" t="n">
+        <v>260</v>
+      </c>
+      <c r="V438" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サンダース
+S8b]</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U439" t="n">
+        <v>1880</v>
+      </c>
+      <c r="V439" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>〔状態C〕シャワーズ
+その他]</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U440" t="n">
+        <v>10800</v>
+      </c>
+      <c r="V440" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エネルギーつけかえ
+XY]</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U441" t="n">
+        <v>16300</v>
+      </c>
+      <c r="V441" t="n">
+        <v>13040</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マルチエネルギー
+その他]</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U442" t="n">
+        <v>2490</v>
+      </c>
+      <c r="V442" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団の幹部(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U443" t="n">
+        <v>580</v>
+      </c>
+      <c r="V443" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルガルガンV
+S7D]</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U444" t="n">
+        <v>450</v>
+      </c>
+      <c r="V444" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リーフィアGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U445" t="n">
+        <v>9980</v>
+      </c>
+      <c r="V445" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タケシのガッツ
+sm9]</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U446" t="n">
+        <v>1890</v>
+      </c>
+      <c r="V446" t="n">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本闘エネルギー(ステーション)
+その他]</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U447" t="n">
+        <v>330</v>
+      </c>
+      <c r="V447" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カビゴンVMAX
+s1]</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U448" t="n">
+        <v>2790</v>
+      </c>
+      <c r="V448" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マオ
+sm2]</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U449" t="n">
+        <v>47800</v>
+      </c>
+      <c r="V449" t="n">
+        <v>38240</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ソルガレオ＆ルナアーラGX
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U450" t="n">
+        <v>1880</v>
+      </c>
+      <c r="V450" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フーディンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U451" t="n">
+        <v>26800</v>
+      </c>
+      <c r="V451" t="n">
+        <v>21440</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>〔状態A-〕れんげきウーラオスV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U452" t="n">
+        <v>930</v>
+      </c>
+      <c r="V452" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>〔状態A-〕インテレオンV
+s1a]</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U453" t="n">
+        <v>690</v>
+      </c>
+      <c r="V453" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウVMAX(RRR仕様/コロコロコミック)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U454" t="n">
+        <v>2490</v>
+      </c>
+      <c r="V454" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キャンプファイヤー
+S9]</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U455" t="n">
+        <v>480</v>
+      </c>
+      <c r="V455" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>〔状態B〕キクコ
+S6K]</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U456" t="n">
+        <v>480</v>
+      </c>
+      <c r="V456" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本鋼エネルギー(in 東京タワー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U457" t="n">
+        <v>3980</v>
+      </c>
+      <c r="V457" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>〔状態B〕アローラライチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U458" t="n">
+        <v>580</v>
+      </c>
+      <c r="V458" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>〔状態B〕リザードンV(SR仕様)</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U459" t="n">
+        <v>198000</v>
+      </c>
+      <c r="V459" t="n">
+        <v>158400</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>〔状態B〕テンガン山
+SM9b]</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U460" t="n">
+        <v>780</v>
+      </c>
+      <c r="V460" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハマナのリサーチ(キラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U461" t="n">
+        <v>15800</v>
+      </c>
+      <c r="V461" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>〔状態B〕バシャーモGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U462" t="n">
+        <v>1780</v>
+      </c>
+      <c r="V462" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>〔状態B〕こわいおねえさん
+XY]</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U463" t="n">
+        <v>108000</v>
+      </c>
+      <c r="V463" t="n">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>〔状態B〕マーマネ
+sm2]</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U464" t="n">
+        <v>6480</v>
+      </c>
+      <c r="V464" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>〔状態C〕カミツルギGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U465" t="n">
+        <v>1080</v>
+      </c>
+      <c r="V465" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>〔状態B〕フライゴンGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U466" t="n">
+        <v>380</v>
+      </c>
+      <c r="V466" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>〔状態B〕ソルガレオGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U467" t="n">
+        <v>1980</v>
+      </c>
+      <c r="V467" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>〔状態B〕炎の結晶
+sm10]</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U468" t="n">
+        <v>880</v>
+      </c>
+      <c r="V468" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>〔状態B〕マオ
+sm2]</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U469" t="n">
+        <v>32800</v>
+      </c>
+      <c r="V469" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>〔状態B〕エール団のしたっぱ
+s1]</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U470" t="n">
+        <v>320</v>
+      </c>
+      <c r="V470" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>〔状態B〕ランダムレシーバー
+その他]</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U471" t="n">
+        <v>5990</v>
+      </c>
+      <c r="V471" t="n">
+        <v>4792</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>〔状態B〕テッカニン
+M1S]</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U472" t="n">
+        <v>280</v>
+      </c>
+      <c r="V472" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>ビビヨン</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U473" t="n">
+        <v>480</v>
+      </c>
+      <c r="V473" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>マスカーニャex</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U474" t="n">
+        <v>580</v>
+      </c>
+      <c r="V474" t="n">
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X474"/>
+  <dimension ref="A1:AB474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20104,6 +20104,26 @@
           <t>2026-03-05_diff</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2026-03-06_price</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2026-03-06_buy</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2026-03-06_ratio</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2026-03-06_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29803,7 +29823,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29828,7 +29847,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29853,7 +29871,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29878,7 +29895,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29903,7 +29919,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29928,7 +29943,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29953,7 +29967,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -29978,7 +29991,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30003,7 +30015,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30028,7 +30039,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30053,7 +30063,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30078,7 +30087,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30103,7 +30111,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30128,7 +30135,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30153,7 +30159,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30178,7 +30183,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30203,7 +30207,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30228,7 +30231,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30253,7 +30255,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30278,7 +30279,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30303,7 +30303,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30328,7 +30327,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30353,7 +30351,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30378,7 +30375,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30403,7 +30399,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30428,7 +30423,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30453,7 +30447,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30478,7 +30471,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30503,7 +30495,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30528,7 +30519,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30553,7 +30543,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30578,7 +30567,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30603,7 +30591,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30628,7 +30615,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30653,7 +30639,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30678,7 +30663,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30703,7 +30687,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30728,7 +30711,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30753,7 +30735,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30778,7 +30759,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30803,7 +30783,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30828,7 +30807,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30853,7 +30831,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30878,7 +30855,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30903,7 +30879,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30928,7 +30903,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30953,7 +30927,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -30978,7 +30951,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31003,7 +30975,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31027,7 +30998,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31052,7 +31022,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31077,7 +31046,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31102,7 +31070,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31127,7 +31094,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31152,7 +31118,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31177,7 +31142,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31202,7 +31166,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31227,7 +31190,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31252,7 +31214,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31277,7 +31238,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31302,7 +31262,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31327,7 +31286,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31352,7 +31310,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31376,7 +31333,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -31400,7 +31356,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
           <t>zaiko_ari</t>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB474"/>
+  <dimension ref="A1:AF474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20124,6 +20124,26 @@
           <t>2026-03-06_diff</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2026-03-07_price</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2026-03-07_buy</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2026-03-07_ratio</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2026-03-07_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF474"/>
+  <dimension ref="A1:AJ474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20144,6 +20144,26 @@
           <t>2026-03-07_diff</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2026-03-08_price</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2026-03-08_buy</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2026-03-08_ratio</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2026-03-08_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ474"/>
+  <dimension ref="A1:AN474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20164,6 +20164,26 @@
           <t>2026-03-08_diff</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2026-03-09_price</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2026-03-09_buy</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2026-03-09_ratio</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2026-03-09_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN474"/>
+  <dimension ref="A1:AR474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20184,6 +20184,26 @@
           <t>2026-03-09_diff</t>
         </is>
       </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2026-03-10_price</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2026-03-10_buy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2026-03-10_ratio</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2026-03-10_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR474"/>
+  <dimension ref="A1:AV474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20204,6 +20204,26 @@
           <t>2026-03-10_diff</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2026-03-11_price</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2026-03-11_buy</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2026-03-11_ratio</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2026-03-11_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV474"/>
+  <dimension ref="A1:AZ474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20224,6 +20224,26 @@
           <t>2026-03-11_diff</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2026-03-12_price</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2026-03-12_buy</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2026-03-12_ratio</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2026-03-12_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ474"/>
+  <dimension ref="A1:BD474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20244,6 +20244,26 @@
           <t>2026-03-12_diff</t>
         </is>
       </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2026-03-13_price</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2026-03-13_buy</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2026-03-13_ratio</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2026-03-13_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD474"/>
+  <dimension ref="A1:BH474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20264,6 +20264,26 @@
           <t>2026-03-13_diff</t>
         </is>
       </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>2026-03-14_price</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>2026-03-14_buy</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>2026-03-14_ratio</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>2026-03-14_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH474"/>
+  <dimension ref="A1:BL474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20284,6 +20284,26 @@
           <t>2026-03-14_diff</t>
         </is>
       </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>2026-03-15_price</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>2026-03-15_buy</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>2026-03-15_ratio</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>2026-03-15_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL474"/>
+  <dimension ref="A1:BP474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20304,6 +20304,26 @@
           <t>2026-03-15_diff</t>
         </is>
       </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>2026-03-16_price</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>2026-03-16_buy</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>2026-03-16_ratio</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>2026-03-16_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP474"/>
+  <dimension ref="A1:BT474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20324,6 +20324,26 @@
           <t>2026-03-16_diff</t>
         </is>
       </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>2026-03-17_price</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>2026-03-17_buy</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>2026-03-17_ratio</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>2026-03-17_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT474"/>
+  <dimension ref="A1:BX474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20344,6 +20344,26 @@
           <t>2026-03-17_diff</t>
         </is>
       </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>2026-03-18_price</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>2026-03-18_buy</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>2026-03-18_ratio</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>2026-03-18_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX474"/>
+  <dimension ref="A1:CB474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20364,6 +20364,26 @@
           <t>2026-03-18_diff</t>
         </is>
       </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>2026-03-19_price</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>2026-03-19_buy</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>2026-03-19_ratio</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>2026-03-19_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB474"/>
+  <dimension ref="A1:CF474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20384,6 +20384,26 @@
           <t>2026-03-19_diff</t>
         </is>
       </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>2026-03-20_price</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>2026-03-20_buy</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>2026-03-20_ratio</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>2026-03-20_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF474"/>
+  <dimension ref="A1:CJ474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20404,6 +20404,26 @@
           <t>2026-03-20_diff</t>
         </is>
       </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>2026-03-21_price</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>2026-03-21_buy</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>2026-03-21_ratio</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>2026-03-21_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ474"/>
+  <dimension ref="A1:CN474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20424,6 +20424,26 @@
           <t>2026-03-21_diff</t>
         </is>
       </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>2026-03-22_price</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>2026-03-22_buy</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>2026-03-22_ratio</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>2026-03-22_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN474"/>
+  <dimension ref="A1:CR474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20444,6 +20444,26 @@
           <t>2026-03-22_diff</t>
         </is>
       </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>2026-03-23_price</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>2026-03-23_buy</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>2026-03-23_ratio</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>2026-03-23_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR474"/>
+  <dimension ref="A1:CV474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20464,6 +20464,26 @@
           <t>2026-03-23_diff</t>
         </is>
       </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>2026-03-24_price</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>2026-03-24_buy</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>2026-03-24_ratio</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>2026-03-24_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV474"/>
+  <dimension ref="A1:CZ474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20484,6 +20484,26 @@
           <t>2026-03-24_diff</t>
         </is>
       </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>2026-03-25_price</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>2026-03-25_buy</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>2026-03-25_ratio</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>2026-03-25_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ474"/>
+  <dimension ref="A1:DD474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20504,6 +20504,26 @@
           <t>2026-03-25_diff</t>
         </is>
       </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>2026-03-26_price</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>2026-03-26_buy</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>2026-03-26_ratio</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>2026-03-26_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD474"/>
+  <dimension ref="A1:DH474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20524,6 +20524,26 @@
           <t>2026-03-26_diff</t>
         </is>
       </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>2026-03-27_price</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>2026-03-27_buy</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>2026-03-27_ratio</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>2026-03-27_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH474"/>
+  <dimension ref="A1:DL474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20544,6 +20544,26 @@
           <t>2026-03-27_diff</t>
         </is>
       </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>2026-03-28_price</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>2026-03-28_buy</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>2026-03-28_ratio</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>2026-03-28_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL474"/>
+  <dimension ref="A1:DP474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20564,6 +20564,26 @@
           <t>2026-03-28_diff</t>
         </is>
       </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>2026-03-29_price</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>2026-03-29_buy</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>2026-03-29_ratio</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>2026-03-29_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP474"/>
+  <dimension ref="A1:DT474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20584,6 +20584,26 @@
           <t>2026-03-29_diff</t>
         </is>
       </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>2026-03-30_price</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>2026-03-30_buy</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>2026-03-30_ratio</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>2026-03-30_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -19980,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DT474"/>
+  <dimension ref="A1:DX474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20604,6 +20604,26 @@
           <t>2026-03-30_diff</t>
         </is>
       </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>2026-03-31_price</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>2026-03-31_buy</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>2026-03-31_ratio</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>2026-03-31_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -12,6 +12,7 @@
     <sheet name="グラフ用" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="graph" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-4" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31871,4 +31872,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>card_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2026-04-01_price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2026-04-01_buy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026-04-01_ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2026-04-01_diff</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31924,6 +31924,26 @@
           <t>2026-04-01_diff</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2026-04-02_price</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026-04-02_buy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-04-02_ratio</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-04-02_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31944,6 +31944,26 @@
           <t>2026-04-02_diff</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026-04-03_price</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2026-04-03_buy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2026-04-03_ratio</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2026-04-03_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31964,6 +31964,26 @@
           <t>2026-04-03_diff</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2026-04-04_price</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2026-04-04_buy</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2026-04-04_ratio</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2026-04-04_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31984,6 +31984,26 @@
           <t>2026-04-04_diff</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2026-04-05_price</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2026-04-05_buy</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2026-04-05_ratio</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2026-04-05_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32004,6 +32004,26 @@
           <t>2026-04-05_diff</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2026-04-06_price</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2026-04-06_buy</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2026-04-06_ratio</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2026-04-06_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32024,6 +32024,26 @@
           <t>2026-04-06_diff</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2026-04-07_price</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2026-04-07_buy</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2026-04-07_ratio</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2026-04-07_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32044,6 +32044,26 @@
           <t>2026-04-07_diff</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2026-04-08_price</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2026-04-08_buy</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2026-04-08_ratio</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2026-04-08_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32064,6 +32064,26 @@
           <t>2026-04-08_diff</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2026-04-09_price</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2026-04-09_buy</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2026-04-09_ratio</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2026-04-09_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32084,6 +32084,26 @@
           <t>2026-04-09_diff</t>
         </is>
       </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2026-04-10_price</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2026-04-10_buy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2026-04-10_ratio</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2026-04-10_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32104,6 +32104,26 @@
           <t>2026-04-10_diff</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2026-04-11_price</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2026-04-11_buy</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2026-04-11_ratio</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2026-04-11_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32124,6 +32124,26 @@
           <t>2026-04-11_diff</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2026-04-12_price</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2026-04-12_buy</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2026-04-12_ratio</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2026-04-12_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:BD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32144,6 +32144,26 @@
           <t>2026-04-12_diff</t>
         </is>
       </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2026-04-13_price</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2026-04-13_buy</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2026-04-13_ratio</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2026-04-13_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD1"/>
+  <dimension ref="A1:BH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32164,6 +32164,26 @@
           <t>2026-04-13_diff</t>
         </is>
       </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>2026-04-14_price</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>2026-04-14_buy</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>2026-04-14_ratio</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>2026-04-14_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32184,6 +32184,26 @@
           <t>2026-04-14_diff</t>
         </is>
       </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>2026-04-15_price</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>2026-04-15_buy</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>2026-04-15_ratio</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>2026-04-15_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL1"/>
+  <dimension ref="A1:BP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32204,6 +32204,26 @@
           <t>2026-04-15_diff</t>
         </is>
       </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>2026-04-16_price</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>2026-04-16_buy</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>2026-04-16_ratio</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>2026-04-16_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32224,6 +32224,26 @@
           <t>2026-04-16_diff</t>
         </is>
       </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>2026-04-17_price</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>2026-04-17_buy</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>2026-04-17_ratio</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>2026-04-17_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT1"/>
+  <dimension ref="A1:BX1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32244,6 +32244,26 @@
           <t>2026-04-17_diff</t>
         </is>
       </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>2026-04-18_price</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>2026-04-18_buy</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>2026-04-18_ratio</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>2026-04-18_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX1"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32264,6 +32264,26 @@
           <t>2026-04-18_diff</t>
         </is>
       </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>2026-04-19_price</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>2026-04-19_buy</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>2026-04-19_ratio</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>2026-04-19_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32284,6 +32284,26 @@
           <t>2026-04-19_diff</t>
         </is>
       </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>2026-04-20_price</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>2026-04-20_buy</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>2026-04-20_ratio</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>2026-04-20_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF1"/>
+  <dimension ref="A1:CJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32304,6 +32304,26 @@
           <t>2026-04-20_diff</t>
         </is>
       </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>2026-04-21_price</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>2026-04-21_buy</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>2026-04-21_ratio</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>2026-04-21_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ1"/>
+  <dimension ref="A1:CN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32324,6 +32324,26 @@
           <t>2026-04-21_diff</t>
         </is>
       </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>2026-04-22_price</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>2026-04-22_buy</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>2026-04-22_ratio</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>2026-04-22_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN1"/>
+  <dimension ref="A1:CR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32344,6 +32344,26 @@
           <t>2026-04-22_diff</t>
         </is>
       </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>2026-04-23_price</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>2026-04-23_buy</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>2026-04-23_ratio</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>2026-04-23_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR1"/>
+  <dimension ref="A1:CV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32364,6 +32364,26 @@
           <t>2026-04-23_diff</t>
         </is>
       </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>2026-04-24_price</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>2026-04-24_buy</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>2026-04-24_ratio</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>2026-04-24_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV1"/>
+  <dimension ref="A1:CZ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32384,6 +32384,26 @@
           <t>2026-04-24_diff</t>
         </is>
       </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>2026-04-25_price</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>2026-04-25_buy</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>2026-04-25_ratio</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>2026-04-25_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ1"/>
+  <dimension ref="A1:DD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32404,6 +32404,26 @@
           <t>2026-04-25_diff</t>
         </is>
       </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>2026-04-26_price</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>2026-04-26_buy</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>2026-04-26_ratio</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>2026-04-26_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD1"/>
+  <dimension ref="A1:DH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32424,6 +32424,26 @@
           <t>2026-04-26_diff</t>
         </is>
       </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>2026-04-27_price</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>2026-04-27_buy</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>2026-04-27_ratio</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>2026-04-27_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH1"/>
+  <dimension ref="A1:DL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32444,6 +32444,26 @@
           <t>2026-04-27_diff</t>
         </is>
       </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>2026-04-28_price</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>2026-04-28_buy</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>2026-04-28_ratio</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>2026-04-28_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL1"/>
+  <dimension ref="A1:DP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32464,6 +32464,26 @@
           <t>2026-04-28_diff</t>
         </is>
       </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>2026-04-29_price</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>2026-04-29_buy</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>2026-04-29_ratio</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>2026-04-29_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -31880,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP1"/>
+  <dimension ref="A1:DT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32484,6 +32484,26 @@
           <t>2026-04-29_diff</t>
         </is>
       </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>2026-04-30_price</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>2026-04-30_buy</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>2026-04-30_ratio</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>2026-04-30_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -13,6 +13,7 @@
     <sheet name="graph" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32508,4 +32509,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>card_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2026-05-01_price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2026-05-01_buy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026-05-01_ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2026-05-01_diff</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32561,6 +32561,26 @@
           <t>2026-05-01_diff</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2026-05-02_price</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026-05-02_buy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-05-02_ratio</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-05-02_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32581,6 +32581,26 @@
           <t>2026-05-02_diff</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026-05-03_price</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2026-05-03_buy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2026-05-03_ratio</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2026-05-03_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32601,6 +32601,26 @@
           <t>2026-05-03_diff</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2026-05-04_price</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2026-05-04_buy</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2026-05-04_ratio</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2026-05-04_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32621,6 +32621,26 @@
           <t>2026-05-04_diff</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2026-05-05_price</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2026-05-05_buy</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2026-05-05_ratio</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2026-05-05_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32641,6 +32641,26 @@
           <t>2026-05-05_diff</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2026-05-06_price</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2026-05-06_buy</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2026-05-06_ratio</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2026-05-06_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32661,6 +32661,26 @@
           <t>2026-05-06_diff</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2026-05-07_price</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2026-05-07_buy</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2026-05-07_ratio</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2026-05-07_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32681,6 +32681,26 @@
           <t>2026-05-07_diff</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2026-05-08_price</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2026-05-08_buy</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2026-05-08_ratio</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2026-05-08_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32701,6 +32701,26 @@
           <t>2026-05-08_diff</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2026-05-09_price</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2026-05-09_buy</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2026-05-09_ratio</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2026-05-09_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32721,6 +32721,26 @@
           <t>2026-05-09_diff</t>
         </is>
       </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2026-05-10_price</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2026-05-10_buy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2026-05-10_ratio</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2026-05-10_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32741,6 +32741,26 @@
           <t>2026-05-10_diff</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2026-05-11_price</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2026-05-11_buy</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2026-05-11_ratio</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2026-05-11_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32761,6 +32761,26 @@
           <t>2026-05-11_diff</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2026-05-12_price</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2026-05-12_buy</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2026-05-12_ratio</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2026-05-12_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:BD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32781,6 +32781,26 @@
           <t>2026-05-12_diff</t>
         </is>
       </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2026-05-13_price</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2026-05-13_buy</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2026-05-13_ratio</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2026-05-13_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD1"/>
+  <dimension ref="A1:BH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32801,6 +32801,26 @@
           <t>2026-05-13_diff</t>
         </is>
       </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>2026-05-14_price</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>2026-05-14_buy</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>2026-05-14_ratio</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>2026-05-14_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32821,6 +32821,26 @@
           <t>2026-05-14_diff</t>
         </is>
       </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>2026-05-15_price</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>2026-05-15_buy</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>2026-05-15_ratio</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>2026-05-15_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL1"/>
+  <dimension ref="A1:BP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32841,6 +32841,26 @@
           <t>2026-05-15_diff</t>
         </is>
       </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>2026-05-16_price</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>2026-05-16_buy</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>2026-05-16_ratio</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>2026-05-16_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32861,6 +32861,26 @@
           <t>2026-05-16_diff</t>
         </is>
       </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>2026-05-17_price</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>2026-05-17_buy</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>2026-05-17_ratio</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>2026-05-17_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT1"/>
+  <dimension ref="A1:BX1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32881,6 +32881,26 @@
           <t>2026-05-17_diff</t>
         </is>
       </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>2026-05-18_price</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>2026-05-18_buy</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>2026-05-18_ratio</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>2026-05-18_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX1"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32901,6 +32901,26 @@
           <t>2026-05-18_diff</t>
         </is>
       </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>2026-05-19_price</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>2026-05-19_buy</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>2026-05-19_ratio</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>2026-05-19_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32921,6 +32921,26 @@
           <t>2026-05-19_diff</t>
         </is>
       </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>2026-05-20_price</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>2026-05-20_buy</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>2026-05-20_ratio</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>2026-05-20_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF1"/>
+  <dimension ref="A1:CJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32941,6 +32941,26 @@
           <t>2026-05-20_diff</t>
         </is>
       </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>2026-05-21_price</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>2026-05-21_buy</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>2026-05-21_ratio</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>2026-05-21_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ1"/>
+  <dimension ref="A1:CN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32961,6 +32961,26 @@
           <t>2026-05-21_diff</t>
         </is>
       </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>2026-05-22_price</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>2026-05-22_buy</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>2026-05-22_ratio</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>2026-05-22_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN1"/>
+  <dimension ref="A1:CR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32981,6 +32981,26 @@
           <t>2026-05-22_diff</t>
         </is>
       </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>2026-05-23_price</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>2026-05-23_buy</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>2026-05-23_ratio</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>2026-05-23_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR1"/>
+  <dimension ref="A1:CV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33001,6 +33001,26 @@
           <t>2026-05-23_diff</t>
         </is>
       </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>2026-05-24_price</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>2026-05-24_buy</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>2026-05-24_ratio</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>2026-05-24_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV1"/>
+  <dimension ref="A1:CZ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33021,6 +33021,26 @@
           <t>2026-05-24_diff</t>
         </is>
       </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>2026-05-25_price</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>2026-05-25_buy</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>2026-05-25_ratio</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>2026-05-25_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ1"/>
+  <dimension ref="A1:DD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33041,6 +33041,26 @@
           <t>2026-05-25_diff</t>
         </is>
       </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>2026-05-26_price</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>2026-05-26_buy</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>2026-05-26_ratio</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>2026-05-26_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD1"/>
+  <dimension ref="A1:DH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33061,6 +33061,26 @@
           <t>2026-05-26_diff</t>
         </is>
       </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>2026-05-27_price</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>2026-05-27_buy</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>2026-05-27_ratio</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>2026-05-27_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH1"/>
+  <dimension ref="A1:DL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33081,6 +33081,26 @@
           <t>2026-05-27_diff</t>
         </is>
       </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>2026-05-28_price</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>2026-05-28_buy</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>2026-05-28_ratio</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>2026-05-28_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL1"/>
+  <dimension ref="A1:DP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33101,6 +33101,26 @@
           <t>2026-05-28_diff</t>
         </is>
       </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>2026-05-29_price</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>2026-05-29_buy</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>2026-05-29_ratio</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>2026-05-29_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP1"/>
+  <dimension ref="A1:DT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33121,6 +33121,26 @@
           <t>2026-05-29_diff</t>
         </is>
       </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>2026-05-30_price</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>2026-05-30_buy</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>2026-05-30_ratio</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>2026-05-30_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -32517,7 +32517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DT1"/>
+  <dimension ref="A1:DX1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33141,6 +33141,26 @@
           <t>2026-05-30_diff</t>
         </is>
       </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>2026-05-31_price</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>2026-05-31_buy</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>2026-05-31_ratio</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>2026-05-31_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -14,6 +14,7 @@
     <sheet name="2026-3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-4" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-6" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33165,4 +33166,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>card_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2026-06-01_price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2026-06-01_buy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026-06-01_ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2026-06-01_diff</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33218,6 +33218,26 @@
           <t>2026-06-01_diff</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2026-06-02_price</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026-06-02_buy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-06-02_ratio</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-06-02_diff</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33238,6 +33238,2863 @@
           <t>2026-06-02_diff</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026-06-03_price</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2026-06-03_buy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2026-06-03_ratio</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2026-06-03_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オーロットEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>790</v>
+      </c>
+      <c r="N2" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カイリキー
+XY]</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>630</v>
+      </c>
+      <c r="N3" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>〔状態B〕イーブイ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>980</v>
+      </c>
+      <c r="N4" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ワシボン
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>730</v>
+      </c>
+      <c r="N5" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>〔状態B〕ロケット団のサカキ(未開封)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1090</v>
+      </c>
+      <c r="N6" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>3780</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カビゴン
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1690</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>〔状態B〕ダストダス
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>420</v>
+      </c>
+      <c r="N9" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハラバリー
+SV3]</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>380</v>
+      </c>
+      <c r="N10" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サカキのカリスマ
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>680</v>
+      </c>
+      <c r="N11" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アクロマの実験
+S11]</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>380</v>
+      </c>
+      <c r="N12" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーVSTAR
+S10b]</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>680</v>
+      </c>
+      <c r="N13" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パルデアケンタロス
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>730</v>
+      </c>
+      <c r="N14" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジジーロン
+その他]</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1180</v>
+      </c>
+      <c r="N15" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カイリキーVMAX
+S12a]</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>350</v>
+      </c>
+      <c r="N16" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キングドラGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>480</v>
+      </c>
+      <c r="N17" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アンノーンVSTAR
+S12]</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>730</v>
+      </c>
+      <c r="N18" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブラッキーVMAX
+S6a]</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1390</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラブトロスV
+S10a]</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1580</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガブリアス＆ギラティナGX
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>2280</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガラルヤドキングV(SA)
+S5a]</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>14300</v>
+      </c>
+      <c r="N22" t="n">
+        <v>11440</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケモンセンターのお姉さん(SR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>31800</v>
+      </c>
+      <c r="N23" t="n">
+        <v>25440</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジュペッタGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1890</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヨクバリスV
+S8]</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>380</v>
+      </c>
+      <c r="N25" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本草エネルギー(ジムチャレンジ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>580</v>
+      </c>
+      <c r="N26" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドヒドイデGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>5480</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シマボシ
+S9a]</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>530</v>
+      </c>
+      <c r="N28" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ふうせん
+s1]</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>13800</v>
+      </c>
+      <c r="N29" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フライゴンGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>630</v>
+      </c>
+      <c r="N30" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リーフィアV(SA)
+S6a]</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>20300</v>
+      </c>
+      <c r="N31" t="n">
+        <v>16240</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハイパーボール
+S9]</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>6480</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>〔状態C〕ボルトロス
+その他]</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1990</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>〔状態B〕アーマーガアVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>630</v>
+      </c>
+      <c r="N34" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルザミーネ
+sm4]</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>158000</v>
+      </c>
+      <c r="N35" t="n">
+        <v>126400</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウVMAX(RRR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>34800</v>
+      </c>
+      <c r="N36" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>〔状態B〕シロナ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>〔状態B〕レックウザEX(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>69800</v>
+      </c>
+      <c r="N38" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲッコウガGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>6980</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>〔状態B〕ホウオウGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>19800</v>
+      </c>
+      <c r="N40" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウツー＆ミュウGX
+sm11]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>23800</v>
+      </c>
+      <c r="N41" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>〔状態B〕ギルガルドV
+s4]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>480</v>
+      </c>
+      <c r="N42" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>〔状態B〕アーゴヨンGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>780</v>
+      </c>
+      <c r="N43" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>〔状態B〕ホミカ
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>7480</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブラッキーGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>69800</v>
+      </c>
+      <c r="N45" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウツーEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>54800</v>
+      </c>
+      <c r="N46" t="n">
+        <v>43840</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>〔状態B〕コダック(ムンク)
+その他]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>198000</v>
+      </c>
+      <c r="N47" t="n">
+        <v>158400</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガジガルデex
+M3]</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>730</v>
+      </c>
+      <c r="N48" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フシギダネ
+M1L]</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>1390</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ロズレイド</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>580</v>
+      </c>
+      <c r="N50" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ラウドボーンex</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>480</v>
+      </c>
+      <c r="N51" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ヒノアラシ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>680</v>
+      </c>
+      <c r="N52" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>リザードンV</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>18800</v>
+      </c>
+      <c r="N53" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>フィオネ</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>680</v>
+      </c>
+      <c r="N54" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕シャワーズ(YU NAGABA)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>26800</v>
+      </c>
+      <c r="N55" t="n">
+        <v>21440</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ひかるコイキング(25th)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>27800</v>
+      </c>
+      <c r="N56" t="n">
+        <v>22240</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>738000</v>
+      </c>
+      <c r="N57" t="n">
+        <v>590400</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>レントラーex</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>980</v>
+      </c>
+      <c r="N58" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ゼラオラV(SA)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>17800</v>
+      </c>
+      <c r="N59" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ダストダス</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>280</v>
+      </c>
+      <c r="N60" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ハバタクカミ</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>480</v>
+      </c>
+      <c r="N61" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>オドリドリGX</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>980</v>
+      </c>
+      <c r="N62" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>メガヤドランex</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>780</v>
+      </c>
+      <c r="N63" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ヒスイウインディ</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>680</v>
+      </c>
+      <c r="N64" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ルガルガンGX</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>280</v>
+      </c>
+      <c r="N65" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>パルデアウパー(AR仕様)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>2180</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MハガネールEX</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>5980</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>テツノワダチex</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>480</v>
+      </c>
+      <c r="N68" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ルカリオ＆メルメタルGX</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>1380</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ボーマンダex</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>12800</v>
+      </c>
+      <c r="N70" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>レックウザV</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>580</v>
+      </c>
+      <c r="N71" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>アーゴヨン＆アクジキングGX</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>1980</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ルギアV(SA)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>228000</v>
+      </c>
+      <c r="N73" t="n">
+        <v>182400</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ケンタロス(未開封)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>15800</v>
+      </c>
+      <c r="N74" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ボーマンダVMAX</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>380</v>
+      </c>
+      <c r="N75" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>クイックボール</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>17800</v>
+      </c>
+      <c r="N76" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>スパイクエネルギー</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>980</v>
+      </c>
+      <c r="N77" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>基本鋼エネルギー(チャンピオンズリーグ2023)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>680</v>
+      </c>
+      <c r="N78" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕Nの筋書き</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>23800</v>
+      </c>
+      <c r="N79" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カシオペア
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>930</v>
+      </c>
+      <c r="N80" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>パルデアの学生</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>680</v>
+      </c>
+      <c r="N81" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ライム</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>480</v>
+      </c>
+      <c r="N82" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ネジキ</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>480</v>
+      </c>
+      <c r="N83" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>アカギの策略(コイン付未開封/キラ)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>39800</v>
+      </c>
+      <c r="N84" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ソニア</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>3280</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>きとうし</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>2580</v>
+      </c>
+      <c r="N86" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>マキシ</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>1480</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ミアレシティ</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>280</v>
+      </c>
+      <c r="N88" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>〔状態B〕スワンナ
+その他]</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>420</v>
+      </c>
+      <c r="N89" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>〔状態B〕ワルビアルEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>1180</v>
+      </c>
+      <c r="N90" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>〔状態C〕トゲキッス
+M2a]</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>220</v>
+      </c>
+      <c r="N91" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>〔状態B〕マフォクシー
+XY]</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>880</v>
+      </c>
+      <c r="N92" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>〔状態C〕マホミル
+SV7]</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>320</v>
+      </c>
+      <c r="N93" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>〔状態C〕イーブイ(未開封/AR仕様/英語版)
+海外版]</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>1080</v>
+      </c>
+      <c r="N94" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>〔状態C〕レックウザGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>330</v>
+      </c>
+      <c r="N95" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>〔状態B〕ボーマンダ
+その他]</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>1580</v>
+      </c>
+      <c r="N96" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゴチルゼル
+その他]</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>630</v>
+      </c>
+      <c r="N97" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゾロア
+その他]</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>8480</v>
+      </c>
+      <c r="N98" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>〔状態C〕コジョフー
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>380</v>
+      </c>
+      <c r="N99" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>〔状態C〕ワルビアル
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>420</v>
+      </c>
+      <c r="N100" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>〔状態B〕ドリュウズex
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>1080</v>
+      </c>
+      <c r="N101" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゾロア
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>2350</v>
+      </c>
+      <c r="N102" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マラカッチ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>930</v>
+      </c>
+      <c r="N103" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シママ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>730</v>
+      </c>
+      <c r="N104" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>〔状態B〕ペンドラー
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>580</v>
+      </c>
+      <c r="N105" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>〔状態B〕ビクトリーカップ(バトルカーニバル2012・3位)
+その他]</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="N106" t="n">
+        <v>1184000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>〔状態C〕ホップのザシアンex
+SV9]</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>380</v>
+      </c>
+      <c r="N107" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>〔状態C〕タロ
+SV7]</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>690</v>
+      </c>
+      <c r="N108" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>〔状態C〕スグリ
+SV6]</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>1280</v>
+      </c>
+      <c r="N109" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>〔状態B〕イワパレス
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>320</v>
+      </c>
+      <c r="N110" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バトルサーチャー
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>990</v>
+      </c>
+      <c r="N111" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>〔状態C〕トドロクツキex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>1090</v>
+      </c>
+      <c r="N112" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゴージャスマント
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>220</v>
+      </c>
+      <c r="N113" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピジョットex
+SV3]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>1280</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケパークのセレビィ
+その他]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>21800</v>
+      </c>
+      <c r="N115" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>〔状態B〕マホミル
+SV7]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>580</v>
+      </c>
+      <c r="N116" t="n">
+        <v>464</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:T180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33258,6 +33258,26 @@
           <t>2026-06-03_diff</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2026-06-04_price</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2026-06-04_buy</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2026-06-04_ratio</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2026-06-04_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33271,7 +33291,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33296,7 +33315,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33321,7 +33339,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33346,7 +33363,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33371,7 +33387,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33396,7 +33411,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33421,7 +33435,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33446,7 +33459,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33471,7 +33483,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33496,7 +33507,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33521,7 +33531,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33546,7 +33555,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33571,7 +33579,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33596,7 +33603,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33621,7 +33627,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33646,7 +33651,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33671,7 +33675,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33696,7 +33699,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33721,7 +33723,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33746,7 +33747,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33771,7 +33771,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33796,7 +33795,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33821,7 +33819,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33846,7 +33843,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33871,7 +33867,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33896,7 +33891,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33921,7 +33915,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33946,7 +33939,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33971,7 +33963,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -33996,7 +33987,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34021,7 +34011,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34046,7 +34035,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34071,7 +34059,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34096,7 +34083,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34121,7 +34107,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34146,7 +34131,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34171,7 +34155,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34196,7 +34179,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34221,7 +34203,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34246,7 +34227,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34271,7 +34251,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34296,7 +34275,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34321,7 +34299,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34346,7 +34323,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34371,7 +34347,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34396,7 +34371,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34421,7 +34395,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34446,7 +34419,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34470,7 +34442,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34494,7 +34465,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34518,7 +34488,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34542,7 +34511,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34566,7 +34534,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34590,7 +34557,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34614,7 +34580,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34638,7 +34603,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34662,7 +34626,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34686,7 +34649,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34710,7 +34672,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34734,7 +34695,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34758,7 +34718,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34782,7 +34741,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34806,7 +34764,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34830,7 +34787,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34854,7 +34810,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34878,7 +34833,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34902,7 +34856,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34926,7 +34879,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34950,7 +34902,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34974,7 +34925,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -34998,7 +34948,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35022,7 +34971,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35046,7 +34994,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35070,7 +35017,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35094,7 +35040,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35118,7 +35063,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35142,7 +35086,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35166,7 +35109,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35191,7 +35133,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35215,7 +35156,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35239,7 +35179,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35263,7 +35202,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35287,7 +35225,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35311,7 +35248,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35335,7 +35271,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35359,7 +35294,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35383,7 +35317,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -35408,7 +35341,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35433,7 +35365,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35458,7 +35389,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35483,7 +35413,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35508,7 +35437,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35533,7 +35461,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35558,7 +35485,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35583,7 +35509,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35608,7 +35533,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35633,7 +35557,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35658,7 +35581,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35683,7 +35605,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35708,7 +35629,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35733,7 +35653,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35758,7 +35677,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35783,7 +35701,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35808,7 +35725,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35833,7 +35749,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35858,7 +35773,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35883,7 +35797,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35908,7 +35821,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35933,7 +35845,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35958,7 +35869,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -35983,7 +35893,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -36008,7 +35917,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -36033,7 +35941,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -36058,7 +35965,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -36083,7 +35989,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -36094,6 +35999,1581 @@
       </c>
       <c r="N116" t="n">
         <v>464</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>〔状態B〕ルギアEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>3790</v>
+      </c>
+      <c r="R117" t="n">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ムウマージex
+M2]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>390</v>
+      </c>
+      <c r="R118" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>〔状態B〕シュバルゴ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>680</v>
+      </c>
+      <c r="R119" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>〔状態B〕メグロコ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>580</v>
+      </c>
+      <c r="R120" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>〔状態B〕オーガポンみどりのめん
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>320</v>
+      </c>
+      <c r="R121" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>〔状態B〕クレッフィ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>280</v>
+      </c>
+      <c r="R122" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フトゥー博士のシナリオ
+SV4M]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>590</v>
+      </c>
+      <c r="R123" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>〔状態B〕イーブイ(YU NAGABA)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>10800</v>
+      </c>
+      <c r="R124" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゴローニャex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>730</v>
+      </c>
+      <c r="R125" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ(R仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>1980</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラウドボーンex
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>680</v>
+      </c>
+      <c r="R127" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>〔状態B〕ペパー
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>590</v>
+      </c>
+      <c r="R128" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒスイヌメルゴン
+S12a]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>380</v>
+      </c>
+      <c r="R129" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>〔状態B〕ホウオウV
+S11a]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>290</v>
+      </c>
+      <c r="R130" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サルノリ
+s4a]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>450</v>
+      </c>
+      <c r="R131" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>〔状態B〕ガラルファイヤーV
+SI]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>2380</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本超エネルギー(ジムチャレンジ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>930</v>
+      </c>
+      <c r="R133" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マクワ
+S6a]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>690</v>
+      </c>
+      <c r="R134" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>〔状態A-〕せせらぎの丘
+sm9]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>6980</v>
+      </c>
+      <c r="R135" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゴツゴツメット
+その他]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>3480</v>
+      </c>
+      <c r="R136" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ソルガレオ＆ルナアーラGX(SA)
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>60800</v>
+      </c>
+      <c r="R137" t="n">
+        <v>48640</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シロナ＆カトレア
+sm12]</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>23800</v>
+      </c>
+      <c r="R138" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シロナ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>3080</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>〔状態A-〕デンリュウGX
+sm8]</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>3680</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルカリオ＆メルメタルGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>9900</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カゲツ
+S8]</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>380</v>
+      </c>
+      <c r="R142" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハマナのバックアップ
+S9]</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>480</v>
+      </c>
+      <c r="R143" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>〔状態B〕ロケット団の幹部(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>680</v>
+      </c>
+      <c r="R144" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケモンカード研究所
+その他]</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>27800</v>
+      </c>
+      <c r="R145" t="n">
+        <v>22240</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>〔状態B〕コバルオン
+その他]</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>5490</v>
+      </c>
+      <c r="R146" t="n">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>1490</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>〔状態C〕サッポロのピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>84800</v>
+      </c>
+      <c r="R148" t="n">
+        <v>67840</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>〔状態C〕イエッサンV
+S-P]</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>6480</v>
+      </c>
+      <c r="R149" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>〔状態B〕エーフィGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>17800</v>
+      </c>
+      <c r="R150" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>〔状態B〕フェローチェ＆マッシブーンGX(SA)
+SM9b]</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>4480</v>
+      </c>
+      <c r="R151" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>〔状態B〕改造ハンマー
+XY]</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>3790</v>
+      </c>
+      <c r="R152" t="n">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケモンいれかえ
+sm1]</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>6480</v>
+      </c>
+      <c r="R153" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タラゴン
+M3]</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>530</v>
+      </c>
+      <c r="R154" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メタング
+M4]</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>450</v>
+      </c>
+      <c r="R155" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ニンフィアGX</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>848000</v>
+      </c>
+      <c r="R156" t="n">
+        <v>678400</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ワナイダーex</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>580</v>
+      </c>
+      <c r="R157" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>アローラナッシーV(RR仕様)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>280</v>
+      </c>
+      <c r="R158" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ヒビキのホウオウex</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>49800</v>
+      </c>
+      <c r="R159" t="n">
+        <v>39840</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>リザードンVSTAR</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>18800</v>
+      </c>
+      <c r="R160" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ハルクジラ</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>580</v>
+      </c>
+      <c r="R161" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ミロカロス</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>680</v>
+      </c>
+      <c r="R162" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>グレイシアVMAX</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>4980</v>
+      </c>
+      <c r="R163" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>カジリガメVMAX</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>980</v>
+      </c>
+      <c r="R164" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>パルキアGX</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>13800</v>
+      </c>
+      <c r="R165" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ルイージピカチュウ</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="R166" t="n">
+        <v>912000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>レントラーGLLV.X(25th)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>2380</v>
+      </c>
+      <c r="R167" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>デンリュウV</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>780</v>
+      </c>
+      <c r="R168" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ミュウVMAX(SA)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>278000</v>
+      </c>
+      <c r="R169" t="n">
+        <v>222400</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ルージュラ</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>480</v>
+      </c>
+      <c r="R170" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ガラルフリーザーV(SA)</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>8480</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>オドリドリGX</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>980</v>
+      </c>
+      <c r="R172" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>アーケン</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>880</v>
+      </c>
+      <c r="R173" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ストリンダーex</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>480</v>
+      </c>
+      <c r="R174" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>バサギリVSTAR</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>280</v>
+      </c>
+      <c r="R175" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ルガルガンGX</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>3280</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ゾロアーク</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>2780</v>
+      </c>
+      <c r="R177" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>レパルダスV</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>780</v>
+      </c>
+      <c r="R178" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ゲッコウガ＆ゾロアークGX</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>21800</v>
+      </c>
+      <c r="R179" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ハガネール</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>680</v>
+      </c>
+      <c r="R180" t="n">
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T180"/>
+  <dimension ref="A1:X260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33278,6 +33278,26 @@
           <t>2026-06-04_diff</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2026-06-05_price</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2026-06-05_buy</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2026-06-05_ratio</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2026-06-05_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36013,7 +36033,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36038,7 +36057,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36063,7 +36081,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36088,7 +36105,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36113,7 +36129,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36138,7 +36153,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36163,7 +36177,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36188,7 +36201,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36213,7 +36225,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36238,7 +36249,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36263,7 +36273,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36288,7 +36297,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36313,7 +36321,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36338,7 +36345,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36363,7 +36369,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36388,7 +36393,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36413,7 +36417,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36438,7 +36441,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36463,7 +36465,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36488,7 +36489,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36513,7 +36513,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36538,7 +36537,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36563,7 +36561,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36588,7 +36585,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36613,7 +36609,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36638,7 +36633,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36663,7 +36657,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36688,7 +36681,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36713,7 +36705,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36738,7 +36729,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36763,7 +36753,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36788,7 +36777,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36813,7 +36801,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36838,7 +36825,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36863,7 +36849,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36888,7 +36873,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36913,7 +36897,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36938,7 +36921,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36963,7 +36945,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -36987,7 +36968,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37011,7 +36991,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37035,7 +37014,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37059,7 +37037,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37083,7 +37060,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37107,7 +37083,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37131,7 +37106,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37155,7 +37129,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37179,7 +37152,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37203,7 +37175,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37227,7 +37198,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37251,7 +37221,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37275,7 +37244,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37299,7 +37267,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37323,7 +37290,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37347,7 +37313,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37371,7 +37336,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37395,7 +37359,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37419,7 +37382,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37443,7 +37405,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37467,7 +37428,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37491,7 +37451,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37515,7 +37474,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37539,7 +37497,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37563,7 +37520,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37574,6 +37530,1984 @@
       </c>
       <c r="R180" t="n">
         <v>544</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>〔状態C〕カイオーガEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U181" t="n">
+        <v>1790</v>
+      </c>
+      <c r="V181" t="n">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>〔状態B〕ギャラドスV
+S7R]</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U182" t="n">
+        <v>420</v>
+      </c>
+      <c r="V182" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒートバーナー
+M2]</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U183" t="n">
+        <v>250</v>
+      </c>
+      <c r="V183" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ホゲータ(マクドナルド)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U184" t="n">
+        <v>630</v>
+      </c>
+      <c r="V184" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>〔状態B〕ダストダス
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U185" t="n">
+        <v>680</v>
+      </c>
+      <c r="V185" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヒヤッキー
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U186" t="n">
+        <v>580</v>
+      </c>
+      <c r="V186" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>〔状態B〕シビシラス
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U187" t="n">
+        <v>1480</v>
+      </c>
+      <c r="V187" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>〔状態B〕パールル
+SV10]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U188" t="n">
+        <v>480</v>
+      </c>
+      <c r="V188" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒビキの冒険
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U189" t="n">
+        <v>830</v>
+      </c>
+      <c r="V189" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パソコン通信
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U190" t="n">
+        <v>250</v>
+      </c>
+      <c r="V190" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カウンターゲイン
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U191" t="n">
+        <v>530</v>
+      </c>
+      <c r="V191" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブライア
+SV7]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U192" t="n">
+        <v>2250</v>
+      </c>
+      <c r="V192" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テツノイサハex
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U193" t="n">
+        <v>390</v>
+      </c>
+      <c r="V193" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>〔状態A-〕センリ
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U194" t="n">
+        <v>580</v>
+      </c>
+      <c r="V194" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U195" t="n">
+        <v>3780</v>
+      </c>
+      <c r="V195" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ザクロ
+S10P]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U196" t="n">
+        <v>380</v>
+      </c>
+      <c r="V196" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>〔状態B〕ギラティナVSTAR
+S11]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U197" t="n">
+        <v>7980</v>
+      </c>
+      <c r="V197" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本鋼エネルギー(チャンピオンズリーグ2023)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U198" t="n">
+        <v>630</v>
+      </c>
+      <c r="V198" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルガルガンVMAX
+S7D]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U199" t="n">
+        <v>260</v>
+      </c>
+      <c r="V199" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ペパー
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U200" t="n">
+        <v>930</v>
+      </c>
+      <c r="V200" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サーナイトex
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U201" t="n">
+        <v>26800</v>
+      </c>
+      <c r="V201" t="n">
+        <v>21440</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バクガメス
+その他]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U202" t="n">
+        <v>390</v>
+      </c>
+      <c r="V202" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本闘エネルギー(チャンピオンズリーグ2020)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U203" t="n">
+        <v>330</v>
+      </c>
+      <c r="V203" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガオガエン
+その他]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U204" t="n">
+        <v>630</v>
+      </c>
+      <c r="V204" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ムゲンダイナVMAX
+S-P]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U205" t="n">
+        <v>1690</v>
+      </c>
+      <c r="V205" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>〔状態C〕リーフィア
+その他]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U206" t="n">
+        <v>10800</v>
+      </c>
+      <c r="V206" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケモンキャッチャー
+その他]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U207" t="n">
+        <v>31800</v>
+      </c>
+      <c r="V207" t="n">
+        <v>25440</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フヨウ
+S5I]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U208" t="n">
+        <v>730</v>
+      </c>
+      <c r="V208" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ナタネ
+sm5]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U209" t="n">
+        <v>23800</v>
+      </c>
+      <c r="V209" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ＆カビゴンGX(SA)
+その他]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U210" t="n">
+        <v>44800</v>
+      </c>
+      <c r="V210" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キノガッサV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U211" t="n">
+        <v>250</v>
+      </c>
+      <c r="V211" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>〔状態B〕ダンサー
+S8]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U212" t="n">
+        <v>420</v>
+      </c>
+      <c r="V212" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピオニー
+S6H]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U213" t="n">
+        <v>530</v>
+      </c>
+      <c r="V213" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピジョットEX
+CP6]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U214" t="n">
+        <v>2790</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルガルガンGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U215" t="n">
+        <v>1530</v>
+      </c>
+      <c r="V215" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニンフィアVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U216" t="n">
+        <v>12800</v>
+      </c>
+      <c r="V216" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マルヤクデV
+S2a]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U217" t="n">
+        <v>450</v>
+      </c>
+      <c r="V217" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シロナ
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U218" t="n">
+        <v>39800</v>
+      </c>
+      <c r="V218" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジュラルドンVMAX(SA)
+S7D]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U219" t="n">
+        <v>15800</v>
+      </c>
+      <c r="V219" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本鋼エネルギー(in 東京タワー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U220" t="n">
+        <v>3980</v>
+      </c>
+      <c r="V220" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>〔状態B〕こくばバドレックスVMAX
+S6K]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U221" t="n">
+        <v>1580</v>
+      </c>
+      <c r="V221" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>〔状態B〕セレビィ
+XY]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U222" t="n">
+        <v>9980</v>
+      </c>
+      <c r="V222" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>〔状態B〕MバンギラスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U223" t="n">
+        <v>21800</v>
+      </c>
+      <c r="V223" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>〔状態B〕カミツルギGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U224" t="n">
+        <v>1980</v>
+      </c>
+      <c r="V224" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハッサムGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U225" t="n">
+        <v>2990</v>
+      </c>
+      <c r="V225" t="n">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>〔状態C〕カツラの一発勝負
+sm6]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U226" t="n">
+        <v>4480</v>
+      </c>
+      <c r="V226" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>〔状態C〕グラードンEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U227" t="n">
+        <v>34800</v>
+      </c>
+      <c r="V227" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本炎エネルギー(ジムチャレンジ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U228" t="n">
+        <v>480</v>
+      </c>
+      <c r="V228" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>〔状態B〕格闘道場
+sm11a]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U229" t="n">
+        <v>680</v>
+      </c>
+      <c r="V229" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>〔状態B〕アクロマ
+その他]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U230" t="n">
+        <v>8990</v>
+      </c>
+      <c r="V230" t="n">
+        <v>7192</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>〔状態B〕なみのりピカチュウ
+XY]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U231" t="n">
+        <v>27800</v>
+      </c>
+      <c r="V231" t="n">
+        <v>22240</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>〔状態B〕リザードンGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U232" t="n">
+        <v>4980</v>
+      </c>
+      <c r="V232" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>〔状態B〕ファイアロー
+M3]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U233" t="n">
+        <v>280</v>
+      </c>
+      <c r="V233" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガゲッコウガex
+M4]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>MUR</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U234" t="n">
+        <v>123000</v>
+      </c>
+      <c r="V234" t="n">
+        <v>98400</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シルヴァディ
+M5]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U235" t="n">
+        <v>390</v>
+      </c>
+      <c r="V235" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ジャローダex</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U236" t="n">
+        <v>3780</v>
+      </c>
+      <c r="V236" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>チオンジェンex</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U237" t="n">
+        <v>580</v>
+      </c>
+      <c r="V237" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>ヒメンカ</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U238" t="n">
+        <v>280</v>
+      </c>
+      <c r="V238" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>クルマユ</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U239" t="n">
+        <v>280</v>
+      </c>
+      <c r="V239" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕メガリザードンXex</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U240" t="n">
+        <v>228000</v>
+      </c>
+      <c r="V240" t="n">
+        <v>182400</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ブースターex</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U241" t="n">
+        <v>8980</v>
+      </c>
+      <c r="V241" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕リザードンEX</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U242" t="n">
+        <v>718000</v>
+      </c>
+      <c r="V242" t="n">
+        <v>574400</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>〔状態B〕トウホクのピカチュウ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U243" t="n">
+        <v>14800</v>
+      </c>
+      <c r="V243" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕名探偵ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U244" t="n">
+        <v>77800</v>
+      </c>
+      <c r="V244" t="n">
+        <v>62240</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ルイージピカチュウ</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U245" t="n">
+        <v>2980000</v>
+      </c>
+      <c r="V245" t="n">
+        <v>2384000</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ゼラオラVSTAR</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U246" t="n">
+        <v>3280</v>
+      </c>
+      <c r="V246" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ピカチュウV</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U247" t="n">
+        <v>880</v>
+      </c>
+      <c r="V247" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>スカル団ごっこピカチュウ(未開封)</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U248" t="n">
+        <v>2480000</v>
+      </c>
+      <c r="V248" t="n">
+        <v>1984000</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ピカチュウ(チャンピオンズリーグ2017)</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U249" t="n">
+        <v>348000</v>
+      </c>
+      <c r="V249" t="n">
+        <v>278400</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>デデンネ</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U250" t="n">
+        <v>580</v>
+      </c>
+      <c r="V250" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>テツノブジンex</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U251" t="n">
+        <v>480</v>
+      </c>
+      <c r="V251" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>オドリドリGX</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U252" t="n">
+        <v>980</v>
+      </c>
+      <c r="V252" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MゲンガーEX(台紙付き未開封)
+XY]]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U253" t="n">
+        <v>113000</v>
+      </c>
+      <c r="V253" t="n">
+        <v>90400</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ランドロス</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U254" t="n">
+        <v>880</v>
+      </c>
+      <c r="V254" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>バサギリ</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U255" t="n">
+        <v>480</v>
+      </c>
+      <c r="V255" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イイネイヌex
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U256" t="n">
+        <v>1530</v>
+      </c>
+      <c r="V256" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>デルビル</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U257" t="n">
+        <v>680</v>
+      </c>
+      <c r="V257" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ルギアV</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U258" t="n">
+        <v>2380</v>
+      </c>
+      <c r="V258" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>イキリンコex</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U259" t="n">
+        <v>380</v>
+      </c>
+      <c r="V259" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ザシアンV</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="U260" t="n">
+        <v>1180</v>
+      </c>
+      <c r="V260" t="n">
+        <v>944</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X260"/>
+  <dimension ref="A1:AB466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33298,6 +33298,26 @@
           <t>2026-06-05_diff</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2026-06-07_price</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2026-06-07_buy</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2026-06-07_ratio</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2026-06-07_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37544,7 +37564,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37569,7 +37588,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37594,7 +37612,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37619,7 +37636,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37644,7 +37660,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37669,7 +37684,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37694,7 +37708,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37719,7 +37732,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37744,7 +37756,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37769,7 +37780,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37794,7 +37804,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37819,7 +37828,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37844,7 +37852,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37869,7 +37876,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37894,7 +37900,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37919,7 +37924,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37944,7 +37948,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37969,7 +37972,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -37994,7 +37996,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38019,7 +38020,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38044,7 +38044,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38069,7 +38068,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38094,7 +38092,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38119,7 +38116,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38144,7 +38140,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38169,7 +38164,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38194,7 +38188,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38219,7 +38212,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38244,7 +38236,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38269,7 +38260,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38294,7 +38284,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38319,7 +38308,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38344,7 +38332,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38369,7 +38356,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38394,7 +38380,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38419,7 +38404,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38444,7 +38428,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38469,7 +38452,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38494,7 +38476,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38519,7 +38500,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38544,7 +38524,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38569,7 +38548,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38594,7 +38572,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38619,7 +38596,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38644,7 +38620,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38669,7 +38644,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38694,7 +38668,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38719,7 +38692,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38744,7 +38716,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38769,7 +38740,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38794,7 +38764,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38819,7 +38788,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38844,7 +38812,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38869,7 +38836,6 @@
           <t>MUR</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38894,7 +38860,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38918,7 +38883,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38942,7 +38906,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38966,7 +38929,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -38990,7 +38952,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39014,7 +38975,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39038,7 +38998,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39062,7 +39021,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39087,7 +39045,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39111,7 +39068,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39135,7 +39091,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39159,7 +39114,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39183,7 +39137,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39207,7 +39160,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39231,7 +39183,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39255,7 +39206,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39279,7 +39229,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39303,7 +39252,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39328,7 +39276,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39352,7 +39299,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39376,7 +39322,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39401,7 +39346,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39425,7 +39369,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39449,7 +39392,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39473,7 +39415,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39497,7 +39438,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39508,6 +39448,5090 @@
       </c>
       <c r="V260" t="n">
         <v>944</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>〔状態B〕カラマネロ
+XY]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y261" t="n">
+        <v>1090</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゾロア
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y262" t="n">
+        <v>2350</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オノノクス
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y263" t="n">
+        <v>1090</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のニドキングex
+SV10]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y264" t="n">
+        <v>12800</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラクライ
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y265" t="n">
+        <v>320</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>〔状態B〕レントラーex
+SV6]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y266" t="n">
+        <v>680</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルチャブル
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y267" t="n">
+        <v>250</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テツノドクガ
+SV4M]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y268" t="n">
+        <v>530</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポッポ
+SV3]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y269" t="n">
+        <v>390</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y270" t="n">
+        <v>52800</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>42240</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ナタネの活気
+S10D]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y271" t="n">
+        <v>1190</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>〔状態B〕ペリーラ
+S10D]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y272" t="n">
+        <v>420</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>〔状態C〕アルティメットゾーン
+その他]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y273" t="n">
+        <v>330</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オトシドリ
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y274" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>〔状態B〕ボタン
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y275" t="n">
+        <v>1780</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>〔状態B〕アクロマの実験
+S12a]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y276" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>〔状態B〕さぎょういん
+S12]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y277" t="n">
+        <v>420</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケモンいれかえ
+その他]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y278" t="n">
+        <v>1090</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒスイマルマインV
+S10a]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y279" t="n">
+        <v>330</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ダートじてんしゃ
+sm11a]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y280" t="n">
+        <v>350</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>〔状態A-〕地底探険隊
+sm6]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y281" t="n">
+        <v>23800</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウオチルドンV
+S6K]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y282" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケモンいれかえ
+XY]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y283" t="n">
+        <v>12800</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ツツジ
+S9a]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y284" t="n">
+        <v>830</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラプラスV
+s1]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y285" t="n">
+        <v>730</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ライチュウ＆アローラライチュウGX
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y286" t="n">
+        <v>10900</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>8720</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ネクロズマV
+S5R]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y287" t="n">
+        <v>730</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウッウロボ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y288" t="n">
+        <v>990</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジュラルドンV
+S7D]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y289" t="n">
+        <v>420</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>〔状態B〕こくばバドレックスV
+S6K]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y290" t="n">
+        <v>680</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リーリエ
+sm1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y291" t="n">
+        <v>498000</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>398400</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>〔状態C〕ビリジオン
+その他]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y292" t="n">
+        <v>11800</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>〔状態B〕エアームドEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y293" t="n">
+        <v>4490</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>〔状態C〕コイキング＆ホエルオーGX(SA)
+sm9]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y294" t="n">
+        <v>69800</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>〔状態C〕アイリス
+その他]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y295" t="n">
+        <v>39800</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>〔状態B〕カイリューGX
+sm11]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y296" t="n">
+        <v>2580</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本超エネルギー(ジムチャレンジ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y297" t="n">
+        <v>680</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲンシグラードンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y298" t="n">
+        <v>9980</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>〔状態B〕ライチュウ＆アローラライチュウGX
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y299" t="n">
+        <v>8980</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガピクシーex
+M3]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y300" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ナッシー</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y301" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スコヴィランex
+SV8]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y302" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>アチゲータ</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y303" t="n">
+        <v>480</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ビクティニV</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y304" t="n">
+        <v>2480</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>フィオネ</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y305" t="n">
+        <v>680</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕グレイシア(YU NAGABA)</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y306" t="n">
+        <v>28800</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>23040</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ヨワシGX</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y307" t="n">
+        <v>480</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ラクライ</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y308" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ラルトス(マクドナルド)</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y309" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ラティアスex</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y310" t="n">
+        <v>33800</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>27040</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>フワライド</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y311" t="n">
+        <v>280</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>カプ・テテフGX(25th)</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y312" t="n">
+        <v>2580</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>アーマードミュウツー(未開封)</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y313" t="n">
+        <v>32800</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ゲンガー＆ミミッキュGX</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y314" t="n">
+        <v>23800</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ゲッコウガex</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y315" t="n">
+        <v>53800</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>43040</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>カイリキーVMAX</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y316" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>れんげきウーラオスV</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y317" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>マシマシラex</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y318" t="n">
+        <v>480</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>ドラピオンV</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y319" t="n">
+        <v>1080</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>ナットレイ</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y320" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ガラルニャイキング</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y321" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>ミルタンク</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y322" t="n">
+        <v>480</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>アルセウスV</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y323" t="n">
+        <v>1380</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>英雄のメダル</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y324" t="n">
+        <v>680</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>ロストミキサー</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y325" t="n">
+        <v>680</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>エネルギーつけかえ</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y326" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>基本雷エネルギー(チャンピオンズリーグ2024)</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y327" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>基本草エネルギー(チャンピオンズリーグ2022)</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y328" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>ウィークガードエネルギー</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y329" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕シロナ＆カトレア</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y330" t="n">
+        <v>47800</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>38240</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>マツバの確信</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y331" t="n">
+        <v>8280</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>6624</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>ハヤト</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y332" t="n">
+        <v>880</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>さぎょういん</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y333" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>デンボク</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y334" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>トウキ</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y335" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>ブルーの探索</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="Y336" t="n">
+        <v>74800</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>59840</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>〔状態B〕ツンデツンデ
+その他]</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y337" t="n">
+        <v>220</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y338" t="n">
+        <v>1180</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>〔状態C〕イーブイ
+その他]</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y339" t="n">
+        <v>320</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>〔状態C〕リザード
+M-P]</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y340" t="n">
+        <v>220</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>〔状態C〕チリーン
+SV6]</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y341" t="n">
+        <v>220</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>〔状態C〕ペパーのヨクバリス
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y342" t="n">
+        <v>320</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲッコウガ☆(英語版)
+海外版]</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y343" t="n">
+        <v>2290</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>〔状態B〕レパルダス
+その他]</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y344" t="n">
+        <v>480</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エアームド
+その他]</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y345" t="n">
+        <v>1880</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>〔状態B〕コダック
+その他]</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y346" t="n">
+        <v>9480</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヒドイデ
+その他]</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y347" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>〔状態C〕シェイミ
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y348" t="n">
+        <v>680</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>〔状態C〕バオッキー
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y349" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジャローダex
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y350" t="n">
+        <v>1480</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タマゲタケ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y351" t="n">
+        <v>930</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミジュマル
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y352" t="n">
+        <v>3980</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のニャース
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y353" t="n">
+        <v>1990</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>〔状態C〕オーガポンかまどのめんex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y354" t="n">
+        <v>420</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウツーEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y355" t="n">
+        <v>1480</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キリンリキ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y356" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>〔状態C〕ブースターex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y357" t="n">
+        <v>4980</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アンノーンV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y358" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本水エネルギー(BWデザイン/ミラー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y359" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>〔状態C〕タロ
+SV7]</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y360" t="n">
+        <v>3280</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミライドンex
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y361" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブースターVMAX(SA仕様/中国語版)
+海外版]</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y362" t="n">
+        <v>24800</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ソーナンス
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y363" t="n">
+        <v>830</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>〔状態B〕チラチーノ
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y364" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>〔状態B〕ウネルミナモex
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y365" t="n">
+        <v>420</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゲノセクト(未開封)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y366" t="n">
+        <v>1180</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルガルガンGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y367" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z367" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y368" t="n">
+        <v>34800</v>
+      </c>
+      <c r="Z368" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>〔状態B〕タマンタ
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y369" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z369" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>〔状態C〕フーパV
+S12a]</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y370" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z370" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>〔状態C〕レックウザVMAX(SA)
+S7R]</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y371" t="n">
+        <v>158000</v>
+      </c>
+      <c r="Z371" t="n">
+        <v>126400</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y372" t="n">
+        <v>4280</v>
+      </c>
+      <c r="Z372" t="n">
+        <v>3424</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>〔状態C〕おじょうさま
+S11]</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y373" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z373" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>〔状態C〕プテラVSTAR
+S11]</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y374" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z374" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本水エネルギー(チャンピオンズリーグ2023)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y375" t="n">
+        <v>1080</v>
+      </c>
+      <c r="Z375" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゴンベ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y376" t="n">
+        <v>123000</v>
+      </c>
+      <c r="Z376" t="n">
+        <v>98400</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルギアV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y377" t="n">
+        <v>830</v>
+      </c>
+      <c r="Z377" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>〔状態B〕チルット
+S12a]</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y378" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z378" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウソッキー
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y379" t="n">
+        <v>480</v>
+      </c>
+      <c r="Z379" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アローラディグダ
+その他]</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y380" t="n">
+        <v>250</v>
+      </c>
+      <c r="Z380" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルージュラ
+S11a]</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y381" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z381" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒードラン
+その他]</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y382" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z382" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルリナ(R仕様/未開封)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y383" t="n">
+        <v>1080</v>
+      </c>
+      <c r="Z383" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポンチョを着たイーブイ(NP)
+その他]</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y384" t="n">
+        <v>123000</v>
+      </c>
+      <c r="Z384" t="n">
+        <v>98400</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本悪エネルギー(XYデザイン/ミラー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y385" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z385" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テッカグヤGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y386" t="n">
+        <v>350</v>
+      </c>
+      <c r="Z386" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>〔状態A-〕あなぬけのヒモ
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y387" t="n">
+        <v>590</v>
+      </c>
+      <c r="Z387" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カプ・レヒレGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y388" t="n">
+        <v>5480</v>
+      </c>
+      <c r="Z388" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>〔状態A-〕救助隊DXのピカチュウ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y389" t="n">
+        <v>65800</v>
+      </c>
+      <c r="Z389" t="n">
+        <v>52640</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y390" t="n">
+        <v>12800</v>
+      </c>
+      <c r="Z390" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>〔状態A-〕セレビィ
+XY]</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y391" t="n">
+        <v>14800</v>
+      </c>
+      <c r="Z391" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>〔状態A-〕セレビィEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y392" t="n">
+        <v>15800</v>
+      </c>
+      <c r="Z392" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マーシャドー＆カイリキーGX
+sm10]</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y393" t="n">
+        <v>4480</v>
+      </c>
+      <c r="Z393" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>〔状態B〕とつげきチョッキ
+XY]</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y394" t="n">
+        <v>880</v>
+      </c>
+      <c r="Z394" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドンカラスV(SA)
+S9]</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y395" t="n">
+        <v>990</v>
+      </c>
+      <c r="Z395" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y396" t="n">
+        <v>8980</v>
+      </c>
+      <c r="Z396" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゲノセクトV(SA)
+S8]</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y397" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Z397" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヒコザル
+その他]</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y398" t="n">
+        <v>8490</v>
+      </c>
+      <c r="Z398" t="n">
+        <v>6792</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>〔状態B〕アロマなおねえさん
+S6a]</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y399" t="n">
+        <v>480</v>
+      </c>
+      <c r="Z399" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>〔状態B〕ギャラドス
+XY]</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y400" t="n">
+        <v>178000</v>
+      </c>
+      <c r="Z400" t="n">
+        <v>142400</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>〔状態B〕ワープエネルギー
+その他]</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y401" t="n">
+        <v>1480</v>
+      </c>
+      <c r="Z401" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>〔状態C〕コイル
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y402" t="n">
+        <v>880</v>
+      </c>
+      <c r="Z402" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジュペッタGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y403" t="n">
+        <v>1190</v>
+      </c>
+      <c r="Z403" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>〔状態C〕シンボラーGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y404" t="n">
+        <v>220</v>
+      </c>
+      <c r="Z404" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>〔状態C〕リーフィアGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y405" t="n">
+        <v>680</v>
+      </c>
+      <c r="Z405" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジュペッタGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y406" t="n">
+        <v>690</v>
+      </c>
+      <c r="Z406" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本鋼エネルギー(バトルカーニバル)
+その他]</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y407" t="n">
+        <v>880</v>
+      </c>
+      <c r="Z407" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>〔状態C〕フシギバナ＆ツタージャGX
+sm11a]</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y408" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Z408" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>〔状態C〕シェイミEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y409" t="n">
+        <v>420</v>
+      </c>
+      <c r="Z409" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>〔状態C〕モルフォンGX
+SM9a]</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y410" t="n">
+        <v>480</v>
+      </c>
+      <c r="Z410" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本炎エネルギー(ジム応援キャンペーン ミラー)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y411" t="n">
+        <v>380</v>
+      </c>
+      <c r="Z411" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ(丸美屋)
+XY]</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y412" t="n">
+        <v>2980</v>
+      </c>
+      <c r="Z412" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>〔状態C〕ライチュウ＆アローラライチュウGX
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y413" t="n">
+        <v>990</v>
+      </c>
+      <c r="Z413" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>〔状態C〕ラティオスGX
+sm11]</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y414" t="n">
+        <v>1980</v>
+      </c>
+      <c r="Z414" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>〔状態C〕フシギバナ＆ツタージャGX(SA)
+sm11a]</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y415" t="n">
+        <v>8480</v>
+      </c>
+      <c r="Z415" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>〔状態C〕ランダムレシーバー
+その他]</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y416" t="n">
+        <v>2990</v>
+      </c>
+      <c r="Z416" t="n">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルカリオGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y417" t="n">
+        <v>8980</v>
+      </c>
+      <c r="Z417" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>〔状態C〕レックウザ
+その他]</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y418" t="n">
+        <v>6480</v>
+      </c>
+      <c r="Z418" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>〔状態C〕ガラルジグザグマ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y419" t="n">
+        <v>280</v>
+      </c>
+      <c r="Z419" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>〔状態C〕こわいおねえさん
+XY]</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y420" t="n">
+        <v>79800</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>〔状態C〕バトルロードスタジアム (バトルロードスタジアムDPクリア賞)
+その他]</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y421" t="n">
+        <v>158000</v>
+      </c>
+      <c r="Z421" t="n">
+        <v>126400</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>〔状態B〕カジリガメV
+S3]</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y422" t="n">
+        <v>320</v>
+      </c>
+      <c r="Z422" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本闘エネルギー(ジム応援キャンペーン ミラー)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y423" t="n">
+        <v>320</v>
+      </c>
+      <c r="Z423" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>〔状態B〕アローラキュウコンGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y424" t="n">
+        <v>4480</v>
+      </c>
+      <c r="Z424" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>〔状態B〕殿堂ベルト
+その他]</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y425" t="n">
+        <v>8490</v>
+      </c>
+      <c r="Z425" t="n">
+        <v>6792</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>〔状態B〕ベトベトン＆アローラベトベトンGX(SA)
+sm10]</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y426" t="n">
+        <v>3780</v>
+      </c>
+      <c r="Z426" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウツーGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y427" t="n">
+        <v>59800</v>
+      </c>
+      <c r="Z427" t="n">
+        <v>47840</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ギラティナEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y428" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="Z428" t="n">
+        <v>1504000</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>〔状態B〕戒めの祠
+sm10]</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y429" t="n">
+        <v>320</v>
+      </c>
+      <c r="Z429" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>〔状態B〕ウツロイドGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y430" t="n">
+        <v>1780</v>
+      </c>
+      <c r="Z430" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>〔状態B〕MレックウザEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y431" t="n">
+        <v>108000</v>
+      </c>
+      <c r="Z431" t="n">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>〔状態B〕マツリカ
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y432" t="n">
+        <v>4480</v>
+      </c>
+      <c r="Z432" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>〔状態C〕モルペコ
+s4a]</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y433" t="n">
+        <v>280</v>
+      </c>
+      <c r="Z433" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>〔状態B〕メガエアームドex
+M3]</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y434" t="n">
+        <v>480</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>〔※状態難/BGS9.5鑑定済〕ポンチョを着たピカチュウ</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y435" t="n">
+        <v>778000</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>622400</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>シャワーズVMAX(SA仕様/中国語版)</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y436" t="n">
+        <v>44800</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕フシギバナEX</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y437" t="n">
+        <v>14800</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>ゲノセクト(未開封)</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y438" t="n">
+        <v>5980</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕セレビィ</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y439" t="n">
+        <v>29800</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕モンジャラ</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y440" t="n">
+        <v>2980</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕セレビィV</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y441" t="n">
+        <v>4980</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕レシラムex</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y442" t="n">
+        <v>27800</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>22240</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ロケット団のファイヤーex</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y443" t="n">
+        <v>8480</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕ヒビキのホウオウex</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y444" t="n">
+        <v>19800</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ビクティニ</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y445" t="n">
+        <v>62800</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>50240</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>〔ACE9鑑定済〕リザードンV</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y446" t="n">
+        <v>9980</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ファイヤー</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y447" t="n">
+        <v>10800</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕リザードンGX</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y448" t="n">
+        <v>16800</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>13440</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>ヒードランGX</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y449" t="n">
+        <v>780</v>
+      </c>
+      <c r="Z449" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕ゲンシカイオーガEX</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y450" t="n">
+        <v>92800</v>
+      </c>
+      <c r="Z450" t="n">
+        <v>74240</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラプラスex
+M-P]</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y451" t="n">
+        <v>220</v>
+      </c>
+      <c r="Z451" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ミジュマル</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y452" t="n">
+        <v>108000</v>
+      </c>
+      <c r="Z452" t="n">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕アシレーヌGX</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y453" t="n">
+        <v>2480</v>
+      </c>
+      <c r="Z453" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ガブリアスex</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y454" t="n">
+        <v>15800</v>
+      </c>
+      <c r="Z454" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕メッソン</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y455" t="n">
+        <v>4980</v>
+      </c>
+      <c r="Z455" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕イースターのピカチュウ</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y456" t="n">
+        <v>278000</v>
+      </c>
+      <c r="Z456" t="n">
+        <v>222400</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ピカチュウ(ともだちのわ)</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y457" t="n">
+        <v>258000</v>
+      </c>
+      <c r="Z457" t="n">
+        <v>206400</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ピカチュウ(R仕様)</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y458" t="n">
+        <v>2480</v>
+      </c>
+      <c r="Z458" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕デンリュウV</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y459" t="n">
+        <v>2480</v>
+      </c>
+      <c r="Z459" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ピカチュウ(1ED)</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y460" t="n">
+        <v>32800</v>
+      </c>
+      <c r="Z460" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>ピカチュウ(SayakaMaruyama)</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y461" t="n">
+        <v>398000</v>
+      </c>
+      <c r="Z461" t="n">
+        <v>318400</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>ライチュウ＆アローラライチュウGX</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y462" t="n">
+        <v>10800</v>
+      </c>
+      <c r="Z462" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>カプ・コケコ</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y463" t="n">
+        <v>280</v>
+      </c>
+      <c r="Z463" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>マルマインGX</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y464" t="n">
+        <v>5280</v>
+      </c>
+      <c r="Z464" t="n">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ホップのオーロット</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y465" t="n">
+        <v>7480</v>
+      </c>
+      <c r="Z465" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ミュウex(25th)</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="Y466" t="n">
+        <v>67800</v>
+      </c>
+      <c r="Z466" t="n">
+        <v>54240</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB466"/>
+  <dimension ref="A1:AF510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33318,6 +33318,26 @@
           <t>2026-06-07_diff</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2026-06-08_price</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2026-06-08_buy</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2026-06-08_ratio</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2026-06-08_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39462,7 +39482,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39487,7 +39506,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39512,7 +39530,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39537,7 +39554,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39562,7 +39578,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39587,7 +39602,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39612,7 +39626,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39637,7 +39650,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39662,7 +39674,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39687,7 +39698,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39712,7 +39722,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39737,7 +39746,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39762,7 +39770,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39787,7 +39794,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39812,7 +39818,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39837,7 +39842,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39862,7 +39866,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39887,7 +39890,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39912,7 +39914,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39937,7 +39938,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39962,7 +39962,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -39987,7 +39986,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40012,7 +40010,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40037,7 +40034,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40062,7 +40058,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40087,7 +40082,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40112,7 +40106,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40137,7 +40130,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40162,7 +40154,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40187,7 +40178,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40212,7 +40202,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40237,7 +40226,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40262,7 +40250,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40287,7 +40274,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40312,7 +40298,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40337,7 +40322,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40362,7 +40346,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40387,7 +40370,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40412,7 +40394,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40437,7 +40418,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40461,7 +40441,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40486,7 +40465,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40510,7 +40488,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40534,7 +40511,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40558,7 +40534,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40582,7 +40557,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40606,7 +40580,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40630,7 +40603,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40654,7 +40626,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40678,7 +40649,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40702,7 +40672,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40726,7 +40695,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40750,7 +40718,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40774,7 +40741,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40798,7 +40764,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40822,7 +40787,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40846,7 +40810,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40870,7 +40833,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40894,7 +40856,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40918,7 +40879,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40942,7 +40902,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40966,7 +40925,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -40990,7 +40948,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41014,7 +40971,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41038,7 +40994,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41062,7 +41017,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41086,7 +41040,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41110,7 +41063,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41134,7 +41086,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41158,7 +41109,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41182,7 +41132,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41206,7 +41155,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41230,7 +41178,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41254,7 +41201,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41278,7 +41224,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41302,7 +41247,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -41327,7 +41271,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41352,7 +41295,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41377,7 +41319,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41402,7 +41343,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41427,7 +41367,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41452,7 +41391,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41477,7 +41415,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41502,7 +41439,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41527,7 +41463,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41552,7 +41487,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41577,7 +41511,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41602,7 +41535,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41627,7 +41559,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41652,7 +41583,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41677,7 +41607,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41702,7 +41631,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41727,7 +41655,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41752,7 +41679,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41777,7 +41703,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41802,7 +41727,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41827,7 +41751,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41852,7 +41775,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41877,7 +41799,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41902,7 +41823,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41927,7 +41847,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41952,7 +41871,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -41977,7 +41895,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42002,7 +41919,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42027,7 +41943,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42052,7 +41967,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42077,7 +41991,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42102,7 +42015,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42127,7 +42039,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42152,7 +42063,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42177,7 +42087,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42202,7 +42111,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42227,7 +42135,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42252,7 +42159,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42277,7 +42183,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42302,7 +42207,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42327,7 +42231,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42352,7 +42255,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42377,7 +42279,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42402,7 +42303,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42427,7 +42327,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42452,7 +42351,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42477,7 +42375,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42502,7 +42399,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42527,7 +42423,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42552,7 +42447,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42577,7 +42471,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42602,7 +42495,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42627,7 +42519,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42652,7 +42543,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42677,7 +42567,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42702,7 +42591,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42727,7 +42615,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42752,7 +42639,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42777,7 +42663,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42802,7 +42687,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42827,7 +42711,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42852,7 +42735,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42877,7 +42759,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42902,7 +42783,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42927,7 +42807,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42952,7 +42831,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -42977,7 +42855,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43002,7 +42879,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43027,7 +42903,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43052,7 +42927,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43077,7 +42951,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43102,7 +42975,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43127,7 +42999,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43152,7 +43023,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43177,7 +43047,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43202,7 +43071,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43227,7 +43095,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43252,7 +43119,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43277,7 +43143,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43302,7 +43167,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43327,7 +43191,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43352,7 +43215,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43377,7 +43239,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43402,7 +43263,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43427,7 +43287,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43452,7 +43311,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43477,7 +43335,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43502,7 +43359,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43527,7 +43383,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43552,7 +43407,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43577,7 +43431,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43602,7 +43455,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43627,7 +43479,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43652,7 +43503,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43677,7 +43527,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43702,7 +43551,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43727,7 +43575,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43752,7 +43599,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43776,7 +43622,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43800,7 +43645,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43824,7 +43668,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43848,7 +43691,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43872,7 +43714,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43896,7 +43737,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43920,7 +43760,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43944,7 +43783,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43968,7 +43806,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -43992,7 +43829,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44016,7 +43852,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44040,7 +43875,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44064,7 +43898,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44088,7 +43921,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44112,7 +43944,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44136,7 +43967,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44161,7 +43991,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44185,7 +44014,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44209,7 +44037,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44233,7 +44060,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44257,7 +44083,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44281,7 +44106,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44305,7 +44129,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44329,7 +44152,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44353,7 +44175,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44377,7 +44198,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44401,7 +44221,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44425,7 +44244,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44449,7 +44267,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44473,7 +44290,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44497,7 +44313,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44521,7 +44336,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -44532,6 +44346,1106 @@
       </c>
       <c r="Z466" t="n">
         <v>54240</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼルネアスEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC467" t="n">
+        <v>1190</v>
+      </c>
+      <c r="AD467" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>〔状態B〕メガヤドランex
+M-P]</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC468" t="n">
+        <v>580</v>
+      </c>
+      <c r="AD468" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フクオカのピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC469" t="n">
+        <v>21800</v>
+      </c>
+      <c r="AD469" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>〔状態B〕ロケット団のサカキ
+SV10]</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC470" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AD470" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オオタチ
+SV9]</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC471" t="n">
+        <v>480</v>
+      </c>
+      <c r="AD471" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テラパゴスex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC472" t="n">
+        <v>1090</v>
+      </c>
+      <c r="AD472" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アカマツ
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC473" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AD473" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC474" t="n">
+        <v>1490</v>
+      </c>
+      <c r="AD474" t="n">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゼロの大空洞
+SV7]</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC475" t="n">
+        <v>2630</v>
+      </c>
+      <c r="AD475" t="n">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シャリタツ
+SV6]</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC476" t="n">
+        <v>1190</v>
+      </c>
+      <c r="AD476" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウミトリオex
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC477" t="n">
+        <v>380</v>
+      </c>
+      <c r="AD477" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニャオハ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC478" t="n">
+        <v>390</v>
+      </c>
+      <c r="AD478" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>〔状態B〕ガブリアスex
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC479" t="n">
+        <v>4780</v>
+      </c>
+      <c r="AD479" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カルボウ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC480" t="n">
+        <v>330</v>
+      </c>
+      <c r="AD480" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グレイシア(YU NAGABA)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC481" t="n">
+        <v>12800</v>
+      </c>
+      <c r="AD481" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハクリュー
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC482" t="n">
+        <v>2180</v>
+      </c>
+      <c r="AD482" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガラルニャイキングV
+S11]</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC483" t="n">
+        <v>380</v>
+      </c>
+      <c r="AD483" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>〔状態B〕オリジンパルキアVSTAR
+S10P]</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC484" t="n">
+        <v>1190</v>
+      </c>
+      <c r="AD484" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ナンジャモ
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC485" t="n">
+        <v>47800</v>
+      </c>
+      <c r="AD485" t="n">
+        <v>38240</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グレンアルマ
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC486" t="n">
+        <v>590</v>
+      </c>
+      <c r="AD486" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オリジンディアルガVSTAR
+S12a]</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC487" t="n">
+        <v>11800</v>
+      </c>
+      <c r="AD487" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルギアVSTAR(RRR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC488" t="n">
+        <v>5290</v>
+      </c>
+      <c r="AD488" t="n">
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レシラム＆ゼクロムGX
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC489" t="n">
+        <v>4090</v>
+      </c>
+      <c r="AD489" t="n">
+        <v>3272</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒナツ
+S10a]</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC490" t="n">
+        <v>930</v>
+      </c>
+      <c r="AD490" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>〔状態C〕MヘラクロスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC491" t="n">
+        <v>6980</v>
+      </c>
+      <c r="AD491" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パルスワンV
+s1a]</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC492" t="n">
+        <v>380</v>
+      </c>
+      <c r="AD492" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コルニの気合い
+S5R]</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC493" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AD493" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>〔状態B〕レントラーGLLV.X(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC494" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AD494" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メモリーカプセル
+s4]</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC495" t="n">
+        <v>680</v>
+      </c>
+      <c r="AD495" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マギアナEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC496" t="n">
+        <v>8990</v>
+      </c>
+      <c r="AD496" t="n">
+        <v>7192</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガラルマッギョV
+S2a]</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC497" t="n">
+        <v>380</v>
+      </c>
+      <c r="AD497" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウVMAX(RRR仕様/コロコロコミック)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC498" t="n">
+        <v>2490</v>
+      </c>
+      <c r="AD498" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウVMAX
+S8]</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC499" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AD499" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>〔状態B〕ガラルギャロップV
+S6H]</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC500" t="n">
+        <v>580</v>
+      </c>
+      <c r="AD500" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>〔状態B〕ちからのハチマキ(ファミ通)
+XY]</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC501" t="n">
+        <v>1290</v>
+      </c>
+      <c r="AD501" t="n">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>〔状態B〕MバンギラスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC502" t="n">
+        <v>21800</v>
+      </c>
+      <c r="AD502" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジュカインGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC503" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AD503" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲッコウガGX
+smP2]</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC504" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AD504" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>〔状態C〕MミュウツーEX(Y)
+その他]</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC505" t="n">
+        <v>29800</v>
+      </c>
+      <c r="AD505" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>〔状態B〕MヤドランEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC506" t="n">
+        <v>11800</v>
+      </c>
+      <c r="AD506" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>〔状態B〕パルキアGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC507" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AD507" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>〔状態B〕アクロマ
+その他]</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC508" t="n">
+        <v>8990</v>
+      </c>
+      <c r="AD508" t="n">
+        <v>7192</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>〔状態B〕アセロラ
+SM9b]</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC509" t="n">
+        <v>590</v>
+      </c>
+      <c r="AD509" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケモンレンジャー
+XY]</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AC510" t="n">
+        <v>9980</v>
+      </c>
+      <c r="AD510" t="n">
+        <v>7984</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF510"/>
+  <dimension ref="A1:AJ525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33338,6 +33338,26 @@
           <t>2026-06-08_diff</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2026-06-09_price</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2026-06-09_buy</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2026-06-09_ratio</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2026-06-09_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44360,7 +44380,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44385,7 +44404,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44410,7 +44428,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44435,7 +44452,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44460,7 +44476,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44485,7 +44500,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44510,7 +44524,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44535,7 +44548,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44560,7 +44572,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44585,7 +44596,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44610,7 +44620,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44635,7 +44644,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44660,7 +44668,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44685,7 +44692,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44710,7 +44716,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44735,7 +44740,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44760,7 +44764,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44785,7 +44788,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44810,7 +44812,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44835,7 +44836,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44860,7 +44860,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44885,7 +44884,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44910,7 +44908,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44935,7 +44932,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44960,7 +44956,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -44985,7 +44980,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45010,7 +45004,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45035,7 +45028,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45060,7 +45052,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45085,7 +45076,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45110,7 +45100,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45135,7 +45124,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45160,7 +45148,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45185,7 +45172,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45210,7 +45196,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45235,7 +45220,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45260,7 +45244,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45285,7 +45268,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45310,7 +45292,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45335,7 +45316,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45360,7 +45340,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45385,7 +45364,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr"/>
       <c r="D508" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45410,7 +45388,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr"/>
       <c r="D509" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45435,7 +45412,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45446,6 +45422,381 @@
       </c>
       <c r="AD510" t="n">
         <v>7984</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>〔状態B〕レシラム
+その他]</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG511" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AH511" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガチグマアカツキex
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG512" t="n">
+        <v>530</v>
+      </c>
+      <c r="AH512" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ギアル
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG513" t="n">
+        <v>730</v>
+      </c>
+      <c r="AH513" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コロモリ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG514" t="n">
+        <v>830</v>
+      </c>
+      <c r="AH514" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ダンゴロ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG515" t="n">
+        <v>930</v>
+      </c>
+      <c r="AH515" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ビリジオン
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG516" t="n">
+        <v>1390</v>
+      </c>
+      <c r="AH516" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>〔状態A-〕Nのゾロアークex
+SV9]</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG517" t="n">
+        <v>8680</v>
+      </c>
+      <c r="AH517" t="n">
+        <v>6944</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウネルミナモex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG518" t="n">
+        <v>730</v>
+      </c>
+      <c r="AH518" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラティアスex
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG519" t="n">
+        <v>2780</v>
+      </c>
+      <c r="AH519" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>〔状態C〕レックウザ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG520" t="n">
+        <v>64800</v>
+      </c>
+      <c r="AH520" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テラパゴスex
+SV7]</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG521" t="n">
+        <v>730</v>
+      </c>
+      <c r="AH521" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タイプ:ヌル
+その他]</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG522" t="n">
+        <v>350</v>
+      </c>
+      <c r="AH522" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>〔状態B〕イルカマン
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG523" t="n">
+        <v>380</v>
+      </c>
+      <c r="AH523" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒョウタ
+SV4M]</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG524" t="n">
+        <v>390</v>
+      </c>
+      <c r="AH524" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本悪エネルギー(チャンピオンズリーグ2024)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AG525" t="n">
+        <v>680</v>
+      </c>
+      <c r="AH525" t="n">
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ525"/>
+  <dimension ref="A1:AN617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33358,6 +33358,26 @@
           <t>2026-06-09_diff</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2026-06-10_price</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2026-06-10_buy</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2026-06-10_ratio</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2026-06-10_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -45436,7 +45456,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45461,7 +45480,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45486,7 +45504,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr"/>
       <c r="D513" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45511,7 +45528,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45536,7 +45552,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45561,7 +45576,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45586,7 +45600,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45611,7 +45624,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45636,7 +45648,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr"/>
       <c r="D519" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45661,7 +45672,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr"/>
       <c r="D520" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45686,7 +45696,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45711,7 +45720,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45736,7 +45744,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr"/>
       <c r="D523" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45761,7 +45768,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr"/>
       <c r="D524" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45786,7 +45792,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr"/>
       <c r="D525" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45797,6 +45802,2269 @@
       </c>
       <c r="AH525" t="n">
         <v>544</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒカリ
+M-P]</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK526" t="n">
+        <v>450</v>
+      </c>
+      <c r="AL526" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>〔状態C〕コイキング
+その他]</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK527" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AL527" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゲッコウガEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK528" t="n">
+        <v>7980</v>
+      </c>
+      <c r="AL528" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フタチマル
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK529" t="n">
+        <v>1090</v>
+      </c>
+      <c r="AL529" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>〔状態B〕デンチュラ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK530" t="n">
+        <v>580</v>
+      </c>
+      <c r="AL530" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タマタマ
+その他]</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK531" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL531" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>〔状態B〕アイリスの闘志
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK532" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL532" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ノココッチex
+SV9]</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK533" t="n">
+        <v>590</v>
+      </c>
+      <c r="AL533" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サンダースex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK534" t="n">
+        <v>8680</v>
+      </c>
+      <c r="AL534" t="n">
+        <v>6944</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アカマツ
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK535" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AL535" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゼラオラ
+SV7]</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK536" t="n">
+        <v>690</v>
+      </c>
+      <c r="AL536" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>〔状態B〕プロテクトキューブ (リザードンメガバトル)
+XY]</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK537" t="n">
+        <v>21800</v>
+      </c>
+      <c r="AL537" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テツノイバラ
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK538" t="n">
+        <v>330</v>
+      </c>
+      <c r="AL538" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>〔状態B〕ウェルカモ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK539" t="n">
+        <v>220</v>
+      </c>
+      <c r="AL539" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グラードン
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK540" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AL540" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>〔状態A-〕おいわいファンファーレ(2022)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK541" t="n">
+        <v>23800</v>
+      </c>
+      <c r="AL541" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーVSTAR
+S10b]</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK542" t="n">
+        <v>680</v>
+      </c>
+      <c r="AL542" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>〔状態B〕フォレトスex
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK543" t="n">
+        <v>380</v>
+      </c>
+      <c r="AL543" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヤドキングex
+SV2P]</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK544" t="n">
+        <v>680</v>
+      </c>
+      <c r="AL544" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本雷エネルギー(SVデザイン)
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK545" t="n">
+        <v>2430</v>
+      </c>
+      <c r="AL545" t="n">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テツノワダチex
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK546" t="n">
+        <v>990</v>
+      </c>
+      <c r="AL546" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リザードンVSTAR
+S12a]</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK547" t="n">
+        <v>1190</v>
+      </c>
+      <c r="AL547" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本雷エネルギー(SS新デザイン)
+S12a]</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK548" t="n">
+        <v>350</v>
+      </c>
+      <c r="AL548" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レジエレキVMAX
+S12]</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK549" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL549" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガラルネギガナイト
+s4a]</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK550" t="n">
+        <v>350</v>
+      </c>
+      <c r="AL550" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マグマ団のグラードン(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK551" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AL551" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガブリアス＆ギラティナGX
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK552" t="n">
+        <v>2280</v>
+      </c>
+      <c r="AL552" t="n">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ススキ
+S10a]</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK553" t="n">
+        <v>450</v>
+      </c>
+      <c r="AL553" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゲノセクトGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK554" t="n">
+        <v>590</v>
+      </c>
+      <c r="AL554" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ツールスクラッパー
+S2]</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK555" t="n">
+        <v>4580</v>
+      </c>
+      <c r="AL555" t="n">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>〔状態A-〕クチートEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK556" t="n">
+        <v>2590</v>
+      </c>
+      <c r="AL556" t="n">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本超エネルギー(チャンピオンズリーグ2022)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK557" t="n">
+        <v>930</v>
+      </c>
+      <c r="AL557" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フラダリの奥の手
+XY]</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK558" t="n">
+        <v>29800</v>
+      </c>
+      <c r="AL558" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゼルネアス
+XY]</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr"/>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK559" t="n">
+        <v>1190</v>
+      </c>
+      <c r="AL559" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ぼんぐり職人
+sm6]</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK560" t="n">
+        <v>3280</v>
+      </c>
+      <c r="AL560" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レシラム＆リザードンGX(SA)
+sm10]</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr"/>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK561" t="n">
+        <v>123000</v>
+      </c>
+      <c r="AL561" t="n">
+        <v>98400</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イエッサンV
+s4a]</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK562" t="n">
+        <v>330</v>
+      </c>
+      <c r="AL562" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マスタードれんげきのかた
+S8b]</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK563" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL563" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>〔状態B〕キュウコンBREAK
+CP6]</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK564" t="n">
+        <v>4980</v>
+      </c>
+      <c r="AL564" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>〔状態B〕サイトウ
+S8b]</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr"/>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK565" t="n">
+        <v>880</v>
+      </c>
+      <c r="AL565" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リザードンGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK566" t="n">
+        <v>368000</v>
+      </c>
+      <c r="AL566" t="n">
+        <v>294400</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>〔状態B〕シャクヤ
+S6K]</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK567" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AL567" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>〔状態C〕エンペルト
+その他]</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK568" t="n">
+        <v>24800</v>
+      </c>
+      <c r="AL568" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>〔状態C〕シブヤのピカチュウ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK569" t="n">
+        <v>25800</v>
+      </c>
+      <c r="AL569" t="n">
+        <v>20640</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケモンセンターのお姉さん(SR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK570" t="n">
+        <v>19800</v>
+      </c>
+      <c r="AL570" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハッサムGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK571" t="n">
+        <v>5480</v>
+      </c>
+      <c r="AL571" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>〔状態B〕メイ
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK572" t="n">
+        <v>32800</v>
+      </c>
+      <c r="AL572" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本草エネルギー(クイックキラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK573" t="n">
+        <v>69800</v>
+      </c>
+      <c r="AL573" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>〔状態B〕ルカリオ＆メルメタルGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK574" t="n">
+        <v>8480</v>
+      </c>
+      <c r="AL574" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>〔状態B〕プラスパワー(サマーカーニバル)
+その他]</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK575" t="n">
+        <v>12800</v>
+      </c>
+      <c r="AL575" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>〔状態B〕ベル
+その他]</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK576" t="n">
+        <v>49800</v>
+      </c>
+      <c r="AL576" t="n">
+        <v>39840</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シェイミ
+M-P]</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK577" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AL577" t="n">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕リーフィアVMAX(SA)</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK578" t="n">
+        <v>124000</v>
+      </c>
+      <c r="AL578" t="n">
+        <v>99200</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>クヌギダマ</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK579" t="n">
+        <v>280</v>
+      </c>
+      <c r="AL579" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>ヒメンカ</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK580" t="n">
+        <v>280</v>
+      </c>
+      <c r="AL580" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>フシギバナ＆ツタージャGX(SA)</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK581" t="n">
+        <v>18800</v>
+      </c>
+      <c r="AL581" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>サーナイトexδ-デルタ種(25th)</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK582" t="n">
+        <v>5280</v>
+      </c>
+      <c r="AL582" t="n">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>ウルガモスGX</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK583" t="n">
+        <v>580</v>
+      </c>
+      <c r="AL583" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミロカロスex
+SV8]</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK584" t="n">
+        <v>12800</v>
+      </c>
+      <c r="AL584" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>ブラックキュレムex</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr"/>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK585" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AL585" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>シャワーズV</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK586" t="n">
+        <v>480</v>
+      </c>
+      <c r="AL586" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>ガラルヒヒダルマVMAX</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK587" t="n">
+        <v>280</v>
+      </c>
+      <c r="AL587" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>グレイシアGX</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK588" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AL588" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガライボルトex
+M1S]</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK589" t="n">
+        <v>390</v>
+      </c>
+      <c r="AL589" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ピカチュウex</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK590" t="n">
+        <v>134000</v>
+      </c>
+      <c r="AL590" t="n">
+        <v>107200</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>テツノイバラ</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK591" t="n">
+        <v>580</v>
+      </c>
+      <c r="AL591" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>カプ・コケコV</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK592" t="n">
+        <v>480</v>
+      </c>
+      <c r="AL592" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>〔状態B〕フーディン
+M1S]</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK593" t="n">
+        <v>680</v>
+      </c>
+      <c r="AL593" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>ラティアスex</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK594" t="n">
+        <v>33800</v>
+      </c>
+      <c r="AL594" t="n">
+        <v>27040</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ミミッキュVMAX</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr"/>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK595" t="n">
+        <v>24800</v>
+      </c>
+      <c r="AL595" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>イワパレス</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK596" t="n">
+        <v>780</v>
+      </c>
+      <c r="AL596" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>コジオ</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK597" t="n">
+        <v>480</v>
+      </c>
+      <c r="AL597" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>ルガルガンVMAX</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK598" t="n">
+        <v>280</v>
+      </c>
+      <c r="AL598" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>セキタンザンVMAX</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK599" t="n">
+        <v>680</v>
+      </c>
+      <c r="AL599" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ブラッキー＆ダークライGX(SA)</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK600" t="n">
+        <v>358000</v>
+      </c>
+      <c r="AL600" t="n">
+        <v>286400</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>ブラッキーVMAX</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr"/>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK601" t="n">
+        <v>16800</v>
+      </c>
+      <c r="AL601" t="n">
+        <v>13440</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>カイリューV(SA)</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK602" t="n">
+        <v>84800</v>
+      </c>
+      <c r="AL602" t="n">
+        <v>67840</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>ボーマンダGX</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK603" t="n">
+        <v>780</v>
+      </c>
+      <c r="AL603" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>イッカネズミex</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK604" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AL604" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>ニャースex</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr"/>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK605" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AL605" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>ロトム図鑑</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK606" t="n">
+        <v>280</v>
+      </c>
+      <c r="AL606" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>基本雷エネルギー</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK607" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AL607" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>基本雷エネルギー(ジムチャレンジ)</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr"/>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK608" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL608" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>れんげきエネルギー</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr"/>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK609" t="n">
+        <v>680</v>
+      </c>
+      <c r="AL609" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>基本草エネルギー(ビクティニBWR争奪戦)</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr"/>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK610" t="n">
+        <v>280</v>
+      </c>
+      <c r="AL610" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>基本鋼エネルギー(DPキラ)</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK611" t="n">
+        <v>7980</v>
+      </c>
+      <c r="AL611" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>マチスの取引</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK612" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AL612" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>アオキの手際</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK613" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AL613" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>アンズの秘技</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK614" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL614" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ポケモンブリーダー</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK615" t="n">
+        <v>64800</v>
+      </c>
+      <c r="AL615" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>キャンデラ</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr"/>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK616" t="n">
+        <v>580</v>
+      </c>
+      <c r="AL616" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>ビート</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr"/>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AK617" t="n">
+        <v>1780</v>
+      </c>
+      <c r="AL617" t="n">
+        <v>1424</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN617"/>
+  <dimension ref="A1:AR622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33378,6 +33378,26 @@
           <t>2026-06-10_diff</t>
         </is>
       </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2026-06-12_price</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2026-06-12_buy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2026-06-12_ratio</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2026-06-12_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -45816,7 +45836,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr"/>
       <c r="D526" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45841,7 +45860,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45866,7 +45884,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45891,7 +45908,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45916,7 +45932,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45941,7 +45956,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45966,7 +45980,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -45991,7 +46004,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46016,7 +46028,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46041,7 +46052,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46066,7 +46076,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46091,7 +46100,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46116,7 +46124,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46141,7 +46148,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46166,7 +46172,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46191,7 +46196,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46216,7 +46220,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46241,7 +46244,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46266,7 +46268,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46291,7 +46292,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46316,7 +46316,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46341,7 +46340,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46366,7 +46364,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46391,7 +46388,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46416,7 +46412,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr"/>
       <c r="D550" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46441,7 +46436,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46466,7 +46460,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46491,7 +46484,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46516,7 +46508,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46541,7 +46532,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46566,7 +46556,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46591,7 +46580,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46616,7 +46604,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46641,7 +46628,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46666,7 +46652,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46691,7 +46676,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46716,7 +46700,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46741,7 +46724,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46766,7 +46748,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46791,7 +46772,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46816,7 +46796,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46841,7 +46820,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46866,7 +46844,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46891,7 +46868,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46916,7 +46892,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46941,7 +46916,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46966,7 +46940,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -46991,7 +46964,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47016,7 +46988,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47041,7 +47012,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47066,7 +47036,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47091,7 +47060,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47115,7 +47083,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47139,7 +47106,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47163,7 +47129,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47187,7 +47152,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47211,7 +47175,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47235,7 +47198,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47260,7 +47222,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47284,7 +47245,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47308,7 +47268,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr"/>
       <c r="D586" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47332,7 +47291,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47356,7 +47314,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47381,7 +47338,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47405,7 +47361,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47429,7 +47384,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47453,7 +47407,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47478,7 +47431,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47502,7 +47454,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47526,7 +47477,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47550,7 +47500,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47574,7 +47523,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47598,7 +47546,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47622,7 +47569,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47646,7 +47592,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47670,7 +47615,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47694,7 +47638,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47718,7 +47661,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47742,7 +47684,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47766,7 +47707,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47790,7 +47730,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47814,7 +47753,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47838,7 +47776,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47862,7 +47799,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47886,7 +47822,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47910,7 +47845,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47934,7 +47868,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47958,7 +47891,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -47982,7 +47914,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48006,7 +47937,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48030,7 +47960,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48054,7 +47983,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48065,6 +47993,130 @@
       </c>
       <c r="AL617" t="n">
         <v>1424</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>ギャラドスごっこピカチュウ(未開封)</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr"/>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AO618" t="n">
+        <v>3480000</v>
+      </c>
+      <c r="AP618" t="n">
+        <v>2784000</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>〔状態B〕MオニゴーリEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AO619" t="n">
+        <v>1790</v>
+      </c>
+      <c r="AP619" t="n">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>〔状態C〕レインボーエネルギー
+その他]</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AO620" t="n">
+        <v>390</v>
+      </c>
+      <c r="AP620" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>〔状態B〕N
+その他]</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AO621" t="n">
+        <v>2780</v>
+      </c>
+      <c r="AP621" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>〔状態B〕モモワロウex
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AO622" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AP622" t="n">
+        <v>1184</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR622"/>
+  <dimension ref="A1:AV806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33398,6 +33398,26 @@
           <t>2026-06-12_diff</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2026-06-13_price</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2026-06-13_buy</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2026-06-13_ratio</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2026-06-13_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48006,7 +48026,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48031,7 +48050,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48056,7 +48074,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48081,7 +48098,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48106,7 +48122,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48117,6 +48132,4555 @@
       </c>
       <c r="AP622" t="n">
         <v>1184</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マシマシラex
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS623" t="n">
+        <v>1230</v>
+      </c>
+      <c r="AT623" t="n">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エモンガ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr"/>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS624" t="n">
+        <v>1190</v>
+      </c>
+      <c r="AT624" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ナゲキ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS625" t="n">
+        <v>730</v>
+      </c>
+      <c r="AT625" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マラカッチ
+SV9]</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS626" t="n">
+        <v>330</v>
+      </c>
+      <c r="AT626" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シャワーズex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS627" t="n">
+        <v>8480</v>
+      </c>
+      <c r="AT627" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr"/>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS628" t="n">
+        <v>330</v>
+      </c>
+      <c r="AT628" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr"/>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS629" t="n">
+        <v>230</v>
+      </c>
+      <c r="AT629" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケパークのセレビィ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS630" t="n">
+        <v>57800</v>
+      </c>
+      <c r="AT630" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タロ
+SV7]</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS631" t="n">
+        <v>1890</v>
+      </c>
+      <c r="AT631" t="n">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>〔状態B〕イルカマンex
+SV6]</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr"/>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS632" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT632" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カイデン
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS633" t="n">
+        <v>330</v>
+      </c>
+      <c r="AT633" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フーディンex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr"/>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS634" t="n">
+        <v>690</v>
+      </c>
+      <c r="AT634" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>〔状態B〕イワパレス
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS635" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT635" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本水エネルギー(チャンピオンズリーグ2024)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS636" t="n">
+        <v>680</v>
+      </c>
+      <c r="AT636" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コライドン(AR仕様)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr"/>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS637" t="n">
+        <v>10900</v>
+      </c>
+      <c r="AT637" t="n">
+        <v>8720</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゴローニャex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr"/>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS638" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT638" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS639" t="n">
+        <v>14800</v>
+      </c>
+      <c r="AT639" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラピオンVSTAR
+S11]</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS640" t="n">
+        <v>250</v>
+      </c>
+      <c r="AT640" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>〔状態B〕プテラV(SA)
+S11]</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr"/>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS641" t="n">
+        <v>14800</v>
+      </c>
+      <c r="AT641" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ワナイダーex
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr"/>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS642" t="n">
+        <v>1290</v>
+      </c>
+      <c r="AT642" t="n">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ネストボール
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS643" t="n">
+        <v>2780</v>
+      </c>
+      <c r="AT643" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本水エネルギー(SS新デザイン)
+S12a]</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS644" t="n">
+        <v>420</v>
+      </c>
+      <c r="AT644" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルギアVSTAR
+S12]</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS645" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AT645" t="n">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジムバッジ(エリカ)
+XY]</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS646" t="n">
+        <v>4180</v>
+      </c>
+      <c r="AT646" t="n">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポンチョを着たイーブイ(GC/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS647" t="n">
+        <v>178000</v>
+      </c>
+      <c r="AT647" t="n">
+        <v>142400</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガラルサニゴーンV
+S3]</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS648" t="n">
+        <v>250</v>
+      </c>
+      <c r="AT648" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS649" t="n">
+        <v>23800</v>
+      </c>
+      <c r="AT649" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>〔状態C〕MボスゴドラEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr"/>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS650" t="n">
+        <v>9980</v>
+      </c>
+      <c r="AT650" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本超エネルギー(チャンピオンズリーグ2020)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS651" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AT651" t="n">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ストリンダーV
+S2]</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS652" t="n">
+        <v>480</v>
+      </c>
+      <c r="AT652" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>〔状態A-〕そらをとぶピカチュウV(25th)
+S8a]</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS653" t="n">
+        <v>1790</v>
+      </c>
+      <c r="AT653" t="n">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>〔状態A-〕TVレポーター
+sm6]</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr"/>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS654" t="n">
+        <v>21800</v>
+      </c>
+      <c r="AT654" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サーナイト
+その他]</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr"/>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS655" t="n">
+        <v>2250</v>
+      </c>
+      <c r="AT655" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フーパGX
+sm8]</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS656" t="n">
+        <v>1090</v>
+      </c>
+      <c r="AT656" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カプ・コケコVMAX
+S5I]</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS657" t="n">
+        <v>680</v>
+      </c>
+      <c r="AT657" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レックウザVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr"/>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS658" t="n">
+        <v>39800</v>
+      </c>
+      <c r="AT658" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウVMAX
+S8]</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS659" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AT659" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>〔状態B〕パルスワンV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr"/>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS660" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AT660" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エリカのおもてなし
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS661" t="n">
+        <v>98000</v>
+      </c>
+      <c r="AT661" t="n">
+        <v>78400</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>〔状態B〕ボーマンダEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr"/>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS662" t="n">
+        <v>3490</v>
+      </c>
+      <c r="AT662" t="n">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヤドキング(グレート)
+その他]</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr"/>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS663" t="n">
+        <v>29800</v>
+      </c>
+      <c r="AT663" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>〔状態B〕MラティオスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS664" t="n">
+        <v>3990</v>
+      </c>
+      <c r="AT664" t="n">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラティオスEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr"/>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS665" t="n">
+        <v>27800</v>
+      </c>
+      <c r="AT665" t="n">
+        <v>22240</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルカリオEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr"/>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS666" t="n">
+        <v>34800</v>
+      </c>
+      <c r="AT666" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>〔状態B〕げんきのハチマキ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr"/>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS667" t="n">
+        <v>11800</v>
+      </c>
+      <c r="AT667" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>〔状態B〕アーゴヨンGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr"/>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS668" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AT668" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>〔状態B〕レシラム＆リザードンGX
+sm10]</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS669" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AT669" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラティアス＆ラティオスGX
+sm9]</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr"/>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS670" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AT670" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガカイリューex
+M2a]</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS671" t="n">
+        <v>34800</v>
+      </c>
+      <c r="AT671" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラムパルドex
+M5]</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS672" t="n">
+        <v>420</v>
+      </c>
+      <c r="AT672" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕カイ</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS673" t="n">
+        <v>18800</v>
+      </c>
+      <c r="AT673" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>カイロス</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS674" t="n">
+        <v>880</v>
+      </c>
+      <c r="AT674" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕リーフィアV(SA)</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr"/>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS675" t="n">
+        <v>18800</v>
+      </c>
+      <c r="AT675" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>ジュナイパーex</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS676" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT676" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>ヒードランVMAX</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr"/>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS677" t="n">
+        <v>680</v>
+      </c>
+      <c r="AT677" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>マルヤクデV</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr"/>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS678" t="n">
+        <v>480</v>
+      </c>
+      <c r="AT678" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>マグカルゴGX</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr"/>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS679" t="n">
+        <v>680</v>
+      </c>
+      <c r="AT679" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>ウッウ</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS680" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT680" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>基本水エネルギー</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS681" t="n">
+        <v>480</v>
+      </c>
+      <c r="AT681" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>ギャラドスex</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS682" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AT682" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>ゼクロムex</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS683" t="n">
+        <v>1380</v>
+      </c>
+      <c r="AT683" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS684" t="n">
+        <v>198000</v>
+      </c>
+      <c r="AT684" t="n">
+        <v>158400</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>R団のサンダー(25th)</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS685" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AT685" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>フクオカのピカチュウ(未開封)</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS686" t="n">
+        <v>23800</v>
+      </c>
+      <c r="AT686" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>ライボルト</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS687" t="n">
+        <v>420</v>
+      </c>
+      <c r="AT687" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヨノワール
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS688" t="n">
+        <v>990</v>
+      </c>
+      <c r="AT688" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>ニンフィアV</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr"/>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS689" t="n">
+        <v>7980</v>
+      </c>
+      <c r="AT689" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕キングドラEX</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS690" t="n">
+        <v>24800</v>
+      </c>
+      <c r="AT690" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>モグリュー</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS691" t="n">
+        <v>880</v>
+      </c>
+      <c r="AT691" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>コジョンド</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr"/>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS692" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT692" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>エルレイドV</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr"/>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS693" t="n">
+        <v>1680</v>
+      </c>
+      <c r="AT693" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>イワンコ</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS694" t="n">
+        <v>480</v>
+      </c>
+      <c r="AT694" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>ワルビアル</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr"/>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS695" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AT695" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>メガゲンガーex</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr"/>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS696" t="n">
+        <v>4980</v>
+      </c>
+      <c r="AT696" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>ハッサムex</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS697" t="n">
+        <v>2580</v>
+      </c>
+      <c r="AT697" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ガブリアスV</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS698" t="n">
+        <v>25800</v>
+      </c>
+      <c r="AT698" t="n">
+        <v>20640</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕MレックウザEX</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr"/>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS699" t="n">
+        <v>64800</v>
+      </c>
+      <c r="AT699" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕イーブイ</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr"/>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS700" t="n">
+        <v>18800</v>
+      </c>
+      <c r="AT700" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕イーブイ＆カビゴンGX</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr"/>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS701" t="n">
+        <v>22800</v>
+      </c>
+      <c r="AT701" t="n">
+        <v>18240</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>ルギアV</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr"/>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS702" t="n">
+        <v>4780</v>
+      </c>
+      <c r="AT702" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>ウッウV</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS703" t="n">
+        <v>680</v>
+      </c>
+      <c r="AT703" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>ポケモン通信</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr"/>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS704" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AT704" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>基本闘エネルギー(チャンピオンズリーグ2024)</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr"/>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS705" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT705" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>基本闘エネルギー(チャンピオンズリーグ2022)</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr"/>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS706" t="n">
+        <v>380</v>
+      </c>
+      <c r="AT706" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕グリーンの戦略</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS707" t="n">
+        <v>14800</v>
+      </c>
+      <c r="AT707" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>キクコ</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr"/>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS708" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT708" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>ポケモンブリーダー</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS709" t="n">
+        <v>35800</v>
+      </c>
+      <c r="AT709" t="n">
+        <v>28640</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>格闘道場</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr"/>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AS710" t="n">
+        <v>980</v>
+      </c>
+      <c r="AT710" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>フシギバナex</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr"/>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS711" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT711" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>〔状態C〕ディアンシー(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS712" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AT712" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メロエッタ
+その他]</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr"/>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS713" t="n">
+        <v>930</v>
+      </c>
+      <c r="AT713" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>〔状態C〕ドーブル
+S11a]</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr"/>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS714" t="n">
+        <v>280</v>
+      </c>
+      <c r="AT714" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>〔状態C〕メガカイリューex
+M2a]</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr"/>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS715" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AT715" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルチャブル
+XY]</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS716" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT716" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>〔状態C〕アチャモ
+XY]</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr"/>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS717" t="n">
+        <v>680</v>
+      </c>
+      <c r="AT717" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>〔状態B〕エンペルト
+その他]</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr"/>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS718" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AT718" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>〔状態A-〕デデンネ(ポケモンパン)
+XY]</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS719" t="n">
+        <v>1230</v>
+      </c>
+      <c r="AT719" t="n">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゲッコウガ
+XY]</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr"/>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS720" t="n">
+        <v>3280</v>
+      </c>
+      <c r="AT720" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>〔状態C〕ダーテング
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr"/>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS721" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT721" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>〔状態C〕トウコ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr"/>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS722" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AT722" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>〔状態C〕エモンガ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr"/>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS723" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT723" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>〔状態B〕メタモン(韓国語版)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS724" t="n">
+        <v>6980</v>
+      </c>
+      <c r="AT724" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>〔状態B〕ワシボン
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS725" t="n">
+        <v>580</v>
+      </c>
+      <c r="AT725" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>〔状態A-〕モロバレル
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr"/>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS726" t="n">
+        <v>1090</v>
+      </c>
+      <c r="AT726" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>〔状態C〕ブリジュラスex
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr"/>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS727" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AT727" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>〔状態B〕フラージェスBREAK
+XY]</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr"/>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS728" t="n">
+        <v>880</v>
+      </c>
+      <c r="AT728" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヤトウモリ
+その他]</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr"/>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS729" t="n">
+        <v>260</v>
+      </c>
+      <c r="AT729" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>〔状態B〕ルカリオLV.X
+その他]</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS730" t="n">
+        <v>12800</v>
+      </c>
+      <c r="AT730" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>〔状態C〕イーブイ
+SV5a]</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS731" t="n">
+        <v>3280</v>
+      </c>
+      <c r="AT731" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レックウザδ-デルタ種(明治/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr"/>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS732" t="n">
+        <v>89800</v>
+      </c>
+      <c r="AT732" t="n">
+        <v>71840</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニャヒート
+その他]</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr"/>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS733" t="n">
+        <v>260</v>
+      </c>
+      <c r="AT733" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>〔状態C〕ナンジャモ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr"/>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS734" t="n">
+        <v>5980</v>
+      </c>
+      <c r="AT734" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼルネアス(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS735" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AT735" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ビクトリーカップ(バトルカーニバル2012スプリング・2位)
+その他]</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr"/>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS736" t="n">
+        <v>1780000</v>
+      </c>
+      <c r="AT736" t="n">
+        <v>1424000</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr"/>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS737" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AT737" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピッチのピカチュウ(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS738" t="n">
+        <v>288000</v>
+      </c>
+      <c r="AT738" t="n">
+        <v>230400</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>〔状態C〕シンボラー
+その他]</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS739" t="n">
+        <v>12800</v>
+      </c>
+      <c r="AT739" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>〔状態C〕ムゲンダイナV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr"/>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS740" t="n">
+        <v>420</v>
+      </c>
+      <c r="AT740" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピーニャ
+SV2P]</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr"/>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS741" t="n">
+        <v>990</v>
+      </c>
+      <c r="AT741" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>〔状態B〕デデンネex
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr"/>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS742" t="n">
+        <v>980</v>
+      </c>
+      <c r="AT742" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>〔状態B〕ライチュウ
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr"/>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS743" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AT743" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サルノリ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr"/>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS744" t="n">
+        <v>9900</v>
+      </c>
+      <c r="AT744" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スカル団ごっこピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr"/>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS745" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="AT745" t="n">
+        <v>864000</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウ(25th)
+S8a]</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr"/>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS746" t="n">
+        <v>17800</v>
+      </c>
+      <c r="AT746" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ツールスクラッパー
+その他]</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr"/>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS747" t="n">
+        <v>7280</v>
+      </c>
+      <c r="AT747" t="n">
+        <v>5824</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジムバッジ(サカキ キラ仕様)
+XY]</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr"/>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS748" t="n">
+        <v>11800</v>
+      </c>
+      <c r="AT748" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>〔状態C〕アルセウスV(SA/未開封)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr"/>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS749" t="n">
+        <v>980</v>
+      </c>
+      <c r="AT749" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メルメタルGX
+その他]</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS750" t="n">
+        <v>450</v>
+      </c>
+      <c r="AT750" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MギャラドスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr"/>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS751" t="n">
+        <v>11800</v>
+      </c>
+      <c r="AT751" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポンチョを着たイーブイ(EF/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr"/>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS752" t="n">
+        <v>118000</v>
+      </c>
+      <c r="AT752" t="n">
+        <v>94400</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>〔状態C〕ランクルス
+その他]</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr"/>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS753" t="n">
+        <v>11800</v>
+      </c>
+      <c r="AT753" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シェイミEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr"/>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS754" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AT754" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フライゴンGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr"/>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS755" t="n">
+        <v>1390</v>
+      </c>
+      <c r="AT755" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サーナイトEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr"/>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS756" t="n">
+        <v>2780</v>
+      </c>
+      <c r="AT756" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS757" t="n">
+        <v>9480</v>
+      </c>
+      <c r="AT757" t="n">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルカリオGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr"/>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS758" t="n">
+        <v>18300</v>
+      </c>
+      <c r="AT758" t="n">
+        <v>14640</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>〔状態A-〕無人発電所
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr"/>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS759" t="n">
+        <v>630</v>
+      </c>
+      <c r="AT759" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>〔状態B〕マルマイン
+S6K]</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr"/>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS760" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AT760" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヒメグマ
+その他]</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS761" t="n">
+        <v>790</v>
+      </c>
+      <c r="AT761" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>〔状態B〕バシャーモV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr"/>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS762" t="n">
+        <v>1790</v>
+      </c>
+      <c r="AT762" t="n">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ギャラドスごっこピカチュウ
+XY]</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS763" t="n">
+        <v>848000</v>
+      </c>
+      <c r="AT763" t="n">
+        <v>678400</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>〔状態B〕ボルケニオンV
+S6H]</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS764" t="n">
+        <v>280</v>
+      </c>
+      <c r="AT764" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>〔状態C〕サンダーex
+その他]</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS765" t="n">
+        <v>12800</v>
+      </c>
+      <c r="AT765" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゾロア
+その他]</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr"/>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS766" t="n">
+        <v>380</v>
+      </c>
+      <c r="AT766" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>〔状態B〕MバンギラスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS767" t="n">
+        <v>21800</v>
+      </c>
+      <c r="AT767" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>〔状態C〕イーブイ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS768" t="n">
+        <v>490</v>
+      </c>
+      <c r="AT768" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>〔状態B〕アーゴヨンGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr"/>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS769" t="n">
+        <v>680</v>
+      </c>
+      <c r="AT769" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>〔状態B〕アップリューV
+S5I]</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr"/>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS770" t="n">
+        <v>280</v>
+      </c>
+      <c r="AT770" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>〔状態C〕トゲデマル
+その他]</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS771" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AT771" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本超エネルギー(バトルカーニバル)
+その他]</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr"/>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS772" t="n">
+        <v>980</v>
+      </c>
+      <c r="AT772" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>〔状態C〕バクガメスGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr"/>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS773" t="n">
+        <v>980</v>
+      </c>
+      <c r="AT773" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>〔状態C〕オリーヴ
+S2]</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr"/>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS774" t="n">
+        <v>630</v>
+      </c>
+      <c r="AT774" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>〔状態C〕改造ハンマー
+XY]</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr"/>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS775" t="n">
+        <v>2190</v>
+      </c>
+      <c r="AT775" t="n">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヤーコン
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr"/>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS776" t="n">
+        <v>480</v>
+      </c>
+      <c r="AT776" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルガルガンGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr"/>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS777" t="n">
+        <v>880</v>
+      </c>
+      <c r="AT777" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミミッキュGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr"/>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS778" t="n">
+        <v>8480</v>
+      </c>
+      <c r="AT778" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本炎エネルギー(in 東京タワー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr"/>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS779" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AT779" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゲンガー＆ミミッキュGX
+sm9]</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr"/>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS780" t="n">
+        <v>19800</v>
+      </c>
+      <c r="AT780" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本炎エネルギー(チャンピオンズリーグ2020)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS781" t="n">
+        <v>380</v>
+      </c>
+      <c r="AT781" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>〔状態C〕ツインエネルギー
+s1a]</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr"/>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS782" t="n">
+        <v>680</v>
+      </c>
+      <c r="AT782" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr"/>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS783" t="n">
+        <v>34800</v>
+      </c>
+      <c r="AT783" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>〔状態B〕セキタンザン
+S3]</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr"/>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS784" t="n">
+        <v>590</v>
+      </c>
+      <c r="AT784" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本闘エネルギー(ジム応援キャンペーン ミラー)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr"/>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS785" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT785" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>〔状態B〕モルペコ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr"/>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS786" t="n">
+        <v>530</v>
+      </c>
+      <c r="AT786" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レックウザEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr"/>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS787" t="n">
+        <v>2480000</v>
+      </c>
+      <c r="AT787" t="n">
+        <v>1984000</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>〔状態C〕レックウザEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr"/>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS788" t="n">
+        <v>328000</v>
+      </c>
+      <c r="AT788" t="n">
+        <v>262400</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>〔状態B〕巨大なカマド
+sm12]</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr"/>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS789" t="n">
+        <v>380</v>
+      </c>
+      <c r="AT789" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼラオラ
+その他]</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr"/>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS790" t="n">
+        <v>980</v>
+      </c>
+      <c r="AT790" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本鋼エネルギー
+sm4]</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr"/>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS791" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AT791" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>〔状態B〕メガシャンデラex
+M5]</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr"/>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS792" t="n">
+        <v>2380</v>
+      </c>
+      <c r="AT792" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕イーブイGX(SA)</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr"/>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS793" t="n">
+        <v>104000</v>
+      </c>
+      <c r="AT793" t="n">
+        <v>83200</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕カトレア</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr"/>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS794" t="n">
+        <v>22800</v>
+      </c>
+      <c r="AT794" t="n">
+        <v>18240</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ツボツボGX</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr"/>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS795" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AT795" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕リーフィアVSTAR</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr"/>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS796" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AT796" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕パラス</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr"/>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS797" t="n">
+        <v>5980</v>
+      </c>
+      <c r="AT797" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕モクロー(ムンク)</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr"/>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS798" t="n">
+        <v>448000</v>
+      </c>
+      <c r="AT798" t="n">
+        <v>358400</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>〔BGS10鑑定済〕ウッウ</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr"/>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS799" t="n">
+        <v>19800</v>
+      </c>
+      <c r="AT799" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>セレビィ(未開封)</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr"/>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS800" t="n">
+        <v>19800</v>
+      </c>
+      <c r="AT800" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕メガリザードンXex</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr"/>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS801" t="n">
+        <v>7980</v>
+      </c>
+      <c r="AT801" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ホゲータ(中国語版)
+海外版]</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr"/>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS802" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AT802" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕レシラム(15周年)</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr"/>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS803" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="AT803" t="n">
+        <v>1024000</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>ファイヤー</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr"/>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS804" t="n">
+        <v>2580</v>
+      </c>
+      <c r="AT804" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕コダック</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr"/>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS805" t="n">
+        <v>19800</v>
+      </c>
+      <c r="AT805" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>タマザラシ</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr"/>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AS806" t="n">
+        <v>480</v>
+      </c>
+      <c r="AT806" t="n">
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV806"/>
+  <dimension ref="A1:AZ1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33418,6 +33418,26 @@
           <t>2026-06-13_diff</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2026-06-14_price</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2026-06-14_buy</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2026-06-14_ratio</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2026-06-14_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48146,7 +48166,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48171,7 +48190,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48196,7 +48214,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48221,7 +48238,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48246,7 +48262,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48271,7 +48286,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48296,7 +48310,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -48321,7 +48334,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr"/>
       <c r="D630" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48346,7 +48358,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48371,7 +48382,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr"/>
       <c r="D632" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48396,7 +48406,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48421,7 +48430,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48446,7 +48454,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48471,7 +48478,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48496,7 +48502,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48521,7 +48526,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48546,7 +48550,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48571,7 +48574,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48596,7 +48598,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48621,7 +48622,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48646,7 +48646,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48671,7 +48670,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48696,7 +48694,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48721,7 +48718,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48746,7 +48742,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48771,7 +48766,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48796,7 +48790,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48821,7 +48814,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48846,7 +48838,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48871,7 +48862,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48896,7 +48886,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48921,7 +48910,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48946,7 +48934,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48971,7 +48958,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -48996,7 +48982,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr"/>
       <c r="D657" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49021,7 +49006,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49046,7 +49030,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49071,7 +49054,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49096,7 +49078,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49121,7 +49102,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49146,7 +49126,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49171,7 +49150,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49196,7 +49174,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49221,7 +49198,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49246,7 +49222,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49271,7 +49246,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49296,7 +49270,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49321,7 +49294,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49346,7 +49318,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49371,7 +49342,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49395,7 +49365,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49419,7 +49388,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49443,7 +49411,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49467,7 +49434,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49491,7 +49457,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49515,7 +49480,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49539,7 +49503,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49563,7 +49526,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49587,7 +49549,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49611,7 +49572,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49635,7 +49595,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49659,7 +49618,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49683,7 +49641,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49707,7 +49664,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49731,7 +49687,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49756,7 +49711,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49780,7 +49734,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49804,7 +49757,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49828,7 +49780,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49852,7 +49803,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49876,7 +49826,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr"/>
       <c r="D693" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49900,7 +49849,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr"/>
       <c r="D694" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49924,7 +49872,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr"/>
       <c r="D695" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49948,7 +49895,6 @@
           <t>MA</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr"/>
       <c r="D696" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49972,7 +49918,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -49996,7 +49941,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50020,7 +49964,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50044,7 +49987,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr"/>
       <c r="D700" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50068,7 +50010,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr"/>
       <c r="D701" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50092,7 +50033,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr"/>
       <c r="D702" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50116,7 +50056,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr"/>
       <c r="D703" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50140,7 +50079,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr"/>
       <c r="D704" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50164,7 +50102,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50188,7 +50125,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr"/>
       <c r="D706" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50212,7 +50148,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50236,7 +50171,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr"/>
       <c r="D708" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50260,7 +50194,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr"/>
       <c r="D709" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50284,7 +50217,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -50308,7 +50240,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr"/>
       <c r="D711" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50333,7 +50264,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr"/>
       <c r="D712" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50358,7 +50288,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50383,7 +50312,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50408,7 +50336,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50433,7 +50360,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50458,7 +50384,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50483,7 +50408,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50508,7 +50432,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50533,7 +50456,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50558,7 +50480,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50583,7 +50504,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50608,7 +50528,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50633,7 +50552,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50658,7 +50576,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50683,7 +50600,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50708,7 +50624,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50733,7 +50648,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50758,7 +50672,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50783,7 +50696,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50808,7 +50720,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50833,7 +50744,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr"/>
       <c r="D732" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50858,7 +50768,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50883,7 +50792,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50908,7 +50816,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50933,7 +50840,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50958,7 +50864,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -50983,7 +50888,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51008,7 +50912,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51033,7 +50936,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51058,7 +50960,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51083,7 +50984,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51108,7 +51008,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51133,7 +51032,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51158,7 +51056,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51183,7 +51080,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51208,7 +51104,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51233,7 +51128,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51258,7 +51152,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51283,7 +51176,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr"/>
       <c r="D750" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51308,7 +51200,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51333,7 +51224,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51358,7 +51248,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51383,7 +51272,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51408,7 +51296,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51433,7 +51320,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51458,7 +51344,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51483,7 +51368,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51508,7 +51392,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51533,7 +51416,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51558,7 +51440,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr"/>
       <c r="D761" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51583,7 +51464,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51608,7 +51488,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51633,7 +51512,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51658,7 +51536,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51683,7 +51560,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51708,7 +51584,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51733,7 +51608,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51758,7 +51632,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr"/>
       <c r="D769" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51783,7 +51656,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr"/>
       <c r="D770" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51808,7 +51680,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51833,7 +51704,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr"/>
       <c r="D772" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51858,7 +51728,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51883,7 +51752,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr"/>
       <c r="D774" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51908,7 +51776,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr"/>
       <c r="D775" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51933,7 +51800,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr"/>
       <c r="D776" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51958,7 +51824,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr"/>
       <c r="D777" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -51983,7 +51848,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr"/>
       <c r="D778" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52008,7 +51872,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr"/>
       <c r="D779" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52033,7 +51896,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr"/>
       <c r="D780" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52058,7 +51920,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr"/>
       <c r="D781" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52083,7 +51944,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr"/>
       <c r="D782" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52108,7 +51968,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr"/>
       <c r="D783" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52133,7 +51992,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr"/>
       <c r="D784" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52158,7 +52016,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr"/>
       <c r="D785" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52183,7 +52040,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr"/>
       <c r="D786" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52208,7 +52064,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr"/>
       <c r="D787" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52233,7 +52088,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr"/>
       <c r="D788" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52258,7 +52112,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52283,7 +52136,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr"/>
       <c r="D790" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52308,7 +52160,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr"/>
       <c r="D791" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52333,7 +52184,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr"/>
       <c r="D792" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52357,7 +52207,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr"/>
       <c r="D793" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52381,7 +52230,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr"/>
       <c r="D794" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52405,7 +52253,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr"/>
       <c r="D795" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52429,7 +52276,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr"/>
       <c r="D796" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52453,7 +52299,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52477,7 +52322,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52501,7 +52345,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52525,7 +52368,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52549,7 +52391,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52574,7 +52415,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52598,7 +52438,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52622,7 +52461,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52646,7 +52484,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52670,7 +52507,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -52681,6 +52517,5791 @@
       </c>
       <c r="AT806" t="n">
         <v>384</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>ストリンダー</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr"/>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW807" t="n">
+        <v>580</v>
+      </c>
+      <c r="AX807" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>〔状態B〕MガルーラEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr"/>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW808" t="n">
+        <v>2490</v>
+      </c>
+      <c r="AX808" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポッチャマ
+M2]</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr"/>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW809" t="n">
+        <v>730</v>
+      </c>
+      <c r="AX809" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テッシード
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr"/>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW810" t="n">
+        <v>830</v>
+      </c>
+      <c r="AX810" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ムーランド
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr"/>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW811" t="n">
+        <v>930</v>
+      </c>
+      <c r="AX811" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ズルッグ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr"/>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW812" t="n">
+        <v>990</v>
+      </c>
+      <c r="AX812" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>〔状態B〕ロケット団のクロバットex
+SV10]</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr"/>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW813" t="n">
+        <v>880</v>
+      </c>
+      <c r="AX813" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ペパーのマフィティフex
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr"/>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW814" t="n">
+        <v>2250</v>
+      </c>
+      <c r="AX814" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リーリエのピッピex
+SV9]</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr"/>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW815" t="n">
+        <v>31800</v>
+      </c>
+      <c r="AX815" t="n">
+        <v>25440</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アローラナッシーex
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr"/>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW816" t="n">
+        <v>2780</v>
+      </c>
+      <c r="AX816" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>〔状態C〕ポケパークのセレビィ
+その他]</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW817" t="n">
+        <v>4990</v>
+      </c>
+      <c r="AX817" t="n">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テラパゴスex
+SV7]</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr"/>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW818" t="n">
+        <v>730</v>
+      </c>
+      <c r="AX818" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テツノイサハex
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW819" t="n">
+        <v>390</v>
+      </c>
+      <c r="AX819" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キラフロルex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr"/>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW820" t="n">
+        <v>260</v>
+      </c>
+      <c r="AX820" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リザードンex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW821" t="n">
+        <v>47800</v>
+      </c>
+      <c r="AX821" t="n">
+        <v>38240</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>〔状態B〕イーブイ(YU NAGABA)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr"/>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW822" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AX822" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フシギバナex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr"/>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW823" t="n">
+        <v>330</v>
+      </c>
+      <c r="AX823" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヨクバリスVMAX
+S8]</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr"/>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW824" t="n">
+        <v>260</v>
+      </c>
+      <c r="AX824" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウツーVSTAR
+S10b]</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr"/>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW825" t="n">
+        <v>5480</v>
+      </c>
+      <c r="AX825" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラウドボーンex
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr"/>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW826" t="n">
+        <v>680</v>
+      </c>
+      <c r="AX826" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>〔状態B〕サーナイトex
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr"/>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW827" t="n">
+        <v>580</v>
+      </c>
+      <c r="AX827" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガラルニャイキング
+s4a]</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr"/>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW828" t="n">
+        <v>330</v>
+      </c>
+      <c r="AX828" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>〔状態A-〕デオキシス
+S12a]</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr"/>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW829" t="n">
+        <v>1680</v>
+      </c>
+      <c r="AX829" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガターボ
+XY]</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr"/>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW830" t="n">
+        <v>2080</v>
+      </c>
+      <c r="AX830" t="n">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>〔状態B〕セレナ
+S11a]</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr"/>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW831" t="n">
+        <v>1880</v>
+      </c>
+      <c r="AX831" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メッソン
+s4a]</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr"/>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW832" t="n">
+        <v>230</v>
+      </c>
+      <c r="AX832" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MヤドランEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr"/>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW833" t="n">
+        <v>14300</v>
+      </c>
+      <c r="AX833" t="n">
+        <v>11440</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エルフーンGX
+sm10]</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr"/>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW834" t="n">
+        <v>1230</v>
+      </c>
+      <c r="AX834" t="n">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>〔状態B〕ルガルガンGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr"/>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW835" t="n">
+        <v>6480</v>
+      </c>
+      <c r="AX835" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジュラルドンVMAX
+S7D]</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr"/>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW836" t="n">
+        <v>730</v>
+      </c>
+      <c r="AX836" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニンフィアV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr"/>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW837" t="n">
+        <v>7280</v>
+      </c>
+      <c r="AX837" t="n">
+        <v>5824</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カキ
+sm3]</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr"/>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW838" t="n">
+        <v>4980</v>
+      </c>
+      <c r="AX838" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リザードン＆テールナーGX
+sm11a]</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr"/>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW839" t="n">
+        <v>14300</v>
+      </c>
+      <c r="AX839" t="n">
+        <v>11440</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr"/>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW840" t="n">
+        <v>3290</v>
+      </c>
+      <c r="AX840" t="n">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒスイダイケンキV
+S9a]</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr"/>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW841" t="n">
+        <v>330</v>
+      </c>
+      <c r="AX841" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラパルトV
+s4a]</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr"/>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW842" t="n">
+        <v>330</v>
+      </c>
+      <c r="AX842" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アーゴヨン＆アクジキングGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr"/>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW843" t="n">
+        <v>1680</v>
+      </c>
+      <c r="AX843" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スクールボーイ
+S7R]</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr"/>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW844" t="n">
+        <v>450</v>
+      </c>
+      <c r="AX844" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>〔状態B〕ネオラントV
+S9]</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr"/>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW845" t="n">
+        <v>320</v>
+      </c>
+      <c r="AX845" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>〔状態B〕そらをとぶピカチュウVMAX(25th)
+S8a]</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr"/>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW846" t="n">
+        <v>1590</v>
+      </c>
+      <c r="AX846" t="n">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケパークのピカチュウ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr"/>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW847" t="n">
+        <v>198000</v>
+      </c>
+      <c r="AX847" t="n">
+        <v>158400</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>〔状態B〕ギャラドスGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr"/>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW848" t="n">
+        <v>17800</v>
+      </c>
+      <c r="AX848" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>〔状態B〕ずがいの化石(キラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW849" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AX849" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本水エネルギー(LAWSON/ミラー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr"/>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW850" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AX850" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本雷エネルギー(in 東京タワー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr"/>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW851" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AX851" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>〔状態C〕カツラの一発勝負
+sm6]</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr"/>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW852" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AX852" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>〔状態C〕グラードンEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr"/>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW853" t="n">
+        <v>34800</v>
+      </c>
+      <c r="AX853" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本草エネルギー(チャンピオンズリーグ2020)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr"/>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW854" t="n">
+        <v>480</v>
+      </c>
+      <c r="AX854" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>〔状態B〕ケンタロスGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr"/>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW855" t="n">
+        <v>2380</v>
+      </c>
+      <c r="AX855" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>〔状態B〕フーパGX
+sm8]</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr"/>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW856" t="n">
+        <v>980</v>
+      </c>
+      <c r="AX856" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>〔状態B〕オーロット＆ヨノワールGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW857" t="n">
+        <v>780</v>
+      </c>
+      <c r="AX857" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>〔状態B〕お公家さまと舞妓はんピカチュウ
+XY]</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr"/>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW858" t="n">
+        <v>89800</v>
+      </c>
+      <c r="AX858" t="n">
+        <v>71840</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガスターミーex
+M3]</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW859" t="n">
+        <v>730</v>
+      </c>
+      <c r="AX859" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フォッコ
+M4]</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr"/>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW860" t="n">
+        <v>630</v>
+      </c>
+      <c r="AX860" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テッカニン
+M1S]</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr"/>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW861" t="n">
+        <v>260</v>
+      </c>
+      <c r="AX861" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>メガヤンマex</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr"/>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW862" t="n">
+        <v>480</v>
+      </c>
+      <c r="AX862" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>ハネッコ</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr"/>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW863" t="n">
+        <v>480</v>
+      </c>
+      <c r="AX863" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>ヒメンカ</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr"/>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW864" t="n">
+        <v>280</v>
+      </c>
+      <c r="AX864" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>フシギバナ＆ツタージャGX(SA)</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr"/>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW865" t="n">
+        <v>18800</v>
+      </c>
+      <c r="AX865" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>レシラム＆リザードンGX</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr"/>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW866" t="n">
+        <v>5980</v>
+      </c>
+      <c r="AX866" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕カメックス＆ポッチャマGX</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr"/>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW867" t="n">
+        <v>32800</v>
+      </c>
+      <c r="AX867" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>セゴール</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr"/>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW868" t="n">
+        <v>280</v>
+      </c>
+      <c r="AX868" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>オリジンパルキアVSTAR</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr"/>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW869" t="n">
+        <v>14800</v>
+      </c>
+      <c r="AX869" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>メッソン</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr"/>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW870" t="n">
+        <v>380</v>
+      </c>
+      <c r="AX870" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕名探偵ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr"/>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW871" t="n">
+        <v>64800</v>
+      </c>
+      <c r="AX871" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr"/>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW872" t="n">
+        <v>12800</v>
+      </c>
+      <c r="AX872" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>いたずら好きのピチュー(未開封)</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr"/>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW873" t="n">
+        <v>4980</v>
+      </c>
+      <c r="AX873" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>サンダースV</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr"/>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW874" t="n">
+        <v>380</v>
+      </c>
+      <c r="AX874" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>モルペコVMAX</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr"/>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW875" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AX875" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>〔CGC10鑑定済〕ミュウツーGX(SR仕様)</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr"/>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW876" t="n">
+        <v>428000</v>
+      </c>
+      <c r="AX876" t="n">
+        <v>342400</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>ザシアンV</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr"/>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW877" t="n">
+        <v>2280</v>
+      </c>
+      <c r="AX877" t="n">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>〔状態B〕リオル
+M1L]</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr"/>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW878" t="n">
+        <v>580</v>
+      </c>
+      <c r="AX878" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>ワルビアル</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr"/>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW879" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AX879" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>キチキギスex</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr"/>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW880" t="n">
+        <v>2780</v>
+      </c>
+      <c r="AX880" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA9鑑定済〕ギラティナV(SA)</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr"/>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW881" t="n">
+        <v>194000</v>
+      </c>
+      <c r="AX881" t="n">
+        <v>155200</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>オリジンディアルガVSTAR</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr"/>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW882" t="n">
+        <v>2180</v>
+      </c>
+      <c r="AX882" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>オンバーンex</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr"/>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW883" t="n">
+        <v>480</v>
+      </c>
+      <c r="AX883" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>ハトーボー</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr"/>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW884" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AX884" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>ポケパッド</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr"/>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW885" t="n">
+        <v>980</v>
+      </c>
+      <c r="AX885" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>バトルコンプレッサー フレア団ギア</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr"/>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW886" t="n">
+        <v>1380</v>
+      </c>
+      <c r="AX886" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>基本鋼エネルギー(ファーストデザインキラ)</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr"/>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW887" t="n">
+        <v>138000</v>
+      </c>
+      <c r="AX887" t="n">
+        <v>110400</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>基本炎エネルギー(ファーストデザイン)</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr"/>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW888" t="n">
+        <v>980</v>
+      </c>
+      <c r="AX888" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕カナリィ</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr"/>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW889" t="n">
+        <v>6480</v>
+      </c>
+      <c r="AX889" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>暗号マニアの解読</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr"/>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW890" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AX890" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕キハダ</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr"/>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW891" t="n">
+        <v>22800</v>
+      </c>
+      <c r="AX891" t="n">
+        <v>18240</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>スズナ</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr"/>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW892" t="n">
+        <v>2380</v>
+      </c>
+      <c r="AX892" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>セキ</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr"/>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW893" t="n">
+        <v>480</v>
+      </c>
+      <c r="AX893" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>ソッドとシルディ</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr"/>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW894" t="n">
+        <v>680</v>
+      </c>
+      <c r="AX894" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>メロン</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr"/>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW895" t="n">
+        <v>680</v>
+      </c>
+      <c r="AX895" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>マオ＆スイレン</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr"/>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW896" t="n">
+        <v>22800</v>
+      </c>
+      <c r="AX896" t="n">
+        <v>18240</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>カスミ＆カンナ</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr"/>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW897" t="n">
+        <v>49800</v>
+      </c>
+      <c r="AX897" t="n">
+        <v>39840</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>タケシのガッツ</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr"/>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW898" t="n">
+        <v>21800</v>
+      </c>
+      <c r="AX898" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>メイのはげまし</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr"/>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="AW899" t="n">
+        <v>18800</v>
+      </c>
+      <c r="AX899" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>〔状態B〕パラレルシティ
+M-P]</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr"/>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW900" t="n">
+        <v>880</v>
+      </c>
+      <c r="AX900" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>〔状態C〕ニャースex
+M3]</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr"/>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW901" t="n">
+        <v>7980</v>
+      </c>
+      <c r="AX901" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジャッジマン
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr"/>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW902" t="n">
+        <v>380</v>
+      </c>
+      <c r="AX902" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジムバッジ(トウキ)
+XY]</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr"/>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW903" t="n">
+        <v>380</v>
+      </c>
+      <c r="AX903" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ズルズキン
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr"/>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW904" t="n">
+        <v>350</v>
+      </c>
+      <c r="AX904" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>〔状態C〕メガカイリューex
+M2a]</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>MUR</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr"/>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW905" t="n">
+        <v>23800</v>
+      </c>
+      <c r="AX905" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>〔状態C〕グラードン
+XY]</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr"/>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW906" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AX906" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>〔状態B〕オノノクス
+その他]</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr"/>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW907" t="n">
+        <v>980</v>
+      </c>
+      <c r="AX907" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガゲンガーex(※表面加工エラー)
+M2a]</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr"/>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW908" t="n">
+        <v>44800</v>
+      </c>
+      <c r="AX908" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>〔状態C〕ロケット団のクロバットex
+SV10]</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr"/>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW909" t="n">
+        <v>580</v>
+      </c>
+      <c r="AX909" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>〔状態C〕リオル(マクドナルド)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr"/>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW910" t="n">
+        <v>280</v>
+      </c>
+      <c r="AX910" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エレズン
+M-P]</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr"/>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW911" t="n">
+        <v>250</v>
+      </c>
+      <c r="AX911" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドレディア
+その他]</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr"/>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW912" t="n">
+        <v>1090</v>
+      </c>
+      <c r="AX912" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウ(ファミリーマート/台湾限定)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr"/>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW913" t="n">
+        <v>2480</v>
+      </c>
+      <c r="AX913" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>〔状態C〕イーブイ
+その他]</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr"/>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW914" t="n">
+        <v>3280</v>
+      </c>
+      <c r="AX914" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>〔状態B〕ココロモリ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr"/>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW915" t="n">
+        <v>680</v>
+      </c>
+      <c r="AX915" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>〔状態B〕ケンホロウ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr"/>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW916" t="n">
+        <v>680</v>
+      </c>
+      <c r="AX916" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ダストダス
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr"/>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW917" t="n">
+        <v>250</v>
+      </c>
+      <c r="AX917" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>〔状態C〕クレセリア
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr"/>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW918" t="n">
+        <v>320</v>
+      </c>
+      <c r="AX918" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グラードンex
+その他]</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr"/>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW919" t="n">
+        <v>20300</v>
+      </c>
+      <c r="AX919" t="n">
+        <v>16240</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>〔状態A-〕かるいし
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr"/>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW920" t="n">
+        <v>830</v>
+      </c>
+      <c r="AX920" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヨコハマのピカチュウ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr"/>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW921" t="n">
+        <v>198000</v>
+      </c>
+      <c r="AX921" t="n">
+        <v>158400</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>〔状態B〕カイリキーGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr"/>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW922" t="n">
+        <v>780</v>
+      </c>
+      <c r="AX922" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>〔状態C〕キュウコンBREAK
+CP6]</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr"/>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW923" t="n">
+        <v>3280</v>
+      </c>
+      <c r="AX923" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>〔状態C〕シキミ
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr"/>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW924" t="n">
+        <v>220</v>
+      </c>
+      <c r="AX924" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トドロクツキex
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr"/>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW925" t="n">
+        <v>260</v>
+      </c>
+      <c r="AX925" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>〔状態C〕すごいつりざお
+SV2P]</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr"/>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW926" t="n">
+        <v>690</v>
+      </c>
+      <c r="AX926" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>〔状態C〕レシラムV
+S11a]</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr"/>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW927" t="n">
+        <v>330</v>
+      </c>
+      <c r="AX927" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>〔状態C〕スター団のしたっぱ
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr"/>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW928" t="n">
+        <v>220</v>
+      </c>
+      <c r="AX928" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>〔状態C〕シャンデラ
+S9a]</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr"/>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW929" t="n">
+        <v>280</v>
+      </c>
+      <c r="AX929" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヒスイオオニューラV
+S10P]</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr"/>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW930" t="n">
+        <v>280</v>
+      </c>
+      <c r="AX930" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>〔状態C〕カイリキーV(SA)
+S10D]</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr"/>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW931" t="n">
+        <v>5980</v>
+      </c>
+      <c r="AX931" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>〔状態C〕ローブシンV(SA)
+S10b]</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr"/>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW932" t="n">
+        <v>380</v>
+      </c>
+      <c r="AX932" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>〔状態B〕ウェーニバルex
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr"/>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW933" t="n">
+        <v>2380</v>
+      </c>
+      <c r="AX933" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルギアV
+S12]</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr"/>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW934" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AX934" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パオジアンex
+SV2P]</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr"/>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW935" t="n">
+        <v>260</v>
+      </c>
+      <c r="AX935" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トレーナーズポスト
+S-P]</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr"/>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW936" t="n">
+        <v>830</v>
+      </c>
+      <c r="AX936" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジニア
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr"/>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW937" t="n">
+        <v>990</v>
+      </c>
+      <c r="AX937" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゾロアーク
+その他]</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr"/>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW938" t="n">
+        <v>330</v>
+      </c>
+      <c r="AX938" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポリゴンZ
+その他]</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr"/>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW939" t="n">
+        <v>330</v>
+      </c>
+      <c r="AX939" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>〔状態A-〕博士の研究/マグノリア博士
+S-P]</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr"/>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW940" t="n">
+        <v>990</v>
+      </c>
+      <c r="AX940" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アローラロコンV
+S11a]</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr"/>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW941" t="n">
+        <v>490</v>
+      </c>
+      <c r="AX941" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヒスイバクフーンV
+S9a]</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr"/>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW942" t="n">
+        <v>320</v>
+      </c>
+      <c r="AX942" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジャローダ
+その他]</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr"/>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW943" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AX943" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポンチョを着たピカチュウ
+XY]</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr"/>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW944" t="n">
+        <v>468000</v>
+      </c>
+      <c r="AX944" t="n">
+        <v>374400</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロトム図鑑
+sm1]</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr"/>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW945" t="n">
+        <v>5780</v>
+      </c>
+      <c r="AX945" t="n">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グズマ
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr"/>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW946" t="n">
+        <v>5780</v>
+      </c>
+      <c r="AX946" t="n">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本鋼エネルギー(ジム応援キャンペーン ミラー)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr"/>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW947" t="n">
+        <v>530</v>
+      </c>
+      <c r="AX947" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ(YU NAGABA)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr"/>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW948" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AX948" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr"/>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW949" t="n">
+        <v>9480</v>
+      </c>
+      <c r="AX949" t="n">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr"/>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW950" t="n">
+        <v>4180</v>
+      </c>
+      <c r="AX950" t="n">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ボルケニオンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr"/>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW951" t="n">
+        <v>9990</v>
+      </c>
+      <c r="AX951" t="n">
+        <v>7992</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジュジュベ＆ハチクマン
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr"/>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW952" t="n">
+        <v>3080</v>
+      </c>
+      <c r="AX952" t="n">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カラマネロVMAX
+S2]</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr"/>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW953" t="n">
+        <v>680</v>
+      </c>
+      <c r="AX953" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジムバッジ(ミクリ)
+XY]</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr"/>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW954" t="n">
+        <v>2480</v>
+      </c>
+      <c r="AX954" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>〔状態B〕ユウリ
+S8b]</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr"/>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW955" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AX955" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ(封筒付き)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr"/>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW956" t="n">
+        <v>44800</v>
+      </c>
+      <c r="AX956" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーEX(20thアニバーサリー)
+XY]</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr"/>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW957" t="n">
+        <v>798000</v>
+      </c>
+      <c r="AX957" t="n">
+        <v>638400</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>〔状態B〕エンニュートGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr"/>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW958" t="n">
+        <v>320</v>
+      </c>
+      <c r="AX958" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>〔状態B〕カリン
+XY]</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr"/>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW959" t="n">
+        <v>2480</v>
+      </c>
+      <c r="AX959" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>〔状態B〕とりかえっこプリーズ!
+XY]</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr"/>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW960" t="n">
+        <v>9480</v>
+      </c>
+      <c r="AX960" t="n">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr"/>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW961" t="n">
+        <v>21800</v>
+      </c>
+      <c r="AX961" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>〔状態C〕フーパ
+XY]</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr"/>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW962" t="n">
+        <v>3990</v>
+      </c>
+      <c r="AX962" t="n">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>〔状態B〕モルペコ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr"/>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW963" t="n">
+        <v>590</v>
+      </c>
+      <c r="AX963" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウ(古代文字2020韓国)
+その他]</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr"/>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW964" t="n">
+        <v>7980</v>
+      </c>
+      <c r="AX964" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>〔状態B〕アローラロコン
+その他]</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr"/>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW965" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AX965" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>〔状態C〕カミツルギGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr"/>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW966" t="n">
+        <v>380</v>
+      </c>
+      <c r="AX966" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>〔状態C〕フェローチェ＆マッシブーンGX
+SM9b]</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr"/>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW967" t="n">
+        <v>880</v>
+      </c>
+      <c r="AX967" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>〔状態C〕フレア団のしたっぱ(Pokemon Game Show)
+XY]</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr"/>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW968" t="n">
+        <v>990</v>
+      </c>
+      <c r="AX968" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>〔状態C〕オーキド博士のセッティング
+sm11a]</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr"/>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW969" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AX969" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>〔状態C〕リザード
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr"/>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW970" t="n">
+        <v>780</v>
+      </c>
+      <c r="AX970" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>〔状態C〕クチートGX
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr"/>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW971" t="n">
+        <v>690</v>
+      </c>
+      <c r="AX971" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>〔状態C〕ビッグパラソル
+S2a]</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr"/>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW972" t="n">
+        <v>490</v>
+      </c>
+      <c r="AX972" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>〔状態C〕ムゲンダイナVMAX
+S3]</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr"/>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW973" t="n">
+        <v>580</v>
+      </c>
+      <c r="AX973" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>〔状態C〕アルセウス＆ディアルガ＆パルキアGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr"/>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW974" t="n">
+        <v>6480</v>
+      </c>
+      <c r="AX974" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルナアーラGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr"/>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW975" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AX975" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジラーチ
+XY]</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr"/>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW976" t="n">
+        <v>79800</v>
+      </c>
+      <c r="AX976" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>〔状態C〕フウロ(SR仕様)
+XY]</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr"/>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW977" t="n">
+        <v>49800</v>
+      </c>
+      <c r="AX977" t="n">
+        <v>39840</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ(gogotake)
+XY]</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr"/>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW978" t="n">
+        <v>59800</v>
+      </c>
+      <c r="AX978" t="n">
+        <v>47840</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>〔状態B〕タフネスマント
+s3a]</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr"/>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW979" t="n">
+        <v>380</v>
+      </c>
+      <c r="AX979" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>〔状態B〕バリヤードGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr"/>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW980" t="n">
+        <v>420</v>
+      </c>
+      <c r="AX980" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>〔状態B〕イーブイ
+その他]</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr"/>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW981" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AX981" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>〔状態B〕アローラキュウコンGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr"/>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW982" t="n">
+        <v>4780</v>
+      </c>
+      <c r="AX982" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>〔状態B〕イエッサンV
+s1]</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr"/>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW983" t="n">
+        <v>280</v>
+      </c>
+      <c r="AX983" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ(バトルフェスタ2014)
+XY]</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr"/>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW984" t="n">
+        <v>348000</v>
+      </c>
+      <c r="AX984" t="n">
+        <v>278400</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本超エネルギー(ストライプ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr"/>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW985" t="n">
+        <v>1780</v>
+      </c>
+      <c r="AX985" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>〔状態C〕ランプラー
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr"/>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW986" t="n">
+        <v>380</v>
+      </c>
+      <c r="AX986" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラッタ
+M3]</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr"/>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW987" t="n">
+        <v>280</v>
+      </c>
+      <c r="AX987" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プリズムタワー
+M4]</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr"/>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW988" t="n">
+        <v>350</v>
+      </c>
+      <c r="AX988" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ケルディオex</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr"/>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW989" t="n">
+        <v>5480</v>
+      </c>
+      <c r="AX989" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>CHAMPIONS FESTIVAL 2014(3枚セット)</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr"/>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW990" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="AX990" t="n">
+        <v>864000</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕リーフィアGX</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr"/>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW991" t="n">
+        <v>35800</v>
+      </c>
+      <c r="AX991" t="n">
+        <v>28640</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ツボツボGX</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr"/>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW992" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AX992" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕MフシギバナEX</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr"/>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW993" t="n">
+        <v>29800</v>
+      </c>
+      <c r="AX993" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>カメックスEX</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr"/>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW994" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AX994" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>ジュカイン</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr"/>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW995" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AX995" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA9鑑定済〕レシラム</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr"/>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW996" t="n">
+        <v>57800</v>
+      </c>
+      <c r="AX996" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>シシコ</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr"/>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW997" t="n">
+        <v>380</v>
+      </c>
+      <c r="AX997" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ミュウδ-デルタ種</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr"/>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW998" t="n">
+        <v>79800</v>
+      </c>
+      <c r="AX998" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕レシラム(15周年)</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr"/>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW999" t="n">
+        <v>348000</v>
+      </c>
+      <c r="AX999" t="n">
+        <v>278400</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>レシラム(15周年)</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr"/>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1000" t="n">
+        <v>548000</v>
+      </c>
+      <c r="AX1000" t="n">
+        <v>438400</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>リザードンGX</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr"/>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1001" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AX1001" t="n">
+        <v>118400</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕グレイシアLv.46</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr"/>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1002" t="n">
+        <v>29800</v>
+      </c>
+      <c r="AX1002" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>ゲッコウガex(SAR仕様/英語版)</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr"/>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1003" t="n">
+        <v>24800</v>
+      </c>
+      <c r="AX1003" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ユキカブリ
+M1S]</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr"/>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1004" t="n">
+        <v>260</v>
+      </c>
+      <c r="AX1004" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ヤドン＆コダックGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr"/>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1005" t="n">
+        <v>29800</v>
+      </c>
+      <c r="AX1005" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕カジリガメVMAX</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr"/>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1006" t="n">
+        <v>3480</v>
+      </c>
+      <c r="AX1006" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕コソクムシ</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr"/>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1007" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AX1007" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ゼニガメ(マクドナルド)</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr"/>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1008" t="n">
+        <v>62800</v>
+      </c>
+      <c r="AX1008" t="n">
+        <v>50240</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ポッチャマ</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr"/>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1009" t="n">
+        <v>9980</v>
+      </c>
+      <c r="AX1009" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>シャワーズEX(未開封)</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr"/>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1010" t="n">
+        <v>21800</v>
+      </c>
+      <c r="AX1010" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>ケルディオEX</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr"/>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1011" t="n">
+        <v>19800</v>
+      </c>
+      <c r="AX1011" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ピカチュウV(s4)</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr"/>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1012" t="n">
+        <v>6980</v>
+      </c>
+      <c r="AX1012" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA9鑑定済〕ピカチュウ(中国語版)</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr"/>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1013" t="n">
+        <v>34800</v>
+      </c>
+      <c r="AX1013" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ボスごっこピカチュウ ロケット団</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr"/>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1014" t="n">
+        <v>628000</v>
+      </c>
+      <c r="AX1014" t="n">
+        <v>502400</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ゼクロムex</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr"/>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1015" t="n">
+        <v>47800</v>
+      </c>
+      <c r="AX1015" t="n">
+        <v>38240</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>〔LGS9.5鑑定済〕ピカチュウ(SR仕様)</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr"/>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1016" t="n">
+        <v>99800</v>
+      </c>
+      <c r="AX1016" t="n">
+        <v>79840</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>〔PSA8鑑定済〕ピカチュウ(1ED)</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr"/>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1017" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AX1017" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>〔PSA5鑑定済〕メガトウキョーのピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr"/>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1018" t="n">
+        <v>79800</v>
+      </c>
+      <c r="AX1018" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ピカチュウ(バトルフェスタ2015)</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr"/>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1019" t="n">
+        <v>658000</v>
+      </c>
+      <c r="AX1019" t="n">
+        <v>526400</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>ピチュー(マクドナルド)</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr"/>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1020" t="n">
+        <v>12800</v>
+      </c>
+      <c r="AX1020" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>パモ</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr"/>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1021" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AX1021" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>アローラライチュウ</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr"/>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1022" t="n">
+        <v>980</v>
+      </c>
+      <c r="AX1022" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>ピカチュウ＆ゼクロムGX</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr"/>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1023" t="n">
+        <v>6480</v>
+      </c>
+      <c r="AX1023" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕マーシャドー＆カイリキーGX</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr"/>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1024" t="n">
+        <v>2480</v>
+      </c>
+      <c r="AX1024" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>リグレー</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr"/>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1025" t="n">
+        <v>780</v>
+      </c>
+      <c r="AX1025" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>サーナイト(未開封)</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr"/>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1026" t="n">
+        <v>4980</v>
+      </c>
+      <c r="AX1026" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>ニャオニクスEX(未開封)</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr"/>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1027" t="n">
+        <v>2780</v>
+      </c>
+      <c r="AX1027" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ナカヌチャン</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr"/>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1028" t="n">
+        <v>3780</v>
+      </c>
+      <c r="AX1028" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ミュウツーEX</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr"/>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1029" t="n">
+        <v>34800</v>
+      </c>
+      <c r="AX1029" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ヤドキング(グレート)</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr"/>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1030" t="n">
+        <v>79800</v>
+      </c>
+      <c r="AX1030" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕キルリア</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr"/>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1031" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AX1031" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>〔ARS10+鑑定済〕サーナイトex</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr"/>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1032" t="n">
+        <v>29800</v>
+      </c>
+      <c r="AX1032" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ミュウツーV(SA)</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr"/>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1033" t="n">
+        <v>5980</v>
+      </c>
+      <c r="AX1033" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>エーフィVMAX(SA)</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr"/>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1034" t="n">
+        <v>52800</v>
+      </c>
+      <c r="AX1034" t="n">
+        <v>42240</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>カプ・テテフGX</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr"/>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1035" t="n">
+        <v>480</v>
+      </c>
+      <c r="AX1035" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>グラードン</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr"/>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1036" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AX1036" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>〔BGS10鑑定済〕ドンファン(25th)</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr"/>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1037" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AX1037" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ゲンシグラードンEX</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr"/>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1038" t="n">
+        <v>59800</v>
+      </c>
+      <c r="AX1038" t="n">
+        <v>47840</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>ゲッコウガ☆(英語版)</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr"/>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1039" t="n">
+        <v>5980</v>
+      </c>
+      <c r="AX1039" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>ペンドラー</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr"/>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1040" t="n">
+        <v>880</v>
+      </c>
+      <c r="AX1040" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕リザードンex</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr"/>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="AW1041" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AX1041" t="n">
+        <v>3184</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1041"/>
+  <dimension ref="A1:BD1215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33438,6 +33438,26 @@
           <t>2026-06-14_diff</t>
         </is>
       </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2026-06-15_price</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2026-06-15_buy</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2026-06-15_ratio</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2026-06-15_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -52530,7 +52550,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52555,7 +52574,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52580,7 +52598,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52605,7 +52622,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52630,7 +52646,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52655,7 +52670,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C812" t="inlineStr"/>
       <c r="D812" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52680,7 +52694,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C813" t="inlineStr"/>
       <c r="D813" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52705,7 +52718,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C814" t="inlineStr"/>
       <c r="D814" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52730,7 +52742,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C815" t="inlineStr"/>
       <c r="D815" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52755,7 +52766,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C816" t="inlineStr"/>
       <c r="D816" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52780,7 +52790,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C817" t="inlineStr"/>
       <c r="D817" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52805,7 +52814,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C818" t="inlineStr"/>
       <c r="D818" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52830,7 +52838,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52855,7 +52862,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52880,7 +52886,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C821" t="inlineStr"/>
       <c r="D821" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52905,7 +52910,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52930,7 +52934,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C823" t="inlineStr"/>
       <c r="D823" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52955,7 +52958,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C824" t="inlineStr"/>
       <c r="D824" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -52980,7 +52982,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C825" t="inlineStr"/>
       <c r="D825" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53005,7 +53006,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C826" t="inlineStr"/>
       <c r="D826" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53030,7 +53030,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C827" t="inlineStr"/>
       <c r="D827" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53055,7 +53054,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C828" t="inlineStr"/>
       <c r="D828" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53080,7 +53078,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C829" t="inlineStr"/>
       <c r="D829" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53105,7 +53102,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C830" t="inlineStr"/>
       <c r="D830" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53130,7 +53126,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C831" t="inlineStr"/>
       <c r="D831" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53155,7 +53150,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C832" t="inlineStr"/>
       <c r="D832" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53180,7 +53174,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C833" t="inlineStr"/>
       <c r="D833" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53205,7 +53198,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C834" t="inlineStr"/>
       <c r="D834" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53230,7 +53222,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C835" t="inlineStr"/>
       <c r="D835" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53255,7 +53246,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C836" t="inlineStr"/>
       <c r="D836" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53280,7 +53270,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C837" t="inlineStr"/>
       <c r="D837" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53305,7 +53294,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C838" t="inlineStr"/>
       <c r="D838" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53330,7 +53318,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C839" t="inlineStr"/>
       <c r="D839" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53355,7 +53342,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C840" t="inlineStr"/>
       <c r="D840" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53380,7 +53366,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C841" t="inlineStr"/>
       <c r="D841" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53405,7 +53390,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C842" t="inlineStr"/>
       <c r="D842" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53430,7 +53414,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53455,7 +53438,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53480,7 +53462,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C845" t="inlineStr"/>
       <c r="D845" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53505,7 +53486,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C846" t="inlineStr"/>
       <c r="D846" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53530,7 +53510,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C847" t="inlineStr"/>
       <c r="D847" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53555,7 +53534,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C848" t="inlineStr"/>
       <c r="D848" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53580,7 +53558,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C849" t="inlineStr"/>
       <c r="D849" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53605,7 +53582,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C850" t="inlineStr"/>
       <c r="D850" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53630,7 +53606,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C851" t="inlineStr"/>
       <c r="D851" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53655,7 +53630,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C852" t="inlineStr"/>
       <c r="D852" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53680,7 +53654,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C853" t="inlineStr"/>
       <c r="D853" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53705,7 +53678,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C854" t="inlineStr"/>
       <c r="D854" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53730,7 +53702,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C855" t="inlineStr"/>
       <c r="D855" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53755,7 +53726,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C856" t="inlineStr"/>
       <c r="D856" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53780,7 +53750,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C857" t="inlineStr"/>
       <c r="D857" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53805,7 +53774,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C858" t="inlineStr"/>
       <c r="D858" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53830,7 +53798,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C859" t="inlineStr"/>
       <c r="D859" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53855,7 +53822,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C860" t="inlineStr"/>
       <c r="D860" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53880,7 +53846,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C861" t="inlineStr"/>
       <c r="D861" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53904,7 +53869,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C862" t="inlineStr"/>
       <c r="D862" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53928,7 +53892,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C863" t="inlineStr"/>
       <c r="D863" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53952,7 +53915,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C864" t="inlineStr"/>
       <c r="D864" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -53976,7 +53938,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54000,7 +53961,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C866" t="inlineStr"/>
       <c r="D866" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54024,7 +53984,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C867" t="inlineStr"/>
       <c r="D867" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54048,7 +54007,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C868" t="inlineStr"/>
       <c r="D868" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54072,7 +54030,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54096,7 +54053,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C870" t="inlineStr"/>
       <c r="D870" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54120,7 +54076,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C871" t="inlineStr"/>
       <c r="D871" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54144,7 +54099,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C872" t="inlineStr"/>
       <c r="D872" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -54168,7 +54122,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C873" t="inlineStr"/>
       <c r="D873" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54192,7 +54145,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C874" t="inlineStr"/>
       <c r="D874" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54216,7 +54168,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C875" t="inlineStr"/>
       <c r="D875" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54240,7 +54191,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C876" t="inlineStr"/>
       <c r="D876" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54264,7 +54214,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C877" t="inlineStr"/>
       <c r="D877" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54289,7 +54238,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C878" t="inlineStr"/>
       <c r="D878" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54313,7 +54261,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C879" t="inlineStr"/>
       <c r="D879" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54337,7 +54284,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C880" t="inlineStr"/>
       <c r="D880" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54361,7 +54307,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C881" t="inlineStr"/>
       <c r="D881" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54385,7 +54330,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C882" t="inlineStr"/>
       <c r="D882" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54409,7 +54353,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C883" t="inlineStr"/>
       <c r="D883" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54433,7 +54376,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C884" t="inlineStr"/>
       <c r="D884" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54457,7 +54399,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C885" t="inlineStr"/>
       <c r="D885" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54481,7 +54422,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C886" t="inlineStr"/>
       <c r="D886" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54505,7 +54445,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C887" t="inlineStr"/>
       <c r="D887" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54529,7 +54468,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C888" t="inlineStr"/>
       <c r="D888" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54553,7 +54491,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C889" t="inlineStr"/>
       <c r="D889" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54577,7 +54514,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C890" t="inlineStr"/>
       <c r="D890" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54601,7 +54537,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C891" t="inlineStr"/>
       <c r="D891" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54625,7 +54560,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C892" t="inlineStr"/>
       <c r="D892" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54649,7 +54583,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C893" t="inlineStr"/>
       <c r="D893" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54673,7 +54606,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C894" t="inlineStr"/>
       <c r="D894" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54697,7 +54629,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C895" t="inlineStr"/>
       <c r="D895" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54721,7 +54652,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C896" t="inlineStr"/>
       <c r="D896" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54745,7 +54675,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C897" t="inlineStr"/>
       <c r="D897" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54769,7 +54698,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C898" t="inlineStr"/>
       <c r="D898" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54793,7 +54721,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C899" t="inlineStr"/>
       <c r="D899" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -54818,7 +54745,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C900" t="inlineStr"/>
       <c r="D900" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -54843,7 +54769,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C901" t="inlineStr"/>
       <c r="D901" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -54868,7 +54793,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C902" t="inlineStr"/>
       <c r="D902" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -54893,7 +54817,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C903" t="inlineStr"/>
       <c r="D903" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -54918,7 +54841,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C904" t="inlineStr"/>
       <c r="D904" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -54943,7 +54865,6 @@
           <t>MUR</t>
         </is>
       </c>
-      <c r="C905" t="inlineStr"/>
       <c r="D905" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -54968,7 +54889,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C906" t="inlineStr"/>
       <c r="D906" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -54993,7 +54913,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C907" t="inlineStr"/>
       <c r="D907" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55018,7 +54937,6 @@
           <t>MA</t>
         </is>
       </c>
-      <c r="C908" t="inlineStr"/>
       <c r="D908" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55043,7 +54961,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C909" t="inlineStr"/>
       <c r="D909" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55068,7 +54985,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C910" t="inlineStr"/>
       <c r="D910" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55093,7 +55009,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C911" t="inlineStr"/>
       <c r="D911" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55118,7 +55033,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C912" t="inlineStr"/>
       <c r="D912" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55143,7 +55057,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C913" t="inlineStr"/>
       <c r="D913" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55168,7 +55081,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C914" t="inlineStr"/>
       <c r="D914" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55193,7 +55105,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C915" t="inlineStr"/>
       <c r="D915" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55218,7 +55129,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C916" t="inlineStr"/>
       <c r="D916" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55243,7 +55153,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C917" t="inlineStr"/>
       <c r="D917" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55268,7 +55177,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C918" t="inlineStr"/>
       <c r="D918" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55293,7 +55201,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C919" t="inlineStr"/>
       <c r="D919" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55318,7 +55225,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C920" t="inlineStr"/>
       <c r="D920" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55343,7 +55249,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C921" t="inlineStr"/>
       <c r="D921" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55368,7 +55273,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C922" t="inlineStr"/>
       <c r="D922" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55393,7 +55297,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C923" t="inlineStr"/>
       <c r="D923" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55418,7 +55321,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C924" t="inlineStr"/>
       <c r="D924" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55443,7 +55345,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C925" t="inlineStr"/>
       <c r="D925" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55468,7 +55369,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C926" t="inlineStr"/>
       <c r="D926" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55493,7 +55393,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C927" t="inlineStr"/>
       <c r="D927" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55518,7 +55417,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C928" t="inlineStr"/>
       <c r="D928" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55543,7 +55441,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C929" t="inlineStr"/>
       <c r="D929" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55568,7 +55465,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C930" t="inlineStr"/>
       <c r="D930" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55593,7 +55489,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C931" t="inlineStr"/>
       <c r="D931" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55618,7 +55513,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C932" t="inlineStr"/>
       <c r="D932" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55643,7 +55537,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C933" t="inlineStr"/>
       <c r="D933" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55668,7 +55561,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C934" t="inlineStr"/>
       <c r="D934" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55693,7 +55585,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C935" t="inlineStr"/>
       <c r="D935" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55718,7 +55609,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C936" t="inlineStr"/>
       <c r="D936" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55743,7 +55633,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C937" t="inlineStr"/>
       <c r="D937" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55768,7 +55657,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C938" t="inlineStr"/>
       <c r="D938" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55793,7 +55681,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C939" t="inlineStr"/>
       <c r="D939" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55818,7 +55705,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C940" t="inlineStr"/>
       <c r="D940" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55843,7 +55729,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C941" t="inlineStr"/>
       <c r="D941" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55868,7 +55753,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C942" t="inlineStr"/>
       <c r="D942" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55893,7 +55777,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C943" t="inlineStr"/>
       <c r="D943" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55918,7 +55801,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C944" t="inlineStr"/>
       <c r="D944" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55943,7 +55825,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C945" t="inlineStr"/>
       <c r="D945" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55968,7 +55849,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C946" t="inlineStr"/>
       <c r="D946" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -55993,7 +55873,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C947" t="inlineStr"/>
       <c r="D947" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56018,7 +55897,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C948" t="inlineStr"/>
       <c r="D948" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56043,7 +55921,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C949" t="inlineStr"/>
       <c r="D949" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56068,7 +55945,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C950" t="inlineStr"/>
       <c r="D950" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56093,7 +55969,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C951" t="inlineStr"/>
       <c r="D951" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56118,7 +55993,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C952" t="inlineStr"/>
       <c r="D952" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56143,7 +56017,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C953" t="inlineStr"/>
       <c r="D953" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56168,7 +56041,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C954" t="inlineStr"/>
       <c r="D954" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56193,7 +56065,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C955" t="inlineStr"/>
       <c r="D955" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56218,7 +56089,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C956" t="inlineStr"/>
       <c r="D956" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56243,7 +56113,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C957" t="inlineStr"/>
       <c r="D957" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56268,7 +56137,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C958" t="inlineStr"/>
       <c r="D958" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56293,7 +56161,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C959" t="inlineStr"/>
       <c r="D959" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56318,7 +56185,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C960" t="inlineStr"/>
       <c r="D960" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56343,7 +56209,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C961" t="inlineStr"/>
       <c r="D961" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56368,7 +56233,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C962" t="inlineStr"/>
       <c r="D962" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56393,7 +56257,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C963" t="inlineStr"/>
       <c r="D963" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56418,7 +56281,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C964" t="inlineStr"/>
       <c r="D964" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56443,7 +56305,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C965" t="inlineStr"/>
       <c r="D965" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56468,7 +56329,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C966" t="inlineStr"/>
       <c r="D966" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56493,7 +56353,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C967" t="inlineStr"/>
       <c r="D967" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56518,7 +56377,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C968" t="inlineStr"/>
       <c r="D968" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56543,7 +56401,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C969" t="inlineStr"/>
       <c r="D969" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56568,7 +56425,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C970" t="inlineStr"/>
       <c r="D970" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56593,7 +56449,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C971" t="inlineStr"/>
       <c r="D971" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56618,7 +56473,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C972" t="inlineStr"/>
       <c r="D972" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56643,7 +56497,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C973" t="inlineStr"/>
       <c r="D973" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56668,7 +56521,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C974" t="inlineStr"/>
       <c r="D974" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56693,7 +56545,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C975" t="inlineStr"/>
       <c r="D975" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56718,7 +56569,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C976" t="inlineStr"/>
       <c r="D976" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56743,7 +56593,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C977" t="inlineStr"/>
       <c r="D977" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56768,7 +56617,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C978" t="inlineStr"/>
       <c r="D978" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56793,7 +56641,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C979" t="inlineStr"/>
       <c r="D979" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56818,7 +56665,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C980" t="inlineStr"/>
       <c r="D980" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56843,7 +56689,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C981" t="inlineStr"/>
       <c r="D981" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56868,7 +56713,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C982" t="inlineStr"/>
       <c r="D982" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56893,7 +56737,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C983" t="inlineStr"/>
       <c r="D983" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56918,7 +56761,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C984" t="inlineStr"/>
       <c r="D984" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56943,7 +56785,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C985" t="inlineStr"/>
       <c r="D985" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56968,7 +56809,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C986" t="inlineStr"/>
       <c r="D986" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -56993,7 +56833,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C987" t="inlineStr"/>
       <c r="D987" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57018,7 +56857,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C988" t="inlineStr"/>
       <c r="D988" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57042,7 +56880,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C989" t="inlineStr"/>
       <c r="D989" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57066,7 +56903,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C990" t="inlineStr"/>
       <c r="D990" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57090,7 +56926,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C991" t="inlineStr"/>
       <c r="D991" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57114,7 +56949,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C992" t="inlineStr"/>
       <c r="D992" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57138,7 +56972,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C993" t="inlineStr"/>
       <c r="D993" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57162,7 +56995,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C994" t="inlineStr"/>
       <c r="D994" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57186,7 +57018,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C995" t="inlineStr"/>
       <c r="D995" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57210,7 +57041,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C996" t="inlineStr"/>
       <c r="D996" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57234,7 +57064,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C997" t="inlineStr"/>
       <c r="D997" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57258,7 +57087,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C998" t="inlineStr"/>
       <c r="D998" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57282,7 +57110,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C999" t="inlineStr"/>
       <c r="D999" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57306,7 +57133,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1000" t="inlineStr"/>
       <c r="D1000" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57330,7 +57156,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1001" t="inlineStr"/>
       <c r="D1001" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57354,7 +57179,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1002" t="inlineStr"/>
       <c r="D1002" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57378,7 +57202,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1003" t="inlineStr"/>
       <c r="D1003" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57403,7 +57226,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1004" t="inlineStr"/>
       <c r="D1004" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57427,7 +57249,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1005" t="inlineStr"/>
       <c r="D1005" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57451,7 +57272,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1006" t="inlineStr"/>
       <c r="D1006" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57475,7 +57295,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1007" t="inlineStr"/>
       <c r="D1007" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57499,7 +57318,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1008" t="inlineStr"/>
       <c r="D1008" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57523,7 +57341,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1009" t="inlineStr"/>
       <c r="D1009" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57547,7 +57364,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1010" t="inlineStr"/>
       <c r="D1010" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57571,7 +57387,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1011" t="inlineStr"/>
       <c r="D1011" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57595,7 +57410,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1012" t="inlineStr"/>
       <c r="D1012" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57619,7 +57433,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1013" t="inlineStr"/>
       <c r="D1013" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57643,7 +57456,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1014" t="inlineStr"/>
       <c r="D1014" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57667,7 +57479,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1015" t="inlineStr"/>
       <c r="D1015" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57691,7 +57502,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1016" t="inlineStr"/>
       <c r="D1016" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57715,7 +57525,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1017" t="inlineStr"/>
       <c r="D1017" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57739,7 +57548,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1018" t="inlineStr"/>
       <c r="D1018" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57763,7 +57571,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1019" t="inlineStr"/>
       <c r="D1019" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57787,7 +57594,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1020" t="inlineStr"/>
       <c r="D1020" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57811,7 +57617,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1021" t="inlineStr"/>
       <c r="D1021" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57835,7 +57640,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1022" t="inlineStr"/>
       <c r="D1022" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57859,7 +57663,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1023" t="inlineStr"/>
       <c r="D1023" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57883,7 +57686,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1024" t="inlineStr"/>
       <c r="D1024" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57907,7 +57709,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1025" t="inlineStr"/>
       <c r="D1025" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57931,7 +57732,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1026" t="inlineStr"/>
       <c r="D1026" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57955,7 +57755,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1027" t="inlineStr"/>
       <c r="D1027" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -57979,7 +57778,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1028" t="inlineStr"/>
       <c r="D1028" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58003,7 +57801,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1029" t="inlineStr"/>
       <c r="D1029" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58027,7 +57824,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1030" t="inlineStr"/>
       <c r="D1030" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58051,7 +57847,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1031" t="inlineStr"/>
       <c r="D1031" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58075,7 +57870,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1032" t="inlineStr"/>
       <c r="D1032" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58099,7 +57893,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1033" t="inlineStr"/>
       <c r="D1033" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58123,7 +57916,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1034" t="inlineStr"/>
       <c r="D1034" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58147,7 +57939,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1035" t="inlineStr"/>
       <c r="D1035" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58171,7 +57962,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1036" t="inlineStr"/>
       <c r="D1036" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58195,7 +57985,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1037" t="inlineStr"/>
       <c r="D1037" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58219,7 +58008,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1038" t="inlineStr"/>
       <c r="D1038" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58243,7 +58031,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1039" t="inlineStr"/>
       <c r="D1039" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58267,7 +58054,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1040" t="inlineStr"/>
       <c r="D1040" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58291,7 +58077,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1041" t="inlineStr"/>
       <c r="D1041" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -58302,6 +58087,4311 @@
       </c>
       <c r="AX1041" t="n">
         <v>3184</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>プロトーガ</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr"/>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1042" t="n">
+        <v>980</v>
+      </c>
+      <c r="BB1042" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>〔状態B〕ルギアEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr"/>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1043" t="n">
+        <v>3790</v>
+      </c>
+      <c r="BB1043" t="n">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>〔状態B〕きずぐすり
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr"/>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1044" t="n">
+        <v>320</v>
+      </c>
+      <c r="BB1044" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イワパレス
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr"/>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1045" t="n">
+        <v>730</v>
+      </c>
+      <c r="BB1045" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キバゴ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr"/>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1046" t="n">
+        <v>1190</v>
+      </c>
+      <c r="BB1046" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のヘルガー
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr"/>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1047" t="n">
+        <v>830</v>
+      </c>
+      <c r="BB1047" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr"/>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1048" t="n">
+        <v>680</v>
+      </c>
+      <c r="BB1048" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>〔状態B〕レックウザGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr"/>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1049" t="n">
+        <v>690</v>
+      </c>
+      <c r="BB1049" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オンバット
+SV9]</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr"/>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1050" t="n">
+        <v>390</v>
+      </c>
+      <c r="BB1050" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サンダースex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr"/>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1051" t="n">
+        <v>8680</v>
+      </c>
+      <c r="BB1051" t="n">
+        <v>6944</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リーフィアex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr"/>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1052" t="n">
+        <v>260</v>
+      </c>
+      <c r="BB1052" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>〔状態A-〕デンチュラex
+SV7]</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr"/>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1053" t="n">
+        <v>380</v>
+      </c>
+      <c r="BB1053" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本雷エネルギー(ステーション/SM新デザイン)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr"/>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1054" t="n">
+        <v>780</v>
+      </c>
+      <c r="BB1054" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>〔状態B〕アカギの策略(コイン付未開封/キラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr"/>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1055" t="n">
+        <v>27800</v>
+      </c>
+      <c r="BB1055" t="n">
+        <v>22240</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハガネール
+SV4M]</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr"/>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1056" t="n">
+        <v>830</v>
+      </c>
+      <c r="BB1056" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ボウルタウン
+SV3]</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr"/>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1057" t="n">
+        <v>690</v>
+      </c>
+      <c r="BB1057" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エースバーンV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr"/>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1058" t="n">
+        <v>260</v>
+      </c>
+      <c r="BB1058" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒスイドレディアV
+S10D]</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr"/>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1059" t="n">
+        <v>380</v>
+      </c>
+      <c r="BB1059" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>〔状態B〕ロトムV(SA)
+S11]</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr"/>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1060" t="n">
+        <v>2180</v>
+      </c>
+      <c r="BB1060" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジジーロン
+その他]</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr"/>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1061" t="n">
+        <v>780</v>
+      </c>
+      <c r="BB1061" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アマージョ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr"/>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1062" t="n">
+        <v>930</v>
+      </c>
+      <c r="BB1062" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ストリンダー
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr"/>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1063" t="n">
+        <v>480</v>
+      </c>
+      <c r="BB1063" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルギアV(SA)
+S12]</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr"/>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1064" t="n">
+        <v>158000</v>
+      </c>
+      <c r="BB1064" t="n">
+        <v>126400</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジムバッジ(ナギ)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr"/>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1065" t="n">
+        <v>5280</v>
+      </c>
+      <c r="BB1065" t="n">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エーフィGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr"/>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1066" t="n">
+        <v>20300</v>
+      </c>
+      <c r="BB1066" t="n">
+        <v>16240</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カラマネロ
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr"/>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1067" t="n">
+        <v>380</v>
+      </c>
+      <c r="BB1067" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本炎エネルギー(ファーストデザイン)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr"/>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1068" t="n">
+        <v>930</v>
+      </c>
+      <c r="BB1068" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>〔状態B〕カプ・テテフGX(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr"/>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1069" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BB1069" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガマゲロゲEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr"/>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1070" t="n">
+        <v>8980</v>
+      </c>
+      <c r="BB1070" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本鋼エネルギー(ジムチャレンジ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr"/>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1071" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1071" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カブ
+S2a]</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr"/>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1072" t="n">
+        <v>330</v>
+      </c>
+      <c r="BB1072" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピィ(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr"/>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1073" t="n">
+        <v>2480</v>
+      </c>
+      <c r="BB1073" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MミュウツーEX(Y)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr"/>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1074" t="n">
+        <v>13800</v>
+      </c>
+      <c r="BB1074" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ふしぎなアメ
+sm1]</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr"/>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1075" t="n">
+        <v>23800</v>
+      </c>
+      <c r="BB1075" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラティアス＆ラティオスGX
+sm9]</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr"/>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1076" t="n">
+        <v>14300</v>
+      </c>
+      <c r="BB1076" t="n">
+        <v>11440</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>〔状態A-〕とりつかい
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr"/>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1077" t="n">
+        <v>630</v>
+      </c>
+      <c r="BB1077" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カブ
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr"/>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1078" t="n">
+        <v>380</v>
+      </c>
+      <c r="BB1078" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>〔状態B〕レックウザEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr"/>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1079" t="n">
+        <v>23800</v>
+      </c>
+      <c r="BB1079" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アズサ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr"/>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1080" t="n">
+        <v>79800</v>
+      </c>
+      <c r="BB1080" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>〔状態B〕オーロンゲVMAX
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr"/>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1081" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1081" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポンチョを着たイーブイ(NP/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr"/>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1082" t="n">
+        <v>158000</v>
+      </c>
+      <c r="BB1082" t="n">
+        <v>126400</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゴリランダーV
+s1a]</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr"/>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1083" t="n">
+        <v>420</v>
+      </c>
+      <c r="BB1083" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr"/>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1084" t="n">
+        <v>9480</v>
+      </c>
+      <c r="BB1084" t="n">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>〔状態C〕お公家さまと舞妓はんピカチュウ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr"/>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1085" t="n">
+        <v>84800</v>
+      </c>
+      <c r="BB1085" t="n">
+        <v>67840</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>〔状態B〕ケンタロスGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr"/>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1086" t="n">
+        <v>2380</v>
+      </c>
+      <c r="BB1086" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>〔状態B〕イーブイ＆カビゴンGX
+sm9]</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr"/>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1087" t="n">
+        <v>8480</v>
+      </c>
+      <c r="BB1087" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>〔状態B〕イワンコ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr"/>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1088" t="n">
+        <v>1280</v>
+      </c>
+      <c r="BB1088" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>〔状態B〕どくさいみん光線
+その他]</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr"/>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1089" t="n">
+        <v>1390</v>
+      </c>
+      <c r="BB1089" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>〔状態B〕メガルカリオex
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr"/>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1090" t="n">
+        <v>890</v>
+      </c>
+      <c r="BB1090" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>タマタマ</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr"/>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1091" t="n">
+        <v>780</v>
+      </c>
+      <c r="BB1091" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>ラフレシア</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr"/>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1092" t="n">
+        <v>380</v>
+      </c>
+      <c r="BB1092" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>カジッチュ</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr"/>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1093" t="n">
+        <v>280</v>
+      </c>
+      <c r="BB1093" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>フシギバナ＆ツタージャGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr"/>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1094" t="n">
+        <v>18800</v>
+      </c>
+      <c r="BB1094" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA9鑑定済〕レシラム＆リザードンGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr"/>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1095" t="n">
+        <v>99800</v>
+      </c>
+      <c r="BB1095" t="n">
+        <v>79840</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕リザードンGX</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr"/>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1096" t="n">
+        <v>388000</v>
+      </c>
+      <c r="BB1096" t="n">
+        <v>310400</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ブースターEX</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr"/>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1097" t="n">
+        <v>118000</v>
+      </c>
+      <c r="BB1097" t="n">
+        <v>94400</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>リザードン</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr"/>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1098" t="n">
+        <v>4980</v>
+      </c>
+      <c r="BB1098" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>レシラム＆リザードンGX</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr"/>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1099" t="n">
+        <v>5980</v>
+      </c>
+      <c r="BB1099" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕クワッス(マクドナルド)</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr"/>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1100" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BB1100" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>ウェルカモ</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr"/>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1101" t="n">
+        <v>380</v>
+      </c>
+      <c r="BB1101" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>グレイシアVSTAR</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr"/>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1102" t="n">
+        <v>6980</v>
+      </c>
+      <c r="BB1102" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr"/>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1103" t="n">
+        <v>21800</v>
+      </c>
+      <c r="BB1103" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕レントラーGLLV.X(25th)</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr"/>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1104" t="n">
+        <v>12800</v>
+      </c>
+      <c r="BB1104" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>ライチュウV</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr"/>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1105" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1105" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA9鑑定済〕ミュウツーEX(フォトンウェーブ)</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr"/>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1106" t="n">
+        <v>67800</v>
+      </c>
+      <c r="BB1106" t="n">
+        <v>54240</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>ラティアスex</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr"/>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1107" t="n">
+        <v>220</v>
+      </c>
+      <c r="BB1107" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕メガルカリオex</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>MUR</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr"/>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1108" t="n">
+        <v>144000</v>
+      </c>
+      <c r="BB1108" t="n">
+        <v>115200</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>チヲハウハネ</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr"/>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1109" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1109" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>カイリキーVMAX</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr"/>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1110" t="n">
+        <v>380</v>
+      </c>
+      <c r="BB1110" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>アクジキングGX</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr"/>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1111" t="n">
+        <v>4480</v>
+      </c>
+      <c r="BB1111" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>ハッサム</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr"/>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1112" t="n">
+        <v>980</v>
+      </c>
+      <c r="BB1112" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ラティアス</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr"/>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1113" t="n">
+        <v>12800</v>
+      </c>
+      <c r="BB1113" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>フルフェイスガード</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr"/>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1114" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1114" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>回収ネット</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr"/>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1115" t="n">
+        <v>1280</v>
+      </c>
+      <c r="BB1115" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>ロトム図鑑</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr"/>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1116" t="n">
+        <v>280</v>
+      </c>
+      <c r="BB1116" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>改造ハンマー</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr"/>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1117" t="n">
+        <v>9980</v>
+      </c>
+      <c r="BB1117" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>基本草エネルギー(ジムチャレンジ)</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr"/>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1118" t="n">
+        <v>680</v>
+      </c>
+      <c r="BB1118" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>〔CGC10黒鑑定済〕マオ</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr"/>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1119" t="n">
+        <v>138000</v>
+      </c>
+      <c r="BB1119" t="n">
+        <v>110400</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>探検家の先導</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr"/>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1120" t="n">
+        <v>780</v>
+      </c>
+      <c r="BB1120" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕エリカのおもてなし</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr"/>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1121" t="n">
+        <v>194000</v>
+      </c>
+      <c r="BB1121" t="n">
+        <v>155200</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>グルーシャ</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr"/>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1122" t="n">
+        <v>1180</v>
+      </c>
+      <c r="BB1122" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>ナタネの活気</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr"/>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1123" t="n">
+        <v>2580</v>
+      </c>
+      <c r="BB1123" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>シャクヤ</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr"/>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1124" t="n">
+        <v>2580</v>
+      </c>
+      <c r="BB1124" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>マオ</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr"/>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1125" t="n">
+        <v>51800</v>
+      </c>
+      <c r="BB1125" t="n">
+        <v>41440</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>シロナ</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr"/>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BA1126" t="n">
+        <v>108000</v>
+      </c>
+      <c r="BB1126" t="n">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>〔状態A-〕チルタリスEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr"/>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1127" t="n">
+        <v>1390</v>
+      </c>
+      <c r="BB1127" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>〔状態C〕バッフロン
+その他]</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr"/>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1128" t="n">
+        <v>280</v>
+      </c>
+      <c r="BB1128" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>〔状態C〕オムナイト
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr"/>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1129" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1129" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>〔状態C〕エンペルト
+その他]</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr"/>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1130" t="n">
+        <v>780</v>
+      </c>
+      <c r="BB1130" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>〔状態C〕ペラップ
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr"/>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1131" t="n">
+        <v>220</v>
+      </c>
+      <c r="BB1131" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>〔状態C〕タロ
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr"/>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1132" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1132" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒトカゲ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr"/>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1133" t="n">
+        <v>7280</v>
+      </c>
+      <c r="BB1133" t="n">
+        <v>5824</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr"/>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1134" t="n">
+        <v>790</v>
+      </c>
+      <c r="BB1134" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>〔状態C〕ロケット団のミュウツーex
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr"/>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1135" t="n">
+        <v>7480</v>
+      </c>
+      <c r="BB1135" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヤナッキー
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr"/>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1136" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1136" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>〔状態B〕アーケン
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr"/>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1137" t="n">
+        <v>680</v>
+      </c>
+      <c r="BB1137" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のニャース
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr"/>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1138" t="n">
+        <v>1990</v>
+      </c>
+      <c r="BB1138" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>〔状態C〕オーガポンかまどのめんex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr"/>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1139" t="n">
+        <v>420</v>
+      </c>
+      <c r="BB1139" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジュカイン
+その他]</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr"/>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1140" t="n">
+        <v>680</v>
+      </c>
+      <c r="BB1140" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウ(ジャンボカード)
+ジャンボカード]</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr"/>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1141" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BB1141" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本草エネルギー(BWデザイン/ミラー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr"/>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1142" t="n">
+        <v>480</v>
+      </c>
+      <c r="BB1142" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>〔状態C〕ハイダイ
+SV7]</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr"/>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1143" t="n">
+        <v>220</v>
+      </c>
+      <c r="BB1143" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラティアスδ-デルタ種
+その他]</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr"/>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1144" t="n">
+        <v>8990</v>
+      </c>
+      <c r="BB1144" t="n">
+        <v>7192</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>〔状態B〕ザングースδ-デルタ種(明治/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr"/>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1145" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BB1145" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジラーチ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr"/>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1146" t="n">
+        <v>1990</v>
+      </c>
+      <c r="BB1146" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イッカネズミ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr"/>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1147" t="n">
+        <v>730</v>
+      </c>
+      <c r="BB1147" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マスクド・ピカチュウ(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr"/>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1148" t="n">
+        <v>198000</v>
+      </c>
+      <c r="BB1148" t="n">
+        <v>158400</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>〔状態C〕カプ・コケコex
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr"/>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1149" t="n">
+        <v>220</v>
+      </c>
+      <c r="BB1149" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>〔状態C〕ウパー(マクドナルド)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr"/>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1150" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BB1150" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>〔状態C〕ウォロ
+S10a]</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr"/>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1151" t="n">
+        <v>220</v>
+      </c>
+      <c r="BB1151" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>〔状態B〕ユキワラシ
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr"/>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1152" t="n">
+        <v>380</v>
+      </c>
+      <c r="BB1152" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジュラルドンV
+S7D]</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr"/>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1153" t="n">
+        <v>220</v>
+      </c>
+      <c r="BB1153" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピチュー(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr"/>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1154" t="n">
+        <v>12800</v>
+      </c>
+      <c r="BB1154" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>〔状態C〕バシャーモV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr"/>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1155" t="n">
+        <v>990</v>
+      </c>
+      <c r="BB1155" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr"/>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1156" t="n">
+        <v>16300</v>
+      </c>
+      <c r="BB1156" t="n">
+        <v>13040</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゲッコウガ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr"/>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1157" t="n">
+        <v>830</v>
+      </c>
+      <c r="BB1157" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>〔状態B〕メッソン
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr"/>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1158" t="n">
+        <v>2180</v>
+      </c>
+      <c r="BB1158" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>〔状態C〕オリジンパルキアVSTAR
+S10P]</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr"/>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1159" t="n">
+        <v>790</v>
+      </c>
+      <c r="BB1159" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>〔状態B〕チャンピオンズフェスティバル(2018/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr"/>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1160" t="n">
+        <v>218000</v>
+      </c>
+      <c r="BB1160" t="n">
+        <v>174400</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>〔状態C〕ブースターV
+S6a]</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr"/>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1161" t="n">
+        <v>730</v>
+      </c>
+      <c r="BB1161" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>〔状態C〕マリィ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr"/>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1162" t="n">
+        <v>4480</v>
+      </c>
+      <c r="BB1162" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウツーGX(HR仕様)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr"/>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1163" t="n">
+        <v>898000</v>
+      </c>
+      <c r="BB1163" t="n">
+        <v>718400</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>〔状態B〕マナフィ
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr"/>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1164" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1164" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハッサムGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr"/>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1165" t="n">
+        <v>9900</v>
+      </c>
+      <c r="BB1165" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ダブルドラゴンエネルギー(メガボーマンダジムバトル入賞)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr"/>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1166" t="n">
+        <v>3580</v>
+      </c>
+      <c r="BB1166" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブースター
+その他]</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr"/>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1167" t="n">
+        <v>17800</v>
+      </c>
+      <c r="BB1167" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エルフーンGX
+sm10]</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr"/>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1168" t="n">
+        <v>260</v>
+      </c>
+      <c r="BB1168" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サトシゲッコウガEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr"/>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1169" t="n">
+        <v>21800</v>
+      </c>
+      <c r="BB1169" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>〔状態B〕ウッウ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr"/>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1170" t="n">
+        <v>44800</v>
+      </c>
+      <c r="BB1170" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>〔状態B〕イベルタル(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr"/>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1171" t="n">
+        <v>1880</v>
+      </c>
+      <c r="BB1171" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>〔状態C〕ニンフィアV(SA)
+S6a]</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr"/>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1172" t="n">
+        <v>10800</v>
+      </c>
+      <c r="BB1172" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドクター
+S6H]</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr"/>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1173" t="n">
+        <v>630</v>
+      </c>
+      <c r="BB1173" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>〔状態C〕ザマゼンタV
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr"/>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1174" t="n">
+        <v>680</v>
+      </c>
+      <c r="BB1174" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ギャラドスGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr"/>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1175" t="n">
+        <v>1880</v>
+      </c>
+      <c r="BB1175" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カビゴンLV.X
+その他]</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr"/>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1176" t="n">
+        <v>268000</v>
+      </c>
+      <c r="BB1176" t="n">
+        <v>214400</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ビクティニEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr"/>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1177" t="n">
+        <v>17800</v>
+      </c>
+      <c r="BB1177" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>〔状態A-〕モルフォンGX
+SM9a]</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr"/>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1178" t="n">
+        <v>1090</v>
+      </c>
+      <c r="BB1178" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr"/>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1179" t="n">
+        <v>198000</v>
+      </c>
+      <c r="BB1179" t="n">
+        <v>158400</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シロナの覇気
+S9]</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr"/>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1180" t="n">
+        <v>990</v>
+      </c>
+      <c r="BB1180" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr"/>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1181" t="n">
+        <v>21800</v>
+      </c>
+      <c r="BB1181" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>〔状態C〕＿のジラーチ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr"/>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1182" t="n">
+        <v>12800</v>
+      </c>
+      <c r="BB1182" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本フェアリーエネルギー(チャンピオンズリーグ2018)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr"/>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1183" t="n">
+        <v>420</v>
+      </c>
+      <c r="BB1183" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>〔状態C〕カトレア
+S6K]</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr"/>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1184" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BB1184" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>〔状態B〕エレキチャージャー
+sm8]</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr"/>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1185" t="n">
+        <v>230</v>
+      </c>
+      <c r="BB1185" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲッコウガ(リザードンメガバトル)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr"/>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1186" t="n">
+        <v>59800</v>
+      </c>
+      <c r="BB1186" t="n">
+        <v>47840</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピチュー兄弟
+その他]</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr"/>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1187" t="n">
+        <v>17800</v>
+      </c>
+      <c r="BB1187" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>〔状態B〕セレビィEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr"/>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1188" t="n">
+        <v>7990</v>
+      </c>
+      <c r="BB1188" t="n">
+        <v>6392</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>〔状態C〕カビゴンVMAX
+s1]</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr"/>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1189" t="n">
+        <v>790</v>
+      </c>
+      <c r="BB1189" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポンチョを着たピカチュウ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr"/>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1190" t="n">
+        <v>748000</v>
+      </c>
+      <c r="BB1190" t="n">
+        <v>598400</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>〔状態B〕サカキの追放
+sm10]</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr"/>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1191" t="n">
+        <v>1090</v>
+      </c>
+      <c r="BB1191" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジガルデGX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr"/>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1192" t="n">
+        <v>780</v>
+      </c>
+      <c r="BB1192" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本フェアリーエネルギー(チャンピオンズリーグ2018)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr"/>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1193" t="n">
+        <v>220</v>
+      </c>
+      <c r="BB1193" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr"/>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1194" t="n">
+        <v>2190</v>
+      </c>
+      <c r="BB1194" t="n">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>〔状態C〕ねがいのバトン
+sm4]</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr"/>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1195" t="n">
+        <v>1280</v>
+      </c>
+      <c r="BB1195" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>〔状態C〕じゃくてんほけん
+XY]</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr"/>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1196" t="n">
+        <v>990</v>
+      </c>
+      <c r="BB1196" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>〔状態C〕メガヤミラミ＆バンギラスGX(SA)
+sm11]</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr"/>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1197" t="n">
+        <v>15800</v>
+      </c>
+      <c r="BB1197" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウツーEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr"/>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1198" t="n">
+        <v>3480</v>
+      </c>
+      <c r="BB1198" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>〔状態C〕トレーナーズポスト
+XY]</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr"/>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1199" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BB1199" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>〔状態C〕シロナ＆カトレア
+sm12]</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr"/>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1200" t="n">
+        <v>10800</v>
+      </c>
+      <c r="BB1200" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>〔状態C〕回収ネット
+S2]</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr"/>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1201" t="n">
+        <v>580</v>
+      </c>
+      <c r="BB1201" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>〔状態C〕MレックウザEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr"/>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1202" t="n">
+        <v>59800</v>
+      </c>
+      <c r="BB1202" t="n">
+        <v>47840</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>〔状態C〕ともだちてちょう
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr"/>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1203" t="n">
+        <v>42800</v>
+      </c>
+      <c r="BB1203" t="n">
+        <v>34240</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウツー＆ミュウGX
+sm11]</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr"/>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1204" t="n">
+        <v>2490</v>
+      </c>
+      <c r="BB1204" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr"/>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1205" t="n">
+        <v>64800</v>
+      </c>
+      <c r="BB1205" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>〔状態B〕レックウザGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr"/>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1206" t="n">
+        <v>84800</v>
+      </c>
+      <c r="BB1206" t="n">
+        <v>67840</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>〔状態B〕おじょうさま
+sm11a]</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr"/>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1207" t="n">
+        <v>590</v>
+      </c>
+      <c r="BB1207" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>〔※状態難/BGS9.5鑑定済〕ポンチョを着たピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr"/>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1208" t="n">
+        <v>778000</v>
+      </c>
+      <c r="BB1208" t="n">
+        <v>622400</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>ブースターVMAX(SA仕様/中国語版)</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr"/>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1209" t="n">
+        <v>44800</v>
+      </c>
+      <c r="BB1209" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>〔PSA8鑑定済〕ルンパッパ</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr"/>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1210" t="n">
+        <v>1780</v>
+      </c>
+      <c r="BB1210" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>ゲノセクト</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr"/>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1211" t="n">
+        <v>1180</v>
+      </c>
+      <c r="BB1211" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕フシギソウ</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr"/>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1212" t="n">
+        <v>12800</v>
+      </c>
+      <c r="BB1212" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ラフレシアGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr"/>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1213" t="n">
+        <v>3980</v>
+      </c>
+      <c r="BB1213" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕セレビィVMAX</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr"/>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1214" t="n">
+        <v>2980</v>
+      </c>
+      <c r="BB1214" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ブースター</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr"/>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BA1215" t="n">
+        <v>9980</v>
+      </c>
+      <c r="BB1215" t="n">
+        <v>7984</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD1215"/>
+  <dimension ref="A1:BH1243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33458,6 +33458,26 @@
           <t>2026-06-15_diff</t>
         </is>
       </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>2026-06-17_price</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>2026-06-17_buy</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>2026-06-17_ratio</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>2026-06-17_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -58100,7 +58120,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1042" t="inlineStr"/>
       <c r="D1042" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58125,7 +58144,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1043" t="inlineStr"/>
       <c r="D1043" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58150,7 +58168,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1044" t="inlineStr"/>
       <c r="D1044" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58175,7 +58192,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1045" t="inlineStr"/>
       <c r="D1045" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58200,7 +58216,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1046" t="inlineStr"/>
       <c r="D1046" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58225,7 +58240,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1047" t="inlineStr"/>
       <c r="D1047" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58250,7 +58264,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1048" t="inlineStr"/>
       <c r="D1048" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58275,7 +58288,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1049" t="inlineStr"/>
       <c r="D1049" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58300,7 +58312,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1050" t="inlineStr"/>
       <c r="D1050" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58325,7 +58336,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1051" t="inlineStr"/>
       <c r="D1051" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58350,7 +58360,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1052" t="inlineStr"/>
       <c r="D1052" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58375,7 +58384,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1053" t="inlineStr"/>
       <c r="D1053" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58400,7 +58408,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1054" t="inlineStr"/>
       <c r="D1054" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58425,7 +58432,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1055" t="inlineStr"/>
       <c r="D1055" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58450,7 +58456,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1056" t="inlineStr"/>
       <c r="D1056" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58475,7 +58480,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1057" t="inlineStr"/>
       <c r="D1057" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58500,7 +58504,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1058" t="inlineStr"/>
       <c r="D1058" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58525,7 +58528,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1059" t="inlineStr"/>
       <c r="D1059" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58550,7 +58552,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1060" t="inlineStr"/>
       <c r="D1060" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58575,7 +58576,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1061" t="inlineStr"/>
       <c r="D1061" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58600,7 +58600,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1062" t="inlineStr"/>
       <c r="D1062" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58625,7 +58624,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1063" t="inlineStr"/>
       <c r="D1063" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58650,7 +58648,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1064" t="inlineStr"/>
       <c r="D1064" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58675,7 +58672,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1065" t="inlineStr"/>
       <c r="D1065" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58700,7 +58696,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1066" t="inlineStr"/>
       <c r="D1066" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58725,7 +58720,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1067" t="inlineStr"/>
       <c r="D1067" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58750,7 +58744,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1068" t="inlineStr"/>
       <c r="D1068" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58775,7 +58768,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1069" t="inlineStr"/>
       <c r="D1069" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58800,7 +58792,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1070" t="inlineStr"/>
       <c r="D1070" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58825,7 +58816,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1071" t="inlineStr"/>
       <c r="D1071" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58850,7 +58840,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1072" t="inlineStr"/>
       <c r="D1072" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58875,7 +58864,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1073" t="inlineStr"/>
       <c r="D1073" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58900,7 +58888,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1074" t="inlineStr"/>
       <c r="D1074" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58925,7 +58912,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1075" t="inlineStr"/>
       <c r="D1075" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58950,7 +58936,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1076" t="inlineStr"/>
       <c r="D1076" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -58975,7 +58960,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1077" t="inlineStr"/>
       <c r="D1077" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59000,7 +58984,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1078" t="inlineStr"/>
       <c r="D1078" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59025,7 +59008,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1079" t="inlineStr"/>
       <c r="D1079" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59050,7 +59032,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1080" t="inlineStr"/>
       <c r="D1080" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59075,7 +59056,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1081" t="inlineStr"/>
       <c r="D1081" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59100,7 +59080,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1082" t="inlineStr"/>
       <c r="D1082" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59125,7 +59104,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1083" t="inlineStr"/>
       <c r="D1083" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59150,7 +59128,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1084" t="inlineStr"/>
       <c r="D1084" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59175,7 +59152,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1085" t="inlineStr"/>
       <c r="D1085" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59200,7 +59176,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1086" t="inlineStr"/>
       <c r="D1086" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59225,7 +59200,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1087" t="inlineStr"/>
       <c r="D1087" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59250,7 +59224,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1088" t="inlineStr"/>
       <c r="D1088" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59275,7 +59248,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1089" t="inlineStr"/>
       <c r="D1089" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59300,7 +59272,6 @@
           <t>MA</t>
         </is>
       </c>
-      <c r="C1090" t="inlineStr"/>
       <c r="D1090" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59324,7 +59295,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1091" t="inlineStr"/>
       <c r="D1091" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59348,7 +59318,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1092" t="inlineStr"/>
       <c r="D1092" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59372,7 +59341,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1093" t="inlineStr"/>
       <c r="D1093" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59396,7 +59364,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1094" t="inlineStr"/>
       <c r="D1094" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59420,7 +59387,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1095" t="inlineStr"/>
       <c r="D1095" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59444,7 +59410,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1096" t="inlineStr"/>
       <c r="D1096" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59468,7 +59433,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1097" t="inlineStr"/>
       <c r="D1097" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59492,7 +59456,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1098" t="inlineStr"/>
       <c r="D1098" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59516,7 +59479,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1099" t="inlineStr"/>
       <c r="D1099" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59540,7 +59502,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1100" t="inlineStr"/>
       <c r="D1100" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59564,7 +59525,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1101" t="inlineStr"/>
       <c r="D1101" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59588,7 +59548,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1102" t="inlineStr"/>
       <c r="D1102" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59612,7 +59571,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1103" t="inlineStr"/>
       <c r="D1103" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59636,7 +59594,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1104" t="inlineStr"/>
       <c r="D1104" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59660,7 +59617,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1105" t="inlineStr"/>
       <c r="D1105" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59684,7 +59640,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1106" t="inlineStr"/>
       <c r="D1106" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59708,7 +59663,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1107" t="inlineStr"/>
       <c r="D1107" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59732,7 +59686,6 @@
           <t>MUR</t>
         </is>
       </c>
-      <c r="C1108" t="inlineStr"/>
       <c r="D1108" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59756,7 +59709,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1109" t="inlineStr"/>
       <c r="D1109" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59780,7 +59732,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1110" t="inlineStr"/>
       <c r="D1110" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59804,7 +59755,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1111" t="inlineStr"/>
       <c r="D1111" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59828,7 +59778,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1112" t="inlineStr"/>
       <c r="D1112" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59852,7 +59801,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1113" t="inlineStr"/>
       <c r="D1113" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59876,7 +59824,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1114" t="inlineStr"/>
       <c r="D1114" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59900,7 +59847,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1115" t="inlineStr"/>
       <c r="D1115" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59924,7 +59870,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C1116" t="inlineStr"/>
       <c r="D1116" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59948,7 +59893,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1117" t="inlineStr"/>
       <c r="D1117" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59972,7 +59916,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1118" t="inlineStr"/>
       <c r="D1118" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -59996,7 +59939,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1119" t="inlineStr"/>
       <c r="D1119" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -60020,7 +59962,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1120" t="inlineStr"/>
       <c r="D1120" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -60044,7 +59985,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1121" t="inlineStr"/>
       <c r="D1121" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -60068,7 +60008,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1122" t="inlineStr"/>
       <c r="D1122" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -60092,7 +60031,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1123" t="inlineStr"/>
       <c r="D1123" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -60116,7 +60054,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1124" t="inlineStr"/>
       <c r="D1124" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -60140,7 +60077,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1125" t="inlineStr"/>
       <c r="D1125" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -60164,7 +60100,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1126" t="inlineStr"/>
       <c r="D1126" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -60189,7 +60124,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1127" t="inlineStr"/>
       <c r="D1127" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60214,7 +60148,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1128" t="inlineStr"/>
       <c r="D1128" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60239,7 +60172,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1129" t="inlineStr"/>
       <c r="D1129" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60264,7 +60196,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1130" t="inlineStr"/>
       <c r="D1130" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60289,7 +60220,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1131" t="inlineStr"/>
       <c r="D1131" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60314,7 +60244,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1132" t="inlineStr"/>
       <c r="D1132" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60339,7 +60268,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1133" t="inlineStr"/>
       <c r="D1133" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60364,7 +60292,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1134" t="inlineStr"/>
       <c r="D1134" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60389,7 +60316,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1135" t="inlineStr"/>
       <c r="D1135" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60414,7 +60340,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1136" t="inlineStr"/>
       <c r="D1136" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60439,7 +60364,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1137" t="inlineStr"/>
       <c r="D1137" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60464,7 +60388,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1138" t="inlineStr"/>
       <c r="D1138" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60489,7 +60412,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1139" t="inlineStr"/>
       <c r="D1139" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60514,7 +60436,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1140" t="inlineStr"/>
       <c r="D1140" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60539,7 +60460,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1141" t="inlineStr"/>
       <c r="D1141" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60564,7 +60484,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1142" t="inlineStr"/>
       <c r="D1142" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60589,7 +60508,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1143" t="inlineStr"/>
       <c r="D1143" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60614,7 +60532,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1144" t="inlineStr"/>
       <c r="D1144" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60639,7 +60556,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1145" t="inlineStr"/>
       <c r="D1145" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60664,7 +60580,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1146" t="inlineStr"/>
       <c r="D1146" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60689,7 +60604,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1147" t="inlineStr"/>
       <c r="D1147" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60714,7 +60628,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1148" t="inlineStr"/>
       <c r="D1148" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60739,7 +60652,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1149" t="inlineStr"/>
       <c r="D1149" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60764,7 +60676,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1150" t="inlineStr"/>
       <c r="D1150" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60789,7 +60700,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1151" t="inlineStr"/>
       <c r="D1151" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60814,7 +60724,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1152" t="inlineStr"/>
       <c r="D1152" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60839,7 +60748,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1153" t="inlineStr"/>
       <c r="D1153" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60864,7 +60772,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1154" t="inlineStr"/>
       <c r="D1154" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60889,7 +60796,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1155" t="inlineStr"/>
       <c r="D1155" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60914,7 +60820,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1156" t="inlineStr"/>
       <c r="D1156" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60939,7 +60844,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1157" t="inlineStr"/>
       <c r="D1157" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60964,7 +60868,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1158" t="inlineStr"/>
       <c r="D1158" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -60989,7 +60892,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1159" t="inlineStr"/>
       <c r="D1159" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61014,7 +60916,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1160" t="inlineStr"/>
       <c r="D1160" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61039,7 +60940,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1161" t="inlineStr"/>
       <c r="D1161" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61064,7 +60964,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1162" t="inlineStr"/>
       <c r="D1162" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61089,7 +60988,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1163" t="inlineStr"/>
       <c r="D1163" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61114,7 +61012,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1164" t="inlineStr"/>
       <c r="D1164" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61139,7 +61036,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1165" t="inlineStr"/>
       <c r="D1165" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61164,7 +61060,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1166" t="inlineStr"/>
       <c r="D1166" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61189,7 +61084,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1167" t="inlineStr"/>
       <c r="D1167" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61214,7 +61108,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1168" t="inlineStr"/>
       <c r="D1168" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61239,7 +61132,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1169" t="inlineStr"/>
       <c r="D1169" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61264,7 +61156,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1170" t="inlineStr"/>
       <c r="D1170" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61289,7 +61180,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1171" t="inlineStr"/>
       <c r="D1171" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61314,7 +61204,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1172" t="inlineStr"/>
       <c r="D1172" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61339,7 +61228,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1173" t="inlineStr"/>
       <c r="D1173" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61364,7 +61252,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1174" t="inlineStr"/>
       <c r="D1174" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61389,7 +61276,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1175" t="inlineStr"/>
       <c r="D1175" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61414,7 +61300,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1176" t="inlineStr"/>
       <c r="D1176" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61439,7 +61324,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1177" t="inlineStr"/>
       <c r="D1177" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61464,7 +61348,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1178" t="inlineStr"/>
       <c r="D1178" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61489,7 +61372,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1179" t="inlineStr"/>
       <c r="D1179" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61514,7 +61396,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1180" t="inlineStr"/>
       <c r="D1180" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61539,7 +61420,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1181" t="inlineStr"/>
       <c r="D1181" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61564,7 +61444,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1182" t="inlineStr"/>
       <c r="D1182" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61589,7 +61468,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1183" t="inlineStr"/>
       <c r="D1183" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61614,7 +61492,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1184" t="inlineStr"/>
       <c r="D1184" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61639,7 +61516,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1185" t="inlineStr"/>
       <c r="D1185" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61664,7 +61540,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1186" t="inlineStr"/>
       <c r="D1186" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61689,7 +61564,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1187" t="inlineStr"/>
       <c r="D1187" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61714,7 +61588,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1188" t="inlineStr"/>
       <c r="D1188" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61739,7 +61612,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1189" t="inlineStr"/>
       <c r="D1189" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61764,7 +61636,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1190" t="inlineStr"/>
       <c r="D1190" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61789,7 +61660,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1191" t="inlineStr"/>
       <c r="D1191" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61814,7 +61684,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1192" t="inlineStr"/>
       <c r="D1192" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61839,7 +61708,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1193" t="inlineStr"/>
       <c r="D1193" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61864,7 +61732,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1194" t="inlineStr"/>
       <c r="D1194" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61889,7 +61756,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1195" t="inlineStr"/>
       <c r="D1195" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61914,7 +61780,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1196" t="inlineStr"/>
       <c r="D1196" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61939,7 +61804,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1197" t="inlineStr"/>
       <c r="D1197" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61964,7 +61828,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1198" t="inlineStr"/>
       <c r="D1198" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -61989,7 +61852,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1199" t="inlineStr"/>
       <c r="D1199" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62014,7 +61876,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1200" t="inlineStr"/>
       <c r="D1200" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62039,7 +61900,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1201" t="inlineStr"/>
       <c r="D1201" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62064,7 +61924,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1202" t="inlineStr"/>
       <c r="D1202" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62089,7 +61948,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1203" t="inlineStr"/>
       <c r="D1203" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62114,7 +61972,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1204" t="inlineStr"/>
       <c r="D1204" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62139,7 +61996,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1205" t="inlineStr"/>
       <c r="D1205" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62164,7 +62020,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1206" t="inlineStr"/>
       <c r="D1206" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62189,7 +62044,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C1207" t="inlineStr"/>
       <c r="D1207" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62213,7 +62067,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1208" t="inlineStr"/>
       <c r="D1208" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62237,7 +62090,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1209" t="inlineStr"/>
       <c r="D1209" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62261,7 +62113,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1210" t="inlineStr"/>
       <c r="D1210" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62285,7 +62136,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1211" t="inlineStr"/>
       <c r="D1211" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62309,7 +62159,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1212" t="inlineStr"/>
       <c r="D1212" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62333,7 +62182,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1213" t="inlineStr"/>
       <c r="D1213" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62357,7 +62205,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1214" t="inlineStr"/>
       <c r="D1214" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62381,7 +62228,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1215" t="inlineStr"/>
       <c r="D1215" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -62392,6 +62238,706 @@
       </c>
       <c r="BB1215" t="n">
         <v>7984</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>〔状態B〕ホワイトキュレムEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr"/>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1216" t="n">
+        <v>2490</v>
+      </c>
+      <c r="BF1216" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>〔状態C〕レシラム
+その他]</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr"/>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1217" t="n">
+        <v>2180</v>
+      </c>
+      <c r="BF1217" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミカンのまなざし
+SV8]</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr"/>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1218" t="n">
+        <v>2480</v>
+      </c>
+      <c r="BF1218" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>〔状態B〕フーディンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr"/>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1219" t="n">
+        <v>2380</v>
+      </c>
+      <c r="BF1219" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>〔状態A-〕チョボマキ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr"/>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1220" t="n">
+        <v>830</v>
+      </c>
+      <c r="BF1220" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メラルバ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr"/>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1221" t="n">
+        <v>730</v>
+      </c>
+      <c r="BF1221" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のサカキ
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr"/>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1222" t="n">
+        <v>1780</v>
+      </c>
+      <c r="BF1222" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サーファー
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr"/>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1223" t="n">
+        <v>730</v>
+      </c>
+      <c r="BF1223" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルギア(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr"/>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1224" t="n">
+        <v>29800</v>
+      </c>
+      <c r="BF1224" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ともだちてちょう
+その他]</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr"/>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1225" t="n">
+        <v>70800</v>
+      </c>
+      <c r="BF1225" t="n">
+        <v>56640</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>〔状態A-〕クレッフィ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr"/>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1226" t="n">
+        <v>380</v>
+      </c>
+      <c r="BF1226" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トドロクツキex
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr"/>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1227" t="n">
+        <v>1290</v>
+      </c>
+      <c r="BF1227" t="n">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シャワーズ(YU NAGABA)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr"/>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1228" t="n">
+        <v>12800</v>
+      </c>
+      <c r="BF1228" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>〔状態B〕グレイシア(YU NAGABA)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr"/>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1229" t="n">
+        <v>9980</v>
+      </c>
+      <c r="BF1229" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フシギダネ
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr"/>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1230" t="n">
+        <v>3580</v>
+      </c>
+      <c r="BF1230" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーV
+S10b]</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr"/>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1231" t="n">
+        <v>2780</v>
+      </c>
+      <c r="BF1231" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr"/>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1232" t="n">
+        <v>490</v>
+      </c>
+      <c r="BF1232" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>〔状態A-〕デカヌチャンex
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr"/>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1233" t="n">
+        <v>490</v>
+      </c>
+      <c r="BF1233" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>〔状態A-〕センパイとコウハイ(20thアニバーサリー)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr"/>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1234" t="n">
+        <v>44800</v>
+      </c>
+      <c r="BF1234" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ププリン
+その他]</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr"/>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1235" t="n">
+        <v>630</v>
+      </c>
+      <c r="BF1235" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コイル
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr"/>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1236" t="n">
+        <v>450</v>
+      </c>
+      <c r="BF1236" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr"/>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1237" t="n">
+        <v>1890</v>
+      </c>
+      <c r="BF1237" t="n">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ペルシアンGX
+sm10]</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr"/>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1238" t="n">
+        <v>380</v>
+      </c>
+      <c r="BF1238" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドータクン
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr"/>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1239" t="n">
+        <v>680</v>
+      </c>
+      <c r="BF1239" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カプ・ブルルGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr"/>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1240" t="n">
+        <v>3280</v>
+      </c>
+      <c r="BF1240" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハラ
+sm2]</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr"/>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1241" t="n">
+        <v>2180</v>
+      </c>
+      <c r="BF1241" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>〔状態B〕ドータクンBREAK
+XY]</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr"/>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1242" t="n">
+        <v>2780</v>
+      </c>
+      <c r="BF1242" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ホップ(SR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr"/>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BE1243" t="n">
+        <v>1890</v>
+      </c>
+      <c r="BF1243" t="n">
+        <v>1512</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1243"/>
+  <dimension ref="A1:BL1368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33478,6 +33478,26 @@
           <t>2026-06-17_diff</t>
         </is>
       </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>2026-06-18_price</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>2026-06-18_buy</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>2026-06-18_ratio</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>2026-06-18_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -62252,7 +62272,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1216" t="inlineStr"/>
       <c r="D1216" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62277,7 +62296,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1217" t="inlineStr"/>
       <c r="D1217" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62302,7 +62320,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1218" t="inlineStr"/>
       <c r="D1218" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62327,7 +62344,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1219" t="inlineStr"/>
       <c r="D1219" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62352,7 +62368,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1220" t="inlineStr"/>
       <c r="D1220" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62377,7 +62392,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1221" t="inlineStr"/>
       <c r="D1221" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62402,7 +62416,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1222" t="inlineStr"/>
       <c r="D1222" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62427,7 +62440,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1223" t="inlineStr"/>
       <c r="D1223" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62452,7 +62464,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1224" t="inlineStr"/>
       <c r="D1224" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62477,7 +62488,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1225" t="inlineStr"/>
       <c r="D1225" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62502,7 +62512,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1226" t="inlineStr"/>
       <c r="D1226" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62527,7 +62536,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1227" t="inlineStr"/>
       <c r="D1227" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62552,7 +62560,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1228" t="inlineStr"/>
       <c r="D1228" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62577,7 +62584,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1229" t="inlineStr"/>
       <c r="D1229" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62602,7 +62608,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1230" t="inlineStr"/>
       <c r="D1230" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62627,7 +62632,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1231" t="inlineStr"/>
       <c r="D1231" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62652,7 +62656,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1232" t="inlineStr"/>
       <c r="D1232" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62677,7 +62680,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1233" t="inlineStr"/>
       <c r="D1233" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62702,7 +62704,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1234" t="inlineStr"/>
       <c r="D1234" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62727,7 +62728,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1235" t="inlineStr"/>
       <c r="D1235" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62752,7 +62752,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1236" t="inlineStr"/>
       <c r="D1236" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62777,7 +62776,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1237" t="inlineStr"/>
       <c r="D1237" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62802,7 +62800,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1238" t="inlineStr"/>
       <c r="D1238" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62827,7 +62824,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1239" t="inlineStr"/>
       <c r="D1239" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62852,7 +62848,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1240" t="inlineStr"/>
       <c r="D1240" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62877,7 +62872,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1241" t="inlineStr"/>
       <c r="D1241" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62902,7 +62896,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1242" t="inlineStr"/>
       <c r="D1242" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62927,7 +62920,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1243" t="inlineStr"/>
       <c r="D1243" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62938,6 +62930,3094 @@
       </c>
       <c r="BF1243" t="n">
         <v>1512</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕オーヤマのピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr"/>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1244" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="BJ1244" t="n">
+        <v>1104000</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MガルーラEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr"/>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1245" t="n">
+        <v>4490</v>
+      </c>
+      <c r="BJ1245" t="n">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケパッド
+M-P]</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr"/>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1246" t="n">
+        <v>450</v>
+      </c>
+      <c r="BJ1246" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>〔状態B〕オドリドリex
+M2]</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr"/>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1247" t="n">
+        <v>5480</v>
+      </c>
+      <c r="BJ1247" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バオッキー
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr"/>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1248" t="n">
+        <v>930</v>
+      </c>
+      <c r="BJ1248" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>〔状態B〕バッフロンex
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr"/>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1249" t="n">
+        <v>320</v>
+      </c>
+      <c r="BJ1249" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のニャース
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr"/>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1250" t="n">
+        <v>1690</v>
+      </c>
+      <c r="BJ1250" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>〔状態B〕オクタン
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr"/>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1251" t="n">
+        <v>320</v>
+      </c>
+      <c r="BJ1251" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラプラス(ジャンボカード)
+ジャンボカード]</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr"/>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1252" t="n">
+        <v>330</v>
+      </c>
+      <c r="BJ1252" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>〔状態B〕なみのりピカチュウV(25th)
+S8a]</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr"/>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1253" t="n">
+        <v>1190</v>
+      </c>
+      <c r="BJ1253" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>〔状態B〕タイム
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr"/>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1254" t="n">
+        <v>220</v>
+      </c>
+      <c r="BJ1254" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ダーテング
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr"/>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1255" t="n">
+        <v>680</v>
+      </c>
+      <c r="BJ1255" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハネッコ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr"/>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1256" t="n">
+        <v>260</v>
+      </c>
+      <c r="BJ1256" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr"/>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1257" t="n">
+        <v>59800</v>
+      </c>
+      <c r="BJ1257" t="n">
+        <v>47840</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本炎エネルギー(SVデザイン/CL2023)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr"/>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1258" t="n">
+        <v>630</v>
+      </c>
+      <c r="BJ1258" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リザードンex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr"/>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1259" t="n">
+        <v>70800</v>
+      </c>
+      <c r="BJ1259" t="n">
+        <v>56640</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バサギリV
+S10P]</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr"/>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1260" t="n">
+        <v>380</v>
+      </c>
+      <c r="BJ1260" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブランシェ
+S10b]</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr"/>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1261" t="n">
+        <v>280</v>
+      </c>
+      <c r="BJ1261" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ワナイダーex
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr"/>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1262" t="n">
+        <v>330</v>
+      </c>
+      <c r="BJ1262" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヒスイダイケンキVSTAR
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr"/>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1263" t="n">
+        <v>880</v>
+      </c>
+      <c r="BJ1263" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>〔状態B〕レジドラゴVSTAR
+S12]</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr"/>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1264" t="n">
+        <v>320</v>
+      </c>
+      <c r="BJ1264" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>〔状態A-〕炎のトーチ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr"/>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1265" t="n">
+        <v>930</v>
+      </c>
+      <c r="BJ1265" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr"/>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1266" t="n">
+        <v>1890</v>
+      </c>
+      <c r="BJ1266" t="n">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トゲピー＆ピィ＆ププリンGX(SA)
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr"/>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1267" t="n">
+        <v>65800</v>
+      </c>
+      <c r="BJ1267" t="n">
+        <v>52640</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サダイジャV
+s1a]</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr"/>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1268" t="n">
+        <v>380</v>
+      </c>
+      <c r="BJ1268" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プレシャスボール
+sm12]</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr"/>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1269" t="n">
+        <v>250</v>
+      </c>
+      <c r="BJ1269" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジュナイパーGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr"/>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1270" t="n">
+        <v>1680</v>
+      </c>
+      <c r="BJ1270" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カビゴンVMAX
+s1]</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr"/>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1271" t="n">
+        <v>8480</v>
+      </c>
+      <c r="BJ1271" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>〔状態B〕リザードンVSTAR
+S9]</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr"/>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1272" t="n">
+        <v>880</v>
+      </c>
+      <c r="BJ1272" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>〔状態B〕MゲンガーEX(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr"/>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1273" t="n">
+        <v>89800</v>
+      </c>
+      <c r="BJ1273" t="n">
+        <v>71840</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゴージャスボール(キラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr"/>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1274" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BJ1274" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>〔状態B〕レシラムEX(SR仕様)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr"/>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1275" t="n">
+        <v>31800</v>
+      </c>
+      <c r="BJ1275" t="n">
+        <v>25440</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本フェアリーエネルギー(ステーション)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr"/>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1276" t="n">
+        <v>320</v>
+      </c>
+      <c r="BJ1276" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>〔状態B〕バンギラスV
+S5I]</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr"/>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1277" t="n">
+        <v>1280</v>
+      </c>
+      <c r="BJ1277" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>〔状態C〕ラティオスEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr"/>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1278" t="n">
+        <v>17800</v>
+      </c>
+      <c r="BJ1278" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケモンブリーダーの育成
+S2a]</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr"/>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1279" t="n">
+        <v>1080</v>
+      </c>
+      <c r="BJ1279" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>〔状態B〕ダークライGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr"/>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1280" t="n">
+        <v>19800</v>
+      </c>
+      <c r="BJ1280" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブルーの探索
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr"/>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1281" t="n">
+        <v>44800</v>
+      </c>
+      <c r="BJ1281" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブラッキーGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr"/>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1282" t="n">
+        <v>69800</v>
+      </c>
+      <c r="BJ1282" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>〔状態B〕レシラム＆リザードンGX
+sm10]</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr"/>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1283" t="n">
+        <v>14800</v>
+      </c>
+      <c r="BJ1283" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>〔状態B〕フウロ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr"/>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1284" t="n">
+        <v>54800</v>
+      </c>
+      <c r="BJ1284" t="n">
+        <v>43840</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ホップのオーロット
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr"/>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1285" t="n">
+        <v>260</v>
+      </c>
+      <c r="BJ1285" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>ワタシラガV</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr"/>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1286" t="n">
+        <v>480</v>
+      </c>
+      <c r="BJ1286" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕サーナイトexδ-デルタ種(25th)</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr"/>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1287" t="n">
+        <v>18800</v>
+      </c>
+      <c r="BJ1287" t="n">
+        <v>15040</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>ブースター(YU NAGABA)</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr"/>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1288" t="n">
+        <v>14800</v>
+      </c>
+      <c r="BJ1288" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕レシラム＆リザードンGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr"/>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1289" t="n">
+        <v>338000</v>
+      </c>
+      <c r="BJ1289" t="n">
+        <v>270400</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>ヒードランGX</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr"/>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1290" t="n">
+        <v>780</v>
+      </c>
+      <c r="BJ1290" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キングドラex
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr"/>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1291" t="n">
+        <v>580</v>
+      </c>
+      <c r="BJ1291" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>グソクムシャex</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr"/>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1292" t="n">
+        <v>480</v>
+      </c>
+      <c r="BJ1292" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>グレイシア(YU NAGABA)</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr"/>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1293" t="n">
+        <v>13800</v>
+      </c>
+      <c r="BJ1293" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>キュレムVMAX</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr"/>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1294" t="n">
+        <v>280</v>
+      </c>
+      <c r="BJ1294" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>ヌオー</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr"/>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1295" t="n">
+        <v>2980</v>
+      </c>
+      <c r="BJ1295" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>メガスターミーex</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr"/>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1296" t="n">
+        <v>4980</v>
+      </c>
+      <c r="BJ1296" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>トウホクのピカチュウ(未開封)</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr"/>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1297" t="n">
+        <v>19800</v>
+      </c>
+      <c r="BJ1297" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>パーモット</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr"/>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1298" t="n">
+        <v>580</v>
+      </c>
+      <c r="BJ1298" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>トゲデマル</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr"/>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1299" t="n">
+        <v>2980</v>
+      </c>
+      <c r="BJ1299" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>エレザード</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr"/>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1300" t="n">
+        <v>480</v>
+      </c>
+      <c r="BJ1300" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>ミュウ(25th)</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr"/>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1301" t="n">
+        <v>43800</v>
+      </c>
+      <c r="BJ1301" t="n">
+        <v>35040</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>モグリュー</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr"/>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1302" t="n">
+        <v>880</v>
+      </c>
+      <c r="BJ1302" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>キョジオーン</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr"/>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1303" t="n">
+        <v>580</v>
+      </c>
+      <c r="BJ1303" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>アーボック</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr"/>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1304" t="n">
+        <v>980</v>
+      </c>
+      <c r="BJ1304" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ゲッコウガ＆ゾロアークGX</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr"/>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1305" t="n">
+        <v>45800</v>
+      </c>
+      <c r="BJ1305" t="n">
+        <v>36640</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>ゲノセクトex</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr"/>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1306" t="n">
+        <v>3480</v>
+      </c>
+      <c r="BJ1306" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>ガラルニャイキング</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr"/>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1307" t="n">
+        <v>380</v>
+      </c>
+      <c r="BJ1307" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>MサーナイトEX</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr"/>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1308" t="n">
+        <v>69800</v>
+      </c>
+      <c r="BJ1308" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>レジドラゴV</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr"/>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1309" t="n">
+        <v>480</v>
+      </c>
+      <c r="BJ1309" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>ガブリアス＆ギラティナGX</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr"/>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1310" t="n">
+        <v>8480</v>
+      </c>
+      <c r="BJ1310" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>ロケット団のニャース</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr"/>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1311" t="n">
+        <v>2480</v>
+      </c>
+      <c r="BJ1311" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>ルギアV(SA)</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr"/>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1312" t="n">
+        <v>178000</v>
+      </c>
+      <c r="BJ1312" t="n">
+        <v>142400</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>学習装置</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr"/>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1313" t="n">
+        <v>3280</v>
+      </c>
+      <c r="BJ1313" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>ランダムレシーバー</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr"/>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1314" t="n">
+        <v>16800</v>
+      </c>
+      <c r="BJ1314" t="n">
+        <v>13440</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>リーリエの決心</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr"/>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1315" t="n">
+        <v>9480</v>
+      </c>
+      <c r="BJ1315" t="n">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>コルサ</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr"/>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1316" t="n">
+        <v>480</v>
+      </c>
+      <c r="BJ1316" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>カシオペア</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr"/>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1317" t="n">
+        <v>980</v>
+      </c>
+      <c r="BJ1317" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ハプウ</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr"/>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1318" t="n">
+        <v>8980</v>
+      </c>
+      <c r="BJ1318" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>ネジキ</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr"/>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1319" t="n">
+        <v>480</v>
+      </c>
+      <c r="BJ1319" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>ルリナ(R仕様)</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr"/>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1320" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BJ1320" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>モミ</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr"/>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1321" t="n">
+        <v>5480</v>
+      </c>
+      <c r="BJ1321" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>ポケモンだいすきクラブ</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr"/>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BI1322" t="n">
+        <v>39800</v>
+      </c>
+      <c r="BJ1322" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マーイーカ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr"/>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1323" t="n">
+        <v>1390</v>
+      </c>
+      <c r="BJ1323" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピッピ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr"/>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1324" t="n">
+        <v>780</v>
+      </c>
+      <c r="BJ1324" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>〔状態C〕オドリドリex
+M2]</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr"/>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1325" t="n">
+        <v>3980</v>
+      </c>
+      <c r="BJ1325" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>〔状態C〕メロエッタ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr"/>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1326" t="n">
+        <v>380</v>
+      </c>
+      <c r="BJ1326" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>〔状態C〕ムウマ
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr"/>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1327" t="n">
+        <v>220</v>
+      </c>
+      <c r="BJ1327" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゲッコウガ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr"/>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1328" t="n">
+        <v>3280</v>
+      </c>
+      <c r="BJ1328" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>〔状態B〕ツツジ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr"/>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1329" t="n">
+        <v>280</v>
+      </c>
+      <c r="BJ1329" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>〔状態B〕ボーマンダEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr"/>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1330" t="n">
+        <v>1080</v>
+      </c>
+      <c r="BJ1330" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>〔状態C〕ナンジャモのタイカイデン
+SV9]</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr"/>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1331" t="n">
+        <v>230</v>
+      </c>
+      <c r="BJ1331" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポリゴンZ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr"/>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1332" t="n">
+        <v>2630</v>
+      </c>
+      <c r="BJ1332" t="n">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>〔状態C〕イシズマイ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr"/>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1333" t="n">
+        <v>680</v>
+      </c>
+      <c r="BJ1333" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラブカス
+その他]</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr"/>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1334" t="n">
+        <v>6480</v>
+      </c>
+      <c r="BJ1334" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>〔状態C〕プロトーガ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr"/>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1335" t="n">
+        <v>420</v>
+      </c>
+      <c r="BJ1335" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>〔状態C〕ギギギアル
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr"/>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1336" t="n">
+        <v>320</v>
+      </c>
+      <c r="BJ1336" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ペンドラー
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr"/>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1337" t="n">
+        <v>830</v>
+      </c>
+      <c r="BJ1337" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サーナイト
+その他]</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr"/>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1338" t="n">
+        <v>3580</v>
+      </c>
+      <c r="BJ1338" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>〔状態C〕ロケット団のソーナンス
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr"/>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1339" t="n">
+        <v>230</v>
+      </c>
+      <c r="BJ1339" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のファイヤーex
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr"/>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1340" t="n">
+        <v>350</v>
+      </c>
+      <c r="BJ1340" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>〔状態B〕シロナのガブリアスex
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr"/>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1341" t="n">
+        <v>24800</v>
+      </c>
+      <c r="BJ1341" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>〔状態C〕ブビィ
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr"/>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1342" t="n">
+        <v>380</v>
+      </c>
+      <c r="BJ1342" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アンノーンV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr"/>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1343" t="n">
+        <v>260</v>
+      </c>
+      <c r="BJ1343" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本水エネルギー(レッドコレクション)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr"/>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1344" t="n">
+        <v>780</v>
+      </c>
+      <c r="BJ1344" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マスターのカギ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr"/>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1345" t="n">
+        <v>2180000</v>
+      </c>
+      <c r="BJ1345" t="n">
+        <v>1744000</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パラダイスリゾート(2024/英語版)
+海外版]</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr"/>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1346" t="n">
+        <v>24800</v>
+      </c>
+      <c r="BJ1346" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本闘エネルギー(チャンピオンズリーグ2025)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr"/>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1347" t="n">
+        <v>680</v>
+      </c>
+      <c r="BJ1347" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>〔状態C〕メガミミロップ＆プリンGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr"/>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1348" t="n">
+        <v>690</v>
+      </c>
+      <c r="BJ1348" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>〔状態B〕バトルサーチャー
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr"/>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1349" t="n">
+        <v>980</v>
+      </c>
+      <c r="BJ1349" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>〔状態C〕ダークルギア(ジャンボカード)
+ジャンボカード]</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr"/>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1350" t="n">
+        <v>4980</v>
+      </c>
+      <c r="BJ1350" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>〔状態C〕ランターン(マクドナルド)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr"/>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1351" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BJ1351" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>〔状態C〕モトトカゲ(コロコロイチバン)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr"/>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1352" t="n">
+        <v>230</v>
+      </c>
+      <c r="BJ1352" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>〔状態C〕マサキの転送
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr"/>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1353" t="n">
+        <v>320</v>
+      </c>
+      <c r="BJ1353" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルカリオVSTAR
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr"/>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1354" t="n">
+        <v>1190</v>
+      </c>
+      <c r="BJ1354" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>〔状態C〕さぎょういん
+S12]</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr"/>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1355" t="n">
+        <v>220</v>
+      </c>
+      <c r="BJ1355" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>〔状態B〕スナバァ
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr"/>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1356" t="n">
+        <v>380</v>
+      </c>
+      <c r="BJ1356" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>〔状態C〕サワロ
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr"/>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1357" t="n">
+        <v>280</v>
+      </c>
+      <c r="BJ1357" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブラッキー(YU NAGABA)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr"/>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1358" t="n">
+        <v>15800</v>
+      </c>
+      <c r="BJ1358" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポピー
+SV3]</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr"/>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1359" t="n">
+        <v>1190</v>
+      </c>
+      <c r="BJ1359" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ザルードV(当選通知書付き)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr"/>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1360" t="n">
+        <v>21800</v>
+      </c>
+      <c r="BJ1360" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ(ポケモンカードファンクラブ)
+旧裏]</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr"/>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1361" t="n">
+        <v>428000</v>
+      </c>
+      <c r="BJ1361" t="n">
+        <v>342400</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フウとラン
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr"/>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1362" t="n">
+        <v>330</v>
+      </c>
+      <c r="BJ1362" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>〔状態C〕基本雷エネルギー(SVデザイン)
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr"/>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1363" t="n">
+        <v>1080</v>
+      </c>
+      <c r="BJ1363" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>〔状態B〕ディンルーex
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr"/>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1364" t="n">
+        <v>420</v>
+      </c>
+      <c r="BJ1364" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シルヴァディGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr"/>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1365" t="n">
+        <v>260</v>
+      </c>
+      <c r="BJ1365" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲッコウガ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr"/>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1366" t="n">
+        <v>1490</v>
+      </c>
+      <c r="BJ1366" t="n">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>〔状態B〕フシギバナEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr"/>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1367" t="n">
+        <v>890</v>
+      </c>
+      <c r="BJ1367" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>〔状態C〕カイオーガex(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr"/>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BI1368" t="n">
+        <v>49800</v>
+      </c>
+      <c r="BJ1368" t="n">
+        <v>39840</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL1368"/>
+  <dimension ref="A1:BP1370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33498,6 +33498,26 @@
           <t>2026-06-18_diff</t>
         </is>
       </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>2026-06-19_price</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>2026-06-19_buy</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>2026-06-19_ratio</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>2026-06-19_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -62943,7 +62963,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1244" t="inlineStr"/>
       <c r="D1244" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62968,7 +62987,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1245" t="inlineStr"/>
       <c r="D1245" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -62993,7 +63011,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1246" t="inlineStr"/>
       <c r="D1246" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63018,7 +63035,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1247" t="inlineStr"/>
       <c r="D1247" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63043,7 +63059,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1248" t="inlineStr"/>
       <c r="D1248" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63068,7 +63083,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1249" t="inlineStr"/>
       <c r="D1249" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63093,7 +63107,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1250" t="inlineStr"/>
       <c r="D1250" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63118,7 +63131,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1251" t="inlineStr"/>
       <c r="D1251" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63143,7 +63155,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1252" t="inlineStr"/>
       <c r="D1252" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63168,7 +63179,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1253" t="inlineStr"/>
       <c r="D1253" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63193,7 +63203,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1254" t="inlineStr"/>
       <c r="D1254" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63218,7 +63227,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1255" t="inlineStr"/>
       <c r="D1255" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63243,7 +63251,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1256" t="inlineStr"/>
       <c r="D1256" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63268,7 +63275,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1257" t="inlineStr"/>
       <c r="D1257" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63293,7 +63299,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1258" t="inlineStr"/>
       <c r="D1258" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63318,7 +63323,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1259" t="inlineStr"/>
       <c r="D1259" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63343,7 +63347,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1260" t="inlineStr"/>
       <c r="D1260" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63368,7 +63371,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1261" t="inlineStr"/>
       <c r="D1261" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63393,7 +63395,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1262" t="inlineStr"/>
       <c r="D1262" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63418,7 +63419,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1263" t="inlineStr"/>
       <c r="D1263" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63443,7 +63443,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1264" t="inlineStr"/>
       <c r="D1264" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63468,7 +63467,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1265" t="inlineStr"/>
       <c r="D1265" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63493,7 +63491,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1266" t="inlineStr"/>
       <c r="D1266" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63518,7 +63515,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1267" t="inlineStr"/>
       <c r="D1267" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63543,7 +63539,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1268" t="inlineStr"/>
       <c r="D1268" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63568,7 +63563,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C1269" t="inlineStr"/>
       <c r="D1269" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63593,7 +63587,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1270" t="inlineStr"/>
       <c r="D1270" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63618,7 +63611,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1271" t="inlineStr"/>
       <c r="D1271" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63643,7 +63635,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1272" t="inlineStr"/>
       <c r="D1272" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63668,7 +63659,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1273" t="inlineStr"/>
       <c r="D1273" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63693,7 +63683,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1274" t="inlineStr"/>
       <c r="D1274" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63718,7 +63707,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1275" t="inlineStr"/>
       <c r="D1275" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63743,7 +63731,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1276" t="inlineStr"/>
       <c r="D1276" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63768,7 +63755,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1277" t="inlineStr"/>
       <c r="D1277" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63793,7 +63779,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1278" t="inlineStr"/>
       <c r="D1278" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63818,7 +63803,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1279" t="inlineStr"/>
       <c r="D1279" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63843,7 +63827,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1280" t="inlineStr"/>
       <c r="D1280" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63868,7 +63851,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1281" t="inlineStr"/>
       <c r="D1281" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63893,7 +63875,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1282" t="inlineStr"/>
       <c r="D1282" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63918,7 +63899,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1283" t="inlineStr"/>
       <c r="D1283" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63943,7 +63923,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1284" t="inlineStr"/>
       <c r="D1284" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63968,7 +63947,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1285" t="inlineStr"/>
       <c r="D1285" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -63992,7 +63970,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1286" t="inlineStr"/>
       <c r="D1286" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64016,7 +63993,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1287" t="inlineStr"/>
       <c r="D1287" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64040,7 +64016,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1288" t="inlineStr"/>
       <c r="D1288" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64064,7 +64039,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1289" t="inlineStr"/>
       <c r="D1289" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64088,7 +64062,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1290" t="inlineStr"/>
       <c r="D1290" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64113,7 +64086,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1291" t="inlineStr"/>
       <c r="D1291" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64137,7 +64109,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1292" t="inlineStr"/>
       <c r="D1292" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64161,7 +64132,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1293" t="inlineStr"/>
       <c r="D1293" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64185,7 +64155,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1294" t="inlineStr"/>
       <c r="D1294" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64209,7 +64178,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1295" t="inlineStr"/>
       <c r="D1295" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64233,7 +64201,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1296" t="inlineStr"/>
       <c r="D1296" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64257,7 +64224,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1297" t="inlineStr"/>
       <c r="D1297" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64281,7 +64247,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1298" t="inlineStr"/>
       <c r="D1298" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64305,7 +64270,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1299" t="inlineStr"/>
       <c r="D1299" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64329,7 +64293,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1300" t="inlineStr"/>
       <c r="D1300" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64353,7 +64316,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1301" t="inlineStr"/>
       <c r="D1301" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64377,7 +64339,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1302" t="inlineStr"/>
       <c r="D1302" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64401,7 +64362,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1303" t="inlineStr"/>
       <c r="D1303" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64425,7 +64385,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1304" t="inlineStr"/>
       <c r="D1304" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64449,7 +64408,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1305" t="inlineStr"/>
       <c r="D1305" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64473,7 +64431,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1306" t="inlineStr"/>
       <c r="D1306" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64497,7 +64454,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1307" t="inlineStr"/>
       <c r="D1307" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64521,7 +64477,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1308" t="inlineStr"/>
       <c r="D1308" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64545,7 +64500,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1309" t="inlineStr"/>
       <c r="D1309" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64569,7 +64523,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1310" t="inlineStr"/>
       <c r="D1310" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64593,7 +64546,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1311" t="inlineStr"/>
       <c r="D1311" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64617,7 +64569,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1312" t="inlineStr"/>
       <c r="D1312" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64641,7 +64592,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1313" t="inlineStr"/>
       <c r="D1313" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64665,7 +64615,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1314" t="inlineStr"/>
       <c r="D1314" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64689,7 +64638,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1315" t="inlineStr"/>
       <c r="D1315" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64713,7 +64661,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1316" t="inlineStr"/>
       <c r="D1316" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64737,7 +64684,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1317" t="inlineStr"/>
       <c r="D1317" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64761,7 +64707,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1318" t="inlineStr"/>
       <c r="D1318" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64785,7 +64730,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1319" t="inlineStr"/>
       <c r="D1319" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64809,7 +64753,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1320" t="inlineStr"/>
       <c r="D1320" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64833,7 +64776,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1321" t="inlineStr"/>
       <c r="D1321" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64857,7 +64799,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1322" t="inlineStr"/>
       <c r="D1322" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -64882,7 +64823,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1323" t="inlineStr"/>
       <c r="D1323" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -64907,7 +64847,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1324" t="inlineStr"/>
       <c r="D1324" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -64932,7 +64871,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1325" t="inlineStr"/>
       <c r="D1325" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -64957,7 +64895,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1326" t="inlineStr"/>
       <c r="D1326" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -64982,7 +64919,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1327" t="inlineStr"/>
       <c r="D1327" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65007,7 +64943,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1328" t="inlineStr"/>
       <c r="D1328" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65032,7 +64967,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1329" t="inlineStr"/>
       <c r="D1329" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65057,7 +64991,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1330" t="inlineStr"/>
       <c r="D1330" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65082,7 +65015,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1331" t="inlineStr"/>
       <c r="D1331" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65107,7 +65039,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1332" t="inlineStr"/>
       <c r="D1332" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65132,7 +65063,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1333" t="inlineStr"/>
       <c r="D1333" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65157,7 +65087,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1334" t="inlineStr"/>
       <c r="D1334" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65182,7 +65111,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1335" t="inlineStr"/>
       <c r="D1335" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65207,7 +65135,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1336" t="inlineStr"/>
       <c r="D1336" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65232,7 +65159,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1337" t="inlineStr"/>
       <c r="D1337" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65257,7 +65183,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1338" t="inlineStr"/>
       <c r="D1338" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65282,7 +65207,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1339" t="inlineStr"/>
       <c r="D1339" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65307,7 +65231,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1340" t="inlineStr"/>
       <c r="D1340" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65332,7 +65255,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1341" t="inlineStr"/>
       <c r="D1341" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65357,7 +65279,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1342" t="inlineStr"/>
       <c r="D1342" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65382,7 +65303,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1343" t="inlineStr"/>
       <c r="D1343" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65407,7 +65327,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1344" t="inlineStr"/>
       <c r="D1344" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65432,7 +65351,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1345" t="inlineStr"/>
       <c r="D1345" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65457,7 +65375,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1346" t="inlineStr"/>
       <c r="D1346" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65482,7 +65399,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1347" t="inlineStr"/>
       <c r="D1347" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65507,7 +65423,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1348" t="inlineStr"/>
       <c r="D1348" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65532,7 +65447,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1349" t="inlineStr"/>
       <c r="D1349" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65557,7 +65471,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1350" t="inlineStr"/>
       <c r="D1350" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65582,7 +65495,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1351" t="inlineStr"/>
       <c r="D1351" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65607,7 +65519,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1352" t="inlineStr"/>
       <c r="D1352" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65632,7 +65543,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1353" t="inlineStr"/>
       <c r="D1353" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65657,7 +65567,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1354" t="inlineStr"/>
       <c r="D1354" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65682,7 +65591,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1355" t="inlineStr"/>
       <c r="D1355" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65707,7 +65615,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1356" t="inlineStr"/>
       <c r="D1356" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65732,7 +65639,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1357" t="inlineStr"/>
       <c r="D1357" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65757,7 +65663,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1358" t="inlineStr"/>
       <c r="D1358" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65782,7 +65687,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1359" t="inlineStr"/>
       <c r="D1359" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65807,7 +65711,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1360" t="inlineStr"/>
       <c r="D1360" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65832,7 +65735,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1361" t="inlineStr"/>
       <c r="D1361" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65857,7 +65759,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C1362" t="inlineStr"/>
       <c r="D1362" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65882,7 +65783,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1363" t="inlineStr"/>
       <c r="D1363" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65907,7 +65807,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1364" t="inlineStr"/>
       <c r="D1364" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65932,7 +65831,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1365" t="inlineStr"/>
       <c r="D1365" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65957,7 +65855,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1366" t="inlineStr"/>
       <c r="D1366" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -65982,7 +65879,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1367" t="inlineStr"/>
       <c r="D1367" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -66007,7 +65903,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1368" t="inlineStr"/>
       <c r="D1368" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -66018,6 +65913,55 @@
       </c>
       <c r="BJ1368" t="n">
         <v>39840</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>メガゲッコウガex</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr"/>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BM1369" t="n">
+        <v>380</v>
+      </c>
+      <c r="BN1369" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>〔状態B〕オドリドリex
+M2]</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr"/>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BM1370" t="n">
+        <v>5480</v>
+      </c>
+      <c r="BN1370" t="n">
+        <v>4384</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP1370"/>
+  <dimension ref="A1:BT1439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33518,6 +33518,26 @@
           <t>2026-06-19_diff</t>
         </is>
       </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>2026-06-20_price</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>2026-06-20_buy</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>2026-06-20_ratio</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>2026-06-20_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -65926,7 +65946,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1369" t="inlineStr"/>
       <c r="D1369" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -65951,7 +65970,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1370" t="inlineStr"/>
       <c r="D1370" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -65962,6 +65980,1703 @@
       </c>
       <c r="BN1370" t="n">
         <v>4384</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>〔状態A-〕クルマユ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr"/>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1371" t="n">
+        <v>930</v>
+      </c>
+      <c r="BR1371" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>〔状態B〕サーファー
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr"/>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1372" t="n">
+        <v>580</v>
+      </c>
+      <c r="BR1372" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハッサムex
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr"/>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1373" t="n">
+        <v>480</v>
+      </c>
+      <c r="BR1373" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>〔状態B〕MフーディンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr"/>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1374" t="n">
+        <v>3780</v>
+      </c>
+      <c r="BR1374" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カルボウ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr"/>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1375" t="n">
+        <v>330</v>
+      </c>
+      <c r="BR1375" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>〔状態B〕カメックスex
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr"/>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1376" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BR1376" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヒスイオオニューラV(SA)
+S10P]</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr"/>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1377" t="n">
+        <v>1380</v>
+      </c>
+      <c r="BR1377" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラパルトVMAX
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr"/>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1378" t="n">
+        <v>260</v>
+      </c>
+      <c r="BR1378" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ(ムンク/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr"/>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1379" t="n">
+        <v>368000</v>
+      </c>
+      <c r="BR1379" t="n">
+        <v>294400</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リーフィアV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr"/>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1380" t="n">
+        <v>450</v>
+      </c>
+      <c r="BR1380" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>〔状態A-〕火消し姿のピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr"/>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1381" t="n">
+        <v>288000</v>
+      </c>
+      <c r="BR1381" t="n">
+        <v>230400</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本鋼エネルギー(ストライプ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr"/>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1382" t="n">
+        <v>2350</v>
+      </c>
+      <c r="BR1382" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミミッキュVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr"/>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1383" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BR1383" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本雷エネルギー(DPキラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr"/>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1384" t="n">
+        <v>6480</v>
+      </c>
+      <c r="BR1384" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MライボルトEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr"/>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1385" t="n">
+        <v>2290</v>
+      </c>
+      <c r="BR1385" t="n">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ナタネ
+sm5]</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr"/>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1386" t="n">
+        <v>23800</v>
+      </c>
+      <c r="BR1386" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ＆カビゴンGX(SA)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr"/>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1387" t="n">
+        <v>39800</v>
+      </c>
+      <c r="BR1387" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カビゴン(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr"/>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1388" t="n">
+        <v>268000</v>
+      </c>
+      <c r="BR1388" t="n">
+        <v>214400</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>〔状態B〕ザマゼンタV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr"/>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1389" t="n">
+        <v>1080</v>
+      </c>
+      <c r="BR1389" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルカリオ＆メルメタルGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr"/>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1390" t="n">
+        <v>990</v>
+      </c>
+      <c r="BR1390" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルカリオEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr"/>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1391" t="n">
+        <v>70800</v>
+      </c>
+      <c r="BR1391" t="n">
+        <v>56640</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カビゴンVMAX
+s1]</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr"/>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1392" t="n">
+        <v>8480</v>
+      </c>
+      <c r="BR1392" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>〔状態B〕ボスごっこピカチュウ アクア団(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr"/>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1393" t="n">
+        <v>198000</v>
+      </c>
+      <c r="BR1393" t="n">
+        <v>158400</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>〔状態A-〕モルペコV-UNION
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr"/>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1394" t="n">
+        <v>2380</v>
+      </c>
+      <c r="BR1394" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>〔状態B〕マスタードれんげきのかた
+S5R]</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr"/>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1395" t="n">
+        <v>420</v>
+      </c>
+      <c r="BR1395" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>〔状態B〕ニンフィアVMAX
+S6a]</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr"/>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1396" t="n">
+        <v>290</v>
+      </c>
+      <c r="BR1396" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>〔状態B〕とりつかい
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr"/>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1397" t="n">
+        <v>480</v>
+      </c>
+      <c r="BR1397" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>〔状態B〕エンペルト
+その他]</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr"/>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1398" t="n">
+        <v>39800</v>
+      </c>
+      <c r="BR1398" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr"/>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1399" t="n">
+        <v>2580</v>
+      </c>
+      <c r="BR1399" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>〔状態B〕キョウの罠
+SM9a]</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr"/>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1400" t="n">
+        <v>680</v>
+      </c>
+      <c r="BR1400" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>〔状態C〕ファイヤー＆サンダー＆フリーザーGX
+sm10b]</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr"/>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1401" t="n">
+        <v>8480</v>
+      </c>
+      <c r="BR1401" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>〔状態B〕カイリューGX
+sm11]</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr"/>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1402" t="n">
+        <v>2580</v>
+      </c>
+      <c r="BR1402" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>〔状態B〕ザシアンV
+s1]</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr"/>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1403" t="n">
+        <v>530</v>
+      </c>
+      <c r="BR1403" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>〔状態B〕レシラム＆リザードンGX(SA)
+sm10]</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr"/>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1404" t="n">
+        <v>74800</v>
+      </c>
+      <c r="BR1404" t="n">
+        <v>59840</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>〔状態B〕マリィ
+s1]</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr"/>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1405" t="n">
+        <v>44800</v>
+      </c>
+      <c r="BR1405" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガゲンガーex
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr"/>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1406" t="n">
+        <v>60800</v>
+      </c>
+      <c r="BR1406" t="n">
+        <v>48640</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガカイリューex
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr"/>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1407" t="n">
+        <v>2290</v>
+      </c>
+      <c r="BR1407" t="n">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガゼラオラex
+M5]</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr"/>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1408" t="n">
+        <v>730</v>
+      </c>
+      <c r="BR1408" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>フシギソウ</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr"/>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1409" t="n">
+        <v>3480</v>
+      </c>
+      <c r="BR1409" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>アマージョGX</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr"/>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1410" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BR1410" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>フェローチェ＆マッシブーンGX</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr"/>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1411" t="n">
+        <v>2980</v>
+      </c>
+      <c r="BR1411" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>オーガポンかまどのめんex</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr"/>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1412" t="n">
+        <v>980</v>
+      </c>
+      <c r="BR1412" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>ニャビー</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr"/>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1413" t="n">
+        <v>1280</v>
+      </c>
+      <c r="BR1413" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>リザード</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr"/>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1414" t="n">
+        <v>3980</v>
+      </c>
+      <c r="BR1414" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>エースバーン</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr"/>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1415" t="n">
+        <v>280</v>
+      </c>
+      <c r="BR1415" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>シャワーズex</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr"/>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1416" t="n">
+        <v>480</v>
+      </c>
+      <c r="BR1416" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>〔状態B〕タッツー
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr"/>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1417" t="n">
+        <v>780</v>
+      </c>
+      <c r="BR1417" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>シャワーズ(YU NAGABA)</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr"/>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1418" t="n">
+        <v>13800</v>
+      </c>
+      <c r="BR1418" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>アローラキュウコンGX</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr"/>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1419" t="n">
+        <v>980</v>
+      </c>
+      <c r="BR1419" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>フリーザーGX</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr"/>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1420" t="n">
+        <v>2180</v>
+      </c>
+      <c r="BR1420" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>エリキテル</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr"/>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1421" t="n">
+        <v>580</v>
+      </c>
+      <c r="BR1421" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ピカチュウEX</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr"/>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1422" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="BR1422" t="n">
+        <v>992000</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ピカチュウ(R仕様)</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr"/>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1423" t="n">
+        <v>26800</v>
+      </c>
+      <c r="BR1423" t="n">
+        <v>21440</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>ユニラン</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr"/>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1424" t="n">
+        <v>2980</v>
+      </c>
+      <c r="BR1424" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>テツノブジンex</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr"/>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1425" t="n">
+        <v>1280</v>
+      </c>
+      <c r="BR1425" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>ミュウツーVSTAR</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr"/>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1426" t="n">
+        <v>22800</v>
+      </c>
+      <c r="BR1426" t="n">
+        <v>18240</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>エーフィVMAX(SA/未開封)</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr"/>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1427" t="n">
+        <v>59800</v>
+      </c>
+      <c r="BR1427" t="n">
+        <v>47840</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>ゲンシグラードンEX</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr"/>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1428" t="n">
+        <v>13800</v>
+      </c>
+      <c r="BR1428" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>バンギラスEX</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr"/>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1429" t="n">
+        <v>4980</v>
+      </c>
+      <c r="BR1429" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キチキギスex
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr"/>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1430" t="n">
+        <v>1430</v>
+      </c>
+      <c r="BR1430" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>アローラダグトリオ</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr"/>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1431" t="n">
+        <v>780</v>
+      </c>
+      <c r="BR1431" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>ザマゼンタV</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr"/>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1432" t="n">
+        <v>1680</v>
+      </c>
+      <c r="BR1432" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>ニダンギル</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr"/>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1433" t="n">
+        <v>580</v>
+      </c>
+      <c r="BR1433" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>アルセウス＆ディアルガ＆パルキアGX</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr"/>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1434" t="n">
+        <v>4780</v>
+      </c>
+      <c r="BR1434" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>トルネロス</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr"/>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1435" t="n">
+        <v>980</v>
+      </c>
+      <c r="BR1435" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>ふしぎなアメ</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr"/>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1436" t="n">
+        <v>280</v>
+      </c>
+      <c r="BR1436" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>基本水エネルギー(チャンピオンズリーグ2025)</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr"/>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1437" t="n">
+        <v>980</v>
+      </c>
+      <c r="BR1437" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>基本鋼エネルギー(DPキラ)</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr"/>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1438" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BR1438" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アセロラのいたずら
+M1S]</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr"/>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BQ1439" t="n">
+        <v>1690</v>
+      </c>
+      <c r="BR1439" t="n">
+        <v>1352</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT1439"/>
+  <dimension ref="A1:BX1439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33538,6 +33538,26 @@
           <t>2026-06-20_diff</t>
         </is>
       </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>2026-06-21_price</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>2026-06-21_buy</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>2026-06-21_ratio</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>2026-06-21_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -65994,7 +66014,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1371" t="inlineStr"/>
       <c r="D1371" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66019,7 +66038,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1372" t="inlineStr"/>
       <c r="D1372" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66044,7 +66062,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1373" t="inlineStr"/>
       <c r="D1373" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66069,7 +66086,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1374" t="inlineStr"/>
       <c r="D1374" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66094,7 +66110,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1375" t="inlineStr"/>
       <c r="D1375" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66119,7 +66134,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1376" t="inlineStr"/>
       <c r="D1376" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66144,7 +66158,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1377" t="inlineStr"/>
       <c r="D1377" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66169,7 +66182,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1378" t="inlineStr"/>
       <c r="D1378" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66194,7 +66206,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1379" t="inlineStr"/>
       <c r="D1379" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66219,7 +66230,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1380" t="inlineStr"/>
       <c r="D1380" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66244,7 +66254,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1381" t="inlineStr"/>
       <c r="D1381" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66269,7 +66278,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1382" t="inlineStr"/>
       <c r="D1382" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66294,7 +66302,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1383" t="inlineStr"/>
       <c r="D1383" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66319,7 +66326,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1384" t="inlineStr"/>
       <c r="D1384" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66344,7 +66350,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1385" t="inlineStr"/>
       <c r="D1385" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66369,7 +66374,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1386" t="inlineStr"/>
       <c r="D1386" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66394,7 +66398,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1387" t="inlineStr"/>
       <c r="D1387" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66419,7 +66422,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1388" t="inlineStr"/>
       <c r="D1388" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66444,7 +66446,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1389" t="inlineStr"/>
       <c r="D1389" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66469,7 +66470,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1390" t="inlineStr"/>
       <c r="D1390" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66494,7 +66494,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1391" t="inlineStr"/>
       <c r="D1391" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66519,7 +66518,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1392" t="inlineStr"/>
       <c r="D1392" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66544,7 +66542,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1393" t="inlineStr"/>
       <c r="D1393" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66569,7 +66566,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1394" t="inlineStr"/>
       <c r="D1394" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66594,7 +66590,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1395" t="inlineStr"/>
       <c r="D1395" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66619,7 +66614,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1396" t="inlineStr"/>
       <c r="D1396" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66644,7 +66638,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66669,7 +66662,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1398" t="inlineStr"/>
       <c r="D1398" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66694,7 +66686,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1399" t="inlineStr"/>
       <c r="D1399" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66719,7 +66710,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1400" t="inlineStr"/>
       <c r="D1400" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66744,7 +66734,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1401" t="inlineStr"/>
       <c r="D1401" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66769,7 +66758,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1402" t="inlineStr"/>
       <c r="D1402" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66794,7 +66782,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1403" t="inlineStr"/>
       <c r="D1403" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66819,7 +66806,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1404" t="inlineStr"/>
       <c r="D1404" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66844,7 +66830,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1405" t="inlineStr"/>
       <c r="D1405" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66869,7 +66854,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1406" t="inlineStr"/>
       <c r="D1406" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66894,7 +66878,6 @@
           <t>MA</t>
         </is>
       </c>
-      <c r="C1407" t="inlineStr"/>
       <c r="D1407" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66919,7 +66902,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1408" t="inlineStr"/>
       <c r="D1408" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66943,7 +66925,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1409" t="inlineStr"/>
       <c r="D1409" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66967,7 +66948,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1410" t="inlineStr"/>
       <c r="D1410" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -66991,7 +66971,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1411" t="inlineStr"/>
       <c r="D1411" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67015,7 +66994,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1412" t="inlineStr"/>
       <c r="D1412" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67039,7 +67017,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1413" t="inlineStr"/>
       <c r="D1413" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67063,7 +67040,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1414" t="inlineStr"/>
       <c r="D1414" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67087,7 +67063,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1415" t="inlineStr"/>
       <c r="D1415" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67111,7 +67086,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1416" t="inlineStr"/>
       <c r="D1416" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67136,7 +67110,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1417" t="inlineStr"/>
       <c r="D1417" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67160,7 +67133,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1418" t="inlineStr"/>
       <c r="D1418" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67184,7 +67156,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1419" t="inlineStr"/>
       <c r="D1419" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67208,7 +67179,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1420" t="inlineStr"/>
       <c r="D1420" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67232,7 +67202,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1421" t="inlineStr"/>
       <c r="D1421" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67256,7 +67225,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1422" t="inlineStr"/>
       <c r="D1422" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67280,7 +67248,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1423" t="inlineStr"/>
       <c r="D1423" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67304,7 +67271,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1424" t="inlineStr"/>
       <c r="D1424" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67328,7 +67294,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1425" t="inlineStr"/>
       <c r="D1425" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67352,7 +67317,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1426" t="inlineStr"/>
       <c r="D1426" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67376,7 +67340,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1427" t="inlineStr"/>
       <c r="D1427" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67400,7 +67363,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1428" t="inlineStr"/>
       <c r="D1428" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67424,7 +67386,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1429" t="inlineStr"/>
       <c r="D1429" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67449,7 +67410,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1430" t="inlineStr"/>
       <c r="D1430" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67473,7 +67433,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1431" t="inlineStr"/>
       <c r="D1431" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67497,7 +67456,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1432" t="inlineStr"/>
       <c r="D1432" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67521,7 +67479,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1433" t="inlineStr"/>
       <c r="D1433" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67545,7 +67502,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1434" t="inlineStr"/>
       <c r="D1434" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67569,7 +67525,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1435" t="inlineStr"/>
       <c r="D1435" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67593,7 +67548,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1436" t="inlineStr"/>
       <c r="D1436" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67617,7 +67571,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1437" t="inlineStr"/>
       <c r="D1437" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67641,7 +67594,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1438" t="inlineStr"/>
       <c r="D1438" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67666,7 +67618,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1439" t="inlineStr"/>
       <c r="D1439" t="inlineStr">
         <is>
           <t>zaiko_ari</t>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX1439"/>
+  <dimension ref="A1:CB1706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33558,6 +33558,26 @@
           <t>2026-06-21_diff</t>
         </is>
       </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>2026-06-22_price</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>2026-06-22_buy</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>2026-06-22_ratio</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>2026-06-22_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -67628,6 +67648,6551 @@
       </c>
       <c r="BR1439" t="n">
         <v>1352</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>〔状態B〕チュリネ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr"/>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1440" t="n">
+        <v>780</v>
+      </c>
+      <c r="BZ1440" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ボルケニオンex
+SV9]</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr"/>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1441" t="n">
+        <v>1880</v>
+      </c>
+      <c r="BZ1441" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マフォクシーBREAK
+XY]</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr"/>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1442" t="n">
+        <v>1680</v>
+      </c>
+      <c r="BZ1442" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラパルトex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr"/>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1443" t="n">
+        <v>2630</v>
+      </c>
+      <c r="BZ1443" t="n">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ナンジャモ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr"/>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1444" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1444" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>〔状態B〕ザングースδ-デルタ種(明治)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr"/>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1445" t="n">
+        <v>1080</v>
+      </c>
+      <c r="BZ1445" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ワザマシンエヴォリューション
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr"/>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1446" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1446" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミミッキュ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr"/>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1447" t="n">
+        <v>1990</v>
+      </c>
+      <c r="BZ1447" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブビィ
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr"/>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1448" t="n">
+        <v>730</v>
+      </c>
+      <c r="BZ1448" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケモンいれかえ
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr"/>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1449" t="n">
+        <v>1290</v>
+      </c>
+      <c r="BZ1449" t="n">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼニガメ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr"/>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1450" t="n">
+        <v>290</v>
+      </c>
+      <c r="BZ1450" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ペパー
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr"/>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1451" t="n">
+        <v>330</v>
+      </c>
+      <c r="BZ1451" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パーモット
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr"/>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1452" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1452" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ボタン
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr"/>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1453" t="n">
+        <v>2250</v>
+      </c>
+      <c r="BZ1453" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒスイビリリダマ
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr"/>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1454" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1454" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ(ムンク/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr"/>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1455" t="n">
+        <v>368000</v>
+      </c>
+      <c r="BZ1455" t="n">
+        <v>294400</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウッウ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr"/>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1456" t="n">
+        <v>65800</v>
+      </c>
+      <c r="BZ1456" t="n">
+        <v>52640</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr"/>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1457" t="n">
+        <v>44800</v>
+      </c>
+      <c r="BZ1457" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウルトラネクロズマGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr"/>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1458" t="n">
+        <v>260</v>
+      </c>
+      <c r="BZ1458" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>〔状態B〕ツツジ
+S9a]</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr"/>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1459" t="n">
+        <v>680</v>
+      </c>
+      <c r="BZ1459" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>〔状態C〕レックウザEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr"/>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1460" t="n">
+        <v>14800</v>
+      </c>
+      <c r="BZ1460" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リーフィアGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr"/>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1461" t="n">
+        <v>1530</v>
+      </c>
+      <c r="BZ1461" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レインボーブラシ
+sm7]</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr"/>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1462" t="n">
+        <v>990</v>
+      </c>
+      <c r="BZ1462" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スイレンのつりざお
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr"/>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1463" t="n">
+        <v>730</v>
+      </c>
+      <c r="BZ1463" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウex(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr"/>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1464" t="n">
+        <v>10800</v>
+      </c>
+      <c r="BZ1464" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カイリューEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr"/>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1465" t="n">
+        <v>5280</v>
+      </c>
+      <c r="BZ1465" t="n">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピジョットEX
+CP6]</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr"/>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1466" t="n">
+        <v>2790</v>
+      </c>
+      <c r="BZ1466" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オーロットEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr"/>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1467" t="n">
+        <v>5990</v>
+      </c>
+      <c r="BZ1467" t="n">
+        <v>4792</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラティアス＆ラティオスGX
+sm9]</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr"/>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1468" t="n">
+        <v>13800</v>
+      </c>
+      <c r="BZ1468" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゴリランダーV
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr"/>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1469" t="n">
+        <v>330</v>
+      </c>
+      <c r="BZ1469" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マクワ
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr"/>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1470" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1470" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>〔状態B〕サナ
+S7R]</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr"/>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1471" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BZ1471" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コルニ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr"/>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1472" t="n">
+        <v>123000</v>
+      </c>
+      <c r="BZ1472" t="n">
+        <v>98400</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>〔状態B〕サザンドラ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr"/>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1473" t="n">
+        <v>17800</v>
+      </c>
+      <c r="BZ1473" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>〔状態C〕ダークライ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr"/>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1474" t="n">
+        <v>8980</v>
+      </c>
+      <c r="BZ1474" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>〔状態B〕ルガルガンGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr"/>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1475" t="n">
+        <v>1680</v>
+      </c>
+      <c r="BZ1475" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>〔状態C〕ウルトラネクロズマGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr"/>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1476" t="n">
+        <v>2480</v>
+      </c>
+      <c r="BZ1476" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲンガー＆ミミッキュGX(SA)
+sm9]</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr"/>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1477" t="n">
+        <v>128000</v>
+      </c>
+      <c r="BZ1477" t="n">
+        <v>102400</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>〔状態B〕炎の結晶
+sm10]</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr"/>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1478" t="n">
+        <v>880</v>
+      </c>
+      <c r="BZ1478" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>〔状態B〕ユニットエネルギー草炎水
+sm5]</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr"/>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1479" t="n">
+        <v>2180</v>
+      </c>
+      <c r="BZ1479" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>〔状態B〕ソルガレオ＆ルナアーラGX(SA)
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr"/>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1480" t="n">
+        <v>34800</v>
+      </c>
+      <c r="BZ1480" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドンメル
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr"/>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1481" t="n">
+        <v>260</v>
+      </c>
+      <c r="BZ1481" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガゲッコウガex
+M4]</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr"/>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1482" t="n">
+        <v>34800</v>
+      </c>
+      <c r="BZ1482" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr"/>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1483" t="n">
+        <v>28800</v>
+      </c>
+      <c r="BZ1483" t="n">
+        <v>23040</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>ナッシー</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr"/>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1484" t="n">
+        <v>580</v>
+      </c>
+      <c r="BZ1484" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>リーフィアV</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr"/>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1485" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1485" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕レシラムex</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>BWR</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr"/>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1486" t="n">
+        <v>64800</v>
+      </c>
+      <c r="BZ1486" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕リザードン＆テールナーGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr"/>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1487" t="n">
+        <v>134000</v>
+      </c>
+      <c r="BZ1487" t="n">
+        <v>107200</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ブースターVMAX(SA仕様)</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr"/>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1488" t="n">
+        <v>758000</v>
+      </c>
+      <c r="BZ1488" t="n">
+        <v>606400</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>マルヤクデV</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr"/>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1489" t="n">
+        <v>980</v>
+      </c>
+      <c r="BZ1489" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>キュレムEX</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr"/>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1490" t="n">
+        <v>5480</v>
+      </c>
+      <c r="BZ1490" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>ミジュマル</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr"/>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1491" t="n">
+        <v>5480</v>
+      </c>
+      <c r="BZ1491" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>ウパー</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr"/>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1492" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1492" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>カメックス＆ポッチャマGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr"/>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1493" t="n">
+        <v>52800</v>
+      </c>
+      <c r="BZ1493" t="n">
+        <v>42240</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕お公家さまと舞妓はんピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr"/>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1494" t="n">
+        <v>378000</v>
+      </c>
+      <c r="BZ1494" t="n">
+        <v>302400</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>ライチュウV</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr"/>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1495" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BZ1495" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>コイル</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr"/>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1496" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BZ1496" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>メガシビルドンex</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr"/>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1497" t="n">
+        <v>780</v>
+      </c>
+      <c r="BZ1497" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ゲンガー＆ミミッキュGX</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr"/>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1498" t="n">
+        <v>108000</v>
+      </c>
+      <c r="BZ1498" t="n">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>エーフィV(SA)</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr"/>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1499" t="n">
+        <v>32800</v>
+      </c>
+      <c r="BZ1499" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>デデンネ</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr"/>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1500" t="n">
+        <v>680</v>
+      </c>
+      <c r="BZ1500" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>ディンルーex</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr"/>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1501" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1501" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>セキタンザンV</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr"/>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1502" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1502" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>ドラピオンV(S11)</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr"/>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1503" t="n">
+        <v>580</v>
+      </c>
+      <c r="BZ1503" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>クスネ</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr"/>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1504" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1504" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>ハッサムGX</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr"/>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1505" t="n">
+        <v>8480</v>
+      </c>
+      <c r="BZ1505" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕レックウザVMAX(SA)</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr"/>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1506" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="BZ1506" t="n">
+        <v>992000</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕MピジョットEX</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr"/>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1507" t="n">
+        <v>17800</v>
+      </c>
+      <c r="BZ1507" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>ビーダル</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr"/>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1508" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1508" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>改造ハンマー</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr"/>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1509" t="n">
+        <v>280</v>
+      </c>
+      <c r="BZ1509" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>基本草エネルギー(フレンドバトル)</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr"/>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1510" t="n">
+        <v>580</v>
+      </c>
+      <c r="BZ1510" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>基本水エネルギー(DPキラ)</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr"/>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1511" t="n">
+        <v>7480</v>
+      </c>
+      <c r="BZ1511" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>マチスの取引</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr"/>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1512" t="n">
+        <v>1080</v>
+      </c>
+      <c r="BZ1512" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>アオキの手際</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr"/>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1513" t="n">
+        <v>980</v>
+      </c>
+      <c r="BZ1513" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>カシオペア</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr"/>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1514" t="n">
+        <v>980</v>
+      </c>
+      <c r="BZ1514" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕シンオウの仲間たち</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr"/>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1515" t="n">
+        <v>12800</v>
+      </c>
+      <c r="BZ1515" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>ネジキ</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr"/>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1516" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1516" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>ダンデ(R仕様/未開封)</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr"/>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1517" t="n">
+        <v>980</v>
+      </c>
+      <c r="BZ1517" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>ボスの指令/サカキ</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr"/>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1518" t="n">
+        <v>17800</v>
+      </c>
+      <c r="BZ1518" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>エリカ</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr"/>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1519" t="n">
+        <v>2980</v>
+      </c>
+      <c r="BZ1519" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>ルスワール</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr"/>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1520" t="n">
+        <v>9480</v>
+      </c>
+      <c r="BZ1520" t="n">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>エキサイトスタジアム</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr"/>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="BY1521" t="n">
+        <v>280</v>
+      </c>
+      <c r="BZ1521" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>〔状態B〕クチートソウルリンク
+XY]</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr"/>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1522" t="n">
+        <v>1680</v>
+      </c>
+      <c r="BZ1522" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>〔状態C〕タラゴン
+M3]</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr"/>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1523" t="n">
+        <v>220</v>
+      </c>
+      <c r="BZ1523" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>〔状態C〕エモンガEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr"/>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1524" t="n">
+        <v>1090</v>
+      </c>
+      <c r="BZ1524" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>〔状態C〕ハリマロン
+M4]</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr"/>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1525" t="n">
+        <v>220</v>
+      </c>
+      <c r="BZ1525" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カラカラ(中国語版)
+海外版]</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr"/>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1526" t="n">
+        <v>8980</v>
+      </c>
+      <c r="BZ1526" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>〔状態C〕ニャース
+XY]</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr"/>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1527" t="n">
+        <v>780</v>
+      </c>
+      <c r="BZ1527" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラティアス
+XY]</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr"/>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1528" t="n">
+        <v>2780</v>
+      </c>
+      <c r="BZ1528" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>〔状態C〕オノノクス
+その他]</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr"/>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1529" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1529" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウLV.13
+その他]</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr"/>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1530" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BZ1530" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラティオス
+XY]</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr"/>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1531" t="n">
+        <v>2180</v>
+      </c>
+      <c r="BZ1531" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>〔状態C〕ケルディオ
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr"/>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1532" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1532" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ザシアン
+M2]</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr"/>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1533" t="n">
+        <v>330</v>
+      </c>
+      <c r="BZ1533" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>〔状態C〕チョロネコ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr"/>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1534" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1534" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガマゲロゲ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr"/>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1535" t="n">
+        <v>6980</v>
+      </c>
+      <c r="BZ1535" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゴルーグ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr"/>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1536" t="n">
+        <v>290</v>
+      </c>
+      <c r="BZ1536" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>〔状態C〕タロ
+SV7]</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr"/>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1537" t="n">
+        <v>690</v>
+      </c>
+      <c r="BZ1537" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>〔状態C〕ガブリアスex
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr"/>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1538" t="n">
+        <v>3280</v>
+      </c>
+      <c r="BZ1538" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>〔状態B〕オーガポンいどのめんex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr"/>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1539" t="n">
+        <v>880</v>
+      </c>
+      <c r="BZ1539" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>〔状態C〕シャリタツex
+SV8]</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr"/>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1540" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1540" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr"/>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1541" t="n">
+        <v>4480</v>
+      </c>
+      <c r="BZ1541" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルギア
+その他]</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr"/>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1542" t="n">
+        <v>5990</v>
+      </c>
+      <c r="BZ1542" t="n">
+        <v>4792</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>〔状態C〕パチリス(コロコロイチバン/ポケモンファン)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr"/>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1543" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1543" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウδ-デルタ種
+その他]</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr"/>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1544" t="n">
+        <v>8480</v>
+      </c>
+      <c r="BZ1544" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>〔状態C〕博士の研究/ウィロー博士
+S10b]</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr"/>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1545" t="n">
+        <v>220</v>
+      </c>
+      <c r="BZ1545" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>〔状態B〕テツノカシラex
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr"/>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1546" t="n">
+        <v>2780</v>
+      </c>
+      <c r="BZ1546" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>〔状態B〕コリンク
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr"/>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1547" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1547" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>〔状態B〕フワライド
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr"/>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1548" t="n">
+        <v>220</v>
+      </c>
+      <c r="BZ1548" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ボルトロス
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr"/>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1549" t="n">
+        <v>260</v>
+      </c>
+      <c r="BZ1549" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バニリッチ
+SV4M]</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr"/>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1550" t="n">
+        <v>330</v>
+      </c>
+      <c r="BZ1550" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゴージャスマント
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr"/>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1551" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1551" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>〔状態B〕オーリム博士の気迫
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr"/>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1552" t="n">
+        <v>1180</v>
+      </c>
+      <c r="BZ1552" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミガルーサ
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr"/>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1553" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1553" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヤドン
+その他]</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr"/>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1554" t="n">
+        <v>64800</v>
+      </c>
+      <c r="BZ1554" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>〔状態D〕トロピカルウインド(2009)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr"/>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1555" t="n">
+        <v>44800</v>
+      </c>
+      <c r="BZ1555" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピチュー(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr"/>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1556" t="n">
+        <v>26800</v>
+      </c>
+      <c r="BZ1556" t="n">
+        <v>21440</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>〔状態C〕すごいつりざお
+SV2P]</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr"/>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1557" t="n">
+        <v>690</v>
+      </c>
+      <c r="BZ1557" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>〔状態C〕ロケット団の幹部(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr"/>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1558" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1558" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>〔状態C〕アローラロコンVSTAR
+S11a]</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr"/>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1559" t="n">
+        <v>290</v>
+      </c>
+      <c r="BZ1559" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミミッキュ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr"/>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1560" t="n">
+        <v>288000</v>
+      </c>
+      <c r="BZ1560" t="n">
+        <v>230400</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーV
+S10b]</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr"/>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1561" t="n">
+        <v>2780</v>
+      </c>
+      <c r="BZ1561" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>〔状態C〕スピアーV
+S10P]</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr"/>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1562" t="n">
+        <v>220</v>
+      </c>
+      <c r="BZ1562" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本鋼エネルギー(ステーション)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr"/>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1563" t="n">
+        <v>350</v>
+      </c>
+      <c r="BZ1563" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミモザ
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr"/>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1564" t="n">
+        <v>7480</v>
+      </c>
+      <c r="BZ1564" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リオル
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr"/>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1565" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BZ1565" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>〔状態B〕活力剤
+XY]</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr"/>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1566" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1566" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr"/>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1567" t="n">
+        <v>29800</v>
+      </c>
+      <c r="BZ1567" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジンダイ
+S12]</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr"/>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1568" t="n">
+        <v>320</v>
+      </c>
+      <c r="BZ1568" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バトルシティ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr"/>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1569" t="n">
+        <v>8990</v>
+      </c>
+      <c r="BZ1569" t="n">
+        <v>7192</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr"/>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1570" t="n">
+        <v>178000</v>
+      </c>
+      <c r="BZ1570" t="n">
+        <v>142400</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レッドの挑戦
+その他]</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr"/>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1571" t="n">
+        <v>2630</v>
+      </c>
+      <c r="BZ1571" t="n">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポンチョを着たイーブイ(NP/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr"/>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1572" t="n">
+        <v>178000</v>
+      </c>
+      <c r="BZ1572" t="n">
+        <v>142400</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>〔状態C〕いちげきウーラオスVMAX(SA)
+S5I]</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr"/>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1573" t="n">
+        <v>23800</v>
+      </c>
+      <c r="BZ1573" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バトルロードスタジアム (バトルロードスタジアムDPクリア賞)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr"/>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1574" t="n">
+        <v>218000</v>
+      </c>
+      <c r="BZ1574" t="n">
+        <v>174400</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ディアルガGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr"/>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1575" t="n">
+        <v>2780</v>
+      </c>
+      <c r="BZ1575" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タイレーツV
+S2]</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr"/>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1576" t="n">
+        <v>450</v>
+      </c>
+      <c r="BZ1576" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>〔状態B〕キテルグマ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr"/>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1577" t="n">
+        <v>1290</v>
+      </c>
+      <c r="BZ1577" t="n">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲノセクトV
+S8]</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr"/>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1578" t="n">
+        <v>320</v>
+      </c>
+      <c r="BZ1578" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イベルタルGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr"/>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1579" t="n">
+        <v>2430</v>
+      </c>
+      <c r="BZ1579" t="n">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ネズ
+S3]</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr"/>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1580" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1580" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウツー
+その他]</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr"/>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1581" t="n">
+        <v>9980</v>
+      </c>
+      <c r="BZ1581" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>〔状態C〕モクロー
+その他]</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr"/>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1582" t="n">
+        <v>4480</v>
+      </c>
+      <c r="BZ1582" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーEX(バーストボール)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr"/>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1583" t="n">
+        <v>123000</v>
+      </c>
+      <c r="BZ1583" t="n">
+        <v>98400</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ダークライEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr"/>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1584" t="n">
+        <v>34800</v>
+      </c>
+      <c r="BZ1584" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レックウザ(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr"/>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1585" t="n">
+        <v>72800</v>
+      </c>
+      <c r="BZ1585" t="n">
+        <v>58240</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>〔状態B〕博士の研究/オーキド博士(25th)
+S8a]</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr"/>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1586" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1586" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>〔状態B〕マスタードれんげきのかた
+S5R]</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr"/>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1587" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1587" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オーダイル(トリプルゲットキャンペーン)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr"/>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1588" t="n">
+        <v>79800</v>
+      </c>
+      <c r="BZ1588" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>〔状態C〕ホウオウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr"/>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1589" t="n">
+        <v>2190</v>
+      </c>
+      <c r="BZ1589" t="n">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヘラクロスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr"/>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1590" t="n">
+        <v>1990</v>
+      </c>
+      <c r="BZ1590" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>〔状態B〕ロトム図鑑
+その他]</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr"/>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1591" t="n">
+        <v>990</v>
+      </c>
+      <c r="BZ1591" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr"/>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1592" t="n">
+        <v>108000</v>
+      </c>
+      <c r="BZ1592" t="n">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>〔状態C〕プテラGX
+sm11]</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr"/>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1593" t="n">
+        <v>370</v>
+      </c>
+      <c r="BZ1593" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>〔状態C〕イシヘンジンVMAX
+s1]</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr"/>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1594" t="n">
+        <v>280</v>
+      </c>
+      <c r="BZ1594" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヘルガーV
+S3]</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr"/>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1595" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1595" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>〔状態C〕エルフーンGX
+sm10]</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr"/>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1596" t="n">
+        <v>680</v>
+      </c>
+      <c r="BZ1596" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>〔状態C〕ギャラドスGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr"/>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1597" t="n">
+        <v>4480</v>
+      </c>
+      <c r="BZ1597" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>〔状態C〕デデンネGX
+SM9a]</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr"/>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1598" t="n">
+        <v>1180</v>
+      </c>
+      <c r="BZ1598" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr"/>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1599" t="n">
+        <v>24800</v>
+      </c>
+      <c r="BZ1599" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルギアGX
+sm8]</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr"/>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1600" t="n">
+        <v>19800</v>
+      </c>
+      <c r="BZ1600" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウツー＆ミュウGX(SA)
+sm11]</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr"/>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1601" t="n">
+        <v>84800</v>
+      </c>
+      <c r="BZ1601" t="n">
+        <v>67840</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>〔状態C〕ひかるホウオウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr"/>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1602" t="n">
+        <v>12800</v>
+      </c>
+      <c r="BZ1602" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>〔状態C〕パンプジン(アートアカデミー)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr"/>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1603" t="n">
+        <v>24800</v>
+      </c>
+      <c r="BZ1603" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>〔状態B〕オニオン
+s3a]</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr"/>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1604" t="n">
+        <v>590</v>
+      </c>
+      <c r="BZ1604" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブースターEX
+CP3]</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr"/>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1605" t="n">
+        <v>89800</v>
+      </c>
+      <c r="BZ1605" t="n">
+        <v>71840</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>〔状態B〕フライゴンGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr"/>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1606" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1606" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>〔状態B〕MヘルガーEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr"/>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1607" t="n">
+        <v>15800</v>
+      </c>
+      <c r="BZ1607" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>〔状態B〕マギアナEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr"/>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1608" t="n">
+        <v>4990</v>
+      </c>
+      <c r="BZ1608" t="n">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>〔状態B〕ライチュウGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr"/>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1609" t="n">
+        <v>980</v>
+      </c>
+      <c r="BZ1609" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>〔状態D〕基本草エネルギー(ファーストデザインキラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr"/>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1610" t="n">
+        <v>54800</v>
+      </c>
+      <c r="BZ1610" t="n">
+        <v>43840</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>〔状態B〕アーゴヨン＆アクジキングGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr"/>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1611" t="n">
+        <v>1180</v>
+      </c>
+      <c r="BZ1611" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジラーチ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr"/>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1612" t="n">
+        <v>580</v>
+      </c>
+      <c r="BZ1612" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>〔状態B〕ギラティナEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr"/>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1613" t="n">
+        <v>998000</v>
+      </c>
+      <c r="BZ1613" t="n">
+        <v>798400</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>〔状態B〕メガフラエッテex
+M4]</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr"/>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1614" t="n">
+        <v>420</v>
+      </c>
+      <c r="BZ1614" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>ラティアス(ジャンボカード)</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr"/>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1615" t="n">
+        <v>980</v>
+      </c>
+      <c r="BZ1615" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>〔ACE10鑑定済〕ニャローテ</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr"/>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1616" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BZ1616" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>〔ARS9鑑定済〕フシギバナex</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr"/>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1617" t="n">
+        <v>2980</v>
+      </c>
+      <c r="BZ1617" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕セレビィ＆フシギバナGX</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr"/>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1618" t="n">
+        <v>9480</v>
+      </c>
+      <c r="BZ1618" t="n">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕フシギバナex</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr"/>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1619" t="n">
+        <v>39800</v>
+      </c>
+      <c r="BZ1619" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕タマタマ</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr"/>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1620" t="n">
+        <v>118000</v>
+      </c>
+      <c r="BZ1620" t="n">
+        <v>94400</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕リーフィアEX</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr"/>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1621" t="n">
+        <v>32800</v>
+      </c>
+      <c r="BZ1621" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>＿のセレビィ</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr"/>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1622" t="n">
+        <v>218000</v>
+      </c>
+      <c r="BZ1622" t="n">
+        <v>174400</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>ザルードV</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr"/>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1623" t="n">
+        <v>15800</v>
+      </c>
+      <c r="BZ1623" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>モクロー＆アローラナッシーGX</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr"/>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1624" t="n">
+        <v>3280</v>
+      </c>
+      <c r="BZ1624" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>ジュカイン</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr"/>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1625" t="n">
+        <v>1180</v>
+      </c>
+      <c r="BZ1625" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>〔CGC10黒鑑定済〕ブースターex</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr"/>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1626" t="n">
+        <v>13800</v>
+      </c>
+      <c r="BZ1626" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕マルヤクデVMAX</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr"/>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1627" t="n">
+        <v>3480</v>
+      </c>
+      <c r="BZ1627" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>〔BGS9.5鑑定済〕サーナイトexδ-デルタ種(25th)</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr"/>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1628" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BZ1628" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>〔BGS10鑑定済〕リザードンVSTAR</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr"/>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1629" t="n">
+        <v>8980</v>
+      </c>
+      <c r="BZ1629" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕リザードン(1ED)</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr"/>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1630" t="n">
+        <v>698000</v>
+      </c>
+      <c r="BZ1630" t="n">
+        <v>558400</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕ゲンシカイオーガEX</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr"/>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1631" t="n">
+        <v>92800</v>
+      </c>
+      <c r="BZ1631" t="n">
+        <v>74240</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラプラスex
+M-P]</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr"/>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1632" t="n">
+        <v>220</v>
+      </c>
+      <c r="BZ1632" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ギャラドスEX</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr"/>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1633" t="n">
+        <v>19800</v>
+      </c>
+      <c r="BZ1633" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕グソクムシャex</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr"/>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1634" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BZ1634" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>ランターン(マクドナルド)</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr"/>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1635" t="n">
+        <v>4980</v>
+      </c>
+      <c r="BZ1635" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕グレイシアGX</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr"/>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1636" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BZ1636" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ギャラドスGX</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr"/>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1637" t="n">
+        <v>37800</v>
+      </c>
+      <c r="BZ1637" t="n">
+        <v>30240</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>カイオーガV</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr"/>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1638" t="n">
+        <v>780</v>
+      </c>
+      <c r="BZ1638" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>〔CGC10鑑定済〕ナンジャモのタイカイデン</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr"/>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1639" t="n">
+        <v>4480</v>
+      </c>
+      <c r="BZ1639" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr"/>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1640" t="n">
+        <v>999999</v>
+      </c>
+      <c r="BZ1640" t="n">
+        <v>799999</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕ナンジャモのハラバリーex</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr"/>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1641" t="n">
+        <v>17800</v>
+      </c>
+      <c r="BZ1641" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr"/>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1642" t="n">
+        <v>3480</v>
+      </c>
+      <c r="BZ1642" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ピカチュウ(おかいもの東京)</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr"/>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1643" t="n">
+        <v>34800</v>
+      </c>
+      <c r="BZ1643" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ゼラオラVMAX</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr"/>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1644" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BZ1644" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>〔PSA8鑑定済〕カプ・コケコGX</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr"/>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1645" t="n">
+        <v>1280</v>
+      </c>
+      <c r="BZ1645" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>〔PSA8鑑定済〕ポンチョを着たピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr"/>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1646" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BZ1646" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ピカチュウ(アンリミ)</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr"/>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1647" t="n">
+        <v>54800</v>
+      </c>
+      <c r="BZ1647" t="n">
+        <v>43840</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>ピカチュウ(おかいもの横浜/未開封)</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr"/>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1648" t="n">
+        <v>218000</v>
+      </c>
+      <c r="BZ1648" t="n">
+        <v>174400</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>デンジュモクGX</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr"/>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1649" t="n">
+        <v>1180</v>
+      </c>
+      <c r="BZ1649" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr"/>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1650" t="n">
+        <v>1980000</v>
+      </c>
+      <c r="BZ1650" t="n">
+        <v>1584000</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ロケット団のソーナンス</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr"/>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1651" t="n">
+        <v>7480</v>
+      </c>
+      <c r="BZ1651" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>ビクティニ</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr"/>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1652" t="n">
+        <v>15800</v>
+      </c>
+      <c r="BZ1652" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>〔BGS9.5鑑定済〕ラルトス</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr"/>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1653" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BZ1653" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>ソーナンス</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr"/>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1654" t="n">
+        <v>980</v>
+      </c>
+      <c r="BZ1654" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>〔ACE10鑑定済〕ザシアンV</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr"/>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1655" t="n">
+        <v>2980</v>
+      </c>
+      <c r="BZ1655" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ミュウVMAX</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr"/>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1656" t="n">
+        <v>54800</v>
+      </c>
+      <c r="BZ1656" t="n">
+        <v>43840</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ガラルフリーザーV</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr"/>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1657" t="n">
+        <v>8980</v>
+      </c>
+      <c r="BZ1657" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>カプ・テテフGX</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr"/>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1658" t="n">
+        <v>6480</v>
+      </c>
+      <c r="BZ1658" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>ダダリン</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr"/>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1659" t="n">
+        <v>480</v>
+      </c>
+      <c r="BZ1659" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>ルナアーラGX</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr"/>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1660" t="n">
+        <v>880</v>
+      </c>
+      <c r="BZ1660" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>ナゲキ</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr"/>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1661" t="n">
+        <v>680</v>
+      </c>
+      <c r="BZ1661" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕イダイナキバex</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr"/>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1662" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BZ1662" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕テツノイワオex</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr"/>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1663" t="n">
+        <v>7480</v>
+      </c>
+      <c r="BZ1663" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>コジオ</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr"/>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1664" t="n">
+        <v>280</v>
+      </c>
+      <c r="BZ1664" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕カイリキーEX</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr"/>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1665" t="n">
+        <v>8980</v>
+      </c>
+      <c r="BZ1665" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>ルカリオEX</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr"/>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1666" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1666" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>カイリキーGX</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr"/>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1667" t="n">
+        <v>6980</v>
+      </c>
+      <c r="BZ1667" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕メガゲンガーex</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr"/>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1668" t="n">
+        <v>9980</v>
+      </c>
+      <c r="BZ1668" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ゲッコウガ＆ゾロアークGX</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr"/>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1669" t="n">
+        <v>23800</v>
+      </c>
+      <c r="BZ1669" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ガチグマアカツキex</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr"/>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1670" t="n">
+        <v>8480</v>
+      </c>
+      <c r="BZ1670" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ゾロアークGX</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr"/>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1671" t="n">
+        <v>21800</v>
+      </c>
+      <c r="BZ1671" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ブラッキーGX</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr"/>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1672" t="n">
+        <v>42800</v>
+      </c>
+      <c r="BZ1672" t="n">
+        <v>34240</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ヘルガー</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr"/>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1673" t="n">
+        <v>6980</v>
+      </c>
+      <c r="BZ1673" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>ムゲンダイナVMAX</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr"/>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1674" t="n">
+        <v>980</v>
+      </c>
+      <c r="BZ1674" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>バンギラスV(RR仕様)</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr"/>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1675" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1675" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>アローラベトベトンGX</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr"/>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1676" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1676" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ホップのザシアンex</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr"/>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1677" t="n">
+        <v>10800</v>
+      </c>
+      <c r="BZ1677" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ブロロン</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr"/>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1678" t="n">
+        <v>2980</v>
+      </c>
+      <c r="BZ1678" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>ダイオウドウVMAX</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr"/>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1679" t="n">
+        <v>280</v>
+      </c>
+      <c r="BZ1679" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>レアコイル</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr"/>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1680" t="n">
+        <v>780</v>
+      </c>
+      <c r="BZ1680" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>デデンネ(ポケモンパン)</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr"/>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1681" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BZ1681" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕サーナイト＆ニンフィアGX</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr"/>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1682" t="n">
+        <v>13800</v>
+      </c>
+      <c r="BZ1682" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕タケルライコex</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr"/>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1683" t="n">
+        <v>9980</v>
+      </c>
+      <c r="BZ1683" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕アーゴヨン＆アクジキングGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr"/>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1684" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BZ1684" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕チラチーノ</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr"/>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1685" t="n">
+        <v>8980</v>
+      </c>
+      <c r="BZ1685" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA9鑑定済〕イーブイ(ムンク)</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr"/>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1686" t="n">
+        <v>114000</v>
+      </c>
+      <c r="BZ1686" t="n">
+        <v>91200</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>レックウザ</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr"/>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1687" t="n">
+        <v>54800</v>
+      </c>
+      <c r="BZ1687" t="n">
+        <v>43840</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕メタモン</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr"/>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1688" t="n">
+        <v>1280</v>
+      </c>
+      <c r="BZ1688" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ルギアEX</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr"/>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1689" t="n">
+        <v>42800</v>
+      </c>
+      <c r="BZ1689" t="n">
+        <v>34240</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕トゲキッスVMAX</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr"/>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1690" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BZ1690" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>ドードリオV(RR仕様)</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr"/>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1691" t="n">
+        <v>380</v>
+      </c>
+      <c r="BZ1691" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>ボーマンダVMAX</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr"/>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1692" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BZ1692" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>アローラキュウコン</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr"/>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1693" t="n">
+        <v>880</v>
+      </c>
+      <c r="BZ1693" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>勝利の証(チャンピオンズリーグ2023京都3位/盾付き)</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr"/>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1694" t="n">
+        <v>1780000</v>
+      </c>
+      <c r="BZ1694" t="n">
+        <v>1424000</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>トレーナーズポスト</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr"/>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1695" t="n">
+        <v>880</v>
+      </c>
+      <c r="BZ1695" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕レベルボール</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr"/>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1696" t="n">
+        <v>7980</v>
+      </c>
+      <c r="BZ1696" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕基本草エネルギー(SVデザイン)</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr"/>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1697" t="n">
+        <v>1980</v>
+      </c>
+      <c r="BZ1697" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>基本水エネルギー(チャンピオンズリーグ2020)</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr"/>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1698" t="n">
+        <v>980</v>
+      </c>
+      <c r="BZ1698" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>基本水エネルギー(ファーストデザイン)</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr"/>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1699" t="n">
+        <v>580</v>
+      </c>
+      <c r="BZ1699" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>基本炎エネルギー(DPキラ)</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr"/>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1700" t="n">
+        <v>8480</v>
+      </c>
+      <c r="BZ1700" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕かんこうきゃく</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr"/>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1701" t="n">
+        <v>10800</v>
+      </c>
+      <c r="BZ1701" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕アンズ</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr"/>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1702" t="n">
+        <v>1780</v>
+      </c>
+      <c r="BZ1702" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>〔※状態難/BGS9鑑定済〕リーリエ</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr"/>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1703" t="n">
+        <v>628000</v>
+      </c>
+      <c r="BZ1703" t="n">
+        <v>502400</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ロケット団のアテナ</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr"/>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1704" t="n">
+        <v>10800</v>
+      </c>
+      <c r="BZ1704" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>〔ARS10鑑定済〕ルチアのアピール</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr"/>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1705" t="n">
+        <v>6980</v>
+      </c>
+      <c r="BZ1705" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕かいじゅうマニア</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr"/>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="BY1706" t="n">
+        <v>1480</v>
+      </c>
+      <c r="BZ1706" t="n">
+        <v>1184</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB1706"/>
+  <dimension ref="A1:CF1809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33578,6 +33578,26 @@
           <t>2026-06-22_diff</t>
         </is>
       </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>2026-06-23_price</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>2026-06-23_buy</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>2026-06-23_ratio</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>2026-06-23_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -67662,7 +67682,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1440" t="inlineStr"/>
       <c r="D1440" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67687,7 +67706,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1441" t="inlineStr"/>
       <c r="D1441" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67712,7 +67730,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1442" t="inlineStr"/>
       <c r="D1442" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67737,7 +67754,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1443" t="inlineStr"/>
       <c r="D1443" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67762,7 +67778,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1444" t="inlineStr"/>
       <c r="D1444" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67787,7 +67802,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1445" t="inlineStr"/>
       <c r="D1445" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67812,7 +67826,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1446" t="inlineStr"/>
       <c r="D1446" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67837,7 +67850,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1447" t="inlineStr"/>
       <c r="D1447" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67862,7 +67874,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1448" t="inlineStr"/>
       <c r="D1448" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67887,7 +67898,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1449" t="inlineStr"/>
       <c r="D1449" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67912,7 +67922,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1450" t="inlineStr"/>
       <c r="D1450" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67937,7 +67946,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1451" t="inlineStr"/>
       <c r="D1451" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67962,7 +67970,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1452" t="inlineStr"/>
       <c r="D1452" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -67987,7 +67994,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1453" t="inlineStr"/>
       <c r="D1453" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68012,7 +68018,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1454" t="inlineStr"/>
       <c r="D1454" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68037,7 +68042,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1455" t="inlineStr"/>
       <c r="D1455" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68062,7 +68066,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68087,7 +68090,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1457" t="inlineStr"/>
       <c r="D1457" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68112,7 +68114,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1458" t="inlineStr"/>
       <c r="D1458" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68137,7 +68138,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1459" t="inlineStr"/>
       <c r="D1459" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68162,7 +68162,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1460" t="inlineStr"/>
       <c r="D1460" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68187,7 +68186,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1461" t="inlineStr"/>
       <c r="D1461" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68212,7 +68210,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1462" t="inlineStr"/>
       <c r="D1462" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68237,7 +68234,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1463" t="inlineStr"/>
       <c r="D1463" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68262,7 +68258,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1464" t="inlineStr"/>
       <c r="D1464" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68287,7 +68282,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1465" t="inlineStr"/>
       <c r="D1465" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68312,7 +68306,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1466" t="inlineStr"/>
       <c r="D1466" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68337,7 +68330,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68362,7 +68354,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1468" t="inlineStr"/>
       <c r="D1468" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68387,7 +68378,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1469" t="inlineStr"/>
       <c r="D1469" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68412,7 +68402,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1470" t="inlineStr"/>
       <c r="D1470" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68437,7 +68426,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1471" t="inlineStr"/>
       <c r="D1471" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68462,7 +68450,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1472" t="inlineStr"/>
       <c r="D1472" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68487,7 +68474,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1473" t="inlineStr"/>
       <c r="D1473" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68512,7 +68498,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1474" t="inlineStr"/>
       <c r="D1474" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68537,7 +68522,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1475" t="inlineStr"/>
       <c r="D1475" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68562,7 +68546,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1476" t="inlineStr"/>
       <c r="D1476" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68587,7 +68570,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1477" t="inlineStr"/>
       <c r="D1477" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68612,7 +68594,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1478" t="inlineStr"/>
       <c r="D1478" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68637,7 +68618,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1479" t="inlineStr"/>
       <c r="D1479" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68662,7 +68642,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1480" t="inlineStr"/>
       <c r="D1480" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68687,7 +68666,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68712,7 +68690,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1482" t="inlineStr"/>
       <c r="D1482" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68736,7 +68713,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1483" t="inlineStr"/>
       <c r="D1483" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68760,7 +68736,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1484" t="inlineStr"/>
       <c r="D1484" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68784,7 +68759,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68808,7 +68782,6 @@
           <t>BWR</t>
         </is>
       </c>
-      <c r="C1486" t="inlineStr"/>
       <c r="D1486" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68832,7 +68805,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1487" t="inlineStr"/>
       <c r="D1487" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68856,7 +68828,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1488" t="inlineStr"/>
       <c r="D1488" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68880,7 +68851,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68904,7 +68874,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1490" t="inlineStr"/>
       <c r="D1490" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68928,7 +68897,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1491" t="inlineStr"/>
       <c r="D1491" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68952,7 +68920,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1492" t="inlineStr"/>
       <c r="D1492" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -68976,7 +68943,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1493" t="inlineStr"/>
       <c r="D1493" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69000,7 +68966,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69024,7 +68989,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69048,7 +69012,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69072,7 +69035,6 @@
           <t>MA</t>
         </is>
       </c>
-      <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69096,7 +69058,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1498" t="inlineStr"/>
       <c r="D1498" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69120,7 +69081,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1499" t="inlineStr"/>
       <c r="D1499" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69144,7 +69104,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1500" t="inlineStr"/>
       <c r="D1500" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69168,7 +69127,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1501" t="inlineStr"/>
       <c r="D1501" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69192,7 +69150,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1502" t="inlineStr"/>
       <c r="D1502" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69216,7 +69173,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1503" t="inlineStr"/>
       <c r="D1503" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69240,7 +69196,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1504" t="inlineStr"/>
       <c r="D1504" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69264,7 +69219,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1505" t="inlineStr"/>
       <c r="D1505" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69288,7 +69242,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1506" t="inlineStr"/>
       <c r="D1506" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69312,7 +69265,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1507" t="inlineStr"/>
       <c r="D1507" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69336,7 +69288,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69360,7 +69311,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C1509" t="inlineStr"/>
       <c r="D1509" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69384,7 +69334,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1510" t="inlineStr"/>
       <c r="D1510" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69408,7 +69357,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69432,7 +69380,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1512" t="inlineStr"/>
       <c r="D1512" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69456,7 +69403,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1513" t="inlineStr"/>
       <c r="D1513" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69480,7 +69426,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1514" t="inlineStr"/>
       <c r="D1514" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69504,7 +69449,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1515" t="inlineStr"/>
       <c r="D1515" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69528,7 +69472,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1516" t="inlineStr"/>
       <c r="D1516" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69552,7 +69495,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1517" t="inlineStr"/>
       <c r="D1517" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69576,7 +69518,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1518" t="inlineStr"/>
       <c r="D1518" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69600,7 +69541,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1519" t="inlineStr"/>
       <c r="D1519" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69624,7 +69564,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1520" t="inlineStr"/>
       <c r="D1520" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69648,7 +69587,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1521" t="inlineStr"/>
       <c r="D1521" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -69673,7 +69611,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1522" t="inlineStr"/>
       <c r="D1522" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69698,7 +69635,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1523" t="inlineStr"/>
       <c r="D1523" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69723,7 +69659,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1524" t="inlineStr"/>
       <c r="D1524" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69748,7 +69683,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1525" t="inlineStr"/>
       <c r="D1525" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69773,7 +69707,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1526" t="inlineStr"/>
       <c r="D1526" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69798,7 +69731,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1527" t="inlineStr"/>
       <c r="D1527" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69823,7 +69755,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1528" t="inlineStr"/>
       <c r="D1528" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69848,7 +69779,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1529" t="inlineStr"/>
       <c r="D1529" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69873,7 +69803,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1530" t="inlineStr"/>
       <c r="D1530" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69898,7 +69827,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1531" t="inlineStr"/>
       <c r="D1531" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69923,7 +69851,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1532" t="inlineStr"/>
       <c r="D1532" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69948,7 +69875,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1533" t="inlineStr"/>
       <c r="D1533" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69973,7 +69899,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1534" t="inlineStr"/>
       <c r="D1534" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -69998,7 +69923,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1535" t="inlineStr"/>
       <c r="D1535" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70023,7 +69947,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1536" t="inlineStr"/>
       <c r="D1536" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70048,7 +69971,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1537" t="inlineStr"/>
       <c r="D1537" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70073,7 +69995,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1538" t="inlineStr"/>
       <c r="D1538" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70098,7 +70019,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1539" t="inlineStr"/>
       <c r="D1539" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70123,7 +70043,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1540" t="inlineStr"/>
       <c r="D1540" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70148,7 +70067,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1541" t="inlineStr"/>
       <c r="D1541" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70173,7 +70091,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1542" t="inlineStr"/>
       <c r="D1542" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70198,7 +70115,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1543" t="inlineStr"/>
       <c r="D1543" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70223,7 +70139,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1544" t="inlineStr"/>
       <c r="D1544" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70248,7 +70163,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1545" t="inlineStr"/>
       <c r="D1545" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70273,7 +70187,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1546" t="inlineStr"/>
       <c r="D1546" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70298,7 +70211,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1547" t="inlineStr"/>
       <c r="D1547" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70323,7 +70235,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1548" t="inlineStr"/>
       <c r="D1548" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70348,7 +70259,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1549" t="inlineStr"/>
       <c r="D1549" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70373,7 +70283,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1550" t="inlineStr"/>
       <c r="D1550" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70398,7 +70307,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1551" t="inlineStr"/>
       <c r="D1551" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70423,7 +70331,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1552" t="inlineStr"/>
       <c r="D1552" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70448,7 +70355,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1553" t="inlineStr"/>
       <c r="D1553" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70473,7 +70379,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1554" t="inlineStr"/>
       <c r="D1554" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70498,7 +70403,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1555" t="inlineStr"/>
       <c r="D1555" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70523,7 +70427,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1556" t="inlineStr"/>
       <c r="D1556" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70548,7 +70451,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1557" t="inlineStr"/>
       <c r="D1557" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70573,7 +70475,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1558" t="inlineStr"/>
       <c r="D1558" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70598,7 +70499,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1559" t="inlineStr"/>
       <c r="D1559" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70623,7 +70523,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1560" t="inlineStr"/>
       <c r="D1560" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70648,7 +70547,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1561" t="inlineStr"/>
       <c r="D1561" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70673,7 +70571,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1562" t="inlineStr"/>
       <c r="D1562" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70698,7 +70595,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1563" t="inlineStr"/>
       <c r="D1563" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70723,7 +70619,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1564" t="inlineStr"/>
       <c r="D1564" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70748,7 +70643,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1565" t="inlineStr"/>
       <c r="D1565" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70773,7 +70667,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1566" t="inlineStr"/>
       <c r="D1566" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70798,7 +70691,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1567" t="inlineStr"/>
       <c r="D1567" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70823,7 +70715,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1568" t="inlineStr"/>
       <c r="D1568" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70848,7 +70739,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1569" t="inlineStr"/>
       <c r="D1569" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70873,7 +70763,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1570" t="inlineStr"/>
       <c r="D1570" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70898,7 +70787,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1571" t="inlineStr"/>
       <c r="D1571" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70923,7 +70811,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1572" t="inlineStr"/>
       <c r="D1572" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70948,7 +70835,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1573" t="inlineStr"/>
       <c r="D1573" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70973,7 +70859,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1574" t="inlineStr"/>
       <c r="D1574" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -70998,7 +70883,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1575" t="inlineStr"/>
       <c r="D1575" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71023,7 +70907,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1576" t="inlineStr"/>
       <c r="D1576" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71048,7 +70931,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1577" t="inlineStr"/>
       <c r="D1577" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71073,7 +70955,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1578" t="inlineStr"/>
       <c r="D1578" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71098,7 +70979,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1579" t="inlineStr"/>
       <c r="D1579" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71123,7 +71003,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1580" t="inlineStr"/>
       <c r="D1580" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71148,7 +71027,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1581" t="inlineStr"/>
       <c r="D1581" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71173,7 +71051,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1582" t="inlineStr"/>
       <c r="D1582" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71198,7 +71075,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1583" t="inlineStr"/>
       <c r="D1583" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71223,7 +71099,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1584" t="inlineStr"/>
       <c r="D1584" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71248,7 +71123,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1585" t="inlineStr"/>
       <c r="D1585" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71273,7 +71147,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1586" t="inlineStr"/>
       <c r="D1586" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71298,7 +71171,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1587" t="inlineStr"/>
       <c r="D1587" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71323,7 +71195,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1588" t="inlineStr"/>
       <c r="D1588" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71348,7 +71219,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1589" t="inlineStr"/>
       <c r="D1589" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71373,7 +71243,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1590" t="inlineStr"/>
       <c r="D1590" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71398,7 +71267,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1591" t="inlineStr"/>
       <c r="D1591" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71423,7 +71291,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1592" t="inlineStr"/>
       <c r="D1592" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71448,7 +71315,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1593" t="inlineStr"/>
       <c r="D1593" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71473,7 +71339,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1594" t="inlineStr"/>
       <c r="D1594" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71498,7 +71363,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1595" t="inlineStr"/>
       <c r="D1595" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71523,7 +71387,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1596" t="inlineStr"/>
       <c r="D1596" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71548,7 +71411,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1597" t="inlineStr"/>
       <c r="D1597" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71573,7 +71435,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1598" t="inlineStr"/>
       <c r="D1598" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71598,7 +71459,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1599" t="inlineStr"/>
       <c r="D1599" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71623,7 +71483,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1600" t="inlineStr"/>
       <c r="D1600" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71648,7 +71507,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1601" t="inlineStr"/>
       <c r="D1601" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71673,7 +71531,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1602" t="inlineStr"/>
       <c r="D1602" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71698,7 +71555,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1603" t="inlineStr"/>
       <c r="D1603" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71723,7 +71579,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1604" t="inlineStr"/>
       <c r="D1604" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71748,7 +71603,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1605" t="inlineStr"/>
       <c r="D1605" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71773,7 +71627,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1606" t="inlineStr"/>
       <c r="D1606" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71798,7 +71651,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1607" t="inlineStr"/>
       <c r="D1607" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71823,7 +71675,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1608" t="inlineStr"/>
       <c r="D1608" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71848,7 +71699,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1609" t="inlineStr"/>
       <c r="D1609" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71873,7 +71723,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1610" t="inlineStr"/>
       <c r="D1610" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71898,7 +71747,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1611" t="inlineStr"/>
       <c r="D1611" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71923,7 +71771,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1612" t="inlineStr"/>
       <c r="D1612" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71948,7 +71795,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1613" t="inlineStr"/>
       <c r="D1613" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71973,7 +71819,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1614" t="inlineStr"/>
       <c r="D1614" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -71997,7 +71842,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1615" t="inlineStr"/>
       <c r="D1615" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72021,7 +71865,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1616" t="inlineStr"/>
       <c r="D1616" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72045,7 +71888,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1617" t="inlineStr"/>
       <c r="D1617" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72069,7 +71911,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1618" t="inlineStr"/>
       <c r="D1618" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72093,7 +71934,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1619" t="inlineStr"/>
       <c r="D1619" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72117,7 +71957,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1620" t="inlineStr"/>
       <c r="D1620" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72141,7 +71980,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1621" t="inlineStr"/>
       <c r="D1621" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72165,7 +72003,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1622" t="inlineStr"/>
       <c r="D1622" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72189,7 +72026,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1623" t="inlineStr"/>
       <c r="D1623" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72213,7 +72049,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1624" t="inlineStr"/>
       <c r="D1624" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72237,7 +72072,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1625" t="inlineStr"/>
       <c r="D1625" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72261,7 +72095,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1626" t="inlineStr"/>
       <c r="D1626" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72285,7 +72118,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1627" t="inlineStr"/>
       <c r="D1627" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72309,7 +72141,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1628" t="inlineStr"/>
       <c r="D1628" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72333,7 +72164,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1629" t="inlineStr"/>
       <c r="D1629" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72357,7 +72187,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1630" t="inlineStr"/>
       <c r="D1630" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72381,7 +72210,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1631" t="inlineStr"/>
       <c r="D1631" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72406,7 +72234,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1632" t="inlineStr"/>
       <c r="D1632" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72430,7 +72257,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1633" t="inlineStr"/>
       <c r="D1633" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72454,7 +72280,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1634" t="inlineStr"/>
       <c r="D1634" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72478,7 +72303,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1635" t="inlineStr"/>
       <c r="D1635" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72502,7 +72326,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1636" t="inlineStr"/>
       <c r="D1636" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72526,7 +72349,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1637" t="inlineStr"/>
       <c r="D1637" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72550,7 +72372,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1638" t="inlineStr"/>
       <c r="D1638" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72574,7 +72395,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1639" t="inlineStr"/>
       <c r="D1639" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72598,7 +72418,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1640" t="inlineStr"/>
       <c r="D1640" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72622,7 +72441,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1641" t="inlineStr"/>
       <c r="D1641" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72646,7 +72464,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1642" t="inlineStr"/>
       <c r="D1642" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72670,7 +72487,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1643" t="inlineStr"/>
       <c r="D1643" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72694,7 +72510,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1644" t="inlineStr"/>
       <c r="D1644" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72718,7 +72533,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1645" t="inlineStr"/>
       <c r="D1645" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72742,7 +72556,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1646" t="inlineStr"/>
       <c r="D1646" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72766,7 +72579,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1647" t="inlineStr"/>
       <c r="D1647" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72790,7 +72602,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1648" t="inlineStr"/>
       <c r="D1648" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72814,7 +72625,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1649" t="inlineStr"/>
       <c r="D1649" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72838,7 +72648,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1650" t="inlineStr"/>
       <c r="D1650" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72862,7 +72671,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1651" t="inlineStr"/>
       <c r="D1651" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72886,7 +72694,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1652" t="inlineStr"/>
       <c r="D1652" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72910,7 +72717,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1653" t="inlineStr"/>
       <c r="D1653" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72934,7 +72740,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1654" t="inlineStr"/>
       <c r="D1654" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72958,7 +72763,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1655" t="inlineStr"/>
       <c r="D1655" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -72982,7 +72786,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1656" t="inlineStr"/>
       <c r="D1656" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73006,7 +72809,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1657" t="inlineStr"/>
       <c r="D1657" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73030,7 +72832,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1658" t="inlineStr"/>
       <c r="D1658" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73054,7 +72855,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1659" t="inlineStr"/>
       <c r="D1659" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73078,7 +72878,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1660" t="inlineStr"/>
       <c r="D1660" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73102,7 +72901,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1661" t="inlineStr"/>
       <c r="D1661" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73126,7 +72924,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1662" t="inlineStr"/>
       <c r="D1662" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73150,7 +72947,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1663" t="inlineStr"/>
       <c r="D1663" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73174,7 +72970,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1664" t="inlineStr"/>
       <c r="D1664" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73198,7 +72993,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1665" t="inlineStr"/>
       <c r="D1665" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73222,7 +73016,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1666" t="inlineStr"/>
       <c r="D1666" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73246,7 +73039,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1667" t="inlineStr"/>
       <c r="D1667" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73270,7 +73062,6 @@
           <t>MA</t>
         </is>
       </c>
-      <c r="C1668" t="inlineStr"/>
       <c r="D1668" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73294,7 +73085,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1669" t="inlineStr"/>
       <c r="D1669" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73318,7 +73108,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1670" t="inlineStr"/>
       <c r="D1670" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73342,7 +73131,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1671" t="inlineStr"/>
       <c r="D1671" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73366,7 +73154,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1672" t="inlineStr"/>
       <c r="D1672" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73390,7 +73177,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1673" t="inlineStr"/>
       <c r="D1673" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73414,7 +73200,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1674" t="inlineStr"/>
       <c r="D1674" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73438,7 +73223,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1675" t="inlineStr"/>
       <c r="D1675" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73462,7 +73246,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1676" t="inlineStr"/>
       <c r="D1676" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73486,7 +73269,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1677" t="inlineStr"/>
       <c r="D1677" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73510,7 +73292,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1678" t="inlineStr"/>
       <c r="D1678" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73534,7 +73315,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1679" t="inlineStr"/>
       <c r="D1679" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73558,7 +73338,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1680" t="inlineStr"/>
       <c r="D1680" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73582,7 +73361,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1681" t="inlineStr"/>
       <c r="D1681" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73606,7 +73384,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1682" t="inlineStr"/>
       <c r="D1682" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73630,7 +73407,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1683" t="inlineStr"/>
       <c r="D1683" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73654,7 +73430,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1684" t="inlineStr"/>
       <c r="D1684" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73678,7 +73453,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1685" t="inlineStr"/>
       <c r="D1685" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73702,7 +73476,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1686" t="inlineStr"/>
       <c r="D1686" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73726,7 +73499,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1687" t="inlineStr"/>
       <c r="D1687" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73750,7 +73522,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1688" t="inlineStr"/>
       <c r="D1688" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73774,7 +73545,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1689" t="inlineStr"/>
       <c r="D1689" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73798,7 +73568,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1690" t="inlineStr"/>
       <c r="D1690" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73822,7 +73591,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1691" t="inlineStr"/>
       <c r="D1691" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73846,7 +73614,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1692" t="inlineStr"/>
       <c r="D1692" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73870,7 +73637,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1693" t="inlineStr"/>
       <c r="D1693" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73894,7 +73660,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1694" t="inlineStr"/>
       <c r="D1694" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73918,7 +73683,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1695" t="inlineStr"/>
       <c r="D1695" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73942,7 +73706,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1696" t="inlineStr"/>
       <c r="D1696" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73966,7 +73729,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1697" t="inlineStr"/>
       <c r="D1697" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -73990,7 +73752,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1698" t="inlineStr"/>
       <c r="D1698" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -74014,7 +73775,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1699" t="inlineStr"/>
       <c r="D1699" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -74038,7 +73798,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1700" t="inlineStr"/>
       <c r="D1700" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -74062,7 +73821,6 @@
           <t>TR</t>
         </is>
       </c>
-      <c r="C1701" t="inlineStr"/>
       <c r="D1701" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -74086,7 +73844,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1702" t="inlineStr"/>
       <c r="D1702" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -74110,7 +73867,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1703" t="inlineStr"/>
       <c r="D1703" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -74134,7 +73890,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1704" t="inlineStr"/>
       <c r="D1704" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -74158,7 +73913,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1705" t="inlineStr"/>
       <c r="D1705" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -74182,7 +73936,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1706" t="inlineStr"/>
       <c r="D1706" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -74193,6 +73946,2541 @@
       </c>
       <c r="BZ1706" t="n">
         <v>1184</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガリザードンXex(※表面加工エラー)
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr"/>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1707" t="n">
+        <v>108000</v>
+      </c>
+      <c r="CD1707" t="n">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マシマシラex
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr"/>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1708" t="n">
+        <v>1230</v>
+      </c>
+      <c r="CD1708" t="n">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>〔状態A-〕こだわりメット
+その他]</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr"/>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1709" t="n">
+        <v>350</v>
+      </c>
+      <c r="CD1709" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>〔状態B〕ロケット団のクロバットex
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr"/>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1710" t="n">
+        <v>780</v>
+      </c>
+      <c r="CD1710" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジャッジマン
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr"/>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1711" t="n">
+        <v>830</v>
+      </c>
+      <c r="CD1711" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>〔状態B〕タロ
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr"/>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1712" t="n">
+        <v>980</v>
+      </c>
+      <c r="CD1712" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タマタマ
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr"/>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1713" t="n">
+        <v>680</v>
+      </c>
+      <c r="CD1713" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>〔状態A-〕セイジ
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr"/>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1714" t="n">
+        <v>1390</v>
+      </c>
+      <c r="CD1714" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr"/>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1715" t="n">
+        <v>3480</v>
+      </c>
+      <c r="CD1715" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ペリッパー
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr"/>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1716" t="n">
+        <v>350</v>
+      </c>
+      <c r="CD1716" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>〔状態A-〕クエスパトラ
+SV4M]</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr"/>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1717" t="n">
+        <v>580</v>
+      </c>
+      <c r="CD1717" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>〔状態B〕コジョンド
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr"/>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1718" t="n">
+        <v>320</v>
+      </c>
+      <c r="CD1718" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ネモ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr"/>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1719" t="n">
+        <v>250</v>
+      </c>
+      <c r="CD1719" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サカキのカリスマ
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr"/>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1720" t="n">
+        <v>680</v>
+      </c>
+      <c r="CD1720" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イキリンコex
+SV2P]</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr"/>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1721" t="n">
+        <v>450</v>
+      </c>
+      <c r="CD1721" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本雷エネルギー(SVデザイン)
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr"/>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1722" t="n">
+        <v>2430</v>
+      </c>
+      <c r="CD1722" t="n">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミモザ
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr"/>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1723" t="n">
+        <v>10800</v>
+      </c>
+      <c r="CD1723" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr"/>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1724" t="n">
+        <v>1390</v>
+      </c>
+      <c r="CD1724" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レジドラゴV
+S12]</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr"/>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1725" t="n">
+        <v>690</v>
+      </c>
+      <c r="CD1725" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カヒリ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr"/>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1726" t="n">
+        <v>1230</v>
+      </c>
+      <c r="CD1726" t="n">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーGX
+smP2]</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr"/>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1727" t="n">
+        <v>2290</v>
+      </c>
+      <c r="CD1727" t="n">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マルチエネルギー
+その他]</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr"/>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1728" t="n">
+        <v>2490</v>
+      </c>
+      <c r="CD1728" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>〔状態B〕いちげきウーラオスVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr"/>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1729" t="n">
+        <v>780</v>
+      </c>
+      <c r="CD1729" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トゲキッスVMAX
+s3a]</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr"/>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1730" t="n">
+        <v>1090</v>
+      </c>
+      <c r="CD1730" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エーテルパラダイス保護区
+SM9a]</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr"/>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1731" t="n">
+        <v>930</v>
+      </c>
+      <c r="CD1731" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レックウザV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr"/>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1732" t="n">
+        <v>7980</v>
+      </c>
+      <c r="CD1732" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MミュウツーEX(Y)
+XY]</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr"/>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1733" t="n">
+        <v>13800</v>
+      </c>
+      <c r="CD1733" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジバコイルEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr"/>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1734" t="n">
+        <v>5490</v>
+      </c>
+      <c r="CD1734" t="n">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゲッコウガ＆ゾロアークGX
+SM9a]</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr"/>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1735" t="n">
+        <v>5780</v>
+      </c>
+      <c r="CD1735" t="n">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラパルトVMAX
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr"/>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1736" t="n">
+        <v>390</v>
+      </c>
+      <c r="CD1736" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミミッキュV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr"/>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1737" t="n">
+        <v>6480</v>
+      </c>
+      <c r="CD1737" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>〔状態B〕シャワーズV
+S6a]</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr"/>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1738" t="n">
+        <v>1780</v>
+      </c>
+      <c r="CD1738" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ルチア
+sm7]</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr"/>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1739" t="n">
+        <v>208000</v>
+      </c>
+      <c r="CD1739" t="n">
+        <v>166400</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>〔状態B〕セレビィV(SA)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr"/>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1740" t="n">
+        <v>14800</v>
+      </c>
+      <c r="CD1740" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>〔状態B〕オニゴーリEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr"/>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1741" t="n">
+        <v>4490</v>
+      </c>
+      <c r="CD1741" t="n">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>〔状態B〕MラティオスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr"/>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1742" t="n">
+        <v>3990</v>
+      </c>
+      <c r="CD1742" t="n">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>〔状態B〕サーナイトGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr"/>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1743" t="n">
+        <v>14800</v>
+      </c>
+      <c r="CD1743" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>〔状態C〕ガブリアス＆ギラティナGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr"/>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1744" t="n">
+        <v>9480</v>
+      </c>
+      <c r="CD1744" t="n">
+        <v>7584</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケモンブリーダーの育成
+S2a]</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr"/>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1745" t="n">
+        <v>780</v>
+      </c>
+      <c r="CD1745" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>〔状態B〕ライボルトEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr"/>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1746" t="n">
+        <v>3790</v>
+      </c>
+      <c r="CD1746" t="n">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>〔状態B〕ライチュウGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr"/>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1747" t="n">
+        <v>21800</v>
+      </c>
+      <c r="CD1747" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>〔状態B〕シロナ＆カトレア
+sm12]</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr"/>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1748" t="n">
+        <v>15800</v>
+      </c>
+      <c r="CD1748" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕アセロラの予感</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr"/>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1749" t="n">
+        <v>14800</v>
+      </c>
+      <c r="CD1749" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>カプ・ブルルGX</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr"/>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1750" t="n">
+        <v>10800</v>
+      </c>
+      <c r="CD1750" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>ビクティニ(未開封/AR仕様)</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr"/>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1751" t="n">
+        <v>3480</v>
+      </c>
+      <c r="CD1751" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スコヴィランex
+SV8]</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr"/>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1752" t="n">
+        <v>580</v>
+      </c>
+      <c r="CD1752" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>ラビフット</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr"/>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1753" t="n">
+        <v>380</v>
+      </c>
+      <c r="CD1753" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>ホウオウGX</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr"/>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1754" t="n">
+        <v>19800</v>
+      </c>
+      <c r="CD1754" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>コソクムシ</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr"/>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1755" t="n">
+        <v>680</v>
+      </c>
+      <c r="CD1755" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>グレイシアVMAX</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr"/>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1756" t="n">
+        <v>1180</v>
+      </c>
+      <c r="CD1756" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>ゲッコウガGX</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr"/>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1757" t="n">
+        <v>39800</v>
+      </c>
+      <c r="CD1757" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>メガスターミーex</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr"/>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1758" t="n">
+        <v>4480</v>
+      </c>
+      <c r="CD1758" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>〔状態B〕トウホクのピカチュウ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr"/>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1759" t="n">
+        <v>12800</v>
+      </c>
+      <c r="CD1759" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr"/>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1760" t="n">
+        <v>778000</v>
+      </c>
+      <c r="CD1760" t="n">
+        <v>622400</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr"/>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1761" t="n">
+        <v>91800</v>
+      </c>
+      <c r="CD1761" t="n">
+        <v>73440</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕漫才ごっこピカチュウ</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr"/>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1762" t="n">
+        <v>158000</v>
+      </c>
+      <c r="CD1762" t="n">
+        <v>126400</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>サンダースV(SA)</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr"/>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1763" t="n">
+        <v>21800</v>
+      </c>
+      <c r="CD1763" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>カプ・テテフGX(25th)</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr"/>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1764" t="n">
+        <v>2580</v>
+      </c>
+      <c r="CD1764" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>マホイップVMAX</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr"/>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1765" t="n">
+        <v>480</v>
+      </c>
+      <c r="CD1765" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>バサギリVSTAR</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr"/>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1766" t="n">
+        <v>680</v>
+      </c>
+      <c r="CD1766" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>グラエナ</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr"/>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1767" t="n">
+        <v>580</v>
+      </c>
+      <c r="CD1767" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>メガズルズキンex</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr"/>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1768" t="n">
+        <v>1580</v>
+      </c>
+      <c r="CD1768" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>ダイオウドウex</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr"/>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1769" t="n">
+        <v>480</v>
+      </c>
+      <c r="CD1769" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ガブリアス＆ギラティナGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr"/>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1770" t="n">
+        <v>178000</v>
+      </c>
+      <c r="CD1770" t="n">
+        <v>142400</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>アルセウス＆ディアルガ＆パルキアGX</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr"/>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1771" t="n">
+        <v>4780</v>
+      </c>
+      <c r="CD1771" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕イーブイ＆カビゴンGX</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr"/>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1772" t="n">
+        <v>43800</v>
+      </c>
+      <c r="CD1772" t="n">
+        <v>35040</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>ハピナスV</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr"/>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1773" t="n">
+        <v>680</v>
+      </c>
+      <c r="CD1773" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>カビゴンVMAX</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr"/>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1774" t="n">
+        <v>8980</v>
+      </c>
+      <c r="CD1774" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>ブレイブバングル</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr"/>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1775" t="n">
+        <v>7980</v>
+      </c>
+      <c r="CD1775" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>まけんきハチマキ</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr"/>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1776" t="n">
+        <v>7980</v>
+      </c>
+      <c r="CD1776" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>スーパーエネルギー回収</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr"/>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1777" t="n">
+        <v>780</v>
+      </c>
+      <c r="CD1777" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>炎の結晶</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr"/>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1778" t="n">
+        <v>1380</v>
+      </c>
+      <c r="CD1778" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>基本雷エネルギー(BWデザイン/ミラー)</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr"/>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1779" t="n">
+        <v>1080</v>
+      </c>
+      <c r="CD1779" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>基本草エネルギー(DPキラ)</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr"/>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1780" t="n">
+        <v>6980</v>
+      </c>
+      <c r="CD1780" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕リーリエの決心</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr"/>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1781" t="n">
+        <v>77800</v>
+      </c>
+      <c r="CD1781" t="n">
+        <v>62240</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>タロ</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr"/>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1782" t="n">
+        <v>5980</v>
+      </c>
+      <c r="CD1782" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>ネルケ</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr"/>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1783" t="n">
+        <v>2380</v>
+      </c>
+      <c r="CD1783" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>オルティガ</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr"/>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1784" t="n">
+        <v>680</v>
+      </c>
+      <c r="CD1784" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>ミモザ</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr"/>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1785" t="n">
+        <v>3280</v>
+      </c>
+      <c r="CD1785" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>ゲン</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr"/>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1786" t="n">
+        <v>280</v>
+      </c>
+      <c r="CD1786" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>ポッドとデントとコーン</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr"/>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1787" t="n">
+        <v>580</v>
+      </c>
+      <c r="CD1787" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>フヨウ</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr"/>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1788" t="n">
+        <v>780</v>
+      </c>
+      <c r="CD1788" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>グズマ＆ハラ</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr"/>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1789" t="n">
+        <v>980</v>
+      </c>
+      <c r="CD1789" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>ノボリとクダリ</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr"/>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CC1790" t="n">
+        <v>4780</v>
+      </c>
+      <c r="CD1790" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>〔状態C〕MヘラクロスEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr"/>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1791" t="n">
+        <v>1290</v>
+      </c>
+      <c r="CD1791" t="n">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>〔状態B〕ニャオニクス
+XY]</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr"/>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1792" t="n">
+        <v>420</v>
+      </c>
+      <c r="CD1792" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>〔状態C〕メイのはげまし
+M3]</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr"/>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1793" t="n">
+        <v>8480</v>
+      </c>
+      <c r="CD1793" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>〔状態C〕ロケット団のアポロ
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr"/>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1794" t="n">
+        <v>420</v>
+      </c>
+      <c r="CD1794" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>〔状態B〕シェイミ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr"/>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1795" t="n">
+        <v>15800</v>
+      </c>
+      <c r="CD1795" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>〔状態C〕メロエッタ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr"/>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1796" t="n">
+        <v>380</v>
+      </c>
+      <c r="CD1796" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>〔状態C〕ムウマ
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr"/>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1797" t="n">
+        <v>220</v>
+      </c>
+      <c r="CD1797" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>〔状態C〕チャデス
+SV5a]</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr"/>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1798" t="n">
+        <v>220</v>
+      </c>
+      <c r="CD1798" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>〔状態B〕ニャース
+その他]</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr"/>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1799" t="n">
+        <v>1080</v>
+      </c>
+      <c r="CD1799" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニャース
+XY]</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr"/>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1800" t="n">
+        <v>1680</v>
+      </c>
+      <c r="CD1800" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ(未開封/中国繁体字版)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr"/>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1801" t="n">
+        <v>128000</v>
+      </c>
+      <c r="CD1801" t="n">
+        <v>102400</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プリン
+その他]</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr"/>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1802" t="n">
+        <v>2630</v>
+      </c>
+      <c r="CD1802" t="n">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エンペルト
+その他]</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr"/>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1803" t="n">
+        <v>1480</v>
+      </c>
+      <c r="CD1803" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本草エネルギー(ファミリーマート/ミラー)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr"/>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1804" t="n">
+        <v>5480</v>
+      </c>
+      <c r="CD1804" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本悪エネルギー(ビクティニBWR争奪戦)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr"/>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1805" t="n">
+        <v>320</v>
+      </c>
+      <c r="CD1805" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>〔状態C〕ビクティニ(未開封/AR仕様)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr"/>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1806" t="n">
+        <v>1280</v>
+      </c>
+      <c r="CD1806" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>〔状態B〕ガマガル
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr"/>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1807" t="n">
+        <v>680</v>
+      </c>
+      <c r="CD1807" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲノセクトex
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr"/>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1808" t="n">
+        <v>480</v>
+      </c>
+      <c r="CD1808" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>〔状態C〕リザードンVSTAR
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr"/>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CC1809" t="n">
+        <v>580</v>
+      </c>
+      <c r="CD1809" t="n">
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF1809"/>
+  <dimension ref="A1:CJ1835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33598,6 +33598,26 @@
           <t>2026-06-23_diff</t>
         </is>
       </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>2026-06-26_price</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>2026-06-26_buy</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>2026-06-26_ratio</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>2026-06-26_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -73960,7 +73980,6 @@
           <t>MA</t>
         </is>
       </c>
-      <c r="C1707" t="inlineStr"/>
       <c r="D1707" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -73985,7 +74004,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1708" t="inlineStr"/>
       <c r="D1708" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74010,7 +74028,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1709" t="inlineStr"/>
       <c r="D1709" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74035,7 +74052,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1710" t="inlineStr"/>
       <c r="D1710" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74060,7 +74076,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1711" t="inlineStr"/>
       <c r="D1711" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74085,7 +74100,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1712" t="inlineStr"/>
       <c r="D1712" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74110,7 +74124,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1713" t="inlineStr"/>
       <c r="D1713" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74135,7 +74148,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1714" t="inlineStr"/>
       <c r="D1714" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74160,7 +74172,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1715" t="inlineStr"/>
       <c r="D1715" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74185,7 +74196,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1716" t="inlineStr"/>
       <c r="D1716" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74210,7 +74220,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1717" t="inlineStr"/>
       <c r="D1717" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74235,7 +74244,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1718" t="inlineStr"/>
       <c r="D1718" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74260,7 +74268,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1719" t="inlineStr"/>
       <c r="D1719" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74285,7 +74292,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1720" t="inlineStr"/>
       <c r="D1720" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74310,7 +74316,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1721" t="inlineStr"/>
       <c r="D1721" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74335,7 +74340,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1722" t="inlineStr"/>
       <c r="D1722" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74360,7 +74364,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1723" t="inlineStr"/>
       <c r="D1723" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74385,7 +74388,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1724" t="inlineStr"/>
       <c r="D1724" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74410,7 +74412,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1725" t="inlineStr"/>
       <c r="D1725" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74435,7 +74436,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1726" t="inlineStr"/>
       <c r="D1726" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74460,7 +74460,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1727" t="inlineStr"/>
       <c r="D1727" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74485,7 +74484,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1728" t="inlineStr"/>
       <c r="D1728" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74510,7 +74508,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1729" t="inlineStr"/>
       <c r="D1729" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74535,7 +74532,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1730" t="inlineStr"/>
       <c r="D1730" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74560,7 +74556,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1731" t="inlineStr"/>
       <c r="D1731" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74585,7 +74580,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1732" t="inlineStr"/>
       <c r="D1732" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74610,7 +74604,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1733" t="inlineStr"/>
       <c r="D1733" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74635,7 +74628,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1734" t="inlineStr"/>
       <c r="D1734" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74660,7 +74652,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1735" t="inlineStr"/>
       <c r="D1735" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74685,7 +74676,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1736" t="inlineStr"/>
       <c r="D1736" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74710,7 +74700,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1737" t="inlineStr"/>
       <c r="D1737" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74735,7 +74724,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1738" t="inlineStr"/>
       <c r="D1738" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74760,7 +74748,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1739" t="inlineStr"/>
       <c r="D1739" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74785,7 +74772,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1740" t="inlineStr"/>
       <c r="D1740" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74810,7 +74796,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1741" t="inlineStr"/>
       <c r="D1741" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74835,7 +74820,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1742" t="inlineStr"/>
       <c r="D1742" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74860,7 +74844,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1743" t="inlineStr"/>
       <c r="D1743" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74885,7 +74868,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1744" t="inlineStr"/>
       <c r="D1744" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74910,7 +74892,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1745" t="inlineStr"/>
       <c r="D1745" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74935,7 +74916,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1746" t="inlineStr"/>
       <c r="D1746" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74960,7 +74940,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1747" t="inlineStr"/>
       <c r="D1747" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -74985,7 +74964,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1748" t="inlineStr"/>
       <c r="D1748" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75009,7 +74987,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1749" t="inlineStr"/>
       <c r="D1749" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75033,7 +75010,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1750" t="inlineStr"/>
       <c r="D1750" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75057,7 +75033,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1751" t="inlineStr"/>
       <c r="D1751" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75082,7 +75057,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1752" t="inlineStr"/>
       <c r="D1752" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75106,7 +75080,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1753" t="inlineStr"/>
       <c r="D1753" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75130,7 +75103,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1754" t="inlineStr"/>
       <c r="D1754" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75154,7 +75126,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1755" t="inlineStr"/>
       <c r="D1755" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75178,7 +75149,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1756" t="inlineStr"/>
       <c r="D1756" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75202,7 +75172,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1757" t="inlineStr"/>
       <c r="D1757" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75226,7 +75195,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1758" t="inlineStr"/>
       <c r="D1758" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75251,7 +75219,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1759" t="inlineStr"/>
       <c r="D1759" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75275,7 +75242,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1760" t="inlineStr"/>
       <c r="D1760" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75299,7 +75265,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1761" t="inlineStr"/>
       <c r="D1761" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75323,7 +75288,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1762" t="inlineStr"/>
       <c r="D1762" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75347,7 +75311,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1763" t="inlineStr"/>
       <c r="D1763" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75371,7 +75334,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1764" t="inlineStr"/>
       <c r="D1764" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75395,7 +75357,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1765" t="inlineStr"/>
       <c r="D1765" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75419,7 +75380,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1766" t="inlineStr"/>
       <c r="D1766" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75443,7 +75403,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1767" t="inlineStr"/>
       <c r="D1767" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75467,7 +75426,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1768" t="inlineStr"/>
       <c r="D1768" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75491,7 +75449,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1769" t="inlineStr"/>
       <c r="D1769" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75515,7 +75472,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1770" t="inlineStr"/>
       <c r="D1770" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75539,7 +75495,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1771" t="inlineStr"/>
       <c r="D1771" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75563,7 +75518,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1772" t="inlineStr"/>
       <c r="D1772" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75587,7 +75541,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1773" t="inlineStr"/>
       <c r="D1773" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75611,7 +75564,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1774" t="inlineStr"/>
       <c r="D1774" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75635,7 +75587,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1775" t="inlineStr"/>
       <c r="D1775" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75659,7 +75610,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1776" t="inlineStr"/>
       <c r="D1776" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75683,7 +75633,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1777" t="inlineStr"/>
       <c r="D1777" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75707,7 +75656,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1778" t="inlineStr"/>
       <c r="D1778" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75731,7 +75679,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1779" t="inlineStr"/>
       <c r="D1779" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75755,7 +75702,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1780" t="inlineStr"/>
       <c r="D1780" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75779,7 +75725,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1781" t="inlineStr"/>
       <c r="D1781" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75803,7 +75748,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1782" t="inlineStr"/>
       <c r="D1782" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75827,7 +75771,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1783" t="inlineStr"/>
       <c r="D1783" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75851,7 +75794,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1784" t="inlineStr"/>
       <c r="D1784" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75875,7 +75817,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1785" t="inlineStr"/>
       <c r="D1785" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75899,7 +75840,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1786" t="inlineStr"/>
       <c r="D1786" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75923,7 +75863,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1787" t="inlineStr"/>
       <c r="D1787" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75947,7 +75886,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1788" t="inlineStr"/>
       <c r="D1788" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75971,7 +75909,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1789" t="inlineStr"/>
       <c r="D1789" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -75995,7 +75932,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1790" t="inlineStr"/>
       <c r="D1790" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76020,7 +75956,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1791" t="inlineStr"/>
       <c r="D1791" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76045,7 +75980,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1792" t="inlineStr"/>
       <c r="D1792" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76070,7 +76004,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1793" t="inlineStr"/>
       <c r="D1793" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76095,7 +76028,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1794" t="inlineStr"/>
       <c r="D1794" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76120,7 +76052,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1795" t="inlineStr"/>
       <c r="D1795" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76145,7 +76076,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1796" t="inlineStr"/>
       <c r="D1796" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76170,7 +76100,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1797" t="inlineStr"/>
       <c r="D1797" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76195,7 +76124,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1798" t="inlineStr"/>
       <c r="D1798" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76220,7 +76148,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1799" t="inlineStr"/>
       <c r="D1799" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76245,7 +76172,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1800" t="inlineStr"/>
       <c r="D1800" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76270,7 +76196,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1801" t="inlineStr"/>
       <c r="D1801" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76295,7 +76220,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1802" t="inlineStr"/>
       <c r="D1802" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76320,7 +76244,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1803" t="inlineStr"/>
       <c r="D1803" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76345,7 +76268,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1804" t="inlineStr"/>
       <c r="D1804" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76370,7 +76292,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1805" t="inlineStr"/>
       <c r="D1805" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76395,7 +76316,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1806" t="inlineStr"/>
       <c r="D1806" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76420,7 +76340,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1807" t="inlineStr"/>
       <c r="D1807" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76445,7 +76364,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1808" t="inlineStr"/>
       <c r="D1808" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76470,7 +76388,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1809" t="inlineStr"/>
       <c r="D1809" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -76481,6 +76398,656 @@
       </c>
       <c r="CD1809" t="n">
         <v>464</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヤドランソウルリンク
+XY]</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr"/>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1810" t="n">
+        <v>1780</v>
+      </c>
+      <c r="CH1810" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本雷エネルギー(フレンドバトル)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr"/>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1811" t="n">
+        <v>350</v>
+      </c>
+      <c r="CH1811" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本悪エネルギー
+その他]</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr"/>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1812" t="n">
+        <v>3080</v>
+      </c>
+      <c r="CH1812" t="n">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ギガイアス
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr"/>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1813" t="n">
+        <v>680</v>
+      </c>
+      <c r="CH1813" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゼブライカ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr"/>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1814" t="n">
+        <v>930</v>
+      </c>
+      <c r="CH1814" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒビキのホウオウex
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr"/>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1815" t="n">
+        <v>4880</v>
+      </c>
+      <c r="CH1815" t="n">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アカマツ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr"/>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1816" t="n">
+        <v>990</v>
+      </c>
+      <c r="CH1816" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>〔状態B〕カキツバタ
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr"/>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1817" t="n">
+        <v>580</v>
+      </c>
+      <c r="CH1817" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>〔状態B〕カイデン
+SV6]</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr"/>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1818" t="n">
+        <v>380</v>
+      </c>
+      <c r="CH1818" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メタグロス
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr"/>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1819" t="n">
+        <v>990</v>
+      </c>
+      <c r="CH1819" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イルカマン
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr"/>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1820" t="n">
+        <v>580</v>
+      </c>
+      <c r="CH1820" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本炎エネルギー(SVデザイン/CL2023)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr"/>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1821" t="n">
+        <v>630</v>
+      </c>
+      <c r="CH1821" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マサキの転送
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr"/>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1822" t="n">
+        <v>730</v>
+      </c>
+      <c r="CH1822" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プテラVSTAR
+S11]</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr"/>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1823" t="n">
+        <v>1690</v>
+      </c>
+      <c r="CH1823" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>〔状態A-〕チャンピオンズフェスティバル(2018)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr"/>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1824" t="n">
+        <v>138000</v>
+      </c>
+      <c r="CH1824" t="n">
+        <v>110400</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パルデアウパー
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr"/>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1825" t="n">
+        <v>580</v>
+      </c>
+      <c r="CH1825" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジニア
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr"/>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1826" t="n">
+        <v>390</v>
+      </c>
+      <c r="CH1826" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>〔状態B〕リーフィアVSTAR
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr"/>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1827" t="n">
+        <v>5980</v>
+      </c>
+      <c r="CH1827" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウォロ
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr"/>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1828" t="n">
+        <v>680</v>
+      </c>
+      <c r="CH1828" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ストリンダー
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr"/>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1829" t="n">
+        <v>260</v>
+      </c>
+      <c r="CH1829" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オーロット＆ヨノワールGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr"/>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1830" t="n">
+        <v>990</v>
+      </c>
+      <c r="CH1830" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アップリュー
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr"/>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1831" t="n">
+        <v>250</v>
+      </c>
+      <c r="CH1831" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MバンギラスEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr"/>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1832" t="n">
+        <v>42800</v>
+      </c>
+      <c r="CH1832" t="n">
+        <v>34240</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>〔状態A-〕結晶の洞窟
+S7D]</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr"/>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1833" t="n">
+        <v>830</v>
+      </c>
+      <c r="CH1833" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ひかるコイキング(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr"/>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1834" t="n">
+        <v>21800</v>
+      </c>
+      <c r="CH1834" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MオニゴーリEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr"/>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CG1835" t="n">
+        <v>11800</v>
+      </c>
+      <c r="CH1835" t="n">
+        <v>9440</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ1835"/>
+  <dimension ref="A1:CN1906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33618,6 +33618,26 @@
           <t>2026-06-26_diff</t>
         </is>
       </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>2026-06-27_price</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>2026-06-27_buy</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>2026-06-27_ratio</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>2026-06-27_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -76412,7 +76432,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1810" t="inlineStr"/>
       <c r="D1810" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76437,7 +76456,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1811" t="inlineStr"/>
       <c r="D1811" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76462,7 +76480,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1812" t="inlineStr"/>
       <c r="D1812" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76487,7 +76504,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1813" t="inlineStr"/>
       <c r="D1813" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76512,7 +76528,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1814" t="inlineStr"/>
       <c r="D1814" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76537,7 +76552,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1815" t="inlineStr"/>
       <c r="D1815" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76562,7 +76576,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1816" t="inlineStr"/>
       <c r="D1816" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76587,7 +76600,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1817" t="inlineStr"/>
       <c r="D1817" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76612,7 +76624,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1818" t="inlineStr"/>
       <c r="D1818" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76637,7 +76648,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1819" t="inlineStr"/>
       <c r="D1819" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76662,7 +76672,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1820" t="inlineStr"/>
       <c r="D1820" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76687,7 +76696,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1821" t="inlineStr"/>
       <c r="D1821" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76712,7 +76720,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1822" t="inlineStr"/>
       <c r="D1822" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76737,7 +76744,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1823" t="inlineStr"/>
       <c r="D1823" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76762,7 +76768,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1824" t="inlineStr"/>
       <c r="D1824" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76787,7 +76792,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1825" t="inlineStr"/>
       <c r="D1825" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76812,7 +76816,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1826" t="inlineStr"/>
       <c r="D1826" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76837,7 +76840,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1827" t="inlineStr"/>
       <c r="D1827" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76862,7 +76864,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1828" t="inlineStr"/>
       <c r="D1828" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76887,7 +76888,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1829" t="inlineStr"/>
       <c r="D1829" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76912,7 +76912,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1830" t="inlineStr"/>
       <c r="D1830" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76937,7 +76936,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1831" t="inlineStr"/>
       <c r="D1831" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76962,7 +76960,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1832" t="inlineStr"/>
       <c r="D1832" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -76987,7 +76984,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1833" t="inlineStr"/>
       <c r="D1833" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77012,7 +77008,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1834" t="inlineStr"/>
       <c r="D1834" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77037,7 +77032,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1835" t="inlineStr"/>
       <c r="D1835" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77048,6 +77042,1761 @@
       </c>
       <c r="CH1835" t="n">
         <v>9440</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>〔状態B〕ビリジオン
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr"/>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1836" t="n">
+        <v>1180</v>
+      </c>
+      <c r="CL1836" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>〔状態B〕デスマス
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr"/>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1837" t="n">
+        <v>680</v>
+      </c>
+      <c r="CL1837" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジヘッド
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr"/>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1838" t="n">
+        <v>680</v>
+      </c>
+      <c r="CL1838" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バシャーモ
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr"/>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1839" t="n">
+        <v>590</v>
+      </c>
+      <c r="CL1839" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>〔状態B〕イワパレス
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr"/>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1840" t="n">
+        <v>320</v>
+      </c>
+      <c r="CL1840" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハッサムex
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr"/>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1841" t="n">
+        <v>2430</v>
+      </c>
+      <c r="CL1841" t="n">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シャリタツ
+SV6]</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr"/>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1842" t="n">
+        <v>1190</v>
+      </c>
+      <c r="CL1842" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ビワ
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr"/>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1843" t="n">
+        <v>680</v>
+      </c>
+      <c r="CL1843" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ペリッパー
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr"/>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1844" t="n">
+        <v>350</v>
+      </c>
+      <c r="CL1844" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テツノカイナex
+SV4M]</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr"/>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1845" t="n">
+        <v>380</v>
+      </c>
+      <c r="CL1845" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>〔状態B〕センリ
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr"/>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1846" t="n">
+        <v>380</v>
+      </c>
+      <c r="CL1846" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本草エネルギー(チャンピオンズリーグ2023)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr"/>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1847" t="n">
+        <v>220</v>
+      </c>
+      <c r="CL1847" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハラバリー
+SV3]</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr"/>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1848" t="n">
+        <v>480</v>
+      </c>
+      <c r="CL1848" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーユイex
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr"/>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1849" t="n">
+        <v>380</v>
+      </c>
+      <c r="CL1849" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>〔状態B〕ニャローテ
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr"/>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1850" t="n">
+        <v>680</v>
+      </c>
+      <c r="CL1850" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スリープ
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr"/>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1851" t="n">
+        <v>2380</v>
+      </c>
+      <c r="CL1851" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本草エネルギー(SS新デザイン)
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr"/>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1852" t="n">
+        <v>530</v>
+      </c>
+      <c r="CL1852" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アオガラス
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr"/>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1853" t="n">
+        <v>260</v>
+      </c>
+      <c r="CL1853" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒスイビリリダマ(R仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr"/>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1854" t="n">
+        <v>580</v>
+      </c>
+      <c r="CL1854" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エリカ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr"/>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1855" t="n">
+        <v>1990</v>
+      </c>
+      <c r="CL1855" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マホイップVMAX
+s3a]</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr"/>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1856" t="n">
+        <v>990</v>
+      </c>
+      <c r="CL1856" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイ＆カビゴンGX
+sm9]</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr"/>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1857" t="n">
+        <v>4490</v>
+      </c>
+      <c r="CL1857" t="n">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドリュウズ
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr"/>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1858" t="n">
+        <v>630</v>
+      </c>
+      <c r="CL1858" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カプ・テテフGX(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr"/>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1859" t="n">
+        <v>2180</v>
+      </c>
+      <c r="CL1859" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カイリューV(SA)
+S7R]</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr"/>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1860" t="n">
+        <v>74800</v>
+      </c>
+      <c r="CL1860" t="n">
+        <v>59840</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラパルトV
+S2]</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr"/>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1861" t="n">
+        <v>790</v>
+      </c>
+      <c r="CL1861" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フラダリの奥の手
+XY]</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr"/>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1862" t="n">
+        <v>29800</v>
+      </c>
+      <c r="CL1862" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ビリジオン
+その他]</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr"/>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1863" t="n">
+        <v>11800</v>
+      </c>
+      <c r="CL1863" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>〔状態A-〕こくばバドレックスVMAX(SA)
+S6K]</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr"/>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1864" t="n">
+        <v>98000</v>
+      </c>
+      <c r="CL1864" t="n">
+        <v>78400</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メタグロスGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr"/>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1865" t="n">
+        <v>2780</v>
+      </c>
+      <c r="CL1865" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニンフィアVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr"/>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1866" t="n">
+        <v>11800</v>
+      </c>
+      <c r="CL1866" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケモンブリーダーの育成
+S2a]</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr"/>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1867" t="n">
+        <v>1430</v>
+      </c>
+      <c r="CL1867" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジュラルドンVMAX(SA)
+S7D]</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr"/>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1868" t="n">
+        <v>15800</v>
+      </c>
+      <c r="CL1868" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>〔状態B〕レックウザV
+S7R]</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr"/>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1869" t="n">
+        <v>420</v>
+      </c>
+      <c r="CL1869" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>〔状態B〕ザングース
+その他]</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr"/>
+      <c r="D1870" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1870" t="n">
+        <v>730</v>
+      </c>
+      <c r="CL1870" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>〔状態B〕ルカリオEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr"/>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1871" t="n">
+        <v>1590</v>
+      </c>
+      <c r="CL1871" t="n">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>〔状態B〕トルネロス
+その他]</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr"/>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1872" t="n">
+        <v>4990</v>
+      </c>
+      <c r="CL1872" t="n">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>〔状態B〕グラードンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr"/>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1873" t="n">
+        <v>7980</v>
+      </c>
+      <c r="CL1873" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>〔状態B〕エンテイGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr"/>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1874" t="n">
+        <v>9980</v>
+      </c>
+      <c r="CL1874" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>〔状態C〕レックウザGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr"/>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1875" t="n">
+        <v>32800</v>
+      </c>
+      <c r="CL1875" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>〔状態C〕ニンフィアEX(エラー版)
+CP3]</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr"/>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1876" t="n">
+        <v>94800</v>
+      </c>
+      <c r="CL1876" t="n">
+        <v>75840</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>〔状態B〕カイリューGX
+sm11]</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr"/>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1877" t="n">
+        <v>2580</v>
+      </c>
+      <c r="CL1877" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>〔状態B〕ザシアンV
+s1]</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr"/>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1878" t="n">
+        <v>530</v>
+      </c>
+      <c r="CL1878" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>〔状態B〕グズマ＆ハラ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr"/>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1879" t="n">
+        <v>680</v>
+      </c>
+      <c r="CL1879" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>〔状態B〕ユニットエネルギー草炎水
+sm5]</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr"/>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1880" t="n">
+        <v>2180</v>
+      </c>
+      <c r="CL1880" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>〔状態B〕アローラキュウコンGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr"/>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1881" t="n">
+        <v>1980</v>
+      </c>
+      <c r="CL1881" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>〔状態B〕フウロ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr"/>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1882" t="n">
+        <v>54800</v>
+      </c>
+      <c r="CL1882" t="n">
+        <v>43840</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>〔状態A-〕Nのゼクロム
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr"/>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1883" t="n">
+        <v>730</v>
+      </c>
+      <c r="CL1883" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ポケパッド
+M3]</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr"/>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1884" t="n">
+        <v>930</v>
+      </c>
+      <c r="CL1884" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガダークライex
+M5]</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>MUR</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr"/>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1885" t="n">
+        <v>72800</v>
+      </c>
+      <c r="CL1885" t="n">
+        <v>58240</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕モクロー＆アローラナッシーGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr"/>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1886" t="n">
+        <v>42800</v>
+      </c>
+      <c r="CL1886" t="n">
+        <v>34240</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>基本炎エネルギー(フレンドバトル)</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr"/>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1887" t="n">
+        <v>480</v>
+      </c>
+      <c r="CL1887" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>MカメックスEX</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr"/>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1888" t="n">
+        <v>12800</v>
+      </c>
+      <c r="CL1888" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>ヒヤッキー</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr"/>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1889" t="n">
+        <v>780</v>
+      </c>
+      <c r="CL1889" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕オリジンパルキアVSTAR</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr"/>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1890" t="n">
+        <v>23800</v>
+      </c>
+      <c r="CL1890" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>ウミディグダ</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr"/>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1891" t="n">
+        <v>980</v>
+      </c>
+      <c r="CL1891" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>ヨワシGX</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr"/>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1892" t="n">
+        <v>680</v>
+      </c>
+      <c r="CL1892" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ライチュウ＆アローラライチュウGX</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr"/>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1893" t="n">
+        <v>24800</v>
+      </c>
+      <c r="CL1893" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>ビリリダマ</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr"/>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1894" t="n">
+        <v>380</v>
+      </c>
+      <c r="CL1894" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕サトシのピカチュウ(カロスキャップver)</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr"/>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1895" t="n">
+        <v>178000</v>
+      </c>
+      <c r="CL1895" t="n">
+        <v>142400</v>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>パーモット</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr"/>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1896" t="n">
+        <v>580</v>
+      </c>
+      <c r="CL1896" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>〔状態A-〕クレセリア
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr"/>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1897" t="n">
+        <v>680</v>
+      </c>
+      <c r="CL1897" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>こくばバドレックスV</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr"/>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1898" t="n">
+        <v>1180</v>
+      </c>
+      <c r="CL1898" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>サーナイト</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr"/>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1899" t="n">
+        <v>880</v>
+      </c>
+      <c r="CL1899" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>アーケオス</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr"/>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1900" t="n">
+        <v>780</v>
+      </c>
+      <c r="CL1900" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>ゴマゾウ</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr"/>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1901" t="n">
+        <v>780</v>
+      </c>
+      <c r="CL1901" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>ディンルーex</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr"/>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1902" t="n">
+        <v>480</v>
+      </c>
+      <c r="CL1902" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>ルガルガンVMAX</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr"/>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1903" t="n">
+        <v>780</v>
+      </c>
+      <c r="CL1903" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>スナノケガワex</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr"/>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1904" t="n">
+        <v>1480</v>
+      </c>
+      <c r="CL1904" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>ブラッキーVMAX</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr"/>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1905" t="n">
+        <v>15800</v>
+      </c>
+      <c r="CL1905" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>オーロンゲV</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr"/>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CK1906" t="n">
+        <v>480</v>
+      </c>
+      <c r="CL1906" t="n">
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN1906"/>
+  <dimension ref="A1:CR2019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33638,6 +33638,26 @@
           <t>2026-06-27_diff</t>
         </is>
       </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>2026-06-28_price</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>2026-06-28_buy</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>2026-06-28_ratio</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>2026-06-28_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -77056,7 +77076,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1836" t="inlineStr"/>
       <c r="D1836" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77081,7 +77100,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1837" t="inlineStr"/>
       <c r="D1837" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77106,7 +77124,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1838" t="inlineStr"/>
       <c r="D1838" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77131,7 +77148,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1839" t="inlineStr"/>
       <c r="D1839" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77156,7 +77172,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1840" t="inlineStr"/>
       <c r="D1840" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77181,7 +77196,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1841" t="inlineStr"/>
       <c r="D1841" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77206,7 +77220,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1842" t="inlineStr"/>
       <c r="D1842" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77231,7 +77244,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1843" t="inlineStr"/>
       <c r="D1843" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77256,7 +77268,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1844" t="inlineStr"/>
       <c r="D1844" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77281,7 +77292,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1845" t="inlineStr"/>
       <c r="D1845" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77306,7 +77316,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1846" t="inlineStr"/>
       <c r="D1846" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77331,7 +77340,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1847" t="inlineStr"/>
       <c r="D1847" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77356,7 +77364,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1848" t="inlineStr"/>
       <c r="D1848" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77381,7 +77388,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1849" t="inlineStr"/>
       <c r="D1849" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77406,7 +77412,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1850" t="inlineStr"/>
       <c r="D1850" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77431,7 +77436,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1851" t="inlineStr"/>
       <c r="D1851" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77456,7 +77460,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1852" t="inlineStr"/>
       <c r="D1852" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77481,7 +77484,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1853" t="inlineStr"/>
       <c r="D1853" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77506,7 +77508,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1854" t="inlineStr"/>
       <c r="D1854" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77531,7 +77532,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1855" t="inlineStr"/>
       <c r="D1855" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77556,7 +77556,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1856" t="inlineStr"/>
       <c r="D1856" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77581,7 +77580,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1857" t="inlineStr"/>
       <c r="D1857" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77606,7 +77604,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1858" t="inlineStr"/>
       <c r="D1858" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77631,7 +77628,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1859" t="inlineStr"/>
       <c r="D1859" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77656,7 +77652,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1860" t="inlineStr"/>
       <c r="D1860" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77681,7 +77676,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1861" t="inlineStr"/>
       <c r="D1861" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77706,7 +77700,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1862" t="inlineStr"/>
       <c r="D1862" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77731,7 +77724,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1863" t="inlineStr"/>
       <c r="D1863" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77756,7 +77748,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1864" t="inlineStr"/>
       <c r="D1864" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77781,7 +77772,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1865" t="inlineStr"/>
       <c r="D1865" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77806,7 +77796,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1866" t="inlineStr"/>
       <c r="D1866" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77831,7 +77820,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1867" t="inlineStr"/>
       <c r="D1867" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77856,7 +77844,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1868" t="inlineStr"/>
       <c r="D1868" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77881,7 +77868,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1869" t="inlineStr"/>
       <c r="D1869" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77906,7 +77892,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1870" t="inlineStr"/>
       <c r="D1870" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77931,7 +77916,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1871" t="inlineStr"/>
       <c r="D1871" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77956,7 +77940,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1872" t="inlineStr"/>
       <c r="D1872" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -77981,7 +77964,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1873" t="inlineStr"/>
       <c r="D1873" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78006,7 +77988,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1874" t="inlineStr"/>
       <c r="D1874" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78031,7 +78012,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1875" t="inlineStr"/>
       <c r="D1875" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78056,7 +78036,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1876" t="inlineStr"/>
       <c r="D1876" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78081,7 +78060,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1877" t="inlineStr"/>
       <c r="D1877" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78106,7 +78084,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1878" t="inlineStr"/>
       <c r="D1878" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78131,7 +78108,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1879" t="inlineStr"/>
       <c r="D1879" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78156,7 +78132,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1880" t="inlineStr"/>
       <c r="D1880" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78181,7 +78156,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1881" t="inlineStr"/>
       <c r="D1881" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78206,7 +78180,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1882" t="inlineStr"/>
       <c r="D1882" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78231,7 +78204,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1883" t="inlineStr"/>
       <c r="D1883" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78256,7 +78228,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1884" t="inlineStr"/>
       <c r="D1884" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78281,7 +78252,6 @@
           <t>MUR</t>
         </is>
       </c>
-      <c r="C1885" t="inlineStr"/>
       <c r="D1885" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78305,7 +78275,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1886" t="inlineStr"/>
       <c r="D1886" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78329,7 +78298,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1887" t="inlineStr"/>
       <c r="D1887" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78353,7 +78321,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1888" t="inlineStr"/>
       <c r="D1888" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78377,7 +78344,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1889" t="inlineStr"/>
       <c r="D1889" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78401,7 +78367,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1890" t="inlineStr"/>
       <c r="D1890" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78425,7 +78390,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1891" t="inlineStr"/>
       <c r="D1891" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78449,7 +78413,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1892" t="inlineStr"/>
       <c r="D1892" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78473,7 +78436,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1893" t="inlineStr"/>
       <c r="D1893" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78497,7 +78459,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1894" t="inlineStr"/>
       <c r="D1894" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78521,7 +78482,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1895" t="inlineStr"/>
       <c r="D1895" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78545,7 +78505,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1896" t="inlineStr"/>
       <c r="D1896" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78570,7 +78529,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1897" t="inlineStr"/>
       <c r="D1897" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78594,7 +78552,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C1898" t="inlineStr"/>
       <c r="D1898" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78618,7 +78575,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C1899" t="inlineStr"/>
       <c r="D1899" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78642,7 +78598,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1900" t="inlineStr"/>
       <c r="D1900" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78666,7 +78621,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1901" t="inlineStr"/>
       <c r="D1901" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78690,7 +78644,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1902" t="inlineStr"/>
       <c r="D1902" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78714,7 +78667,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1903" t="inlineStr"/>
       <c r="D1903" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78738,7 +78690,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1904" t="inlineStr"/>
       <c r="D1904" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78762,7 +78713,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1905" t="inlineStr"/>
       <c r="D1905" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78786,7 +78736,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1906" t="inlineStr"/>
       <c r="D1906" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78797,6 +78746,2793 @@
       </c>
       <c r="CL1906" t="n">
         <v>384</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>メガゲッコウガex</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr"/>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1907" t="n">
+        <v>380</v>
+      </c>
+      <c r="CP1907" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>メガガルーラex</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr"/>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1908" t="n">
+        <v>280</v>
+      </c>
+      <c r="CP1908" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フシギバナEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr"/>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1909" t="n">
+        <v>4490</v>
+      </c>
+      <c r="CP1909" t="n">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>〔状態B〕コバルオン
+その他]</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr"/>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1910" t="n">
+        <v>980</v>
+      </c>
+      <c r="CP1910" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>〔状態A-〕おいわいファンファーレ(2025)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr"/>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1911" t="n">
+        <v>14800</v>
+      </c>
+      <c r="CP1911" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミカンのまなざし
+SV8]</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr"/>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1912" t="n">
+        <v>3780</v>
+      </c>
+      <c r="CP1912" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>〔状態C〕MゲンガーEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr"/>
+      <c r="D1913" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1913" t="n">
+        <v>11800</v>
+      </c>
+      <c r="CP1913" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドッコラー
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr"/>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1914" t="n">
+        <v>730</v>
+      </c>
+      <c r="CP1914" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>〔状態B〕ガマガル
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr"/>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1915" t="n">
+        <v>680</v>
+      </c>
+      <c r="CP1915" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ビクティニ(AR仕様)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr"/>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1916" t="n">
+        <v>2490</v>
+      </c>
+      <c r="CP1916" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハルクジラex
+SV10]</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr"/>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1917" t="n">
+        <v>630</v>
+      </c>
+      <c r="CP1917" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本鋼エネルギー(チャンピオンズリーグ2025)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr"/>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1918" t="n">
+        <v>680</v>
+      </c>
+      <c r="CP1918" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>〔状態C〕ポケパークのアチャモ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr"/>
+      <c r="D1919" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1919" t="n">
+        <v>39800</v>
+      </c>
+      <c r="CP1919" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブライア
+SV7]</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr"/>
+      <c r="D1920" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1920" t="n">
+        <v>1480</v>
+      </c>
+      <c r="CP1920" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>〔状態A-〕かるいし
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr"/>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1921" t="n">
+        <v>830</v>
+      </c>
+      <c r="CP1921" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>〔状態B〕ドーミラー
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr"/>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1922" t="n">
+        <v>420</v>
+      </c>
+      <c r="CP1922" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プクリンex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr"/>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1923" t="n">
+        <v>260</v>
+      </c>
+      <c r="CP1923" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ディンルーex
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr"/>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1924" t="n">
+        <v>730</v>
+      </c>
+      <c r="CP1924" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>〔状態B〕グラードン
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr"/>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1925" t="n">
+        <v>2980</v>
+      </c>
+      <c r="CP1925" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>〔状態B〕サンダース(YU NAGABA)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr"/>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1926" t="n">
+        <v>10800</v>
+      </c>
+      <c r="CP1926" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バンギラスex
+SV3]</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr"/>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1927" t="n">
+        <v>260</v>
+      </c>
+      <c r="CP1927" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケモンいれかえ
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr"/>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1928" t="n">
+        <v>1080</v>
+      </c>
+      <c r="CP1928" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウツーVSTAR
+S10b]</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr"/>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1929" t="n">
+        <v>480</v>
+      </c>
+      <c r="CP1929" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ワナイダーex
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr"/>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1930" t="n">
+        <v>330</v>
+      </c>
+      <c r="CP1930" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>〔状態B〕ボタン
+SV1S]</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr"/>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1931" t="n">
+        <v>630</v>
+      </c>
+      <c r="CP1931" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヒスイダイケンキV
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr"/>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1932" t="n">
+        <v>1280</v>
+      </c>
+      <c r="CP1932" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ギラティナVSTAR
+S12a]</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr"/>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1933" t="n">
+        <v>260</v>
+      </c>
+      <c r="CP1933" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ひかるコイキング(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr"/>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1934" t="n">
+        <v>21800</v>
+      </c>
+      <c r="CP1934" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ツンデツンデGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr"/>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1935" t="n">
+        <v>590</v>
+      </c>
+      <c r="CP1935" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>〔状態B〕エネルギーリサイクル
+XY]</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr"/>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1936" t="n">
+        <v>1180</v>
+      </c>
+      <c r="CP1936" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヘルガーV
+S3]</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr"/>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1937" t="n">
+        <v>990</v>
+      </c>
+      <c r="CP1937" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ライチ(SR仕様)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr"/>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1938" t="n">
+        <v>16300</v>
+      </c>
+      <c r="CP1938" t="n">
+        <v>13040</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツー＆ミュウGX
+sm11]</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr"/>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1939" t="n">
+        <v>47800</v>
+      </c>
+      <c r="CP1939" t="n">
+        <v>38240</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr"/>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1940" t="n">
+        <v>3580</v>
+      </c>
+      <c r="CP1940" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>〔状態C〕ピカチュウδ-デルタ種(明治)
+その他]</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr"/>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1941" t="n">
+        <v>10800</v>
+      </c>
+      <c r="CP1941" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リザードンGX
+smP2]</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr"/>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1942" t="n">
+        <v>4090</v>
+      </c>
+      <c r="CP1942" t="n">
+        <v>3272</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グレイシアGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr"/>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1943" t="n">
+        <v>8480</v>
+      </c>
+      <c r="CP1943" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニンフィアVMAX
+S6a]</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr"/>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1944" t="n">
+        <v>7980</v>
+      </c>
+      <c r="CP1944" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オーロット＆ヨノワールGX(SA)
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr"/>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1945" t="n">
+        <v>11800</v>
+      </c>
+      <c r="CP1945" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウ(YU NAGABA/未開封)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr"/>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1946" t="n">
+        <v>23800</v>
+      </c>
+      <c r="CP1946" t="n">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マグマの滝壺
+S9]</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr"/>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1947" t="n">
+        <v>630</v>
+      </c>
+      <c r="CP1947" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>〔状態B〕チェレン
+その他]</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr"/>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1948" t="n">
+        <v>1180</v>
+      </c>
+      <c r="CP1948" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エリカのおもてなし
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr"/>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1949" t="n">
+        <v>98000</v>
+      </c>
+      <c r="CP1949" t="n">
+        <v>78400</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>〔状態C〕ライコウEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr"/>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1950" t="n">
+        <v>8980</v>
+      </c>
+      <c r="CP1950" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>〔状態B〕ビリジオンEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr"/>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1951" t="n">
+        <v>5490</v>
+      </c>
+      <c r="CP1951" t="n">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケモンごっこ
+s4a]</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr"/>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1952" t="n">
+        <v>2380</v>
+      </c>
+      <c r="CP1952" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>〔状態B〕シンカソーダ
+XY]</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr"/>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1953" t="n">
+        <v>1480</v>
+      </c>
+      <c r="CP1953" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>〔状態C〕ベル
+その他]</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr"/>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1954" t="n">
+        <v>29800</v>
+      </c>
+      <c r="CP1954" t="n">
+        <v>23840</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>〔状態B〕エーフィGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr"/>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1955" t="n">
+        <v>14800</v>
+      </c>
+      <c r="CP1955" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr"/>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1956" t="n">
+        <v>1590</v>
+      </c>
+      <c r="CP1956" t="n">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲンシグラードンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr"/>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1957" t="n">
+        <v>74800</v>
+      </c>
+      <c r="CP1957" t="n">
+        <v>59840</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>〔状態B〕オドリドリex
+M2]</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr"/>
+      <c r="D1958" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1958" t="n">
+        <v>480</v>
+      </c>
+      <c r="CP1958" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のダグトリオ
+M2a]</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr"/>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1959" t="n">
+        <v>330</v>
+      </c>
+      <c r="CP1959" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>〔状態B〕マチエール
+M4]</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr"/>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1960" t="n">
+        <v>580</v>
+      </c>
+      <c r="CP1960" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ライボルト
+M5]</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr"/>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1961" t="n">
+        <v>370</v>
+      </c>
+      <c r="CP1961" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ブラッキー☆(25th)</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr"/>
+      <c r="D1962" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1962" t="n">
+        <v>57800</v>
+      </c>
+      <c r="CP1962" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>テツノイサハex</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr"/>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1963" t="n">
+        <v>220</v>
+      </c>
+      <c r="CP1963" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヤバソチャex
+SV5a]</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr"/>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1964" t="n">
+        <v>2050</v>
+      </c>
+      <c r="CP1964" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>フシギバナex</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr"/>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1965" t="n">
+        <v>24800</v>
+      </c>
+      <c r="CP1965" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>コダック(ムンク)</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr"/>
+      <c r="D1966" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1966" t="n">
+        <v>448000</v>
+      </c>
+      <c r="CP1966" t="n">
+        <v>358400</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>メガリザードンXex</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr"/>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1967" t="n">
+        <v>128000</v>
+      </c>
+      <c r="CP1967" t="n">
+        <v>102400</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ブースターex</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr"/>
+      <c r="D1968" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1968" t="n">
+        <v>19800</v>
+      </c>
+      <c r="CP1968" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>ケロマツ</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr"/>
+      <c r="D1969" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1969" t="n">
+        <v>1780</v>
+      </c>
+      <c r="CP1969" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>トサキント</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr"/>
+      <c r="D1970" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1970" t="n">
+        <v>580</v>
+      </c>
+      <c r="CP1970" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>〔状態B〕エリキテル
+M1S]</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr"/>
+      <c r="D1971" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1971" t="n">
+        <v>320</v>
+      </c>
+      <c r="CP1971" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>テツノカイナex</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr"/>
+      <c r="D1972" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1972" t="n">
+        <v>1180</v>
+      </c>
+      <c r="CP1972" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>リーリエのアブリボン</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr"/>
+      <c r="D1973" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1973" t="n">
+        <v>980</v>
+      </c>
+      <c r="CP1973" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>ラティアスex</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr"/>
+      <c r="D1974" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1974" t="n">
+        <v>33800</v>
+      </c>
+      <c r="CP1974" t="n">
+        <v>27040</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ミミッキュ</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr"/>
+      <c r="D1975" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1975" t="n">
+        <v>15800</v>
+      </c>
+      <c r="CP1975" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>デデンネex</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr"/>
+      <c r="D1976" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1976" t="n">
+        <v>1280</v>
+      </c>
+      <c r="CP1976" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>クチートV</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr"/>
+      <c r="D1977" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1977" t="n">
+        <v>1380</v>
+      </c>
+      <c r="CP1977" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>ソルガレオ＆ルナアーラGX(SA)</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr"/>
+      <c r="D1978" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1978" t="n">
+        <v>64800</v>
+      </c>
+      <c r="CP1978" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>メガヤドランex</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr"/>
+      <c r="D1979" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1979" t="n">
+        <v>880</v>
+      </c>
+      <c r="CP1979" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>バンバドロ</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr"/>
+      <c r="D1980" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1980" t="n">
+        <v>580</v>
+      </c>
+      <c r="CP1980" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>ロケット団のダグトリオ</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr"/>
+      <c r="D1981" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1981" t="n">
+        <v>580</v>
+      </c>
+      <c r="CP1981" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕サザンドラex</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr"/>
+      <c r="D1982" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1982" t="n">
+        <v>11800</v>
+      </c>
+      <c r="CP1982" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>ゲッコウガ＆ゾロアークGX</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr"/>
+      <c r="D1983" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1983" t="n">
+        <v>21800</v>
+      </c>
+      <c r="CP1983" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>ハガネール</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr"/>
+      <c r="D1984" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1984" t="n">
+        <v>580</v>
+      </c>
+      <c r="CP1984" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>ブリジュラス</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr"/>
+      <c r="D1985" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1985" t="n">
+        <v>680</v>
+      </c>
+      <c r="CP1985" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>ヤレユータン</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr"/>
+      <c r="D1986" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1986" t="n">
+        <v>480</v>
+      </c>
+      <c r="CP1986" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>ニャースex</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr"/>
+      <c r="D1987" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1987" t="n">
+        <v>2980</v>
+      </c>
+      <c r="CP1987" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>望遠スコープ</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr"/>
+      <c r="D1988" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1988" t="n">
+        <v>680</v>
+      </c>
+      <c r="CP1988" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>ミッシングクローバー</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr"/>
+      <c r="D1989" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1989" t="n">
+        <v>1980</v>
+      </c>
+      <c r="CP1989" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>基本闘エネルギー(チャンピオンズリーグ2026)</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr"/>
+      <c r="D1990" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1990" t="n">
+        <v>780</v>
+      </c>
+      <c r="CP1990" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>基本草エネルギー</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr"/>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1991" t="n">
+        <v>3180</v>
+      </c>
+      <c r="CP1991" t="n">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>〔PSA8鑑定済〕メイのはげまし</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr"/>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1992" t="n">
+        <v>13800</v>
+      </c>
+      <c r="CP1992" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ミカン</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr"/>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1993" t="n">
+        <v>32800</v>
+      </c>
+      <c r="CP1993" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>ポケモンごっこ</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr"/>
+      <c r="D1994" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1994" t="n">
+        <v>3480</v>
+      </c>
+      <c r="CP1994" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>モノマネむすめ</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr"/>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1995" t="n">
+        <v>680</v>
+      </c>
+      <c r="CP1995" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>とりつかい</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr"/>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1996" t="n">
+        <v>780</v>
+      </c>
+      <c r="CP1996" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>マリィ</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr"/>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1997" t="n">
+        <v>11800</v>
+      </c>
+      <c r="CP1997" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>ムサシとコジロウ</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr"/>
+      <c r="D1998" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1998" t="n">
+        <v>37800</v>
+      </c>
+      <c r="CP1998" t="n">
+        <v>30240</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>リーリエ</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr"/>
+      <c r="D1999" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CO1999" t="n">
+        <v>69800</v>
+      </c>
+      <c r="CP1999" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メタモン(未開封/バリヤード)
+その他]</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr"/>
+      <c r="D2000" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2000" t="n">
+        <v>54800</v>
+      </c>
+      <c r="CP2000" t="n">
+        <v>43840</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カイリキーEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr"/>
+      <c r="D2001" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2001" t="n">
+        <v>790</v>
+      </c>
+      <c r="CP2001" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>〔状態C〕キバゴ
+その他]</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr"/>
+      <c r="D2002" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2002" t="n">
+        <v>280</v>
+      </c>
+      <c r="CP2002" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>〔状態C〕MプテラEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr"/>
+      <c r="D2003" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2003" t="n">
+        <v>1080</v>
+      </c>
+      <c r="CP2003" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>〔状態C〕マホミル
+SV7]</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr"/>
+      <c r="D2004" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2004" t="n">
+        <v>380</v>
+      </c>
+      <c r="CP2004" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>〔状態C〕アローラナッシーex
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr"/>
+      <c r="D2005" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2005" t="n">
+        <v>1080</v>
+      </c>
+      <c r="CP2005" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>〔状態B〕フライゴン
+その他]</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr"/>
+      <c r="D2006" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2006" t="n">
+        <v>1580</v>
+      </c>
+      <c r="CP2006" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フライゴン
+その他]</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr"/>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2007" t="n">
+        <v>4880</v>
+      </c>
+      <c r="CP2007" t="n">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>〔状態C〕チュリネ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr"/>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2008" t="n">
+        <v>380</v>
+      </c>
+      <c r="CP2008" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>〔状態C〕ラティアスex
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr"/>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2009" t="n">
+        <v>1180</v>
+      </c>
+      <c r="CP2009" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>〔状態C〕ギギギアル
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr"/>
+      <c r="D2010" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2010" t="n">
+        <v>320</v>
+      </c>
+      <c r="CP2010" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゲッコウガex
+SV5a]</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr"/>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2011" t="n">
+        <v>980</v>
+      </c>
+      <c r="CP2011" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>〔状態B〕スワンナ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr"/>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2012" t="n">
+        <v>780</v>
+      </c>
+      <c r="CP2012" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>〔状態C〕ニャローテ
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr"/>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2013" t="n">
+        <v>380</v>
+      </c>
+      <c r="CP2013" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウ
+その他]</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr"/>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2014" t="n">
+        <v>3780</v>
+      </c>
+      <c r="CP2014" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>〔状態B〕ニャオニクスEX(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr"/>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2015" t="n">
+        <v>1980</v>
+      </c>
+      <c r="CP2015" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>〔状態C〕ギラティナ
+XY]</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr"/>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2016" t="n">
+        <v>1080</v>
+      </c>
+      <c r="CP2016" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>〔状態C〕Nのゾロアークex
+SV9]</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr"/>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2017" t="n">
+        <v>1280</v>
+      </c>
+      <c r="CP2017" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>〔状態B〕ワタルのリザードン(未開封/中国語版)
+海外版]</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr"/>
+      <c r="D2018" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2018" t="n">
+        <v>1480</v>
+      </c>
+      <c r="CP2018" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケるんTVのピカチュウとなかまたち(ジャンボカード)
+ジャンボカード]</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr"/>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="CO2019" t="n">
+        <v>1780</v>
+      </c>
+      <c r="CP2019" t="n">
+        <v>1424</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR2019"/>
+  <dimension ref="A1:CV2041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33658,6 +33658,26 @@
           <t>2026-06-28_diff</t>
         </is>
       </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>2026-06-29_price</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>2026-06-29_buy</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>2026-06-29_ratio</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>2026-06-29_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -78759,7 +78779,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1907" t="inlineStr"/>
       <c r="D1907" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78783,7 +78802,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1908" t="inlineStr"/>
       <c r="D1908" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78808,7 +78826,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1909" t="inlineStr"/>
       <c r="D1909" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78833,7 +78850,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1910" t="inlineStr"/>
       <c r="D1910" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78858,7 +78874,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1911" t="inlineStr"/>
       <c r="D1911" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78883,7 +78898,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1912" t="inlineStr"/>
       <c r="D1912" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78908,7 +78922,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1913" t="inlineStr"/>
       <c r="D1913" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78933,7 +78946,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1914" t="inlineStr"/>
       <c r="D1914" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78958,7 +78970,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1915" t="inlineStr"/>
       <c r="D1915" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -78983,7 +78994,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1916" t="inlineStr"/>
       <c r="D1916" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79008,7 +79018,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1917" t="inlineStr"/>
       <c r="D1917" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79033,7 +79042,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1918" t="inlineStr"/>
       <c r="D1918" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79058,7 +79066,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1919" t="inlineStr"/>
       <c r="D1919" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79083,7 +79090,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1920" t="inlineStr"/>
       <c r="D1920" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79108,7 +79114,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1921" t="inlineStr"/>
       <c r="D1921" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79133,7 +79138,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1922" t="inlineStr"/>
       <c r="D1922" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79158,7 +79162,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1923" t="inlineStr"/>
       <c r="D1923" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79183,7 +79186,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1924" t="inlineStr"/>
       <c r="D1924" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79208,7 +79210,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1925" t="inlineStr"/>
       <c r="D1925" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79233,7 +79234,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1926" t="inlineStr"/>
       <c r="D1926" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79258,7 +79258,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1927" t="inlineStr"/>
       <c r="D1927" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79283,7 +79282,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1928" t="inlineStr"/>
       <c r="D1928" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79308,7 +79306,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1929" t="inlineStr"/>
       <c r="D1929" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79333,7 +79330,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1930" t="inlineStr"/>
       <c r="D1930" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79358,7 +79354,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1931" t="inlineStr"/>
       <c r="D1931" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79383,7 +79378,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1932" t="inlineStr"/>
       <c r="D1932" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79408,7 +79402,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C1933" t="inlineStr"/>
       <c r="D1933" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79433,7 +79426,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1934" t="inlineStr"/>
       <c r="D1934" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79458,7 +79450,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C1935" t="inlineStr"/>
       <c r="D1935" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79483,7 +79474,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1936" t="inlineStr"/>
       <c r="D1936" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79508,7 +79498,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1937" t="inlineStr"/>
       <c r="D1937" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79533,7 +79522,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1938" t="inlineStr"/>
       <c r="D1938" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79558,7 +79546,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1939" t="inlineStr"/>
       <c r="D1939" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79583,7 +79570,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1940" t="inlineStr"/>
       <c r="D1940" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79608,7 +79594,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1941" t="inlineStr"/>
       <c r="D1941" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79633,7 +79618,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1942" t="inlineStr"/>
       <c r="D1942" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79658,7 +79642,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1943" t="inlineStr"/>
       <c r="D1943" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79683,7 +79666,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1944" t="inlineStr"/>
       <c r="D1944" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79708,7 +79690,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1945" t="inlineStr"/>
       <c r="D1945" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79733,7 +79714,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1946" t="inlineStr"/>
       <c r="D1946" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79758,7 +79738,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1947" t="inlineStr"/>
       <c r="D1947" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79783,7 +79762,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1948" t="inlineStr"/>
       <c r="D1948" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79808,7 +79786,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1949" t="inlineStr"/>
       <c r="D1949" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79833,7 +79810,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1950" t="inlineStr"/>
       <c r="D1950" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79858,7 +79834,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1951" t="inlineStr"/>
       <c r="D1951" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79883,7 +79858,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1952" t="inlineStr"/>
       <c r="D1952" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79908,7 +79882,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1953" t="inlineStr"/>
       <c r="D1953" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79933,7 +79906,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1954" t="inlineStr"/>
       <c r="D1954" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79958,7 +79930,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1955" t="inlineStr"/>
       <c r="D1955" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -79983,7 +79954,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1956" t="inlineStr"/>
       <c r="D1956" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80008,7 +79978,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1957" t="inlineStr"/>
       <c r="D1957" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80033,7 +80002,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1958" t="inlineStr"/>
       <c r="D1958" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80058,7 +80026,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1959" t="inlineStr"/>
       <c r="D1959" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80083,7 +80050,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1960" t="inlineStr"/>
       <c r="D1960" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80108,7 +80074,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1961" t="inlineStr"/>
       <c r="D1961" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80132,7 +80097,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1962" t="inlineStr"/>
       <c r="D1962" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80156,7 +80120,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C1963" t="inlineStr"/>
       <c r="D1963" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80181,7 +80144,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1964" t="inlineStr"/>
       <c r="D1964" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80205,7 +80167,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1965" t="inlineStr"/>
       <c r="D1965" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80229,7 +80190,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1966" t="inlineStr"/>
       <c r="D1966" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80253,7 +80213,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1967" t="inlineStr"/>
       <c r="D1967" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80277,7 +80236,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1968" t="inlineStr"/>
       <c r="D1968" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80301,7 +80259,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1969" t="inlineStr"/>
       <c r="D1969" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80325,7 +80282,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1970" t="inlineStr"/>
       <c r="D1970" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80350,7 +80306,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1971" t="inlineStr"/>
       <c r="D1971" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80374,7 +80329,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1972" t="inlineStr"/>
       <c r="D1972" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80398,7 +80352,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1973" t="inlineStr"/>
       <c r="D1973" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80422,7 +80375,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1974" t="inlineStr"/>
       <c r="D1974" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80446,7 +80398,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1975" t="inlineStr"/>
       <c r="D1975" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80470,7 +80421,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1976" t="inlineStr"/>
       <c r="D1976" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80494,7 +80444,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1977" t="inlineStr"/>
       <c r="D1977" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80518,7 +80467,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1978" t="inlineStr"/>
       <c r="D1978" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80542,7 +80490,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1979" t="inlineStr"/>
       <c r="D1979" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80566,7 +80513,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1980" t="inlineStr"/>
       <c r="D1980" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80590,7 +80536,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1981" t="inlineStr"/>
       <c r="D1981" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80614,7 +80559,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1982" t="inlineStr"/>
       <c r="D1982" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80638,7 +80582,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1983" t="inlineStr"/>
       <c r="D1983" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80662,7 +80605,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1984" t="inlineStr"/>
       <c r="D1984" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80686,7 +80628,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C1985" t="inlineStr"/>
       <c r="D1985" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80710,7 +80651,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C1986" t="inlineStr"/>
       <c r="D1986" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80734,7 +80674,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1987" t="inlineStr"/>
       <c r="D1987" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80758,7 +80697,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1988" t="inlineStr"/>
       <c r="D1988" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80782,7 +80720,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1989" t="inlineStr"/>
       <c r="D1989" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80806,7 +80743,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1990" t="inlineStr"/>
       <c r="D1990" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80830,7 +80766,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C1991" t="inlineStr"/>
       <c r="D1991" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80854,7 +80789,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C1992" t="inlineStr"/>
       <c r="D1992" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80878,7 +80812,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1993" t="inlineStr"/>
       <c r="D1993" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80902,7 +80835,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1994" t="inlineStr"/>
       <c r="D1994" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80926,7 +80858,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1995" t="inlineStr"/>
       <c r="D1995" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80950,7 +80881,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1996" t="inlineStr"/>
       <c r="D1996" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80974,7 +80904,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C1997" t="inlineStr"/>
       <c r="D1997" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -80998,7 +80927,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C1998" t="inlineStr"/>
       <c r="D1998" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81022,7 +80950,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C1999" t="inlineStr"/>
       <c r="D1999" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81047,7 +80974,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2000" t="inlineStr"/>
       <c r="D2000" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81072,7 +80998,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2001" t="inlineStr"/>
       <c r="D2001" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81097,7 +81022,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2002" t="inlineStr"/>
       <c r="D2002" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81122,7 +81046,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2003" t="inlineStr"/>
       <c r="D2003" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81147,7 +81070,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2004" t="inlineStr"/>
       <c r="D2004" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81172,7 +81094,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2005" t="inlineStr"/>
       <c r="D2005" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81197,7 +81118,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2006" t="inlineStr"/>
       <c r="D2006" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81222,7 +81142,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2007" t="inlineStr"/>
       <c r="D2007" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81247,7 +81166,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2008" t="inlineStr"/>
       <c r="D2008" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81272,7 +81190,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2009" t="inlineStr"/>
       <c r="D2009" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81297,7 +81214,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2010" t="inlineStr"/>
       <c r="D2010" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81322,7 +81238,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2011" t="inlineStr"/>
       <c r="D2011" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81347,7 +81262,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2012" t="inlineStr"/>
       <c r="D2012" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81372,7 +81286,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2013" t="inlineStr"/>
       <c r="D2013" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81397,7 +81310,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2014" t="inlineStr"/>
       <c r="D2014" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81422,7 +81334,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2015" t="inlineStr"/>
       <c r="D2015" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81447,7 +81358,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2016" t="inlineStr"/>
       <c r="D2016" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81472,7 +81382,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C2017" t="inlineStr"/>
       <c r="D2017" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81497,7 +81406,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2018" t="inlineStr"/>
       <c r="D2018" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81522,7 +81430,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2019" t="inlineStr"/>
       <c r="D2019" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -81533,6 +81440,555 @@
       </c>
       <c r="CP2019" t="n">
         <v>1424</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>メガゲッコウガex</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr"/>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2020" t="n">
+        <v>380</v>
+      </c>
+      <c r="CT2020" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キュレムEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr"/>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2021" t="n">
+        <v>3490</v>
+      </c>
+      <c r="CT2021" t="n">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケパッド
+M-P]</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr"/>
+      <c r="D2022" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2022" t="n">
+        <v>320</v>
+      </c>
+      <c r="CT2022" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>〔状態B〕イーブイ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr"/>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2023" t="n">
+        <v>980</v>
+      </c>
+      <c r="CT2023" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>〔状態B〕オタマロ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr"/>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2024" t="n">
+        <v>580</v>
+      </c>
+      <c r="CT2024" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>〔状態B〕メラルバ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr"/>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2025" t="n">
+        <v>580</v>
+      </c>
+      <c r="CT2025" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr"/>
+      <c r="D2026" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2026" t="n">
+        <v>680</v>
+      </c>
+      <c r="CT2026" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>〔状態B〕アイリスの闘志
+SV9]</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr"/>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2027" t="n">
+        <v>880</v>
+      </c>
+      <c r="CT2027" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブロスターBREAK
+XY]</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr"/>
+      <c r="D2028" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2028" t="n">
+        <v>4180</v>
+      </c>
+      <c r="CT2028" t="n">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タマタマ
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr"/>
+      <c r="D2029" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2029" t="n">
+        <v>680</v>
+      </c>
+      <c r="CT2029" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本水エネルギー(フレンドバトル)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr"/>
+      <c r="D2030" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2030" t="n">
+        <v>350</v>
+      </c>
+      <c r="CT2030" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オーガポンいしずえのめんex
+SV6]</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr"/>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2031" t="n">
+        <v>580</v>
+      </c>
+      <c r="CT2031" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウミディグダ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr"/>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2032" t="n">
+        <v>380</v>
+      </c>
+      <c r="CT2032" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エーフィ(YU NAGABA)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr"/>
+      <c r="D2033" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2033" t="n">
+        <v>12800</v>
+      </c>
+      <c r="CT2033" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アローラナッシーV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr"/>
+      <c r="D2034" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2034" t="n">
+        <v>260</v>
+      </c>
+      <c r="CT2034" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヘラクロス
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2035" t="inlineStr"/>
+      <c r="D2035" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2035" t="n">
+        <v>730</v>
+      </c>
+      <c r="CT2035" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>〔状態A-〕タマンチュラ
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2036" t="inlineStr"/>
+      <c r="D2036" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2036" t="n">
+        <v>480</v>
+      </c>
+      <c r="CT2036" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2037" t="inlineStr"/>
+      <c r="D2037" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2037" t="n">
+        <v>2780</v>
+      </c>
+      <c r="CT2037" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イーブイVMAX
+S-P]</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2038" t="inlineStr"/>
+      <c r="D2038" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2038" t="n">
+        <v>4480</v>
+      </c>
+      <c r="CT2038" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リザードンVSTAR
+S12a]</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C2039" t="inlineStr"/>
+      <c r="D2039" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2039" t="n">
+        <v>14300</v>
+      </c>
+      <c r="CT2039" t="n">
+        <v>11440</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>〔状態C〕アセロラの予感
+S8b]</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2040" t="inlineStr"/>
+      <c r="D2040" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2040" t="n">
+        <v>3980</v>
+      </c>
+      <c r="CT2040" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レジエレキV
+S12]</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2041" t="inlineStr"/>
+      <c r="D2041" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CS2041" t="n">
+        <v>260</v>
+      </c>
+      <c r="CT2041" t="n">
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -33174,7 +33174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV2041"/>
+  <dimension ref="A1:CZ2122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33678,6 +33678,26 @@
           <t>2026-06-29_diff</t>
         </is>
       </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>2026-06-30_price</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>2026-06-30_buy</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>2026-06-30_ratio</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>2026-06-30_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -81453,7 +81473,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2020" t="inlineStr"/>
       <c r="D2020" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81478,7 +81497,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2021" t="inlineStr"/>
       <c r="D2021" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81503,7 +81521,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2022" t="inlineStr"/>
       <c r="D2022" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81528,7 +81545,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2023" t="inlineStr"/>
       <c r="D2023" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81553,7 +81569,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2024" t="inlineStr"/>
       <c r="D2024" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81578,7 +81593,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2025" t="inlineStr"/>
       <c r="D2025" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81603,7 +81617,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2026" t="inlineStr"/>
       <c r="D2026" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81628,7 +81641,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2027" t="inlineStr"/>
       <c r="D2027" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81653,7 +81665,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2028" t="inlineStr"/>
       <c r="D2028" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81678,7 +81689,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2029" t="inlineStr"/>
       <c r="D2029" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81703,7 +81713,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2030" t="inlineStr"/>
       <c r="D2030" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81728,7 +81737,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2031" t="inlineStr"/>
       <c r="D2031" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81753,7 +81761,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C2032" t="inlineStr"/>
       <c r="D2032" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81778,7 +81785,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2033" t="inlineStr"/>
       <c r="D2033" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81803,7 +81809,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2034" t="inlineStr"/>
       <c r="D2034" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81828,7 +81833,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2035" t="inlineStr"/>
       <c r="D2035" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81853,7 +81857,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2036" t="inlineStr"/>
       <c r="D2036" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81878,7 +81881,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2037" t="inlineStr"/>
       <c r="D2037" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81903,7 +81905,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2038" t="inlineStr"/>
       <c r="D2038" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81928,7 +81929,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2039" t="inlineStr"/>
       <c r="D2039" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81953,7 +81953,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2040" t="inlineStr"/>
       <c r="D2040" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81978,7 +81977,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2041" t="inlineStr"/>
       <c r="D2041" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -81989,6 +81987,2001 @@
       </c>
       <c r="CT2041" t="n">
         <v>208</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>〔状態B〕ギギギアル(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2042" t="inlineStr"/>
+      <c r="D2042" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2042" t="n">
+        <v>1580</v>
+      </c>
+      <c r="CX2042" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キュレムEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2043" t="inlineStr"/>
+      <c r="D2043" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2043" t="n">
+        <v>3490</v>
+      </c>
+      <c r="CX2043" t="n">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハトーボー
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr"/>
+      <c r="D2044" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2044" t="n">
+        <v>390</v>
+      </c>
+      <c r="CX2044" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>〔状態B〕シビシラス
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr"/>
+      <c r="D2045" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2045" t="n">
+        <v>1480</v>
+      </c>
+      <c r="CX2045" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パールル
+SV10]</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2046" t="inlineStr"/>
+      <c r="D2046" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2046" t="n">
+        <v>680</v>
+      </c>
+      <c r="CX2046" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラパルトex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C2047" t="inlineStr"/>
+      <c r="D2047" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2047" t="n">
+        <v>2630</v>
+      </c>
+      <c r="CX2047" t="n">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>〔状態B〕ビブラーバ
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2048" t="inlineStr"/>
+      <c r="D2048" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2048" t="n">
+        <v>380</v>
+      </c>
+      <c r="CX2048" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼイユ
+SV6]</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2049" t="inlineStr"/>
+      <c r="D2049" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2049" t="n">
+        <v>1480</v>
+      </c>
+      <c r="CX2049" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハヤシガメ
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2050" t="inlineStr"/>
+      <c r="D2050" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2050" t="n">
+        <v>480</v>
+      </c>
+      <c r="CX2050" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>〔状態A-〕パルデアケンタロス
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2051" t="inlineStr"/>
+      <c r="D2051" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2051" t="n">
+        <v>330</v>
+      </c>
+      <c r="CX2051" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リップ
+SV4M]</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2052" t="inlineStr"/>
+      <c r="D2052" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2052" t="n">
+        <v>630</v>
+      </c>
+      <c r="CX2052" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本超エネルギー(チャンピオンズリーグ2024)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2053" t="inlineStr"/>
+      <c r="D2053" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2053" t="n">
+        <v>480</v>
+      </c>
+      <c r="CX2053" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>〔状態B〕オモダカ
+SV3]</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C2054" t="inlineStr"/>
+      <c r="D2054" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2054" t="n">
+        <v>1080</v>
+      </c>
+      <c r="CX2054" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カヌチャン
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2055" t="inlineStr"/>
+      <c r="D2055" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2055" t="n">
+        <v>630</v>
+      </c>
+      <c r="CX2055" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プテラVSTAR
+S11]</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C2056" t="inlineStr"/>
+      <c r="D2056" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2056" t="n">
+        <v>260</v>
+      </c>
+      <c r="CX2056" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラプラスGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2057" t="inlineStr"/>
+      <c r="D2057" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2057" t="n">
+        <v>490</v>
+      </c>
+      <c r="CX2057" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジバコイル
+S12a]</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2058" t="inlineStr"/>
+      <c r="D2058" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2058" t="n">
+        <v>730</v>
+      </c>
+      <c r="CX2058" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>〔状態A-〕イカサマコイン
+XY]</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2059" t="inlineStr"/>
+      <c r="D2059" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2059" t="n">
+        <v>1480</v>
+      </c>
+      <c r="CX2059" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バクガメス
+その他]</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2060" t="inlineStr"/>
+      <c r="D2060" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2060" t="n">
+        <v>390</v>
+      </c>
+      <c r="CX2060" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レアコイル
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2061" t="inlineStr"/>
+      <c r="D2061" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2061" t="n">
+        <v>680</v>
+      </c>
+      <c r="CX2061" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マリィ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2062" t="inlineStr"/>
+      <c r="D2062" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2062" t="n">
+        <v>730</v>
+      </c>
+      <c r="CX2062" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ネストボール
+sm1]</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C2063" t="inlineStr"/>
+      <c r="D2063" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2063" t="n">
+        <v>18300</v>
+      </c>
+      <c r="CX2063" t="n">
+        <v>14640</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>〔状態B〕サイトウ(R仕様/未開封)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2064" t="inlineStr"/>
+      <c r="D2064" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2064" t="n">
+        <v>1980</v>
+      </c>
+      <c r="CX2064" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ベトベトン＆アローラベトベトンGX
+sm10]</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr"/>
+      <c r="D2065" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2065" t="n">
+        <v>2050</v>
+      </c>
+      <c r="CX2065" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レパルダスV
+S6H]</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr"/>
+      <c r="D2066" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2066" t="n">
+        <v>490</v>
+      </c>
+      <c r="CX2066" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>〔状態A-〕うねりの扇
+S5a]</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr"/>
+      <c r="D2067" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2067" t="n">
+        <v>730</v>
+      </c>
+      <c r="CX2067" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カイリキーGX
+sm2]</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr"/>
+      <c r="D2068" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2068" t="n">
+        <v>930</v>
+      </c>
+      <c r="CX2068" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エレキパワー
+sm7]</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr"/>
+      <c r="D2069" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2069" t="n">
+        <v>2050</v>
+      </c>
+      <c r="CX2069" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガブリアスCLV.X(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr"/>
+      <c r="D2070" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2070" t="n">
+        <v>2880</v>
+      </c>
+      <c r="CX2070" t="n">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>〔状態A-〕MピジョットEX
+CP6]</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr"/>
+      <c r="D2071" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2071" t="n">
+        <v>4780</v>
+      </c>
+      <c r="CX2071" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジュナイパーGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr"/>
+      <c r="D2072" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2072" t="n">
+        <v>1680</v>
+      </c>
+      <c r="CX2072" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ファイヤー＆サンダー＆フリーザーGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr"/>
+      <c r="D2073" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2073" t="n">
+        <v>31800</v>
+      </c>
+      <c r="CX2073" t="n">
+        <v>25440</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アルセウスV(SA/未開封)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr"/>
+      <c r="D2074" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2074" t="n">
+        <v>2350</v>
+      </c>
+      <c r="CX2074" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>〔状態B〕アルセウスVSTAR
+S9]</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr"/>
+      <c r="D2075" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2075" t="n">
+        <v>320</v>
+      </c>
+      <c r="CX2075" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>〔状態B〕ロケット団の幹部(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr"/>
+      <c r="D2076" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2076" t="n">
+        <v>680</v>
+      </c>
+      <c r="CX2076" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グレイシアVMAX(SA)
+S6a]</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr"/>
+      <c r="D2077" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2077" t="n">
+        <v>113000</v>
+      </c>
+      <c r="CX2077" t="n">
+        <v>90400</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>〔状態C〕バトルシティ
+その他]</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr"/>
+      <c r="D2078" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2078" t="n">
+        <v>1990</v>
+      </c>
+      <c r="CX2078" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハガネールEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr"/>
+      <c r="D2079" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2079" t="n">
+        <v>7980</v>
+      </c>
+      <c r="CX2079" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>〔状態B〕ジバコイル
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr"/>
+      <c r="D2080" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2080" t="n">
+        <v>320</v>
+      </c>
+      <c r="CX2080" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>〔状態C〕フラダリの奥の手
+XY]</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr"/>
+      <c r="D2081" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2081" t="n">
+        <v>9980</v>
+      </c>
+      <c r="CX2081" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>〔状態C〕イーブイ(ムンク)
+その他]</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr"/>
+      <c r="D2082" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2082" t="n">
+        <v>138000</v>
+      </c>
+      <c r="CX2082" t="n">
+        <v>110400</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本超エネルギー(ジムチャレンジ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr"/>
+      <c r="D2083" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2083" t="n">
+        <v>680</v>
+      </c>
+      <c r="CX2083" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラランテスGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr"/>
+      <c r="D2084" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2084" t="n">
+        <v>1980</v>
+      </c>
+      <c r="CX2084" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>〔状態B〕ヨシダ警部補
+smP2]</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr"/>
+      <c r="D2085" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2085" t="n">
+        <v>5980</v>
+      </c>
+      <c r="CX2085" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>〔状態B〕レスキュータンカ
+sm3]</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr"/>
+      <c r="D2086" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2086" t="n">
+        <v>8480</v>
+      </c>
+      <c r="CX2086" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>〔状態B〕ロトムex
+M2]</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr"/>
+      <c r="D2087" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2087" t="n">
+        <v>880</v>
+      </c>
+      <c r="CX2087" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニャースex
+M3]</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr"/>
+      <c r="D2088" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2088" t="n">
+        <v>12800</v>
+      </c>
+      <c r="CX2088" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガダークライex
+M5]</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr"/>
+      <c r="D2089" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2089" t="n">
+        <v>1190</v>
+      </c>
+      <c r="CX2089" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>MヘラクロスEX</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr"/>
+      <c r="D2090" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2090" t="n">
+        <v>5980</v>
+      </c>
+      <c r="CX2090" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>クルマユ</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr"/>
+      <c r="D2091" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2091" t="n">
+        <v>980</v>
+      </c>
+      <c r="CX2091" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>フェローチェGX</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr"/>
+      <c r="D2092" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2092" t="n">
+        <v>2980</v>
+      </c>
+      <c r="CX2092" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ブースターVMAX(SA仕様)</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr"/>
+      <c r="D2093" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2093" t="n">
+        <v>728000</v>
+      </c>
+      <c r="CX2093" t="n">
+        <v>582400</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕リザードンV(SR仕様)</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr"/>
+      <c r="D2094" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2094" t="n">
+        <v>408000</v>
+      </c>
+      <c r="CX2094" t="n">
+        <v>326400</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕MカメックスEX</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr"/>
+      <c r="D2095" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2095" t="n">
+        <v>158000</v>
+      </c>
+      <c r="CX2095" t="n">
+        <v>126400</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>バニリッチ</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr"/>
+      <c r="D2096" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2096" t="n">
+        <v>880</v>
+      </c>
+      <c r="CX2096" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕スターミーV</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr"/>
+      <c r="D2097" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2097" t="n">
+        <v>37800</v>
+      </c>
+      <c r="CX2097" t="n">
+        <v>30240</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>セゴール</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr"/>
+      <c r="D2098" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2098" t="n">
+        <v>680</v>
+      </c>
+      <c r="CX2098" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒロシマのピカチュウ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr"/>
+      <c r="D2099" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2099" t="n">
+        <v>19400</v>
+      </c>
+      <c r="CX2099" t="n">
+        <v>15520</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ピカチュウV-UNION(25th/4枚セット)</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr"/>
+      <c r="D2100" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2100" t="n">
+        <v>79800</v>
+      </c>
+      <c r="CX2100" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>マイナン</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr"/>
+      <c r="D2101" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2101" t="n">
+        <v>2780</v>
+      </c>
+      <c r="CX2101" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>バチュル</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr"/>
+      <c r="D2102" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2102" t="n">
+        <v>680</v>
+      </c>
+      <c r="CX2102" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕ピカチュウex</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr"/>
+      <c r="D2103" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2103" t="n">
+        <v>64800</v>
+      </c>
+      <c r="CX2103" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ナンジャモのハラバリーex</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr"/>
+      <c r="D2104" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2104" t="n">
+        <v>17800</v>
+      </c>
+      <c r="CX2104" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr"/>
+      <c r="D2105" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2105" t="n">
+        <v>3280</v>
+      </c>
+      <c r="CX2105" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウex
+SV8]</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr"/>
+      <c r="D2106" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2106" t="n">
+        <v>26800</v>
+      </c>
+      <c r="CX2106" t="n">
+        <v>21440</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>名探偵ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr"/>
+      <c r="D2107" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2107" t="n">
+        <v>34800</v>
+      </c>
+      <c r="CX2107" t="n">
+        <v>27840</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>パルスワンV</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr"/>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2108" t="n">
+        <v>480</v>
+      </c>
+      <c r="CX2108" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>ピカチュウVMAX</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr"/>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2109" t="n">
+        <v>79800</v>
+      </c>
+      <c r="CX2109" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕リーリエのピッピex</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr"/>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2110" t="n">
+        <v>39800</v>
+      </c>
+      <c r="CX2110" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エムリット
+SV8]</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr"/>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2111" t="n">
+        <v>830</v>
+      </c>
+      <c r="CX2111" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>ミュウ</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr"/>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2112" t="n">
+        <v>8280</v>
+      </c>
+      <c r="CX2112" t="n">
+        <v>6624</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>ラブトロスV</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr"/>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2113" t="n">
+        <v>480</v>
+      </c>
+      <c r="CX2113" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ルカリオEX</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr"/>
+      <c r="D2114" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2114" t="n">
+        <v>178000</v>
+      </c>
+      <c r="CX2114" t="n">
+        <v>142400</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>ナゲキ</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr"/>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2115" t="n">
+        <v>780</v>
+      </c>
+      <c r="CX2115" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>ゴーリキー</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr"/>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2116" t="n">
+        <v>1580</v>
+      </c>
+      <c r="CX2116" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>いちげきウーラオスV</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr"/>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2117" t="n">
+        <v>1280</v>
+      </c>
+      <c r="CX2117" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>マグマ団のグラードン(25th)</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr"/>
+      <c r="D2118" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2118" t="n">
+        <v>4980</v>
+      </c>
+      <c r="CX2118" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>マニューラGX</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr"/>
+      <c r="D2119" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2119" t="n">
+        <v>1780</v>
+      </c>
+      <c r="CX2119" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>ピッピ</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr"/>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2120" t="n">
+        <v>64800</v>
+      </c>
+      <c r="CX2120" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>ドラパルトex</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr"/>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2121" t="n">
+        <v>1580</v>
+      </c>
+      <c r="CX2121" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>ガブリアスV</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr"/>
+      <c r="D2122" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="CW2122" t="n">
+        <v>8980</v>
+      </c>
+      <c r="CX2122" t="n">
+        <v>7184</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -15,6 +15,7 @@
     <sheet name="2026-4" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-5" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2026-6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-7" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82001,7 +82002,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2042" t="inlineStr"/>
       <c r="D2042" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82026,7 +82026,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2043" t="inlineStr"/>
       <c r="D2043" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82051,7 +82050,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2044" t="inlineStr"/>
       <c r="D2044" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82076,7 +82074,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2045" t="inlineStr"/>
       <c r="D2045" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82101,7 +82098,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2046" t="inlineStr"/>
       <c r="D2046" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82126,7 +82122,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2047" t="inlineStr"/>
       <c r="D2047" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82151,7 +82146,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2048" t="inlineStr"/>
       <c r="D2048" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82176,7 +82170,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2049" t="inlineStr"/>
       <c r="D2049" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82201,7 +82194,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2050" t="inlineStr"/>
       <c r="D2050" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82226,7 +82218,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C2051" t="inlineStr"/>
       <c r="D2051" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82251,7 +82242,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2052" t="inlineStr"/>
       <c r="D2052" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82276,7 +82266,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2053" t="inlineStr"/>
       <c r="D2053" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82301,7 +82290,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2054" t="inlineStr"/>
       <c r="D2054" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82326,7 +82314,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2055" t="inlineStr"/>
       <c r="D2055" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82351,7 +82338,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C2056" t="inlineStr"/>
       <c r="D2056" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82376,7 +82362,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2057" t="inlineStr"/>
       <c r="D2057" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82401,7 +82386,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2058" t="inlineStr"/>
       <c r="D2058" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82426,7 +82410,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2059" t="inlineStr"/>
       <c r="D2059" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82451,7 +82434,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2060" t="inlineStr"/>
       <c r="D2060" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82476,7 +82458,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C2061" t="inlineStr"/>
       <c r="D2061" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82501,7 +82482,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2062" t="inlineStr"/>
       <c r="D2062" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82526,7 +82506,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C2063" t="inlineStr"/>
       <c r="D2063" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82551,7 +82530,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2064" t="inlineStr"/>
       <c r="D2064" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82576,7 +82554,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2065" t="inlineStr"/>
       <c r="D2065" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82601,7 +82578,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2066" t="inlineStr"/>
       <c r="D2066" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82626,7 +82602,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C2067" t="inlineStr"/>
       <c r="D2067" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82651,7 +82626,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2068" t="inlineStr"/>
       <c r="D2068" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82676,7 +82650,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C2069" t="inlineStr"/>
       <c r="D2069" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82701,7 +82674,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2070" t="inlineStr"/>
       <c r="D2070" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82726,7 +82698,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2071" t="inlineStr"/>
       <c r="D2071" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82751,7 +82722,6 @@
           <t>SSR</t>
         </is>
       </c>
-      <c r="C2072" t="inlineStr"/>
       <c r="D2072" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82776,7 +82746,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C2073" t="inlineStr"/>
       <c r="D2073" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82801,7 +82770,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2074" t="inlineStr"/>
       <c r="D2074" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82826,7 +82794,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C2075" t="inlineStr"/>
       <c r="D2075" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82851,7 +82818,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2076" t="inlineStr"/>
       <c r="D2076" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82876,7 +82842,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C2077" t="inlineStr"/>
       <c r="D2077" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82901,7 +82866,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2078" t="inlineStr"/>
       <c r="D2078" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82926,7 +82890,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2079" t="inlineStr"/>
       <c r="D2079" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82951,7 +82914,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C2080" t="inlineStr"/>
       <c r="D2080" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -82976,7 +82938,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2081" t="inlineStr"/>
       <c r="D2081" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83001,7 +82962,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2082" t="inlineStr"/>
       <c r="D2082" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83026,7 +82986,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2083" t="inlineStr"/>
       <c r="D2083" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83051,7 +83010,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C2084" t="inlineStr"/>
       <c r="D2084" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83076,7 +83034,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2085" t="inlineStr"/>
       <c r="D2085" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83101,7 +83058,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C2086" t="inlineStr"/>
       <c r="D2086" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83126,7 +83082,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2087" t="inlineStr"/>
       <c r="D2087" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83151,7 +83106,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2088" t="inlineStr"/>
       <c r="D2088" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83176,7 +83130,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2089" t="inlineStr"/>
       <c r="D2089" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83200,7 +83153,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C2090" t="inlineStr"/>
       <c r="D2090" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83224,7 +83176,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2091" t="inlineStr"/>
       <c r="D2091" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83248,7 +83199,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C2092" t="inlineStr"/>
       <c r="D2092" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83272,7 +83222,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2093" t="inlineStr"/>
       <c r="D2093" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83296,7 +83245,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2094" t="inlineStr"/>
       <c r="D2094" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83320,7 +83268,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2095" t="inlineStr"/>
       <c r="D2095" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83344,7 +83291,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2096" t="inlineStr"/>
       <c r="D2096" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83368,7 +83314,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C2097" t="inlineStr"/>
       <c r="D2097" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83392,7 +83337,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2098" t="inlineStr"/>
       <c r="D2098" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83417,7 +83361,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2099" t="inlineStr"/>
       <c r="D2099" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83441,7 +83384,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C2100" t="inlineStr"/>
       <c r="D2100" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83465,7 +83407,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2101" t="inlineStr"/>
       <c r="D2101" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83489,7 +83430,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2102" t="inlineStr"/>
       <c r="D2102" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83513,7 +83453,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2103" t="inlineStr"/>
       <c r="D2103" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83537,7 +83476,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2104" t="inlineStr"/>
       <c r="D2104" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83561,7 +83499,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2105" t="inlineStr"/>
       <c r="D2105" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83586,7 +83523,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C2106" t="inlineStr"/>
       <c r="D2106" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83610,7 +83546,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2107" t="inlineStr"/>
       <c r="D2107" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83634,7 +83569,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2108" t="inlineStr"/>
       <c r="D2108" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83658,7 +83592,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C2109" t="inlineStr"/>
       <c r="D2109" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83682,7 +83615,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2110" t="inlineStr"/>
       <c r="D2110" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83707,7 +83639,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2111" t="inlineStr"/>
       <c r="D2111" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83731,7 +83662,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2112" t="inlineStr"/>
       <c r="D2112" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83755,7 +83685,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2113" t="inlineStr"/>
       <c r="D2113" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83779,7 +83708,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2114" t="inlineStr"/>
       <c r="D2114" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83803,7 +83731,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2115" t="inlineStr"/>
       <c r="D2115" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83827,7 +83754,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C2116" t="inlineStr"/>
       <c r="D2116" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83851,7 +83777,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C2117" t="inlineStr"/>
       <c r="D2117" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83875,7 +83800,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2118" t="inlineStr"/>
       <c r="D2118" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83899,7 +83823,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C2119" t="inlineStr"/>
       <c r="D2119" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83923,7 +83846,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2120" t="inlineStr"/>
       <c r="D2120" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83947,7 +83869,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C2121" t="inlineStr"/>
       <c r="D2121" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83971,7 +83892,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C2122" t="inlineStr"/>
       <c r="D2122" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83982,6 +83902,2108 @@
       </c>
       <c r="CX2122" t="n">
         <v>7184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>card_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2026-07-01_price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2026-07-01_buy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026-07-01_ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2026-07-01_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>〔状態B〕プラズマ団のしたっぱ
+その他]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3780</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガマガル
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>830</v>
+      </c>
+      <c r="F3" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ビクティニ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガヤンマex
+SV9a]</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>〔状態A-〕Nのレシラム
+SV9]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2480</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブロスターBREAK
+XY]</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2580</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>〔状態B〕セイジ
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>320</v>
+      </c>
+      <c r="F8" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハッサムex
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>480</v>
+      </c>
+      <c r="F9" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガブリアスEX(XY激アツ始動キャンペーン)
+XY]</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2790</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スターミー
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>390</v>
+      </c>
+      <c r="F11" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>〔状態B〕ピカチュウ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6480</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>〔状態A-〕サーフゴーex
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4580</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トドロクツキex
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6480</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本草エネルギー(チャンピオンズリーグ2024)
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>480</v>
+      </c>
+      <c r="F15" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウツーV(RR仕様)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カメール
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オリジンディアルガV
+S10D]</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F18" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーVSTAR
+S10b]</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>9180</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7344</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>〔状態B〕フォレトスex
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>380</v>
+      </c>
+      <c r="F20" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>〔状態A-〕チオンジェンex
+SV2P]</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジュペッタex
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>380</v>
+      </c>
+      <c r="F22" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レジドラゴV(SA)
+S12]</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3080</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ガラルサニーゴ
+s4a]</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>230</v>
+      </c>
+      <c r="F24" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本水エネルギー(チャンピオンズリーグ2020)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>930</v>
+      </c>
+      <c r="F25" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>〔状態A-〕グレイシアGX
+sm5]</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>12800</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カイリューGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4580</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>〔状態A-〕チャンピオンズフェスティバル(2013)
+その他]</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>268000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>214400</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マクワ
+S6a]</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>690</v>
+      </c>
+      <c r="F29" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本雷エネルギー(DPキラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5780</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>〔状態A-〕いちげきウーラオスVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>〔状態A-〕テッカグヤGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ホワイトキュレムGX
+sm6]</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5480</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アルセウス＆ディアルガ＆パルキアGX
+sm12]</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2790</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドガース
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3080</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トルネロス
+その他]</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>8990</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7192</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コイキング＆ホエルオーGX
+sm9]</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>12800</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヤレユータン
+s3a]</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F38" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブラッキーVMAX
+S8b]</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>830</v>
+      </c>
+      <c r="F39" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼラオラV(SA)
+S6K]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>12800</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>〔状態B〕ホエルオーEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>580</v>
+      </c>
+      <c r="F41" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>〔状態B〕ニンフィアVMAX
+S6a]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6980</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>〔状態B〕グラードンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4480</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>〔状態B〕レシラム
+その他]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>44800</v>
+      </c>
+      <c r="F44" t="n">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウ(古代文字Nintedo)
+その他]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>39800</v>
+      </c>
+      <c r="F45" t="n">
+        <v>31840</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>〔状態C〕ラティオスEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>17800</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>〔状態B〕博士の研究/マグノリア博士
+S-P]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>880</v>
+      </c>
+      <c r="F47" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>〔状態B〕ビッケ
+sm3]</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>17800</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゾロアークGX
+sm3]</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミミッキュ(ムンク)
+その他]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>998000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>798400</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>〔状態B〕大きなおまもり
+s1a]</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>990</v>
+      </c>
+      <c r="F51" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>〔状態B〕回収ネット
+S2]</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>880</v>
+      </c>
+      <c r="F52" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>〔状態B〕ユカリ
+M3]</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>680</v>
+      </c>
+      <c r="F53" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガカエンジシex
+M4]</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>630</v>
+      </c>
+      <c r="F54" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ナッシー</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>580</v>
+      </c>
+      <c r="F55" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>シガロコ</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>280</v>
+      </c>
+      <c r="F56" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>グレンアルマ</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>380</v>
+      </c>
+      <c r="F57" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>リザード</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3980</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>リザードン＆テールナーGX</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>16800</v>
+      </c>
+      <c r="F59" t="n">
+        <v>13440</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>キュレムex</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4980</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ウェルカモ</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>580</v>
+      </c>
+      <c r="F61" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>はくばバドレックスVMAX</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>はくばバドレックスV(SA)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3780</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>トウホクのピカチュウ</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>16800</v>
+      </c>
+      <c r="F64" t="n">
+        <v>13440</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ナンジャモのタイカイデン</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F65" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕_のピカチュウ(25th)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>52800</v>
+      </c>
+      <c r="F66" t="n">
+        <v>42240</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>_のピカチュウ(25th)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>79800</v>
+      </c>
+      <c r="F67" t="n">
+        <v>63840</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ポケパークのピカチュウ(未開封)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>398000</v>
+      </c>
+      <c r="F68" t="n">
+        <v>318400</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>カプ・コケコ</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>基本超エネルギー(フレンドバトル)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>380</v>
+      </c>
+      <c r="F70" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ゴビット</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>880</v>
+      </c>
+      <c r="F71" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ニンフィアex</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>20800</v>
+      </c>
+      <c r="F72" t="n">
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラブトロス
+SV5a]</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>580</v>
+      </c>
+      <c r="F73" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ニンフィアVMAX(SA)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>208000</v>
+      </c>
+      <c r="F74" t="n">
+        <v>166400</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ヨノワール</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>480</v>
+      </c>
+      <c r="F75" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>スナノケガワex</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F76" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ルカリオVSTAR</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4980</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>れんげきウーラオスVMAX(SA)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>94800</v>
+      </c>
+      <c r="F78" t="n">
+        <v>75840</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ホイーガ</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>880</v>
+      </c>
+      <c r="F79" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ブラッキーVMAX</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1680</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ザマゼンタV</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1680</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>トゲピー＆ピィ＆ププリンGX</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>14800</v>
+      </c>
+      <c r="F82" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>レジドラゴV(RR仕様)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>780</v>
+      </c>
+      <c r="F83" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>イーブイGX</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>9480</v>
+      </c>
+      <c r="F84" t="n">
+        <v>7584</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -83915,7 +83915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:L217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83959,6 +83959,26 @@
           <t>2026-07-01_diff</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2026-07-02_price</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026-07-02_buy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-07-02_ratio</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-07-02_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -83972,7 +83992,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -83997,7 +84016,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84022,7 +84040,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84047,7 +84064,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84072,7 +84088,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84097,7 +84112,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84122,7 +84136,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84147,7 +84160,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84172,7 +84184,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84197,7 +84208,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84222,7 +84232,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84247,7 +84256,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84272,7 +84280,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84297,7 +84304,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84322,7 +84328,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84347,7 +84352,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84372,7 +84376,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84397,7 +84400,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84422,7 +84424,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84447,7 +84448,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84472,7 +84472,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84497,7 +84496,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84522,7 +84520,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84547,7 +84544,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84572,7 +84568,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84597,7 +84592,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84622,7 +84616,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84647,7 +84640,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84672,7 +84664,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84697,7 +84688,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84722,7 +84712,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84747,7 +84736,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84772,7 +84760,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84797,7 +84784,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84822,7 +84808,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84847,7 +84832,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84872,7 +84856,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84897,7 +84880,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84922,7 +84904,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84947,7 +84928,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84972,7 +84952,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -84997,7 +84976,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85022,7 +85000,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85047,7 +85024,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85072,7 +85048,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85097,7 +85072,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85122,7 +85096,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85147,7 +85120,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85172,7 +85144,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85197,7 +85168,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85222,7 +85192,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85247,7 +85216,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85272,7 +85240,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85296,7 +85263,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85320,7 +85286,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85344,7 +85309,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85368,7 +85332,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85392,7 +85355,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85416,7 +85378,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85440,7 +85401,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85464,7 +85424,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85488,7 +85447,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85512,7 +85470,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85536,7 +85493,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85560,7 +85516,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85584,7 +85539,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85608,7 +85562,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85632,7 +85585,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85656,7 +85608,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85680,7 +85631,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85704,7 +85654,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85729,7 +85678,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85753,7 +85701,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85777,7 +85724,6 @@
           <t>CHR</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85801,7 +85747,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85825,7 +85770,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85849,7 +85793,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85873,7 +85816,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85897,7 +85839,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85921,7 +85862,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85945,7 +85885,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85969,7 +85908,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85993,7 +85931,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86004,6 +85941,3285 @@
       </c>
       <c r="F84" t="n">
         <v>7584</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕オーヤマのピカチュウ</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1104000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガマフォクシーex
+M-P]</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>990</v>
+      </c>
+      <c r="J86" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼクロムEX
+その他]</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1990</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エンペルトex
+M2]</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>200</v>
+      </c>
+      <c r="J88" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>〔状態C〕ミュウVMAX
+S8]</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>780</v>
+      </c>
+      <c r="J89" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レパルダス
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>1090</v>
+      </c>
+      <c r="J90" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>〔状態B〕バティックシャツのピカチュウ(未開封/ネイティオ柄)
+海外版]</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>3480</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>〔状態A-〕モトトカゲex
+SV7a]</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>380</v>
+      </c>
+      <c r="J92" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポケパークのゴニョニョ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>19800</v>
+      </c>
+      <c r="J93" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブライア
+SV7]</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>680</v>
+      </c>
+      <c r="J94" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ナンジャモ(SR仕様/英語版)
+海外版]</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>3980</v>
+      </c>
+      <c r="J95" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>〔状態A-〕チラチーノ
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>990</v>
+      </c>
+      <c r="J96" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>〔状態B〕ナンジャモ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>8980</v>
+      </c>
+      <c r="J97" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>〔状態B〕キョジオーン
+SV4K]</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>320</v>
+      </c>
+      <c r="J98" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハガネール
+SV4M]</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>530</v>
+      </c>
+      <c r="J99" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本炎エネルギー
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>480</v>
+      </c>
+      <c r="J100" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゼニガメ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>490</v>
+      </c>
+      <c r="J101" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フシギダネ
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>3780</v>
+      </c>
+      <c r="J102" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オリジンディアルガVSTAR
+S10D]</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>2050</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒノヤコマ
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>480</v>
+      </c>
+      <c r="J104" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>〔状態B〕ベラカス
+SV2P]</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>420</v>
+      </c>
+      <c r="J105" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ボスの指令/ゲーチス
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>3280</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ネジキ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>350</v>
+      </c>
+      <c r="J107" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アブソル
+S12a]</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>730</v>
+      </c>
+      <c r="J108" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バクガメス
+その他]</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>390</v>
+      </c>
+      <c r="J109" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ハッサムVMAX
+S3]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>260</v>
+      </c>
+      <c r="J110" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メッソン
+s4a]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>230</v>
+      </c>
+      <c r="J111" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ネストボール
+sm1]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>18300</v>
+      </c>
+      <c r="J112" t="n">
+        <v>14640</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ラブトロスV
+S10a]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>380</v>
+      </c>
+      <c r="J113" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>〔状態B〕サイトウ(R仕様/未開封)
+S-P]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>〔状態A-〕レックウザVMAX
+S7R]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>52800</v>
+      </c>
+      <c r="J115" t="n">
+        <v>42240</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本鋼エネルギー(DPキラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>4990</v>
+      </c>
+      <c r="J116" t="n">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミュウツーEX(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>12800</v>
+      </c>
+      <c r="J117" t="n">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドラパルトV
+S2]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>790</v>
+      </c>
+      <c r="J118" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スイクンV
+S7D]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>990</v>
+      </c>
+      <c r="J119" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エール団のしたっぱ
+s1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>580</v>
+      </c>
+      <c r="J120" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジュカインGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>1880</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ブラッキー＆ダークライGX
+sm12a]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>31800</v>
+      </c>
+      <c r="J122" t="n">
+        <v>25440</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>〔状態A-〕博士の研究/オーキド博士(25th)
+S8a]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>580</v>
+      </c>
+      <c r="J123" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>〔状態A-〕アルセウスVSTAR
+S9]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>450</v>
+      </c>
+      <c r="J124" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>〔状態B〕イシヘンジンVMAX
+s1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>220</v>
+      </c>
+      <c r="J125" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミュウex(25th)
+S8a-P]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>14800</v>
+      </c>
+      <c r="J126" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゼラオラV
+S6K]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J127" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヒトカゲ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>390</v>
+      </c>
+      <c r="J128" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>〔状態C〕ヒガナ
+sm6]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>17800</v>
+      </c>
+      <c r="J129" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>〔状態C〕セレビィex
+その他]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>42800</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34240</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>〔状態B〕リサイクルエネルギー
+sm10b]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>980</v>
+      </c>
+      <c r="J131" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>〔状態B〕グズマ＆ハラ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>680</v>
+      </c>
+      <c r="J132" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>〔状態B〕ドラパルトVMAX
+S2]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>1090</v>
+      </c>
+      <c r="J133" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>〔状態B〕トレーナーズポスト
+XY]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>11800</v>
+      </c>
+      <c r="J134" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本炎エネルギー(クイックキラ)
+その他]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>69800</v>
+      </c>
+      <c r="J135" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>〔状態B〕ラムパルドex
+M5]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>320</v>
+      </c>
+      <c r="J136" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕モクロー＆アローラナッシーGX</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>36800</v>
+      </c>
+      <c r="J137" t="n">
+        <v>29440</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ヤバソチャex</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>480</v>
+      </c>
+      <c r="J138" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ジャローダV</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>580</v>
+      </c>
+      <c r="J139" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>オーロットEX</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>9980</v>
+      </c>
+      <c r="J140" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ダーテングGX</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>1380</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ブースターex</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>7980</v>
+      </c>
+      <c r="J142" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>キュウコンex</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>280</v>
+      </c>
+      <c r="J143" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ブースターVMAX(SA仕様)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>718000</v>
+      </c>
+      <c r="J144" t="n">
+        <v>574400</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>マルヤクデV</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>980</v>
+      </c>
+      <c r="J145" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕MカメックスEX</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>148000</v>
+      </c>
+      <c r="J146" t="n">
+        <v>118400</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>バニリッチ</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>880</v>
+      </c>
+      <c r="J147" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ユキワラシ</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>680</v>
+      </c>
+      <c r="J148" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>オリジンパルキアV</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J149" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>トサキント</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>580</v>
+      </c>
+      <c r="J150" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>〔状態A-〕トウホクのピカチュウ(未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>15800</v>
+      </c>
+      <c r="J151" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>サンダースex</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>380</v>
+      </c>
+      <c r="J152" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>1880</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>そらをとぶピカチュウVMAX(25th)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>4180</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ポンチョを着たピカチュウ</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>298000</v>
+      </c>
+      <c r="J155" t="n">
+        <v>238400</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>〔状態A-〕メガサーナイトex
+M1S]</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>690</v>
+      </c>
+      <c r="J156" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ロケット団のソーナンス</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>1180</v>
+      </c>
+      <c r="J157" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シロデスナex
+SV8]</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>480</v>
+      </c>
+      <c r="J158" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ミュウツー</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>5480</v>
+      </c>
+      <c r="J159" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>アーゴヨンGX</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J160" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ハブネーク</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>680</v>
+      </c>
+      <c r="J161" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>基本闘エネルギー(フレンドバトル)</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>480</v>
+      </c>
+      <c r="J162" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>シロナのガブリアスex</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>7480</v>
+      </c>
+      <c r="J163" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>メガジガルデex</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>4280</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3424</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ブラッキー＆ダークライGX(SA)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>258000</v>
+      </c>
+      <c r="J165" t="n">
+        <v>206400</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ヒスイダイケンキV</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>580</v>
+      </c>
+      <c r="J166" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>コマタナ</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>780</v>
+      </c>
+      <c r="J167" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MサーナイトEX</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>69800</v>
+      </c>
+      <c r="J168" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>レックウザV</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>580</v>
+      </c>
+      <c r="J169" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>アーゴヨン＆アクジキングGX</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>680</v>
+      </c>
+      <c r="J170" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕トルネロスEX</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>31800</v>
+      </c>
+      <c r="J171" t="n">
+        <v>25440</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ラッキー</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>2280</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ヨクバリスV</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>480</v>
+      </c>
+      <c r="J173" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ダイブボール</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>15800</v>
+      </c>
+      <c r="J174" t="n">
+        <v>12640</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>トウコ</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>2980</v>
+      </c>
+      <c r="J175" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>レホール</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>680</v>
+      </c>
+      <c r="J176" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕スズナ</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>9980</v>
+      </c>
+      <c r="J177" t="n">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>アクロマの実験</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>480</v>
+      </c>
+      <c r="J178" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>チェレンの気くばり</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>580</v>
+      </c>
+      <c r="J179" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>クララ</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>580</v>
+      </c>
+      <c r="J180" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>コルニの気合い</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J181" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>シロナ＆カトレア</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>24800</v>
+      </c>
+      <c r="J182" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>グラジオの決戦</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>580</v>
+      </c>
+      <c r="J183" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>おいわいファンファーレ(2021)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>32800</v>
+      </c>
+      <c r="J184" t="n">
+        <v>26240</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>〔状態B〕かるいし
+M-P]</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>580</v>
+      </c>
+      <c r="J185" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>〔状態C〕ニャースex
+M3]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>6980</v>
+      </c>
+      <c r="J186" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>〔状態A-〕キバゴ
+その他]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>530</v>
+      </c>
+      <c r="J187" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>〔状態C〕タマタマ
+S-P]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>280</v>
+      </c>
+      <c r="J188" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>〔状態C〕やまおとこ
+その他]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>220</v>
+      </c>
+      <c r="J189" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本水エネルギー(チャンピオンズリーグ2026)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>580</v>
+      </c>
+      <c r="J190" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>〔状態C〕モモワロウex
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>420</v>
+      </c>
+      <c r="J191" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>〔状態C〕ゾウドウ
+SV6a]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>280</v>
+      </c>
+      <c r="J192" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エモンガ
+その他]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>8480</v>
+      </c>
+      <c r="J193" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>〔状態C〕メロコ
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>280</v>
+      </c>
+      <c r="J194" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ゲッコウガ
+XY]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>6980</v>
+      </c>
+      <c r="J195" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>〔状態A-〕プラズマ団のモンスターボール
+その他]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>530</v>
+      </c>
+      <c r="J196" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>〔状態B〕エモンガ
+その他]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>7480</v>
+      </c>
+      <c r="J197" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジジーロン
+SV5M]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>380</v>
+      </c>
+      <c r="J198" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>〔状態C〕トウコ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>2980</v>
+      </c>
+      <c r="J199" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>〔状態B〕ランクルス
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>290</v>
+      </c>
+      <c r="J200" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>〔状態B〕ちからのハチマキ
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>320</v>
+      </c>
+      <c r="J201" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>〔状態B〕セレビィ(未開封/カードe)
+その他]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>7480</v>
+      </c>
+      <c r="J202" t="n">
+        <v>5984</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ニャヒート
+その他]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>260</v>
+      </c>
+      <c r="J203" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>〔状態B〕Nのゾロアークex
+SV9]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>2180</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>〔状態C〕ソウブレイズ
+SV8]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>370</v>
+      </c>
+      <c r="J205" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>〔状態C〕ハピナスex
+SV6]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>220</v>
+      </c>
+      <c r="J206" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>〔状態B〕ニャビー
+その他]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>1480</v>
+      </c>
+      <c r="J207" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>〔状態C〕ビワ
+SV5K]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>1180</v>
+      </c>
+      <c r="J208" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>〔状態B〕サザンドラEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>880</v>
+      </c>
+      <c r="J209" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ダブルドラゴンエネルギー
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>730</v>
+      </c>
+      <c r="J210" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>〔状態B〕フォッコ(R仕様)
+XY]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>390</v>
+      </c>
+      <c r="J211" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>〔状態A-〕幻影のゾロア
+その他]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>548000</v>
+      </c>
+      <c r="J212" t="n">
+        <v>438400</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>〔状態B〕ケーシィ
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>220</v>
+      </c>
+      <c r="J213" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>〔状態C〕ジュラルドンV(SA)
+S7D]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>3280</v>
+      </c>
+      <c r="J214" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ディアンシー(未開封)
+XY]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>2430</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>〔状態B〕タマンタ
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>980</v>
+      </c>
+      <c r="J216" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>〔状態A-〕チリ
+SV3a]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>zaiko_nashi</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>3080</v>
+      </c>
+      <c r="J217" t="n">
+        <v>2464</v>
       </c>
     </row>
   </sheetData>

--- a/card_prices.xlsx
+++ b/card_prices.xlsx
@@ -83915,7 +83915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L217"/>
+  <dimension ref="A1:P333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83979,6 +83979,26 @@
           <t>2026-07-02_diff</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026-07-03_price</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2026-07-03_buy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2026-07-03_ratio</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2026-07-03_diff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -85954,7 +85974,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -85979,7 +85998,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86004,7 +86022,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86029,7 +86046,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86054,7 +86070,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86079,7 +86094,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86104,7 +86118,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86129,7 +86142,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86154,7 +86166,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86179,7 +86190,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86204,7 +86214,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86229,7 +86238,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86254,7 +86262,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86279,7 +86286,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86304,7 +86310,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86329,7 +86334,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86354,7 +86358,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86379,7 +86382,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86404,7 +86406,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86429,7 +86430,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86454,7 +86454,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86479,7 +86478,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86504,7 +86502,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86529,7 +86526,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86554,7 +86550,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86579,7 +86574,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86604,7 +86598,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86629,7 +86622,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86654,7 +86646,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86679,7 +86670,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86704,7 +86694,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86729,7 +86718,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86754,7 +86742,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86779,7 +86766,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86804,7 +86790,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86829,7 +86814,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86854,7 +86838,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86879,7 +86862,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86904,7 +86886,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86929,7 +86910,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86954,7 +86934,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -86979,7 +86958,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87004,7 +86982,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87029,7 +87006,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87054,7 +87030,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87079,7 +87054,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87104,7 +87078,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87129,7 +87102,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87154,7 +87126,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87179,7 +87150,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87204,7 +87174,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87229,7 +87198,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87253,7 +87221,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87277,7 +87244,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87301,7 +87267,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87325,7 +87290,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87349,7 +87313,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87373,7 +87336,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87397,7 +87359,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87421,7 +87382,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87445,7 +87405,6 @@
           <t>CSR</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87469,7 +87428,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87493,7 +87451,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87517,7 +87474,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87541,7 +87497,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87565,7 +87520,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87590,7 +87544,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87614,7 +87567,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87638,7 +87590,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87662,7 +87613,6 @@
           <t>RRR</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87686,7 +87636,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87711,7 +87660,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87735,7 +87683,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87760,7 +87707,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87784,7 +87730,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87808,7 +87753,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87832,7 +87776,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87856,7 +87799,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87880,7 +87822,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87904,7 +87845,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87928,7 +87868,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87952,7 +87891,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -87976,7 +87914,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88000,7 +87937,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88024,7 +87960,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88048,7 +87983,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88072,7 +88006,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88096,7 +88029,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88120,7 +88052,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88144,7 +88075,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88168,7 +88098,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88192,7 +88121,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88216,7 +88144,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88240,7 +88167,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88264,7 +88190,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88288,7 +88213,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88312,7 +88236,6 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88336,7 +88259,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88360,7 +88282,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88384,7 +88305,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>zaiko_ari</t>
@@ -88409,7 +88329,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88434,7 +88353,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88459,7 +88377,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88484,7 +88401,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88509,7 +88425,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88534,7 +88449,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88559,7 +88473,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88584,7 +88497,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88609,7 +88521,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88634,7 +88545,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88659,7 +88569,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88684,7 +88593,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88709,7 +88617,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88734,7 +88641,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88759,7 +88665,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88784,7 +88689,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88809,7 +88713,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88834,7 +88737,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88859,7 +88761,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88884,7 +88785,6 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88909,7 +88809,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88934,7 +88833,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88959,7 +88857,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -88984,7 +88881,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89009,7 +88905,6 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89034,7 +88929,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89059,7 +88953,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89084,7 +88977,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89109,7 +89001,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89134,7 +89025,6 @@
           <t>SR</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89159,7 +89049,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89184,7 +89073,6 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89209,7 +89097,6 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>zaiko_nashi</t>
@@ -89220,6 +89107,2863 @@
       </c>
       <c r="J217" t="n">
         <v>2464</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>〔状態B〕ハガネールEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M218" t="n">
+        <v>690</v>
+      </c>
+      <c r="N218" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>〔状態A-〕基本超エネルギー(チャンピオンズリーグ2026)
+M-P]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M219" t="n">
+        <v>1090</v>
+      </c>
+      <c r="N219" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エルフーンex
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M220" t="n">
+        <v>2530</v>
+      </c>
+      <c r="N220" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>〔状態A-〕スワンナ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M221" t="n">
+        <v>930</v>
+      </c>
+      <c r="N221" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>〔状態B〕ダルマッカ
+SV11B]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M222" t="n">
+        <v>780</v>
+      </c>
+      <c r="N222" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ミネズミ
+SV11W]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M223" t="n">
+        <v>730</v>
+      </c>
+      <c r="N223" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ロケット団のニドキングex
+SV10]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M224" t="n">
+        <v>330</v>
+      </c>
+      <c r="N224" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マラカッチ
+SV9]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M225" t="n">
+        <v>330</v>
+      </c>
+      <c r="N225" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>〔状態A-〕オーガポンいどのめんex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M226" t="n">
+        <v>990</v>
+      </c>
+      <c r="N226" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>〔状態A-〕エーフィex
+SV8a]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M227" t="n">
+        <v>9180</v>
+      </c>
+      <c r="N227" t="n">
+        <v>7344</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>〔状態C〕ルカリオLV.X
+その他]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M228" t="n">
+        <v>8480</v>
+      </c>
+      <c r="N228" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>〔状態C〕ロトム図鑑
+その他]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M229" t="n">
+        <v>690</v>
+      </c>
+      <c r="N229" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コドラ
+SV6]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M230" t="n">
+        <v>380</v>
+      </c>
+      <c r="N230" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>〔状態B〕カイリューEX
+SV-P]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M231" t="n">
+        <v>2580</v>
+      </c>
+      <c r="N231" t="n">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ともだちてちょう
+その他]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M232" t="n">
+        <v>70800</v>
+      </c>
+      <c r="N232" t="n">
+        <v>56640</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マッシブーンGX
+sm8b]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M233" t="n">
+        <v>260</v>
+      </c>
+      <c r="N233" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドードー
+SV4a]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M234" t="n">
+        <v>230</v>
+      </c>
+      <c r="N234" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>〔状態B〕基本鋼エネルギー(ステーション/SM新デザイン)
+その他]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M235" t="n">
+        <v>880</v>
+      </c>
+      <c r="N235" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒトカゲ
+SV2a]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M236" t="n">
+        <v>4680</v>
+      </c>
+      <c r="N236" t="n">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>〔状態A-〕リキキリン
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M237" t="n">
+        <v>480</v>
+      </c>
+      <c r="N237" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>〔状態B〕ナンジャモ
+SV2D]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M238" t="n">
+        <v>4780</v>
+      </c>
+      <c r="N238" t="n">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>〔状態A-〕コイキング
+SV1a]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M239" t="n">
+        <v>21800</v>
+      </c>
+      <c r="N239" t="n">
+        <v>17440</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ウインディex
+SV1V]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M240" t="n">
+        <v>990</v>
+      </c>
+      <c r="N240" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>〔状態A-〕バオッキーVSTAR
+S12a]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M241" t="n">
+        <v>3980</v>
+      </c>
+      <c r="N241" t="n">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ジムトレーナー
+S-P]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M242" t="n">
+        <v>490</v>
+      </c>
+      <c r="N242" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>〔状態A-〕カプ・コケコVMAX
+S5I]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M243" t="n">
+        <v>260</v>
+      </c>
+      <c r="N243" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>〔状態B〕ミミッキュGX
+sm7]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M244" t="n">
+        <v>1190</v>
+      </c>
+      <c r="N244" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>〔状態A-〕フェローチェGX
+sm4]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M245" t="n">
+        <v>1390</v>
+      </c>
+      <c r="N245" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ボーマンダVMAX
+S3]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M246" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N246" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ソルガレオGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M247" t="n">
+        <v>6480</v>
+      </c>
+      <c r="N247" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ピカチュウVMAX(s4)
+s4]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
+        <v>1980</v>
+      </c>
+      <c r="N248" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>〔状態A-〕マツブサの隠し玉
+XY]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M249" t="n">
+        <v>9490</v>
+      </c>
+      <c r="N249" t="n">
+        <v>7592</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ユキノオー
+S8b]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M250" t="n">
+        <v>380</v>
+      </c>
+      <c r="N250" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ぼんぐり職人
+sm6]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M251" t="n">
+        <v>3280</v>
+      </c>
+      <c r="N251" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ベトベトン＆アローラベトベトンGX(SA)
+sm10]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M252" t="n">
+        <v>5480</v>
+      </c>
+      <c r="N252" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ザマゼンタV
+s4a]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M253" t="n">
+        <v>1430</v>
+      </c>
+      <c r="N253" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ザシアンV
+S8b]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M254" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N254" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>〔状態B〕シャクヤ
+S6K]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M255" t="n">
+        <v>880</v>
+      </c>
+      <c r="N255" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゲノセクトV(SA)
+S8]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M256" t="n">
+        <v>2180</v>
+      </c>
+      <c r="N256" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>〔状態A-〕シロナ
+sm5]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M257" t="n">
+        <v>89800</v>
+      </c>
+      <c r="N257" t="n">
+        <v>71840</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>〔状態B〕オーロンゲVMAX
+s4a]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M258" t="n">
+        <v>580</v>
+      </c>
+      <c r="N258" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>〔状態B〕ポンチョを着たイーブイ(NP/未開封)
+その他]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M259" t="n">
+        <v>158000</v>
+      </c>
+      <c r="N259" t="n">
+        <v>126400</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>〔状態B〕グラードンEX
+XY]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M260" t="n">
+        <v>7980</v>
+      </c>
+      <c r="N260" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>〔状態B〕ゴリランダーV
+s1a]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M261" t="n">
+        <v>420</v>
+      </c>
+      <c r="N261" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>〔状態C〕ボスごっこピカチュウ ロケット団
+その他]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M262" t="n">
+        <v>158000</v>
+      </c>
+      <c r="N262" t="n">
+        <v>126400</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>〔状態B〕シロナ
+sm5]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M263" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N263" t="n">
+        <v>51840</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>〔状態B〕ブラッキーGX
+sm1]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M264" t="n">
+        <v>4990</v>
+      </c>
+      <c r="N264" t="n">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>〔状態B〕エルレイド
+sm11b]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M265" t="n">
+        <v>880</v>
+      </c>
+      <c r="N265" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>〔状態B〕タッグスイッチ
+sm10a]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M266" t="n">
+        <v>580</v>
+      </c>
+      <c r="N266" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>〔状態B〕カメックス(1ED)
+その他]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M267" t="n">
+        <v>69800</v>
+      </c>
+      <c r="N267" t="n">
+        <v>55840</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ヒカリ
+M2]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M268" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N268" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>〔状態B〕ニャースex
+M3]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M269" t="n">
+        <v>2180</v>
+      </c>
+      <c r="N269" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>〔状態B〕パンプジンex
+M4]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M270" t="n">
+        <v>320</v>
+      </c>
+      <c r="N270" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>〔状態A-〕ドデカバシ
+M5]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M271" t="n">
+        <v>370</v>
+      </c>
+      <c r="N271" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕カスミのおねがい</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M272" t="n">
+        <v>54800</v>
+      </c>
+      <c r="N272" t="n">
+        <v>43840</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>メガフシギバナex</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M273" t="n">
+        <v>7980</v>
+      </c>
+      <c r="N273" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>リーフィアV(RR仕様)</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M274" t="n">
+        <v>480</v>
+      </c>
+      <c r="N274" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ボルケニオンex</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M275" t="n">
+        <v>2180</v>
+      </c>
+      <c r="N275" t="n">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>コータス</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M276" t="n">
+        <v>580</v>
+      </c>
+      <c r="N276" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>〔PSA9鑑定済〕リザードンV</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M277" t="n">
+        <v>14800</v>
+      </c>
+      <c r="N277" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ブースター</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>CHR</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M278" t="n">
+        <v>2780</v>
+      </c>
+      <c r="N278" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>バスラオ</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M279" t="n">
+        <v>880</v>
+      </c>
+      <c r="N279" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>シャワーズex</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M280" t="n">
+        <v>8480</v>
+      </c>
+      <c r="N280" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ケロマツ</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M281" t="n">
+        <v>1780</v>
+      </c>
+      <c r="N281" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ウェルカモ</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M282" t="n">
+        <v>580</v>
+      </c>
+      <c r="N282" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>エンペルトV(SA)</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>16800</v>
+      </c>
+      <c r="N283" t="n">
+        <v>13440</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA9鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M284" t="n">
+        <v>19800</v>
+      </c>
+      <c r="N284" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>〔※状態難/PSA10鑑定済〕ピカチュウMLV.X</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M285" t="n">
+        <v>878000</v>
+      </c>
+      <c r="N285" t="n">
+        <v>702400</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ピカチュウ</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M286" t="n">
+        <v>438000</v>
+      </c>
+      <c r="N286" t="n">
+        <v>350400</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>パチリス</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M287" t="n">
+        <v>880</v>
+      </c>
+      <c r="N287" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>サーナイトex</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M288" t="n">
+        <v>1280</v>
+      </c>
+      <c r="N288" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ミミッキュVMAX</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>CSR</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
+        <v>19800</v>
+      </c>
+      <c r="N289" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ミュウツーV(SA)</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M290" t="n">
+        <v>24800</v>
+      </c>
+      <c r="N290" t="n">
+        <v>19840</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ミミッキュVMAX</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M291" t="n">
+        <v>1080</v>
+      </c>
+      <c r="N291" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ガラルサンダー</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M292" t="n">
+        <v>880</v>
+      </c>
+      <c r="N292" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>イシヘンジンVMAX</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M293" t="n">
+        <v>680</v>
+      </c>
+      <c r="N293" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ダストダス</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M294" t="n">
+        <v>880</v>
+      </c>
+      <c r="N294" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ニンフィアGX</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M295" t="n">
+        <v>37800</v>
+      </c>
+      <c r="N295" t="n">
+        <v>30240</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>アローラナッシーex</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M296" t="n">
+        <v>3480</v>
+      </c>
+      <c r="N296" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ジュラルドンVMAX(SA)</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M297" t="n">
+        <v>25800</v>
+      </c>
+      <c r="N297" t="n">
+        <v>20640</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>レックウザGX</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M298" t="n">
+        <v>178000</v>
+      </c>
+      <c r="N298" t="n">
+        <v>142400</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>メガミミロップex</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M299" t="n">
+        <v>680</v>
+      </c>
+      <c r="N299" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>〔PSA10鑑定済〕ファイヤー＆サンダー＆フリーザーGX(SA)</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M300" t="n">
+        <v>428000</v>
+      </c>
+      <c r="N300" t="n">
+        <v>342400</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>メガミミロップ＆プリンGX</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>zaiko_ari</t>
+        </is>
+      </c>
+      <c r="M301" t="n">
+        <v>3480</v>
+      </c>
+      <c r="N301" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>基本悪エネルギー(チャンピオンズリーグ2023)</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+   